--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/Library/CloudStorage/OneDrive-CoxAutomotive/Documents/BrianMcGrathDocs/RadioProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5840C6CB-4221-144D-884F-1EDCF39A731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604330D-0D27-114D-9A71-97566CF9CD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3516" uniqueCount="2103">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6403,6 +6403,36 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>The Proclaimers</t>
+  </si>
+  <si>
+    <t>Nicki Manaj</t>
+  </si>
+  <si>
+    <t>Starships</t>
+  </si>
+  <si>
+    <t>Hi Infidelity</t>
+  </si>
+  <si>
+    <t>Don't Let Him Go</t>
+  </si>
+  <si>
+    <t>I’m Gonna Be (500 Miles)</t>
+  </si>
+  <si>
+    <t>Sunshine on Leith</t>
+  </si>
+  <si>
+    <t>The Remedy (I Won’t Worry)</t>
+  </si>
+  <si>
+    <t>Waiting for My Rocket to Come</t>
+  </si>
+  <si>
+    <t>Pink Friday: Roman Reloaded</t>
   </si>
 </sst>
 </file>
@@ -11145,7 +11175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F576"/>
+  <dimension ref="A1:F585"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -21283,6 +21313,89 @@
       <c r="F576" t="s">
         <v>1451</v>
       </c>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A577" t="s">
+        <v>90</v>
+      </c>
+      <c r="B577" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C577" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E577" s="1">
+        <v>1980</v>
+      </c>
+      <c r="F577" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A578" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B578" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C578" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E578" s="1">
+        <v>1988</v>
+      </c>
+      <c r="F578" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A579" t="s">
+        <v>244</v>
+      </c>
+      <c r="B579" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C579" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E579" s="1">
+        <v>2002</v>
+      </c>
+      <c r="F579" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A580" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B580" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C580" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E580" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F580" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E581" s="1"/>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E582" s="1"/>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E583" s="1"/>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E584" s="1"/>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E585" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A114:E497">

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2014CF4C-C579-FB4A-BCED-D33BDDB1BF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E891F564-EAEF-924E-AF90-83B395A19254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Bumpers" sheetId="19" r:id="rId4"/>
     <sheet name="Seasonal" sheetId="20" r:id="rId5"/>
     <sheet name="Broadway" sheetId="21" r:id="rId6"/>
+    <sheet name="1940s" sheetId="22" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Playlist'!$A$1:$F$497</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3448" uniqueCount="2085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3470" uniqueCount="2103">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6379,6 +6380,72 @@
   </si>
   <si>
     <t>Peter Paul and Mary</t>
+  </si>
+  <si>
+    <t>Band</t>
+  </si>
+  <si>
+    <t>album</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>The Woodpecker Song</t>
+  </si>
+  <si>
+    <t>Glenn Miller</t>
+  </si>
+  <si>
+    <t>The Andrews Sisters</t>
+  </si>
+  <si>
+    <t>Ferryboat Serenade</t>
+  </si>
+  <si>
+    <t>Sammy Kaye</t>
+  </si>
+  <si>
+    <t>Daddy</t>
+  </si>
+  <si>
+    <t>Elmer’s Tune</t>
+  </si>
+  <si>
+    <t>Jimmy Dorsey</t>
+  </si>
+  <si>
+    <t>Blue Champagne</t>
+  </si>
+  <si>
+    <t>Edelweiss (Reprise)</t>
+  </si>
+  <si>
+    <t>The Sound of Music (Original Soundtrack Recording)</t>
+  </si>
+  <si>
+    <t>Julie Andrews, Bill Lee, and the child cast</t>
+  </si>
+  <si>
+    <t>The Surrey with the Fringe on Top</t>
+  </si>
+  <si>
+    <t>Gordon MacRae, Shirley Jones, Charlotte Greenwood</t>
+  </si>
+  <si>
+    <r>
+      <t>Rodgers &amp; Hammerstein’s Oklahoma!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Film Soundtrack)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -10273,7 +10340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F616"/>
+  <dimension ref="A1:F618"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -21089,6 +21156,40 @@
         <v>1967</v>
       </c>
       <c r="F616" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B617" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C617" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E617">
+        <v>1965</v>
+      </c>
+      <c r="F617" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A618" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B618" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C618" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E618">
+        <v>1955</v>
+      </c>
+      <c r="F618" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -21736,4 +21837,78 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
+  <dimension ref="A2:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1940</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="4" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1941</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E891F564-EAEF-924E-AF90-83B395A19254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B7471D-F521-7245-902E-894567F6FF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="16" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3470" uniqueCount="2103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="2136">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6446,6 +6446,105 @@
       </rPr>
       <t xml:space="preserve"> (Film Soundtrack)</t>
     </r>
+  </si>
+  <si>
+    <t>Frenesi</t>
+  </si>
+  <si>
+    <t>Artie Shaw</t>
+  </si>
+  <si>
+    <t>Artie Shaw &amp; His Orchestra</t>
+  </si>
+  <si>
+    <t>Blues in the Night</t>
+  </si>
+  <si>
+    <t>The Waltons Theme</t>
+  </si>
+  <si>
+    <t>Jerry Goldsmith</t>
+  </si>
+  <si>
+    <t>Amazon: The Waltons Theme Geek Music</t>
+  </si>
+  <si>
+    <t>Petula Clark</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>Dusty Springfield</t>
+  </si>
+  <si>
+    <t>Wishin’ and Hopin’</t>
+  </si>
+  <si>
+    <t>Stay Awhile/I Only Want to Be With You</t>
+  </si>
+  <si>
+    <t>Moonlight Cocktail</t>
+  </si>
+  <si>
+    <t>Kay Kyser and His Orchestra</t>
+  </si>
+  <si>
+    <t>Jingle Jangle Jingle</t>
+  </si>
+  <si>
+    <t>Benny Goodman</t>
+  </si>
+  <si>
+    <t>Jersey Bounce</t>
+  </si>
+  <si>
+    <t>Doris Day</t>
+  </si>
+  <si>
+    <t>Sentimental Journey</t>
+  </si>
+  <si>
+    <t>Harry James with Helen Forrest</t>
+  </si>
+  <si>
+    <t>I’ve Heard That Song Before</t>
+  </si>
+  <si>
+    <t>The Mills Brothers</t>
+  </si>
+  <si>
+    <t>Paper Doll</t>
+  </si>
+  <si>
+    <t>Duke Ellington</t>
+  </si>
+  <si>
+    <t>Don’t Get Around Much Anymore</t>
+  </si>
+  <si>
+    <t>The Merry Macs</t>
+  </si>
+  <si>
+    <t>Mairzy Doats</t>
+  </si>
+  <si>
+    <t>It’s Love‑Love‑Love</t>
+  </si>
+  <si>
+    <t>Guy Lombardo</t>
+  </si>
+  <si>
+    <t>Bing Crosby</t>
+  </si>
+  <si>
+    <t>I’ll Be Seeing You</t>
+  </si>
+  <si>
+    <t>Dinah Shore</t>
+  </si>
+  <si>
+    <t>I’ll Walk Alone</t>
   </si>
 </sst>
 </file>
@@ -10340,7 +10439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F618"/>
+  <dimension ref="A1:F621"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -21191,6 +21290,60 @@
       </c>
       <c r="F618" t="s">
         <v>1370</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A619" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B619" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D619" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E619">
+        <v>1972</v>
+      </c>
+      <c r="F619" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B620" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C620" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E620">
+        <v>1964</v>
+      </c>
+      <c r="F620" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B621" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C621" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E621">
+        <v>1964</v>
+      </c>
+      <c r="F621" t="s">
+        <v>1369</v>
       </c>
     </row>
   </sheetData>
@@ -21841,10 +21994,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E8"/>
+  <dimension ref="A2:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21872,6 +22025,12 @@
       <c r="C3" s="4" t="s">
         <v>2088</v>
       </c>
+      <c r="D3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E3">
+        <v>1940</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
@@ -21880,32 +22039,235 @@
       <c r="C4" s="4" t="s">
         <v>2091</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="D4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E4">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E5">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>1941</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>2092</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>2093</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2094</v>
+      <c r="E7">
+        <v>1941</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E8">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>2095</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>2096</v>
+      </c>
+      <c r="E9">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E10">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1942</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E12">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E13">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E14">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1943</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E16">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E17">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E18">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1944</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E21">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E22">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E23">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E24">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E30">
+        <v>1945</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101CC953-B233-D944-AD0A-BE6BE6D56107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDF4E3E-1AA0-AB4D-BEAF-0D2A1C71D973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3572" uniqueCount="2163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="2170">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6626,6 +6626,27 @@
   </si>
   <si>
     <t>I Can Dream, Can’t I?</t>
+  </si>
+  <si>
+    <t>How High the Moon</t>
+  </si>
+  <si>
+    <t>Les Paul &amp; Mary Ford</t>
+  </si>
+  <si>
+    <t>Rosemary Clooney</t>
+  </si>
+  <si>
+    <t>Come On‑a My House</t>
+  </si>
+  <si>
+    <t>Come On‑A My House</t>
+  </si>
+  <si>
+    <t>The Four Aces</t>
+  </si>
+  <si>
+    <t>(It’s No) Sin</t>
   </si>
 </sst>
 </file>
@@ -22075,7 +22096,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E55"/>
+  <dimension ref="A2:E57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
@@ -22593,6 +22614,46 @@
       <c r="A55">
         <v>1951</v>
       </c>
+      <c r="B55" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E55">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E56">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E57">
+        <v>1951</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDF4E3E-1AA0-AB4D-BEAF-0D2A1C71D973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC7DDC2-D94A-494D-82DC-90A1E2D1015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Bumpers" sheetId="19" r:id="rId4"/>
     <sheet name="Seasonal" sheetId="20" r:id="rId5"/>
     <sheet name="Broadway" sheetId="21" r:id="rId6"/>
-    <sheet name="1940s" sheetId="22" r:id="rId7"/>
+    <sheet name="1940-1960" sheetId="22" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Playlist'!$A$1:$F$497</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="2170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="2187">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6647,6 +6647,57 @@
   </si>
   <si>
     <t>(It’s No) Sin</t>
+  </si>
+  <si>
+    <t>You Belong to Me</t>
+  </si>
+  <si>
+    <t>Jo Stafford</t>
+  </si>
+  <si>
+    <t>Comes A‑Long A‑Love</t>
+  </si>
+  <si>
+    <t>Kay Starr</t>
+  </si>
+  <si>
+    <t>The Glow‑Worm</t>
+  </si>
+  <si>
+    <t>The Song from Moulin Rouge (Where Is Your Heart)</t>
+  </si>
+  <si>
+    <t>Percy Faith &amp; Felicia Sanders</t>
+  </si>
+  <si>
+    <t>The Ames Brothers</t>
+  </si>
+  <si>
+    <t>You, You, You</t>
+  </si>
+  <si>
+    <t>That’s Amore</t>
+  </si>
+  <si>
+    <t>Dean Martin</t>
+  </si>
+  <si>
+    <t>Dean Martin Sings</t>
+  </si>
+  <si>
+    <t>Make Love to Me!</t>
+  </si>
+  <si>
+    <t>Mr. Sandman</t>
+  </si>
+  <si>
+    <t>The Chordettes</t>
+  </si>
+  <si>
+    <t>Sh‑Boom (Life Could Be a Dream)</t>
+  </si>
+  <si>
+    <t>The Crew‑Cuts</t>
   </si>
 </sst>
 </file>
@@ -22096,7 +22147,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E57"/>
+  <dimension ref="A2:E75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
@@ -22655,6 +22706,146 @@
         <v>1951</v>
       </c>
     </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>1952</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E60">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="B61" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E61">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="B62" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E62">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>1953</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E65">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="B66" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E66">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E67">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>1954</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E70">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E71">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="B72" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E72">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>1955</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC7DDC2-D94A-494D-82DC-90A1E2D1015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB0498-DE4D-D249-9F61-3DF40C3553D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3632" uniqueCount="2204">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6698,6 +6698,57 @@
   </si>
   <si>
     <t>The Crew‑Cuts</t>
+  </si>
+  <si>
+    <t>(We’re Gonna) Rock Around the Clock</t>
+  </si>
+  <si>
+    <t>Bill Haley &amp; His Comets</t>
+  </si>
+  <si>
+    <t>Rock Around the Clock</t>
+  </si>
+  <si>
+    <t>Little Richard</t>
+  </si>
+  <si>
+    <t>Tutti Frutti</t>
+  </si>
+  <si>
+    <t>Here’s Little Richard</t>
+  </si>
+  <si>
+    <t>Bo Diddley</t>
+  </si>
+  <si>
+    <t>Ain’t That a Shame</t>
+  </si>
+  <si>
+    <t>Fats Domino</t>
+  </si>
+  <si>
+    <t>Rock and Rollin’ with Fats Domino</t>
+  </si>
+  <si>
+    <t>Hound Dog</t>
+  </si>
+  <si>
+    <t>Elvis’ Golden Records</t>
+  </si>
+  <si>
+    <t>Why Do Fools Fall in Love</t>
+  </si>
+  <si>
+    <t>Frankie Lymon &amp; The Teenagers</t>
+  </si>
+  <si>
+    <t>The Teenagers Featuring Frankie Lymon</t>
+  </si>
+  <si>
+    <t>Let the Good Times Roll</t>
+  </si>
+  <si>
+    <t>Shirley &amp; Lee</t>
   </si>
 </sst>
 </file>
@@ -22147,7 +22198,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E75"/>
+  <dimension ref="A2:E84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
@@ -22845,6 +22896,116 @@
       <c r="A75">
         <v>1955</v>
       </c>
+      <c r="B75" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E75">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E76">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E77">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="B78" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>1956</v>
+      </c>
+      <c r="B81" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D81" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="B82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E82">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="B83" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E83">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="B84" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E84">
+        <v>1956</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3B4819-2C35-9E4D-8F56-2C831BE6F805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A35F8-645E-C54F-9F83-32B34710F6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="2072">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6317,12 +6317,60 @@
   <si>
     <t>Rebels on the Run</t>
   </si>
+  <si>
+    <t>Nick Drake</t>
+  </si>
+  <si>
+    <t>Pink Moon</t>
+  </si>
+  <si>
+    <t>I Want You</t>
+  </si>
+  <si>
+    <t>Suzanne Vega</t>
+  </si>
+  <si>
+    <t>Luka</t>
+  </si>
+  <si>
+    <t>Solitude Standing</t>
+  </si>
+  <si>
+    <t>Build Me Up Buttercup</t>
+  </si>
+  <si>
+    <t>The Foundations</t>
+  </si>
+  <si>
+    <t>Michael Holliday</t>
+  </si>
+  <si>
+    <t>Stairway of Love</t>
+  </si>
+  <si>
+    <t>Guy Mitchell</t>
+  </si>
+  <si>
+    <t>Feet Up (Pat Him on the Po‑Po</t>
+  </si>
+  <si>
+    <t>We Can Work It Out</t>
+  </si>
+  <si>
+    <t>eTown Webisode 67</t>
+  </si>
+  <si>
+    <t>Flobots, Teddy Thompson, Nick &amp; Helen Forster, the eTones</t>
+  </si>
+  <si>
+    <t>Need to get permission/mp3 from eTown</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6764,13 +6812,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:B265"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="95.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>381</v>
       </c>
@@ -6778,7 +6826,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>382</v>
       </c>
@@ -6786,7 +6834,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>383</v>
       </c>
@@ -6794,7 +6842,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>377</v>
       </c>
@@ -6802,7 +6850,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -6810,7 +6858,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>262</v>
       </c>
@@ -6818,7 +6866,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -6826,7 +6874,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -6834,7 +6882,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>314</v>
       </c>
@@ -6842,7 +6890,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>433</v>
       </c>
@@ -6850,7 +6898,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>263</v>
       </c>
@@ -6858,7 +6906,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -6866,7 +6914,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>384</v>
       </c>
@@ -6874,7 +6922,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>264</v>
       </c>
@@ -6882,7 +6930,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>212</v>
       </c>
@@ -6890,7 +6938,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>434</v>
       </c>
@@ -6898,7 +6946,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>265</v>
       </c>
@@ -6906,7 +6954,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -6914,7 +6962,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -6922,7 +6970,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>385</v>
       </c>
@@ -6930,7 +6978,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -6938,7 +6986,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>352</v>
       </c>
@@ -6946,7 +6994,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -6954,7 +7002,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>386</v>
       </c>
@@ -6962,7 +7010,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>90</v>
       </c>
@@ -6970,7 +7018,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>353</v>
       </c>
@@ -6978,7 +7026,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>387</v>
       </c>
@@ -6986,7 +7034,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>315</v>
       </c>
@@ -6994,7 +7042,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -7002,7 +7050,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -7010,7 +7058,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>157</v>
       </c>
@@ -7018,7 +7066,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>204</v>
       </c>
@@ -7026,7 +7074,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -7034,7 +7082,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -7042,7 +7090,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -7050,7 +7098,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>231</v>
       </c>
@@ -7058,7 +7106,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>388</v>
       </c>
@@ -7066,7 +7114,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>389</v>
       </c>
@@ -7074,7 +7122,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>316</v>
       </c>
@@ -7082,7 +7130,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>232</v>
       </c>
@@ -7090,7 +7138,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>448</v>
       </c>
@@ -7098,7 +7146,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>354</v>
       </c>
@@ -7106,7 +7154,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -7114,7 +7162,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -7122,7 +7170,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -7130,7 +7178,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>266</v>
       </c>
@@ -7138,7 +7186,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>159</v>
       </c>
@@ -7146,7 +7194,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>415</v>
       </c>
@@ -7154,7 +7202,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>71</v>
       </c>
@@ -7162,7 +7210,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>317</v>
       </c>
@@ -7170,7 +7218,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>435</v>
       </c>
@@ -7178,7 +7226,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>233</v>
       </c>
@@ -7186,7 +7234,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>390</v>
       </c>
@@ -7194,7 +7242,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>160</v>
       </c>
@@ -7202,7 +7250,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -7210,7 +7258,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -7218,7 +7266,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>391</v>
       </c>
@@ -7226,7 +7274,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -7234,7 +7282,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -7242,7 +7290,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -7250,7 +7298,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>163</v>
       </c>
@@ -7258,7 +7306,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -7266,7 +7314,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>416</v>
       </c>
@@ -7274,7 +7322,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>164</v>
       </c>
@@ -7282,7 +7330,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>392</v>
       </c>
@@ -7290,7 +7338,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>449</v>
       </c>
@@ -7298,7 +7346,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>318</v>
       </c>
@@ -7306,7 +7354,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>319</v>
       </c>
@@ -7314,7 +7362,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>320</v>
       </c>
@@ -7322,7 +7370,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>321</v>
       </c>
@@ -7330,7 +7378,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -7338,7 +7386,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -7346,7 +7394,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>322</v>
       </c>
@@ -7354,7 +7402,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>323</v>
       </c>
@@ -7362,7 +7410,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>267</v>
       </c>
@@ -7370,7 +7418,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>450</v>
       </c>
@@ -7378,7 +7426,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>187</v>
       </c>
@@ -7386,7 +7434,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -7394,7 +7442,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -7402,7 +7450,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>393</v>
       </c>
@@ -7410,7 +7458,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -7418,7 +7466,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>47</v>
       </c>
@@ -7426,7 +7474,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>54</v>
       </c>
@@ -7434,7 +7482,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -7442,7 +7490,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>324</v>
       </c>
@@ -7450,7 +7498,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>355</v>
       </c>
@@ -7458,7 +7506,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -7466,7 +7514,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>394</v>
       </c>
@@ -7474,7 +7522,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>68</v>
       </c>
@@ -7482,7 +7530,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>325</v>
       </c>
@@ -7490,7 +7538,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>166</v>
       </c>
@@ -7498,7 +7546,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>417</v>
       </c>
@@ -7506,7 +7554,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>326</v>
       </c>
@@ -7514,7 +7562,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>167</v>
       </c>
@@ -7522,7 +7570,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>436</v>
       </c>
@@ -7530,7 +7578,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -7538,7 +7586,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>327</v>
       </c>
@@ -7546,7 +7594,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -7554,7 +7602,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>328</v>
       </c>
@@ -7562,7 +7610,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -7570,7 +7618,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>418</v>
       </c>
@@ -7578,7 +7626,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>395</v>
       </c>
@@ -7586,7 +7634,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>168</v>
       </c>
@@ -7594,7 +7642,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>169</v>
       </c>
@@ -7602,7 +7650,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -7610,7 +7658,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>329</v>
       </c>
@@ -7618,7 +7666,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>194</v>
       </c>
@@ -7626,7 +7674,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>396</v>
       </c>
@@ -7634,7 +7682,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>451</v>
       </c>
@@ -7642,7 +7690,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -7650,7 +7698,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>437</v>
       </c>
@@ -7658,7 +7706,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>419</v>
       </c>
@@ -7666,7 +7714,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>397</v>
       </c>
@@ -7674,7 +7722,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>20</v>
       </c>
@@ -7682,7 +7730,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>269</v>
       </c>
@@ -7690,7 +7738,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -7698,7 +7746,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>438</v>
       </c>
@@ -7706,7 +7754,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>38</v>
       </c>
@@ -7714,7 +7762,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>398</v>
       </c>
@@ -7722,7 +7770,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>452</v>
       </c>
@@ -7730,7 +7778,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>171</v>
       </c>
@@ -7738,7 +7786,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>235</v>
       </c>
@@ -7746,7 +7794,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>507</v>
       </c>
@@ -7754,7 +7802,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>172</v>
       </c>
@@ -7762,7 +7810,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>439</v>
       </c>
@@ -7770,7 +7818,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -7778,7 +7826,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>330</v>
       </c>
@@ -7786,7 +7834,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -7794,7 +7842,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>440</v>
       </c>
@@ -7802,7 +7850,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>42</v>
       </c>
@@ -7810,7 +7858,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>271</v>
       </c>
@@ -7818,7 +7866,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>399</v>
       </c>
@@ -7826,7 +7874,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>400</v>
       </c>
@@ -7834,7 +7882,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>211</v>
       </c>
@@ -7842,7 +7890,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>401</v>
       </c>
@@ -7850,7 +7898,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>189</v>
       </c>
@@ -7858,7 +7906,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>331</v>
       </c>
@@ -7866,7 +7914,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>402</v>
       </c>
@@ -7874,7 +7922,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>173</v>
       </c>
@@ -7882,7 +7930,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>403</v>
       </c>
@@ -7890,7 +7938,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>420</v>
       </c>
@@ -7898,7 +7946,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>174</v>
       </c>
@@ -7906,7 +7954,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>124</v>
       </c>
@@ -7914,7 +7962,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>111</v>
       </c>
@@ -7922,7 +7970,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>404</v>
       </c>
@@ -7930,7 +7978,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>453</v>
       </c>
@@ -7938,7 +7986,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>356</v>
       </c>
@@ -7946,7 +7994,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>332</v>
       </c>
@@ -7954,7 +8002,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>454</v>
       </c>
@@ -7962,7 +8010,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>441</v>
       </c>
@@ -7970,7 +8018,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>217</v>
       </c>
@@ -7978,7 +8026,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>442</v>
       </c>
@@ -7986,7 +8034,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>272</v>
       </c>
@@ -7994,7 +8042,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>114</v>
       </c>
@@ -8002,7 +8050,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>26</v>
       </c>
@@ -8010,7 +8058,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>30</v>
       </c>
@@ -8018,7 +8066,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -8026,7 +8074,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -8034,7 +8082,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>273</v>
       </c>
@@ -8042,7 +8090,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -8050,7 +8098,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>8</v>
       </c>
@@ -8058,7 +8106,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -8066,7 +8114,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>25</v>
       </c>
@@ -8074,7 +8122,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>27</v>
       </c>
@@ -8082,7 +8130,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -8090,7 +8138,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>64</v>
       </c>
@@ -8098,7 +8146,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>175</v>
       </c>
@@ -8106,7 +8154,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>216</v>
       </c>
@@ -8114,7 +8162,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>61</v>
       </c>
@@ -8122,7 +8170,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -8130,7 +8178,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>63</v>
       </c>
@@ -8138,7 +8186,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>12</v>
       </c>
@@ -8146,7 +8194,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -8154,7 +8202,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -8162,7 +8210,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>201</v>
       </c>
@@ -8170,7 +8218,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>176</v>
       </c>
@@ -8178,7 +8226,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>236</v>
       </c>
@@ -8186,7 +8234,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -8194,7 +8242,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>33</v>
       </c>
@@ -8202,7 +8250,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>56</v>
       </c>
@@ -8210,7 +8258,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>209</v>
       </c>
@@ -8218,7 +8266,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>177</v>
       </c>
@@ -8226,7 +8274,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -8234,7 +8282,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>31</v>
       </c>
@@ -8242,7 +8290,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>67</v>
       </c>
@@ -8250,7 +8298,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>514</v>
       </c>
@@ -8258,7 +8306,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>405</v>
       </c>
@@ -8266,7 +8314,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>29</v>
       </c>
@@ -8274,7 +8322,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -8282,7 +8330,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>100</v>
       </c>
@@ -8290,7 +8338,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>3</v>
       </c>
@@ -8298,7 +8346,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>82</v>
       </c>
@@ -8306,7 +8354,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2">
       <c r="A193" t="s">
         <v>406</v>
       </c>
@@ -8314,7 +8362,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2">
       <c r="A194" t="s">
         <v>19</v>
       </c>
@@ -8322,7 +8370,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2">
       <c r="A195" t="s">
         <v>237</v>
       </c>
@@ -8330,7 +8378,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2">
       <c r="A196" t="s">
         <v>407</v>
       </c>
@@ -8338,7 +8386,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -8346,7 +8394,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -8354,7 +8402,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -8362,7 +8410,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2">
       <c r="A200" t="s">
         <v>32</v>
       </c>
@@ -8370,7 +8418,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -8378,7 +8426,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2">
       <c r="A202" t="s">
         <v>118</v>
       </c>
@@ -8386,7 +8434,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2">
       <c r="A203" t="s">
         <v>408</v>
       </c>
@@ -8394,7 +8442,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2">
       <c r="A204" t="s">
         <v>28</v>
       </c>
@@ -8402,7 +8450,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2">
       <c r="A205" t="s">
         <v>443</v>
       </c>
@@ -8410,7 +8458,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2">
       <c r="A206" t="s">
         <v>192</v>
       </c>
@@ -8418,7 +8466,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2">
       <c r="A207" t="s">
         <v>409</v>
       </c>
@@ -8426,7 +8474,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2">
       <c r="A208" t="s">
         <v>410</v>
       </c>
@@ -8434,7 +8482,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2">
       <c r="A209" t="s">
         <v>334</v>
       </c>
@@ -8442,7 +8490,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2">
       <c r="A210" t="s">
         <v>238</v>
       </c>
@@ -8450,7 +8498,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2">
       <c r="A211" t="s">
         <v>455</v>
       </c>
@@ -8458,7 +8506,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2">
       <c r="A212" t="s">
         <v>178</v>
       </c>
@@ -8466,7 +8514,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2">
       <c r="A213" t="s">
         <v>87</v>
       </c>
@@ -8474,7 +8522,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2">
       <c r="A214" t="s">
         <v>335</v>
       </c>
@@ -8482,7 +8530,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2">
       <c r="A215" t="s">
         <v>444</v>
       </c>
@@ -8490,7 +8538,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2">
       <c r="A216" t="s">
         <v>456</v>
       </c>
@@ -8498,7 +8546,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2">
       <c r="A217" t="s">
         <v>179</v>
       </c>
@@ -8506,7 +8554,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2">
       <c r="A218" t="s">
         <v>7</v>
       </c>
@@ -8514,7 +8562,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2">
       <c r="A219" t="s">
         <v>24</v>
       </c>
@@ -8522,7 +8570,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2">
       <c r="A220" t="s">
         <v>186</v>
       </c>
@@ -8530,7 +8578,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2">
       <c r="A221" t="s">
         <v>180</v>
       </c>
@@ -8538,7 +8586,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2">
       <c r="A222" t="s">
         <v>86</v>
       </c>
@@ -8546,7 +8594,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2">
       <c r="A223" t="s">
         <v>336</v>
       </c>
@@ -8554,7 +8602,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2">
       <c r="A224" t="s">
         <v>337</v>
       </c>
@@ -8562,7 +8610,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -8570,7 +8618,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2">
       <c r="A226" t="s">
         <v>338</v>
       </c>
@@ -8578,7 +8626,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2">
       <c r="A227" t="s">
         <v>120</v>
       </c>
@@ -8586,7 +8634,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2">
       <c r="A228" t="s">
         <v>339</v>
       </c>
@@ -8594,7 +8642,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2">
       <c r="A229" t="s">
         <v>422</v>
       </c>
@@ -8602,7 +8650,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2">
       <c r="A230" t="s">
         <v>181</v>
       </c>
@@ -8610,7 +8658,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2">
       <c r="A231" t="s">
         <v>411</v>
       </c>
@@ -8618,7 +8666,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2">
       <c r="A232" t="s">
         <v>423</v>
       </c>
@@ -8626,7 +8674,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2">
       <c r="A233" t="s">
         <v>457</v>
       </c>
@@ -8634,7 +8682,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2">
       <c r="A234" t="s">
         <v>341</v>
       </c>
@@ -8642,7 +8690,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2">
       <c r="A235" t="s">
         <v>340</v>
       </c>
@@ -8650,7 +8698,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2">
       <c r="A236" t="s">
         <v>182</v>
       </c>
@@ -8658,7 +8706,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2">
       <c r="A237" t="s">
         <v>421</v>
       </c>
@@ -8666,7 +8714,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2">
       <c r="A238" t="s">
         <v>75</v>
       </c>
@@ -8674,7 +8722,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2">
       <c r="A239" t="s">
         <v>445</v>
       </c>
@@ -8682,7 +8730,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2">
       <c r="A240" t="s">
         <v>102</v>
       </c>
@@ -8690,7 +8738,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2">
       <c r="A241" t="s">
         <v>200</v>
       </c>
@@ -8698,7 +8746,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2">
       <c r="A242" t="s">
         <v>458</v>
       </c>
@@ -8706,7 +8754,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2">
       <c r="A243" t="s">
         <v>424</v>
       </c>
@@ -8714,7 +8762,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2">
       <c r="A244" t="s">
         <v>240</v>
       </c>
@@ -8722,7 +8770,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2">
       <c r="A245" t="s">
         <v>342</v>
       </c>
@@ -8730,7 +8778,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2">
       <c r="A246" t="s">
         <v>357</v>
       </c>
@@ -8738,7 +8786,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2">
       <c r="A247" t="s">
         <v>446</v>
       </c>
@@ -8746,7 +8794,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2">
       <c r="A248" t="s">
         <v>412</v>
       </c>
@@ -8754,7 +8802,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2">
       <c r="A249" t="s">
         <v>70</v>
       </c>
@@ -8762,7 +8810,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2">
       <c r="A250" t="s">
         <v>459</v>
       </c>
@@ -8770,7 +8818,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2">
       <c r="A251" t="s">
         <v>358</v>
       </c>
@@ -8778,7 +8826,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2">
       <c r="A252" t="s">
         <v>274</v>
       </c>
@@ -8786,7 +8834,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2">
       <c r="A253" t="s">
         <v>425</v>
       </c>
@@ -8794,7 +8842,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2">
       <c r="A254" t="s">
         <v>413</v>
       </c>
@@ -8802,7 +8850,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2">
       <c r="A255" t="s">
         <v>214</v>
       </c>
@@ -8810,7 +8858,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2">
       <c r="A256" t="s">
         <v>426</v>
       </c>
@@ -8818,7 +8866,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2">
       <c r="A257" t="s">
         <v>414</v>
       </c>
@@ -8826,7 +8874,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2">
       <c r="A258" t="s">
         <v>183</v>
       </c>
@@ -8834,7 +8882,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2">
       <c r="A259" t="s">
         <v>343</v>
       </c>
@@ -8842,7 +8890,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2">
       <c r="A260" t="s">
         <v>460</v>
       </c>
@@ -8850,7 +8898,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:2">
       <c r="A261" t="s">
         <v>184</v>
       </c>
@@ -8858,7 +8906,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:2">
       <c r="A262" t="s">
         <v>447</v>
       </c>
@@ -8866,7 +8914,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:2">
       <c r="A263" t="s">
         <v>23</v>
       </c>
@@ -8874,7 +8922,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:2">
       <c r="A264" t="s">
         <v>185</v>
       </c>
@@ -8882,7 +8930,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:2">
       <c r="A265" t="s">
         <v>215</v>
       </c>
@@ -8898,8 +8946,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F587"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F594"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" bestFit="1" customWidth="1"/>
@@ -8908,7 +8956,7 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="6" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>461</v>
       </c>
@@ -8928,7 +8976,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>520</v>
       </c>
@@ -8942,7 +8990,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>523</v>
       </c>
@@ -8956,7 +9004,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>526</v>
       </c>
@@ -8970,7 +9018,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>528</v>
       </c>
@@ -8984,7 +9032,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>299</v>
       </c>
@@ -8998,7 +9046,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>590</v>
       </c>
@@ -9012,7 +9060,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>593</v>
       </c>
@@ -9029,7 +9077,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>596</v>
       </c>
@@ -9043,7 +9091,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -9059,7 +9107,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>620</v>
       </c>
@@ -9077,7 +9125,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>634</v>
       </c>
@@ -9095,7 +9143,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -9110,7 +9158,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>624</v>
       </c>
@@ -9128,7 +9176,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>627</v>
       </c>
@@ -9146,7 +9194,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>630</v>
       </c>
@@ -9166,7 +9214,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>637</v>
       </c>
@@ -9184,7 +9232,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>257</v>
       </c>
@@ -9201,7 +9249,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" s="1" customFormat="1">
       <c r="A19" s="1" t="s">
         <v>405</v>
       </c>
@@ -9215,7 +9263,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" s="1" customFormat="1">
       <c r="A20" s="1" t="s">
         <v>646</v>
       </c>
@@ -9235,7 +9283,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>649</v>
       </c>
@@ -9252,7 +9300,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>650</v>
       </c>
@@ -9269,7 +9317,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>655</v>
       </c>
@@ -9286,7 +9334,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" s="1" customFormat="1">
       <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
@@ -9303,7 +9351,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>658</v>
       </c>
@@ -9321,7 +9369,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" s="1" customFormat="1">
       <c r="A26" s="1" t="s">
         <v>222</v>
       </c>
@@ -9338,7 +9386,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" s="1" customFormat="1">
       <c r="A27" s="1" t="s">
         <v>663</v>
       </c>
@@ -9355,7 +9403,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" s="1" customFormat="1">
       <c r="A28" s="1" t="s">
         <v>666</v>
       </c>
@@ -9372,7 +9420,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" s="1" customFormat="1">
       <c r="A29" s="1" t="s">
         <v>669</v>
       </c>
@@ -9389,7 +9437,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" s="1" customFormat="1">
       <c r="A30" s="1" t="s">
         <v>672</v>
       </c>
@@ -9406,7 +9454,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" s="1" customFormat="1">
       <c r="A31" s="1" t="s">
         <v>675</v>
       </c>
@@ -9423,7 +9471,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" s="1" customFormat="1">
       <c r="A32" s="1" t="s">
         <v>678</v>
       </c>
@@ -9440,7 +9488,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" s="1" customFormat="1">
       <c r="A33" s="1" t="s">
         <v>228</v>
       </c>
@@ -9457,7 +9505,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" s="8" customFormat="1">
       <c r="A34" s="1" t="s">
         <v>685</v>
       </c>
@@ -9475,7 +9523,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" s="8" customFormat="1">
       <c r="A35" s="1" t="s">
         <v>688</v>
       </c>
@@ -9493,7 +9541,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" s="8" customFormat="1">
       <c r="A36" s="1" t="s">
         <v>689</v>
       </c>
@@ -9511,7 +9559,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" s="8" customFormat="1">
       <c r="A37" s="1" t="s">
         <v>692</v>
       </c>
@@ -9529,7 +9577,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" s="1" customFormat="1">
       <c r="A38" s="1" t="s">
         <v>698</v>
       </c>
@@ -9546,7 +9594,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" s="8" customFormat="1">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -9564,7 +9612,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" s="1" customFormat="1">
       <c r="A40" s="1" t="s">
         <v>701</v>
       </c>
@@ -9581,7 +9629,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" s="1" customFormat="1">
       <c r="A41" s="1" t="s">
         <v>703</v>
       </c>
@@ -9598,7 +9646,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" s="1" customFormat="1">
       <c r="A42" s="1" t="s">
         <v>706</v>
       </c>
@@ -9615,7 +9663,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" s="1" customFormat="1">
       <c r="A43" s="1" t="s">
         <v>708</v>
       </c>
@@ -9632,7 +9680,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="44" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" s="1" customFormat="1">
       <c r="A44" s="1" t="s">
         <v>710</v>
       </c>
@@ -9649,7 +9697,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
         <v>711</v>
       </c>
@@ -9666,7 +9714,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="46" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" s="1" customFormat="1">
       <c r="A46" s="1" t="s">
         <v>235</v>
       </c>
@@ -9683,7 +9731,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" s="1" customFormat="1">
       <c r="A47" s="1" t="s">
         <v>289</v>
       </c>
@@ -9700,7 +9748,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" s="1" customFormat="1">
       <c r="A48" s="1" t="s">
         <v>718</v>
       </c>
@@ -9717,7 +9765,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" s="1" customFormat="1">
       <c r="A49" s="1" t="s">
         <v>719</v>
       </c>
@@ -9734,7 +9782,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" s="1" customFormat="1">
       <c r="A50" s="1" t="s">
         <v>720</v>
       </c>
@@ -9751,7 +9799,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" s="1" customFormat="1">
       <c r="A51" s="1" t="s">
         <v>721</v>
       </c>
@@ -9768,7 +9816,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" s="1" customFormat="1">
       <c r="A52" s="1" t="s">
         <v>722</v>
       </c>
@@ -9785,7 +9833,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
         <v>733</v>
       </c>
@@ -9803,7 +9851,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
         <v>736</v>
       </c>
@@ -9821,7 +9869,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
         <v>737</v>
       </c>
@@ -9839,7 +9887,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
         <v>740</v>
       </c>
@@ -9857,7 +9905,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
         <v>777</v>
       </c>
@@ -9874,7 +9922,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
         <v>778</v>
       </c>
@@ -9891,7 +9939,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
         <v>778</v>
       </c>
@@ -9908,7 +9956,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
         <v>745</v>
       </c>
@@ -9926,7 +9974,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
         <v>748</v>
       </c>
@@ -9944,7 +9992,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
         <v>752</v>
       </c>
@@ -9962,7 +10010,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="63" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" s="1" customFormat="1">
       <c r="A63" s="1" t="s">
         <v>755</v>
       </c>
@@ -9979,7 +10027,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="64" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" s="1" customFormat="1">
       <c r="A64" s="1" t="s">
         <v>759</v>
       </c>
@@ -9996,7 +10044,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" s="1" customFormat="1">
       <c r="A65" s="1" t="s">
         <v>519</v>
       </c>
@@ -10013,7 +10061,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" s="1" customFormat="1">
       <c r="A66" s="1" t="s">
         <v>762</v>
       </c>
@@ -10030,7 +10078,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" s="1" customFormat="1">
       <c r="A67" s="1" t="s">
         <v>764</v>
       </c>
@@ -10047,7 +10095,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" s="1" customFormat="1">
       <c r="A68" s="1" t="s">
         <v>768</v>
       </c>
@@ -10064,7 +10112,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" s="1" customFormat="1">
       <c r="A69" s="1" t="s">
         <v>770</v>
       </c>
@@ -10081,7 +10129,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" s="1" customFormat="1">
       <c r="A70" s="1" t="s">
         <v>263</v>
       </c>
@@ -10098,7 +10146,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" s="1" customFormat="1">
       <c r="A71" s="1" t="s">
         <v>779</v>
       </c>
@@ -10115,7 +10163,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
         <v>782</v>
       </c>
@@ -10133,7 +10181,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
         <v>785</v>
       </c>
@@ -10151,7 +10199,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
         <v>788</v>
       </c>
@@ -10169,7 +10217,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
         <v>256</v>
       </c>
@@ -10187,7 +10235,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
         <v>793</v>
       </c>
@@ -10205,7 +10253,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
         <v>795</v>
       </c>
@@ -10223,7 +10271,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
         <v>798</v>
       </c>
@@ -10241,7 +10289,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
         <v>800</v>
       </c>
@@ -10259,7 +10307,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
         <v>804</v>
       </c>
@@ -10277,7 +10325,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>192</v>
       </c>
@@ -10295,7 +10343,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
         <v>807</v>
       </c>
@@ -10313,7 +10361,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
         <v>30</v>
       </c>
@@ -10331,7 +10379,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
         <v>367</v>
       </c>
@@ -10349,7 +10397,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
         <v>813</v>
       </c>
@@ -10367,7 +10415,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
         <v>816</v>
       </c>
@@ -10385,7 +10433,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6">
       <c r="A87" s="1" t="s">
         <v>819</v>
       </c>
@@ -10403,7 +10451,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
         <v>822</v>
       </c>
@@ -10421,7 +10469,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="A89" s="1" t="s">
         <v>824</v>
       </c>
@@ -10439,7 +10487,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
         <v>827</v>
       </c>
@@ -10457,7 +10505,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
         <v>830</v>
       </c>
@@ -10475,7 +10523,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
         <v>206</v>
       </c>
@@ -10493,7 +10541,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6">
       <c r="A93" s="1" t="s">
         <v>835</v>
       </c>
@@ -10511,7 +10559,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
         <v>201</v>
       </c>
@@ -10529,7 +10577,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="1" t="s">
         <v>840</v>
       </c>
@@ -10547,7 +10595,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
         <v>368</v>
       </c>
@@ -10565,7 +10613,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6">
       <c r="A97" s="1" t="s">
         <v>845</v>
       </c>
@@ -10583,7 +10631,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
         <v>848</v>
       </c>
@@ -10601,7 +10649,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6">
       <c r="A99" s="1" t="s">
         <v>164</v>
       </c>
@@ -10619,7 +10667,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
         <v>75</v>
       </c>
@@ -10637,7 +10685,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="1" t="s">
         <v>855</v>
       </c>
@@ -10655,7 +10703,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="1" t="s">
         <v>858</v>
       </c>
@@ -10673,7 +10721,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="1" t="s">
         <v>861</v>
       </c>
@@ -10691,7 +10739,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="1" t="s">
         <v>864</v>
       </c>
@@ -10709,7 +10757,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="1" t="s">
         <v>867</v>
       </c>
@@ -10727,7 +10775,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="1" t="s">
         <v>870</v>
       </c>
@@ -10745,7 +10793,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="1" t="s">
         <v>873</v>
       </c>
@@ -10763,7 +10811,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
         <v>876</v>
       </c>
@@ -10781,7 +10829,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6">
       <c r="A109" s="1" t="s">
         <v>16</v>
       </c>
@@ -10799,7 +10847,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="1" t="s">
         <v>881</v>
       </c>
@@ -10817,7 +10865,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="1" t="s">
         <v>884</v>
       </c>
@@ -10835,7 +10883,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="1" t="s">
         <v>13</v>
       </c>
@@ -10853,7 +10901,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="1" t="s">
         <v>888</v>
       </c>
@@ -10871,7 +10919,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="1" t="s">
         <v>890</v>
       </c>
@@ -10889,7 +10937,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6">
       <c r="A115" s="1" t="s">
         <v>33</v>
       </c>
@@ -10907,7 +10955,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="1" t="s">
         <v>894</v>
       </c>
@@ -10925,7 +10973,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="1" t="s">
         <v>897</v>
       </c>
@@ -10943,7 +10991,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="1" t="s">
         <v>900</v>
       </c>
@@ -10961,7 +11009,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="1" t="s">
         <v>903</v>
       </c>
@@ -10979,7 +11027,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="A120" s="1" t="s">
         <v>15</v>
       </c>
@@ -10997,7 +11045,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="A121" s="1" t="s">
         <v>190</v>
       </c>
@@ -11015,7 +11063,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="A122" s="1" t="s">
         <v>261</v>
       </c>
@@ -11033,7 +11081,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6">
       <c r="A123" s="1" t="s">
         <v>911</v>
       </c>
@@ -11051,7 +11099,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="A124" s="1" t="s">
         <v>205</v>
       </c>
@@ -11069,7 +11117,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="A125" s="1" t="s">
         <v>76</v>
       </c>
@@ -11087,7 +11135,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6">
       <c r="A126" s="1" t="s">
         <v>50</v>
       </c>
@@ -11105,7 +11153,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6">
       <c r="A127" s="1" t="s">
         <v>919</v>
       </c>
@@ -11123,7 +11171,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6">
       <c r="A128" s="1" t="s">
         <v>51</v>
       </c>
@@ -11141,7 +11189,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6">
       <c r="A129" s="1" t="s">
         <v>0</v>
       </c>
@@ -11159,7 +11207,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6">
       <c r="A130" s="1" t="s">
         <v>80</v>
       </c>
@@ -11177,7 +11225,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6">
       <c r="A131" s="1" t="s">
         <v>230</v>
       </c>
@@ -11195,7 +11243,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6">
       <c r="A132" s="1" t="s">
         <v>233</v>
       </c>
@@ -11213,7 +11261,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6">
       <c r="A133" s="1" t="s">
         <v>220</v>
       </c>
@@ -11231,7 +11279,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6">
       <c r="A134" s="1" t="s">
         <v>227</v>
       </c>
@@ -11249,7 +11297,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="A135" s="1" t="s">
         <v>364</v>
       </c>
@@ -11267,7 +11315,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="A136" s="1" t="s">
         <v>360</v>
       </c>
@@ -11285,7 +11333,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6">
       <c r="A137" s="1" t="s">
         <v>134</v>
       </c>
@@ -11303,7 +11351,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="A138" s="1" t="s">
         <v>135</v>
       </c>
@@ -11321,7 +11369,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -11339,7 +11387,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="A140" s="1" t="s">
         <v>146</v>
       </c>
@@ -11357,7 +11405,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="A141" s="1" t="s">
         <v>149</v>
       </c>
@@ -11375,7 +11423,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6">
       <c r="A142" s="1" t="s">
         <v>161</v>
       </c>
@@ -11393,7 +11441,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="A143" s="1" t="s">
         <v>184</v>
       </c>
@@ -11411,7 +11459,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="A144" s="1" t="s">
         <v>122</v>
       </c>
@@ -11429,7 +11477,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="A145" s="1" t="s">
         <v>129</v>
       </c>
@@ -11447,7 +11495,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6">
       <c r="A146" s="1" t="s">
         <v>130</v>
       </c>
@@ -11465,7 +11513,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6">
       <c r="A147" s="1" t="s">
         <v>136</v>
       </c>
@@ -11483,7 +11531,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6">
       <c r="A148" s="1" t="s">
         <v>954</v>
       </c>
@@ -11501,7 +11549,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6">
       <c r="A149" s="1" t="s">
         <v>957</v>
       </c>
@@ -11519,7 +11567,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6">
       <c r="A150" s="1" t="s">
         <v>961</v>
       </c>
@@ -11537,7 +11585,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6">
       <c r="A151" s="1" t="s">
         <v>962</v>
       </c>
@@ -11555,7 +11603,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6">
       <c r="A152" s="1" t="s">
         <v>965</v>
       </c>
@@ -11573,7 +11621,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6">
       <c r="A153" s="1" t="s">
         <v>968</v>
       </c>
@@ -11591,7 +11639,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="A154" s="1" t="s">
         <v>971</v>
       </c>
@@ -11609,7 +11657,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="A155" s="1" t="s">
         <v>141</v>
       </c>
@@ -11627,7 +11675,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>151</v>
       </c>
@@ -11645,7 +11693,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="A157" s="1" t="s">
         <v>152</v>
       </c>
@@ -11663,7 +11711,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -11681,7 +11729,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6">
       <c r="A159" s="1" t="s">
         <v>77</v>
       </c>
@@ -11699,7 +11747,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="A160" s="1" t="s">
         <v>45</v>
       </c>
@@ -11717,7 +11765,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6">
       <c r="A161" s="1" t="s">
         <v>92</v>
       </c>
@@ -11735,7 +11783,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6">
       <c r="A162" s="1" t="s">
         <v>8</v>
       </c>
@@ -11753,7 +11801,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6">
       <c r="A163" s="1" t="s">
         <v>144</v>
       </c>
@@ -11771,7 +11819,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>277</v>
       </c>
@@ -11789,7 +11837,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6">
       <c r="A165" s="1" t="s">
         <v>278</v>
       </c>
@@ -11807,7 +11855,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6">
       <c r="A166" s="1" t="s">
         <v>283</v>
       </c>
@@ -11825,7 +11873,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6">
       <c r="A167" s="1" t="s">
         <v>285</v>
       </c>
@@ -11843,7 +11891,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6">
       <c r="A168" s="1" t="s">
         <v>150</v>
       </c>
@@ -11861,7 +11909,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6">
       <c r="A169" s="1" t="s">
         <v>153</v>
       </c>
@@ -11879,7 +11927,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6">
       <c r="A170" s="1" t="s">
         <v>159</v>
       </c>
@@ -11897,7 +11945,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6">
       <c r="A171" s="1" t="s">
         <v>177</v>
       </c>
@@ -11915,7 +11963,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6">
       <c r="A172" s="1" t="s">
         <v>1004</v>
       </c>
@@ -11932,7 +11980,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -11950,7 +11998,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6">
       <c r="A174" s="1" t="s">
         <v>294</v>
       </c>
@@ -11968,7 +12016,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6">
       <c r="A175" s="1" t="s">
         <v>276</v>
       </c>
@@ -11986,7 +12034,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6">
       <c r="A176" s="1" t="s">
         <v>279</v>
       </c>
@@ -12004,7 +12052,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6">
       <c r="A177" s="1" t="s">
         <v>280</v>
       </c>
@@ -12022,7 +12070,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6">
       <c r="A178" s="1" t="s">
         <v>281</v>
       </c>
@@ -12040,7 +12088,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6">
       <c r="A179" s="1" t="s">
         <v>1018</v>
       </c>
@@ -12058,7 +12106,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6">
       <c r="A180" s="1" t="s">
         <v>1021</v>
       </c>
@@ -12076,7 +12124,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6">
       <c r="A181" s="1" t="s">
         <v>1026</v>
       </c>
@@ -12094,7 +12142,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6">
       <c r="A182" s="1" t="s">
         <v>290</v>
       </c>
@@ -12112,7 +12160,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6">
       <c r="A183" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12130,7 +12178,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6">
       <c r="A184" s="1" t="s">
         <v>293</v>
       </c>
@@ -12148,7 +12196,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6">
       <c r="A185" s="1" t="s">
         <v>1034</v>
       </c>
@@ -12166,7 +12214,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6">
       <c r="A186" s="1" t="s">
         <v>318</v>
       </c>
@@ -12184,7 +12232,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6">
       <c r="A187" s="1" t="s">
         <v>320</v>
       </c>
@@ -12202,7 +12250,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6">
       <c r="A188" s="1" t="s">
         <v>312</v>
       </c>
@@ -12220,7 +12268,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6">
       <c r="A189" s="1" t="s">
         <v>304</v>
       </c>
@@ -12238,7 +12286,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6">
       <c r="A190" s="1" t="s">
         <v>1044</v>
       </c>
@@ -12256,7 +12304,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6">
       <c r="A191" s="1" t="s">
         <v>12</v>
       </c>
@@ -12274,7 +12322,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6">
       <c r="A192" s="1" t="s">
         <v>1047</v>
       </c>
@@ -12292,7 +12340,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6">
       <c r="A193" s="1" t="s">
         <v>1050</v>
       </c>
@@ -12310,7 +12358,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6">
       <c r="A194" s="1" t="s">
         <v>1052</v>
       </c>
@@ -12328,7 +12376,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>1055</v>
       </c>
@@ -12346,7 +12394,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>1058</v>
       </c>
@@ -12363,7 +12411,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6">
       <c r="A197" s="1" t="s">
         <v>292</v>
       </c>
@@ -12381,7 +12429,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6">
       <c r="A198" s="1" t="s">
         <v>607</v>
       </c>
@@ -12399,7 +12447,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>39</v>
       </c>
@@ -12417,7 +12465,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>363</v>
       </c>
@@ -12435,7 +12483,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>1069</v>
       </c>
@@ -12453,7 +12501,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>297</v>
       </c>
@@ -12471,7 +12519,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>1073</v>
       </c>
@@ -12489,7 +12537,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>1076</v>
       </c>
@@ -12507,7 +12555,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>1079</v>
       </c>
@@ -12525,7 +12573,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>295</v>
       </c>
@@ -12543,7 +12591,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>1082</v>
       </c>
@@ -12561,7 +12609,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>1085</v>
       </c>
@@ -12578,7 +12626,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>1087</v>
       </c>
@@ -12596,7 +12644,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>770</v>
       </c>
@@ -12614,7 +12662,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>1092</v>
       </c>
@@ -12632,7 +12680,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>1094</v>
       </c>
@@ -12650,7 +12698,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>1097</v>
       </c>
@@ -12668,7 +12716,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>858</v>
       </c>
@@ -12686,7 +12734,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>1100</v>
       </c>
@@ -12704,7 +12752,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>1102</v>
       </c>
@@ -12722,7 +12770,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>1104</v>
       </c>
@@ -12740,7 +12788,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>1107</v>
       </c>
@@ -12758,7 +12806,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>1110</v>
       </c>
@@ -12776,7 +12824,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>1112</v>
       </c>
@@ -12794,7 +12842,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>398</v>
       </c>
@@ -12812,7 +12860,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>1117</v>
       </c>
@@ -12830,7 +12878,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>1120</v>
       </c>
@@ -12848,7 +12896,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6">
       <c r="A224" s="1" t="s">
         <v>298</v>
       </c>
@@ -12866,7 +12914,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6">
       <c r="A225" s="1" t="s">
         <v>300</v>
       </c>
@@ -12884,7 +12932,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6">
       <c r="A226" s="1" t="s">
         <v>301</v>
       </c>
@@ -12902,7 +12950,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6">
       <c r="A227" s="1" t="s">
         <v>302</v>
       </c>
@@ -12920,7 +12968,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>1129</v>
       </c>
@@ -12938,7 +12986,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6">
       <c r="A229" s="1" t="s">
         <v>303</v>
       </c>
@@ -12956,7 +13004,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6">
       <c r="A230" s="1" t="s">
         <v>305</v>
       </c>
@@ -12974,7 +13022,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6">
       <c r="A231" s="1" t="s">
         <v>306</v>
       </c>
@@ -12992,7 +13040,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6">
       <c r="A232" s="1" t="s">
         <v>307</v>
       </c>
@@ -13010,7 +13058,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6">
       <c r="A233" s="1" t="s">
         <v>308</v>
       </c>
@@ -13028,7 +13076,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6">
       <c r="A234" s="1" t="s">
         <v>309</v>
       </c>
@@ -13046,7 +13094,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6">
       <c r="A235" s="1" t="s">
         <v>310</v>
       </c>
@@ -13064,7 +13112,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6">
       <c r="A236" s="1" t="s">
         <v>311</v>
       </c>
@@ -13082,7 +13130,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6">
       <c r="A237" s="1" t="s">
         <v>316</v>
       </c>
@@ -13100,7 +13148,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6">
       <c r="A238" s="1" t="s">
         <v>322</v>
       </c>
@@ -13118,7 +13166,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6">
       <c r="A239" s="1" t="s">
         <v>1156</v>
       </c>
@@ -13136,7 +13184,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6">
       <c r="A240" s="1" t="s">
         <v>1159</v>
       </c>
@@ -13154,7 +13202,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6">
       <c r="A241" s="1" t="s">
         <v>1162</v>
       </c>
@@ -13172,7 +13220,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6">
       <c r="A242" s="1" t="s">
         <v>1165</v>
       </c>
@@ -13190,7 +13238,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6">
       <c r="A243" s="1" t="s">
         <v>1168</v>
       </c>
@@ -13208,7 +13256,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6">
       <c r="A244" s="1" t="s">
         <v>1170</v>
       </c>
@@ -13226,7 +13274,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>1178</v>
       </c>
@@ -13244,7 +13292,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>1173</v>
       </c>
@@ -13262,7 +13310,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>1179</v>
       </c>
@@ -13280,7 +13328,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>1182</v>
       </c>
@@ -13298,7 +13346,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>1185</v>
       </c>
@@ -13316,7 +13364,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>1187</v>
       </c>
@@ -13334,7 +13382,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>1189</v>
       </c>
@@ -13352,7 +13400,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6">
       <c r="A252" s="9" t="s">
         <v>1192</v>
       </c>
@@ -13370,7 +13418,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>94</v>
       </c>
@@ -13388,7 +13436,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>191</v>
       </c>
@@ -13406,7 +13454,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>1197</v>
       </c>
@@ -13424,7 +13472,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>1200</v>
       </c>
@@ -13442,7 +13490,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>1203</v>
       </c>
@@ -13460,7 +13508,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>1203</v>
       </c>
@@ -13478,7 +13526,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>1206</v>
       </c>
@@ -13496,7 +13544,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>1209</v>
       </c>
@@ -13514,7 +13562,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>1212</v>
       </c>
@@ -13532,7 +13580,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>1214</v>
       </c>
@@ -13550,7 +13598,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>1217</v>
       </c>
@@ -13568,7 +13616,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>1220</v>
       </c>
@@ -13586,7 +13634,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>1223</v>
       </c>
@@ -13604,7 +13652,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>1226</v>
       </c>
@@ -13622,7 +13670,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>1230</v>
       </c>
@@ -13640,7 +13688,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>1232</v>
       </c>
@@ -13658,7 +13706,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>1235</v>
       </c>
@@ -13676,7 +13724,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>1239</v>
       </c>
@@ -13694,7 +13742,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>1240</v>
       </c>
@@ -13712,7 +13760,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>1243</v>
       </c>
@@ -13730,7 +13778,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>1245</v>
       </c>
@@ -13748,7 +13796,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>1247</v>
       </c>
@@ -13766,7 +13814,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>1250</v>
       </c>
@@ -13784,7 +13832,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>1250</v>
       </c>
@@ -13802,7 +13850,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>79</v>
       </c>
@@ -13820,7 +13868,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>1257</v>
       </c>
@@ -13838,7 +13886,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>1260</v>
       </c>
@@ -13856,7 +13904,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>1261</v>
       </c>
@@ -13874,7 +13922,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>1263</v>
       </c>
@@ -13892,7 +13940,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>1266</v>
       </c>
@@ -13910,7 +13958,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>1269</v>
       </c>
@@ -13928,7 +13976,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>93</v>
       </c>
@@ -13946,7 +13994,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>1274</v>
       </c>
@@ -13964,7 +14012,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>1277</v>
       </c>
@@ -13982,7 +14030,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>1280</v>
       </c>
@@ -14000,7 +14048,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>1283</v>
       </c>
@@ -14018,7 +14066,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>1286</v>
       </c>
@@ -14036,7 +14084,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>1289</v>
       </c>
@@ -14054,7 +14102,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>1292</v>
       </c>
@@ -14072,7 +14120,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>1295</v>
       </c>
@@ -14090,7 +14138,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>1298</v>
       </c>
@@ -14108,7 +14156,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>367</v>
       </c>
@@ -14126,7 +14174,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>1302</v>
       </c>
@@ -14144,7 +14192,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>1306</v>
       </c>
@@ -14162,7 +14210,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6">
       <c r="A297" t="s">
         <v>1309</v>
       </c>
@@ -14180,7 +14228,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6">
       <c r="A298" t="s">
         <v>1311</v>
       </c>
@@ -14198,7 +14246,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6">
       <c r="A299" t="s">
         <v>127</v>
       </c>
@@ -14216,7 +14264,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6">
       <c r="A300" t="s">
         <v>143</v>
       </c>
@@ -14234,7 +14282,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6">
       <c r="A301" t="s">
         <v>1318</v>
       </c>
@@ -14252,7 +14300,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6">
       <c r="A302" t="s">
         <v>373</v>
       </c>
@@ -14270,7 +14318,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6">
       <c r="A303" t="s">
         <v>1323</v>
       </c>
@@ -14288,7 +14336,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6">
       <c r="A304" t="s">
         <v>1326</v>
       </c>
@@ -14306,7 +14354,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6">
       <c r="A305" s="11" t="s">
         <v>1329</v>
       </c>
@@ -14323,7 +14371,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
         <v>172</v>
       </c>
@@ -14341,7 +14389,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
         <v>159</v>
       </c>
@@ -14359,7 +14407,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
         <v>1333</v>
       </c>
@@ -14377,7 +14425,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6">
       <c r="A309" t="s">
         <v>1335</v>
       </c>
@@ -14395,7 +14443,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
         <v>1337</v>
       </c>
@@ -14413,7 +14461,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
         <v>1341</v>
       </c>
@@ -14431,7 +14479,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6">
       <c r="A312" t="s">
         <v>1343</v>
       </c>
@@ -14449,7 +14497,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6">
       <c r="A313" t="s">
         <v>1346</v>
       </c>
@@ -14467,7 +14515,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6">
       <c r="A314" t="s">
         <v>1349</v>
       </c>
@@ -14485,7 +14533,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>1352</v>
       </c>
@@ -14503,7 +14551,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6">
       <c r="A316" t="s">
         <v>1355</v>
       </c>
@@ -14521,7 +14569,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6">
       <c r="A317" t="s">
         <v>752</v>
       </c>
@@ -14539,7 +14587,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6">
       <c r="A318" t="s">
         <v>1360</v>
       </c>
@@ -14557,7 +14605,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6">
       <c r="A319" s="1" t="s">
         <v>31</v>
       </c>
@@ -14575,7 +14623,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6">
       <c r="A320" t="s">
         <v>1364</v>
       </c>
@@ -14593,7 +14641,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6">
       <c r="A321" t="s">
         <v>1366</v>
       </c>
@@ -14611,7 +14659,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6">
       <c r="A322" t="s">
         <v>1370</v>
       </c>
@@ -14629,7 +14677,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6">
       <c r="A323" t="s">
         <v>1371</v>
       </c>
@@ -14647,7 +14695,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6">
       <c r="A324" t="s">
         <v>1378</v>
       </c>
@@ -14665,7 +14713,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6">
       <c r="A325" t="s">
         <v>1376</v>
       </c>
@@ -14683,7 +14731,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6">
       <c r="A326" t="s">
         <v>1379</v>
       </c>
@@ -14701,7 +14749,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6">
       <c r="A327" t="s">
         <v>1382</v>
       </c>
@@ -14719,7 +14767,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6">
       <c r="A328" t="s">
         <v>1386</v>
       </c>
@@ -14737,7 +14785,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6">
       <c r="A329" t="s">
         <v>1388</v>
       </c>
@@ -14755,7 +14803,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6">
       <c r="A330" t="s">
         <v>1391</v>
       </c>
@@ -14773,7 +14821,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6">
       <c r="A331" t="s">
         <v>369</v>
       </c>
@@ -14791,7 +14839,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6">
       <c r="A332" t="s">
         <v>385</v>
       </c>
@@ -14809,7 +14857,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6">
       <c r="A333" t="s">
         <v>588</v>
       </c>
@@ -14827,7 +14875,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6">
       <c r="A334" t="s">
         <v>1400</v>
       </c>
@@ -14845,7 +14893,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6">
       <c r="A335" t="s">
         <v>1403</v>
       </c>
@@ -14863,7 +14911,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6">
       <c r="A336" t="s">
         <v>84</v>
       </c>
@@ -14881,7 +14929,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6">
       <c r="A337" t="s">
         <v>254</v>
       </c>
@@ -14899,7 +14947,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6">
       <c r="A338" t="s">
         <v>1409</v>
       </c>
@@ -14917,7 +14965,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6">
       <c r="A339" t="s">
         <v>1412</v>
       </c>
@@ -14935,7 +14983,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6">
       <c r="A340" s="1" t="s">
         <v>324</v>
       </c>
@@ -14953,7 +15001,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6">
       <c r="A341" s="1" t="s">
         <v>325</v>
       </c>
@@ -14971,7 +15019,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6">
       <c r="A342" s="1" t="s">
         <v>326</v>
       </c>
@@ -14989,7 +15037,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6">
       <c r="A343" s="1" t="s">
         <v>327</v>
       </c>
@@ -15007,7 +15055,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6">
       <c r="A344" s="1" t="s">
         <v>328</v>
       </c>
@@ -15025,7 +15073,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6">
       <c r="A345" s="1" t="s">
         <v>330</v>
       </c>
@@ -15043,7 +15091,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6">
       <c r="A346" s="1" t="s">
         <v>333</v>
       </c>
@@ -15061,7 +15109,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6">
       <c r="A347" s="1" t="s">
         <v>335</v>
       </c>
@@ -15079,7 +15127,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6">
       <c r="A348" s="1" t="s">
         <v>1426</v>
       </c>
@@ -15097,7 +15145,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6">
       <c r="A349" s="1" t="s">
         <v>341</v>
       </c>
@@ -15115,7 +15163,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6">
       <c r="A350" s="1" t="s">
         <v>341</v>
       </c>
@@ -15133,7 +15181,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6">
       <c r="A351" s="1" t="s">
         <v>343</v>
       </c>
@@ -15151,7 +15199,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6">
       <c r="A352" s="1" t="s">
         <v>52</v>
       </c>
@@ -15169,7 +15217,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6">
       <c r="A353" s="1" t="s">
         <v>36</v>
       </c>
@@ -15187,7 +15235,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6">
       <c r="A354" s="1" t="s">
         <v>59</v>
       </c>
@@ -15205,7 +15253,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6">
       <c r="A355" s="1" t="s">
         <v>62</v>
       </c>
@@ -15223,7 +15271,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6">
       <c r="A356" s="1" t="s">
         <v>22</v>
       </c>
@@ -15241,7 +15289,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6">
       <c r="A357" s="1" t="s">
         <v>44</v>
       </c>
@@ -15259,7 +15307,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6">
       <c r="A358" s="1" t="s">
         <v>60</v>
       </c>
@@ -15277,7 +15325,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6">
       <c r="A359" s="1" t="s">
         <v>35</v>
       </c>
@@ -15295,7 +15343,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6">
       <c r="A360" s="1" t="s">
         <v>37</v>
       </c>
@@ -15313,7 +15361,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6">
       <c r="A361" t="s">
         <v>1452</v>
       </c>
@@ -15331,7 +15379,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6">
       <c r="A362" s="1" t="s">
         <v>2</v>
       </c>
@@ -15349,7 +15397,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6">
       <c r="A363" s="1" t="s">
         <v>47</v>
       </c>
@@ -15367,7 +15415,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6">
       <c r="A364" s="1" t="s">
         <v>81</v>
       </c>
@@ -15385,7 +15433,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6">
       <c r="A365" s="1" t="s">
         <v>26</v>
       </c>
@@ -15403,7 +15451,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6">
       <c r="A366" s="1" t="s">
         <v>1460</v>
       </c>
@@ -15421,7 +15469,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ht="17" customHeight="1">
       <c r="A367" s="1" t="s">
         <v>1460</v>
       </c>
@@ -15439,7 +15487,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6">
       <c r="A368" s="1" t="s">
         <v>1</v>
       </c>
@@ -15457,7 +15505,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6">
       <c r="A369" s="1" t="s">
         <v>68</v>
       </c>
@@ -15475,7 +15523,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6">
       <c r="A370" t="s">
         <v>18</v>
       </c>
@@ -15493,7 +15541,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6">
       <c r="A371" t="s">
         <v>18</v>
       </c>
@@ -15511,7 +15559,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6">
       <c r="A372" s="1" t="s">
         <v>34</v>
       </c>
@@ -15529,7 +15577,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6">
       <c r="A373" t="s">
         <v>3</v>
       </c>
@@ -15547,7 +15595,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -15565,7 +15613,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6">
       <c r="A375" s="1" t="s">
         <v>17</v>
       </c>
@@ -15583,7 +15631,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6">
       <c r="A376" s="1" t="s">
         <v>1476</v>
       </c>
@@ -15601,7 +15649,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6">
       <c r="A377" s="1" t="s">
         <v>1478</v>
       </c>
@@ -15619,7 +15667,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6">
       <c r="A378" s="1" t="s">
         <v>1483</v>
       </c>
@@ -15637,7 +15685,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6">
       <c r="A379" s="1" t="s">
         <v>1485</v>
       </c>
@@ -15655,7 +15703,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6">
       <c r="A380" s="1" t="s">
         <v>63</v>
       </c>
@@ -15673,7 +15721,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6">
       <c r="A381" s="1" t="s">
         <v>67</v>
       </c>
@@ -15691,7 +15739,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6">
       <c r="A382" s="1" t="s">
         <v>7</v>
       </c>
@@ -15709,7 +15757,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6">
       <c r="A383" s="1" t="s">
         <v>23</v>
       </c>
@@ -15727,7 +15775,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6">
       <c r="A384" s="1" t="s">
         <v>21</v>
       </c>
@@ -15745,7 +15793,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6">
       <c r="A385" s="1" t="s">
         <v>344</v>
       </c>
@@ -15763,7 +15811,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6">
       <c r="A386" s="1" t="s">
         <v>345</v>
       </c>
@@ -15781,7 +15829,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6">
       <c r="A387" s="1" t="s">
         <v>346</v>
       </c>
@@ -15799,7 +15847,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6">
       <c r="A388" s="1" t="s">
         <v>347</v>
       </c>
@@ -15817,7 +15865,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6">
       <c r="A389" s="1" t="s">
         <v>348</v>
       </c>
@@ -15835,7 +15883,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6">
       <c r="A390" s="1" t="s">
         <v>349</v>
       </c>
@@ -15853,7 +15901,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6">
       <c r="A391" s="1" t="s">
         <v>350</v>
       </c>
@@ -15871,7 +15919,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6">
       <c r="A392" s="1" t="s">
         <v>351</v>
       </c>
@@ -15889,7 +15937,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6">
       <c r="A393" s="1" t="s">
         <v>352</v>
       </c>
@@ -15907,7 +15955,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6">
       <c r="A394" s="1" t="s">
         <v>353</v>
       </c>
@@ -15925,7 +15973,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6">
       <c r="A395" s="1" t="s">
         <v>1512</v>
       </c>
@@ -15943,7 +15991,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6">
       <c r="A396" s="1" t="s">
         <v>355</v>
       </c>
@@ -15961,7 +16009,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6">
       <c r="A397" s="1" t="s">
         <v>356</v>
       </c>
@@ -15979,7 +16027,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6">
       <c r="A398" s="1" t="s">
         <v>357</v>
       </c>
@@ -15997,7 +16045,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6">
       <c r="A399" s="1" t="s">
         <v>1515</v>
       </c>
@@ -16015,7 +16063,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6">
       <c r="A400" s="1" t="s">
         <v>189</v>
       </c>
@@ -16033,7 +16081,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6">
       <c r="A401" s="1" t="s">
         <v>199</v>
       </c>
@@ -16051,7 +16099,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6">
       <c r="A402" s="1" t="s">
         <v>359</v>
       </c>
@@ -16069,7 +16117,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6">
       <c r="A403" s="1" t="s">
         <v>361</v>
       </c>
@@ -16087,7 +16135,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
         <v>362</v>
       </c>
@@ -16105,7 +16153,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6">
       <c r="A405" s="1" t="s">
         <v>365</v>
       </c>
@@ -16123,7 +16171,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6">
       <c r="A406" s="1" t="s">
         <v>366</v>
       </c>
@@ -16141,7 +16189,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6">
       <c r="A407" t="s">
         <v>1534</v>
       </c>
@@ -16159,7 +16207,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6">
       <c r="A408" t="s">
         <v>1537</v>
       </c>
@@ -16177,7 +16225,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6">
       <c r="A409" s="1" t="s">
         <v>370</v>
       </c>
@@ -16195,7 +16243,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6">
       <c r="A410" s="1" t="s">
         <v>371</v>
       </c>
@@ -16213,7 +16261,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6">
       <c r="A411" s="1" t="s">
         <v>374</v>
       </c>
@@ -16231,7 +16279,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6">
       <c r="A412" s="1" t="s">
         <v>376</v>
       </c>
@@ -16249,7 +16297,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6">
       <c r="A413" s="1" t="s">
         <v>378</v>
       </c>
@@ -16267,7 +16315,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6">
       <c r="A414" s="1" t="s">
         <v>379</v>
       </c>
@@ -16285,7 +16333,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6">
       <c r="A415" s="1" t="s">
         <v>380</v>
       </c>
@@ -16303,7 +16351,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6">
       <c r="A416" s="1" t="s">
         <v>382</v>
       </c>
@@ -16321,7 +16369,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6">
       <c r="A417" s="1" t="s">
         <v>377</v>
       </c>
@@ -16339,7 +16387,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6">
       <c r="A418" s="1" t="s">
         <v>384</v>
       </c>
@@ -16357,7 +16405,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6">
       <c r="A419" s="1" t="s">
         <v>1559</v>
       </c>
@@ -16375,7 +16423,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6">
       <c r="A420" s="1" t="s">
         <v>388</v>
       </c>
@@ -16393,7 +16441,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6">
       <c r="A421" s="1" t="s">
         <v>389</v>
       </c>
@@ -16411,7 +16459,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6">
       <c r="A422" s="1" t="s">
         <v>390</v>
       </c>
@@ -16429,7 +16477,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6">
       <c r="A423" s="1" t="s">
         <v>391</v>
       </c>
@@ -16447,7 +16495,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6">
       <c r="A424" s="1" t="s">
         <v>397</v>
       </c>
@@ -16465,7 +16513,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6">
       <c r="A425" s="1" t="s">
         <v>400</v>
       </c>
@@ -16483,7 +16531,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6">
       <c r="A426" s="1" t="s">
         <v>402</v>
       </c>
@@ -16501,7 +16549,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6">
       <c r="A427" s="1" t="s">
         <v>403</v>
       </c>
@@ -16519,7 +16567,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6">
       <c r="A428" s="1" t="s">
         <v>406</v>
       </c>
@@ -16537,7 +16585,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6">
       <c r="A429" s="1" t="s">
         <v>407</v>
       </c>
@@ -16555,7 +16603,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6">
       <c r="A430" s="1" t="s">
         <v>408</v>
       </c>
@@ -16573,7 +16621,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6">
       <c r="A431" s="1" t="s">
         <v>411</v>
       </c>
@@ -16591,7 +16639,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6">
       <c r="A432" s="1" t="s">
         <v>412</v>
       </c>
@@ -16609,7 +16657,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6">
       <c r="A433" s="1" t="s">
         <v>413</v>
       </c>
@@ -16627,7 +16675,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6">
       <c r="A434" s="1" t="s">
         <v>414</v>
       </c>
@@ -16645,7 +16693,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6">
       <c r="A435" s="1" t="s">
         <v>1575</v>
       </c>
@@ -16663,7 +16711,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6">
       <c r="A436" s="1" t="s">
         <v>1599</v>
       </c>
@@ -16681,7 +16729,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6">
       <c r="A437" t="s">
         <v>218</v>
       </c>
@@ -16698,7 +16746,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6">
       <c r="A438" t="s">
         <v>428</v>
       </c>
@@ -16715,7 +16763,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6">
       <c r="A439" t="s">
         <v>128</v>
       </c>
@@ -16732,7 +16780,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6">
       <c r="A440" t="s">
         <v>241</v>
       </c>
@@ -16749,7 +16797,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6">
       <c r="A441" t="s">
         <v>195</v>
       </c>
@@ -16766,7 +16814,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6">
       <c r="A442" t="s">
         <v>131</v>
       </c>
@@ -16783,7 +16831,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6">
       <c r="A443" t="s">
         <v>219</v>
       </c>
@@ -16800,7 +16848,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6">
       <c r="A444" t="s">
         <v>1613</v>
       </c>
@@ -16817,7 +16865,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6">
       <c r="A445" t="s">
         <v>1616</v>
       </c>
@@ -16834,7 +16882,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6">
       <c r="A446" t="s">
         <v>1618</v>
       </c>
@@ -16854,7 +16902,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6">
       <c r="A447" t="s">
         <v>242</v>
       </c>
@@ -16871,7 +16919,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6">
       <c r="A448" t="s">
         <v>1624</v>
       </c>
@@ -16888,7 +16936,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6">
       <c r="A449" t="s">
         <v>1625</v>
       </c>
@@ -16905,7 +16953,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6">
       <c r="A450" t="s">
         <v>1627</v>
       </c>
@@ -16922,7 +16970,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6">
       <c r="A451" t="s">
         <v>1629</v>
       </c>
@@ -16939,7 +16987,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6">
       <c r="A452" t="s">
         <v>1632</v>
       </c>
@@ -16956,7 +17004,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6">
       <c r="A453" t="s">
         <v>1635</v>
       </c>
@@ -16973,7 +17021,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6">
       <c r="A454" t="s">
         <v>1631</v>
       </c>
@@ -16990,7 +17038,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6">
       <c r="A455" t="s">
         <v>1638</v>
       </c>
@@ -17007,7 +17055,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6">
       <c r="A456" t="s">
         <v>1641</v>
       </c>
@@ -17024,7 +17072,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6">
       <c r="A457" t="s">
         <v>1644</v>
       </c>
@@ -17041,7 +17089,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6">
       <c r="A458" t="s">
         <v>220</v>
       </c>
@@ -17058,7 +17106,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6">
       <c r="A459" t="s">
         <v>429</v>
       </c>
@@ -17075,7 +17123,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6">
       <c r="A460" t="s">
         <v>132</v>
       </c>
@@ -17092,7 +17140,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6">
       <c r="A461" t="s">
         <v>110</v>
       </c>
@@ -17109,7 +17157,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6">
       <c r="A462" t="s">
         <v>89</v>
       </c>
@@ -17126,7 +17174,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6">
       <c r="A463" t="s">
         <v>133</v>
       </c>
@@ -17143,7 +17191,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6">
       <c r="A464" t="s">
         <v>243</v>
       </c>
@@ -17160,7 +17208,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:6">
       <c r="A465" t="s">
         <v>1657</v>
       </c>
@@ -17177,7 +17225,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6">
       <c r="A466" t="s">
         <v>275</v>
       </c>
@@ -17194,7 +17242,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6">
       <c r="A467" t="s">
         <v>1660</v>
       </c>
@@ -17211,7 +17259,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6">
       <c r="A468" t="s">
         <v>106</v>
       </c>
@@ -17228,7 +17276,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6">
       <c r="A469" t="s">
         <v>244</v>
       </c>
@@ -17245,7 +17293,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6">
       <c r="A470" t="s">
         <v>74</v>
       </c>
@@ -17262,7 +17310,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6">
       <c r="A471" t="s">
         <v>245</v>
       </c>
@@ -17279,7 +17327,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6">
       <c r="A472" t="s">
         <v>246</v>
       </c>
@@ -17296,7 +17344,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6">
       <c r="A473" t="s">
         <v>115</v>
       </c>
@@ -17313,7 +17361,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6">
       <c r="A474" t="s">
         <v>115</v>
       </c>
@@ -17330,7 +17378,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6">
       <c r="A475" t="s">
         <v>221</v>
       </c>
@@ -17347,7 +17395,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6">
       <c r="A476" t="s">
         <v>430</v>
       </c>
@@ -17364,7 +17412,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6">
       <c r="A477" t="s">
         <v>247</v>
       </c>
@@ -17381,7 +17429,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6">
       <c r="A478" t="s">
         <v>1681</v>
       </c>
@@ -17398,7 +17446,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6">
       <c r="A479" t="s">
         <v>1684</v>
       </c>
@@ -17415,7 +17463,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6">
       <c r="A480" t="s">
         <v>1686</v>
       </c>
@@ -17432,7 +17480,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6">
       <c r="A481" t="s">
         <v>1686</v>
       </c>
@@ -17449,7 +17497,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6">
       <c r="A482" t="s">
         <v>46</v>
       </c>
@@ -17466,7 +17514,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6">
       <c r="A483" t="s">
         <v>1690</v>
       </c>
@@ -17483,7 +17531,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6">
       <c r="A484" t="s">
         <v>88</v>
       </c>
@@ -17500,7 +17548,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6">
       <c r="A485" t="s">
         <v>1695</v>
       </c>
@@ -17517,7 +17565,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6">
       <c r="A486" t="s">
         <v>282</v>
       </c>
@@ -17534,7 +17582,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6">
       <c r="A487" t="s">
         <v>48</v>
       </c>
@@ -17551,7 +17599,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6">
       <c r="A488" t="s">
         <v>138</v>
       </c>
@@ -17568,7 +17616,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6">
       <c r="A489" t="s">
         <v>108</v>
       </c>
@@ -17585,7 +17633,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6">
       <c r="A490" t="s">
         <v>284</v>
       </c>
@@ -17602,7 +17650,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6">
       <c r="A491" t="s">
         <v>248</v>
       </c>
@@ -17619,7 +17667,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6">
       <c r="A492" t="s">
         <v>222</v>
       </c>
@@ -17636,7 +17684,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6">
       <c r="A493" t="s">
         <v>53</v>
       </c>
@@ -17653,7 +17701,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6">
       <c r="A494" t="s">
         <v>1712</v>
       </c>
@@ -17670,7 +17718,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6">
       <c r="A495" t="s">
         <v>1715</v>
       </c>
@@ -17687,7 +17735,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6">
       <c r="A496" t="s">
         <v>1718</v>
       </c>
@@ -17704,7 +17752,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6">
       <c r="A497" t="s">
         <v>125</v>
       </c>
@@ -17721,7 +17769,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6">
       <c r="A498" t="s">
         <v>223</v>
       </c>
@@ -17738,7 +17786,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6">
       <c r="A499" t="s">
         <v>1756</v>
       </c>
@@ -17755,7 +17803,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6">
       <c r="A500" t="s">
         <v>1759</v>
       </c>
@@ -17772,7 +17820,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6">
       <c r="A501" t="s">
         <v>1763</v>
       </c>
@@ -17789,7 +17837,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6">
       <c r="A502" t="s">
         <v>1209</v>
       </c>
@@ -17806,7 +17854,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6">
       <c r="A503" t="s">
         <v>139</v>
       </c>
@@ -17823,7 +17871,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6">
       <c r="A504" t="s">
         <v>73</v>
       </c>
@@ -17840,7 +17888,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6">
       <c r="A505" t="s">
         <v>1768</v>
       </c>
@@ -17857,7 +17905,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6">
       <c r="A506" t="s">
         <v>427</v>
       </c>
@@ -17874,7 +17922,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6">
       <c r="A507" t="s">
         <v>203</v>
       </c>
@@ -17891,7 +17939,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6">
       <c r="A508" t="s">
         <v>431</v>
       </c>
@@ -17908,7 +17956,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6">
       <c r="A509" t="s">
         <v>1776</v>
       </c>
@@ -17925,7 +17973,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6">
       <c r="A510" t="s">
         <v>1779</v>
       </c>
@@ -17942,7 +17990,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6">
       <c r="A511" t="s">
         <v>1782</v>
       </c>
@@ -17959,7 +18007,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6">
       <c r="A512" t="s">
         <v>1785</v>
       </c>
@@ -17976,7 +18024,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6">
       <c r="A513" t="s">
         <v>1788</v>
       </c>
@@ -17993,7 +18041,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6">
       <c r="A514" t="s">
         <v>1791</v>
       </c>
@@ -18010,7 +18058,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6">
       <c r="A515" t="s">
         <v>1534</v>
       </c>
@@ -18027,7 +18075,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6">
       <c r="A516" t="s">
         <v>85</v>
       </c>
@@ -18044,7 +18092,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6">
       <c r="A517" t="s">
         <v>1795</v>
       </c>
@@ -18061,7 +18109,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6">
       <c r="A518" t="s">
         <v>206</v>
       </c>
@@ -18078,7 +18126,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6">
       <c r="A519" t="s">
         <v>1796</v>
       </c>
@@ -18095,7 +18143,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6">
       <c r="A520" t="s">
         <v>112</v>
       </c>
@@ -18112,7 +18160,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6">
       <c r="A521" t="s">
         <v>1806</v>
       </c>
@@ -18129,7 +18177,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6">
       <c r="A522" t="s">
         <v>1349</v>
       </c>
@@ -18146,7 +18194,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6">
       <c r="A523" t="s">
         <v>249</v>
       </c>
@@ -18163,7 +18211,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6">
       <c r="A524" t="s">
         <v>250</v>
       </c>
@@ -18180,7 +18228,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6">
       <c r="A525" t="s">
         <v>251</v>
       </c>
@@ -18197,7 +18245,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6">
       <c r="A526" t="s">
         <v>140</v>
       </c>
@@ -18214,7 +18262,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6">
       <c r="A527" t="s">
         <v>286</v>
       </c>
@@ -18231,7 +18279,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6">
       <c r="A528" t="s">
         <v>287</v>
       </c>
@@ -18248,7 +18296,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6">
       <c r="A529" t="s">
         <v>252</v>
       </c>
@@ -18265,7 +18313,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6">
       <c r="A530" t="s">
         <v>66</v>
       </c>
@@ -18282,7 +18330,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6">
       <c r="A531" t="s">
         <v>288</v>
       </c>
@@ -18299,7 +18347,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6">
       <c r="A532" t="s">
         <v>49</v>
       </c>
@@ -18316,7 +18364,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6">
       <c r="A533" t="s">
         <v>116</v>
       </c>
@@ -18333,7 +18381,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6">
       <c r="A534" t="s">
         <v>349</v>
       </c>
@@ -18350,7 +18398,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6">
       <c r="A535" t="s">
         <v>1836</v>
       </c>
@@ -18367,7 +18415,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6">
       <c r="A536" t="s">
         <v>253</v>
       </c>
@@ -18384,7 +18432,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6">
       <c r="A537" t="s">
         <v>208</v>
       </c>
@@ -18401,7 +18449,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:6">
       <c r="A538" t="s">
         <v>225</v>
       </c>
@@ -18418,7 +18466,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6">
       <c r="A539" t="s">
         <v>224</v>
       </c>
@@ -18435,7 +18483,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6">
       <c r="A540" t="s">
         <v>142</v>
       </c>
@@ -18452,7 +18500,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6">
       <c r="A541" t="s">
         <v>143</v>
       </c>
@@ -18469,7 +18517,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6">
       <c r="A542" t="s">
         <v>432</v>
       </c>
@@ -18486,7 +18534,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6">
       <c r="A543" t="s">
         <v>226</v>
       </c>
@@ -18503,7 +18551,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6">
       <c r="A544" t="s">
         <v>45</v>
       </c>
@@ -18520,7 +18568,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6">
       <c r="A545" t="s">
         <v>291</v>
       </c>
@@ -18537,7 +18585,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6">
       <c r="A546" t="s">
         <v>145</v>
       </c>
@@ -18554,7 +18602,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6">
       <c r="A547" t="s">
         <v>372</v>
       </c>
@@ -18571,7 +18619,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6">
       <c r="A548" t="s">
         <v>210</v>
       </c>
@@ -18588,7 +18636,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6">
       <c r="A549" t="s">
         <v>259</v>
       </c>
@@ -18605,7 +18653,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6">
       <c r="A550" t="s">
         <v>123</v>
       </c>
@@ -18622,7 +18670,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6">
       <c r="A551" t="s">
         <v>196</v>
       </c>
@@ -18639,7 +18687,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6">
       <c r="A552" t="s">
         <v>78</v>
       </c>
@@ -18656,7 +18704,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6">
       <c r="A553" t="s">
         <v>119</v>
       </c>
@@ -18673,7 +18721,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6">
       <c r="A554" t="s">
         <v>25</v>
       </c>
@@ -18690,7 +18738,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6">
       <c r="A555" t="s">
         <v>1866</v>
       </c>
@@ -18707,7 +18755,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:6">
       <c r="A556" t="s">
         <v>1878</v>
       </c>
@@ -18724,7 +18772,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6">
       <c r="A557" t="s">
         <v>1880</v>
       </c>
@@ -18741,7 +18789,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6">
       <c r="A558" t="s">
         <v>1885</v>
       </c>
@@ -18761,7 +18809,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6">
       <c r="A559" t="s">
         <v>1887</v>
       </c>
@@ -18778,7 +18826,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6">
       <c r="A560" t="s">
         <v>1889</v>
       </c>
@@ -18795,7 +18843,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6">
       <c r="A561" t="s">
         <v>330</v>
       </c>
@@ -18812,7 +18860,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6">
       <c r="A562" t="s">
         <v>1983</v>
       </c>
@@ -18829,7 +18877,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6">
       <c r="A563" t="s">
         <v>1984</v>
       </c>
@@ -18846,7 +18894,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6">
       <c r="A564" t="s">
         <v>1986</v>
       </c>
@@ -18863,7 +18911,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:6">
       <c r="A565" t="s">
         <v>1987</v>
       </c>
@@ -18880,7 +18928,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:6">
       <c r="A566" t="s">
         <v>202</v>
       </c>
@@ -18897,7 +18945,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6">
       <c r="A567" t="s">
         <v>255</v>
       </c>
@@ -18914,7 +18962,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6">
       <c r="A568" t="s">
         <v>487</v>
       </c>
@@ -18931,7 +18979,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6">
       <c r="A569" t="s">
         <v>296</v>
       </c>
@@ -18948,7 +18996,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6">
       <c r="A570" t="s">
         <v>147</v>
       </c>
@@ -18965,7 +19013,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6">
       <c r="A571" t="s">
         <v>83</v>
       </c>
@@ -18982,7 +19030,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6">
       <c r="A572" t="s">
         <v>104</v>
       </c>
@@ -18999,7 +19047,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6">
       <c r="A573" t="s">
         <v>103</v>
       </c>
@@ -19016,7 +19064,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6">
       <c r="A574" t="s">
         <v>258</v>
       </c>
@@ -19033,7 +19081,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6">
       <c r="A575" t="s">
         <v>148</v>
       </c>
@@ -19050,7 +19098,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:6">
       <c r="A576" t="s">
         <v>2032</v>
       </c>
@@ -19067,7 +19115,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:6">
       <c r="A577" t="s">
         <v>198</v>
       </c>
@@ -19084,7 +19132,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:6">
       <c r="A578" t="s">
         <v>72</v>
       </c>
@@ -19101,7 +19149,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:6">
       <c r="A579" t="s">
         <v>375</v>
       </c>
@@ -19118,7 +19166,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:6">
       <c r="A580" t="s">
         <v>213</v>
       </c>
@@ -19135,7 +19183,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:6">
       <c r="A581" t="s">
         <v>260</v>
       </c>
@@ -19152,7 +19200,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:6">
       <c r="A582" t="s">
         <v>107</v>
       </c>
@@ -19169,7 +19217,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:6">
       <c r="A583" t="s">
         <v>2047</v>
       </c>
@@ -19186,7 +19234,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:6">
       <c r="A584" t="s">
         <v>229</v>
       </c>
@@ -19203,7 +19251,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:6">
       <c r="A585" t="s">
         <v>154</v>
       </c>
@@ -19220,7 +19268,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:6">
       <c r="A586" t="s">
         <v>57</v>
       </c>
@@ -19237,7 +19285,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:6">
       <c r="A587" t="s">
         <v>313</v>
       </c>
@@ -19251,6 +19299,128 @@
         <v>2011</v>
       </c>
       <c r="F587" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6">
+      <c r="A588" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B588" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C588" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E588">
+        <v>1972</v>
+      </c>
+      <c r="F588" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6">
+      <c r="A589" t="s">
+        <v>97</v>
+      </c>
+      <c r="B589" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C589" t="s">
+        <v>97</v>
+      </c>
+      <c r="E589">
+        <v>1997</v>
+      </c>
+      <c r="F589" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6">
+      <c r="A590" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B590" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C590" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E590">
+        <v>1987</v>
+      </c>
+      <c r="F590" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6">
+      <c r="A591" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B591" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C591" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E591">
+        <v>1968</v>
+      </c>
+      <c r="F591" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6">
+      <c r="A592" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B592" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C592" t="s">
+        <v>802</v>
+      </c>
+      <c r="E592">
+        <v>1958</v>
+      </c>
+      <c r="F592" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
+      <c r="A593" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B593" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C593" t="s">
+        <v>802</v>
+      </c>
+      <c r="E593">
+        <v>1952</v>
+      </c>
+      <c r="F593" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
+      <c r="A594" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B594" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C594" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D594" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E594">
+        <v>2011</v>
+      </c>
+      <c r="F594" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -19276,9 +19446,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EC353B-9472-6C41-B69A-ADB0079B268A}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="6" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>461</v>
       </c>
@@ -19298,13 +19468,13 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="17">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="17">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="17">
       <c r="C4" s="2"/>
     </row>
   </sheetData>
@@ -19315,7 +19485,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920847D-946C-2D4C-9334-79F517AB3056}">
   <dimension ref="A1:D73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
@@ -19323,7 +19493,7 @@
     <col min="4" max="4" width="136.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>461</v>
       </c>
@@ -19337,7 +19507,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="4" customFormat="1">
       <c r="A2" s="4" t="s">
         <v>568</v>
       </c>
@@ -19351,12 +19521,12 @@
         <v>607</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="C3" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>618</v>
       </c>
@@ -19370,22 +19540,22 @@
         <v>607</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="C5" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="C6" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="C7" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>619</v>
       </c>
@@ -19399,72 +19569,72 @@
         <v>607</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="C9" s="7" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="B17" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="B18" s="4" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" s="4" customFormat="1">
       <c r="B19" s="4" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" s="4" customFormat="1">
       <c r="B20" s="4" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" s="4" customFormat="1">
       <c r="B21" s="4" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" s="4" customFormat="1">
       <c r="B22" s="4" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" s="4" customFormat="1">
       <c r="B23" s="4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" s="4" customFormat="1">
       <c r="B24" s="4" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" s="4" customFormat="1">
       <c r="B25" s="4" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" s="4" customFormat="1">
       <c r="A26" s="4" t="s">
         <v>568</v>
       </c>
@@ -19472,7 +19642,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" s="4" customFormat="1">
       <c r="A27" s="4" t="s">
         <v>568</v>
       </c>
@@ -19480,7 +19650,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" s="4" customFormat="1">
       <c r="A28" s="4" t="s">
         <v>568</v>
       </c>
@@ -19488,197 +19658,197 @@
         <v>572</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="B30" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="B31" s="4" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="B32" s="4" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2">
       <c r="B33" s="4" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2">
       <c r="B34" s="4" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2">
       <c r="B35" s="4" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:2">
       <c r="B37" s="3" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2">
       <c r="B38" s="4" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2">
       <c r="B39" s="4" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2">
       <c r="B40" s="4" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2">
       <c r="B41" s="4" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2">
       <c r="B42" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:2">
       <c r="B43" s="4" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:2">
       <c r="B45" s="3" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:2">
       <c r="B46" s="4" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:2">
       <c r="B47" s="4" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:2">
       <c r="B48" s="4" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:2">
       <c r="B49" s="4" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:2">
       <c r="B50" s="4" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:2">
       <c r="B52" s="3" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:2">
       <c r="B53" s="4" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:2">
       <c r="B54" s="4" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:2">
       <c r="B55" s="4" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:2">
       <c r="B56" s="4" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:2">
       <c r="B57" s="4" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:2">
       <c r="B59" s="3" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:2">
       <c r="B60" s="4" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:2">
       <c r="B61" s="4" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:2">
       <c r="B62" s="4" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:2">
       <c r="B63" s="4" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:2">
       <c r="B64" s="4" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:2">
       <c r="B65" s="4" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:2">
       <c r="B66" s="4" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:2">
       <c r="B67" s="4" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:2">
       <c r="B68" s="4" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:2">
       <c r="B70" s="3" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:2">
       <c r="B71" s="4" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:2">
       <c r="B72" s="4" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:2">
       <c r="B73" s="4" t="s">
         <v>586</v>
       </c>
@@ -19696,7 +19866,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61D73BC-D245-FA4B-BDD8-C658F1B5BB4A}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="28.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="12"/>
@@ -19704,7 +19874,7 @@
     <col min="4" max="16384" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="13" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>1723</v>
       </c>
@@ -19712,7 +19882,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
         <v>1724</v>
       </c>
@@ -19720,7 +19890,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="12" t="s">
         <v>1725</v>
       </c>
@@ -19728,7 +19898,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
         <v>1726</v>
       </c>
@@ -19736,7 +19906,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="12" t="s">
         <v>1727</v>
       </c>
@@ -19744,7 +19914,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="12" t="s">
         <v>1728</v>
       </c>
@@ -19752,7 +19922,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="12" t="s">
         <v>1729</v>
       </c>
@@ -19760,7 +19930,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="12" t="s">
         <v>1730</v>
       </c>
@@ -19768,7 +19938,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="12" t="s">
         <v>1731</v>
       </c>
@@ -19776,7 +19946,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="12" t="s">
         <v>1732</v>
       </c>
@@ -19784,7 +19954,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="12" t="s">
         <v>1733</v>
       </c>
@@ -19792,7 +19962,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="12" t="s">
         <v>1734</v>
       </c>
@@ -19800,7 +19970,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="12" t="s">
         <v>1735</v>
       </c>
@@ -19808,7 +19978,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="12" t="s">
         <v>1736</v>
       </c>
@@ -19816,7 +19986,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="12" t="s">
         <v>1737</v>
       </c>
@@ -19824,7 +19994,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
         <v>1738</v>
       </c>
@@ -19840,14 +20010,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
   <dimension ref="A2:E102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="B2" s="3" t="s">
         <v>1867</v>
       </c>
@@ -19861,7 +20031,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1940</v>
       </c>
@@ -19878,7 +20048,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="B4" s="4" t="s">
         <v>1872</v>
       </c>
@@ -19892,7 +20062,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="B5" t="s">
         <v>1883</v>
       </c>
@@ -19906,7 +20076,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1941</v>
       </c>
@@ -19923,7 +20093,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="B8" t="s">
         <v>1871</v>
       </c>
@@ -19937,7 +20107,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="B9" s="4" t="s">
         <v>1872</v>
       </c>
@@ -19951,7 +20121,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1942</v>
       </c>
@@ -19968,7 +20138,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="B12" t="s">
         <v>1893</v>
       </c>
@@ -19982,7 +20152,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="B13" t="s">
         <v>1895</v>
       </c>
@@ -19996,7 +20166,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1943</v>
       </c>
@@ -20013,7 +20183,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="B16" t="s">
         <v>1899</v>
       </c>
@@ -20027,7 +20197,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="B17" t="s">
         <v>1901</v>
       </c>
@@ -20041,7 +20211,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1944</v>
       </c>
@@ -20058,7 +20228,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="B21" t="s">
         <v>1905</v>
       </c>
@@ -20072,7 +20242,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="B22" t="s">
         <v>1910</v>
       </c>
@@ -20083,7 +20253,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1945</v>
       </c>
@@ -20100,7 +20270,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="B26" s="4" t="s">
         <v>1872</v>
       </c>
@@ -20114,7 +20284,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="B27" t="s">
         <v>1917</v>
       </c>
@@ -20128,7 +20298,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>1946</v>
       </c>
@@ -20145,7 +20315,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="B31" t="s">
         <v>695</v>
       </c>
@@ -20159,7 +20329,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="B32" t="s">
         <v>1922</v>
       </c>
@@ -20173,7 +20343,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>1947</v>
       </c>
@@ -20190,7 +20360,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="B36" t="s">
         <v>1925</v>
       </c>
@@ -20204,7 +20374,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="B37" t="s">
         <v>1927</v>
       </c>
@@ -20218,7 +20388,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>1948</v>
       </c>
@@ -20235,7 +20405,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="B41" t="s">
         <v>1907</v>
       </c>
@@ -20249,7 +20419,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="B42" t="s">
         <v>1932</v>
       </c>
@@ -20263,7 +20433,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>1949</v>
       </c>
@@ -20280,7 +20450,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="B46" t="s">
         <v>1936</v>
       </c>
@@ -20294,7 +20464,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="B47" t="s">
         <v>1938</v>
       </c>
@@ -20308,7 +20478,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>1950</v>
       </c>
@@ -20325,7 +20495,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="B51" t="s">
         <v>1940</v>
       </c>
@@ -20339,7 +20509,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="B52" t="s">
         <v>1872</v>
       </c>
@@ -20353,7 +20523,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>1951</v>
       </c>
@@ -20370,7 +20540,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="B56" t="s">
         <v>1947</v>
       </c>
@@ -20384,7 +20554,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="B57" t="s">
         <v>1950</v>
       </c>
@@ -20398,7 +20568,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>1952</v>
       </c>
@@ -20415,7 +20585,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="B61" t="s">
         <v>1955</v>
       </c>
@@ -20429,7 +20599,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="B62" t="s">
         <v>1899</v>
       </c>
@@ -20443,7 +20613,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>1953</v>
       </c>
@@ -20460,7 +20630,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="B66" t="s">
         <v>1959</v>
       </c>
@@ -20474,7 +20644,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="B67" t="s">
         <v>1962</v>
       </c>
@@ -20488,7 +20658,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>1954</v>
       </c>
@@ -20505,7 +20675,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5">
       <c r="B71" t="s">
         <v>1966</v>
       </c>
@@ -20519,7 +20689,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5">
       <c r="B72" t="s">
         <v>1968</v>
       </c>
@@ -20533,7 +20703,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>1955</v>
       </c>
@@ -20550,7 +20720,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5">
       <c r="B76" t="s">
         <v>1972</v>
       </c>
@@ -20564,7 +20734,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5">
       <c r="B77" t="s">
         <v>1974</v>
       </c>
@@ -20575,7 +20745,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>1956</v>
       </c>
@@ -20592,7 +20762,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5">
       <c r="B81" t="s">
         <v>0</v>
       </c>
@@ -20606,7 +20776,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5">
       <c r="B82" t="s">
         <v>1979</v>
       </c>
@@ -20620,7 +20790,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>1957</v>
       </c>
@@ -20637,7 +20807,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5">
       <c r="B86" t="s">
         <v>1991</v>
       </c>
@@ -20651,7 +20821,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5">
       <c r="B87" t="s">
         <v>1993</v>
       </c>
@@ -20665,7 +20835,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>1958</v>
       </c>
@@ -20682,7 +20852,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5">
       <c r="B91" t="s">
         <v>1997</v>
       </c>
@@ -20696,7 +20866,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5">
       <c r="B92" t="s">
         <v>2000</v>
       </c>
@@ -20710,7 +20880,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>1959</v>
       </c>
@@ -20727,7 +20897,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5">
       <c r="B96" t="s">
         <v>2003</v>
       </c>
@@ -20741,7 +20911,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5">
       <c r="B97" t="s">
         <v>3</v>
       </c>
@@ -20755,7 +20925,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>1960</v>
       </c>
@@ -20772,7 +20942,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5">
       <c r="B101" t="s">
         <v>2012</v>
       </c>
@@ -20786,7 +20956,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5">
       <c r="B102" t="s">
         <v>2014</v>
       </c>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A35F8-645E-C54F-9F83-32B34710F6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C646F27-B53C-B24E-AE84-AB77516D00F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="2072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="2089">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6365,12 +6365,63 @@
   <si>
     <t>Need to get permission/mp3 from eTown</t>
   </si>
+  <si>
+    <t>Andy Kim</t>
+  </si>
+  <si>
+    <t>Rock Me Gently</t>
+  </si>
+  <si>
+    <t>Mandisa</t>
+  </si>
+  <si>
+    <t>Stronger</t>
+  </si>
+  <si>
+    <t>What If We Were Real</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>California (All the way)</t>
+  </si>
+  <si>
+    <t>Bewitched</t>
+  </si>
+  <si>
+    <t>A Little Bit of Soul</t>
+  </si>
+  <si>
+    <t>The Music Explosion</t>
+  </si>
+  <si>
+    <t>Little Bit O’ Soul</t>
+  </si>
+  <si>
+    <t>Son Volt</t>
+  </si>
+  <si>
+    <t>Drown</t>
+  </si>
+  <si>
+    <t>Trace</t>
+  </si>
+  <si>
+    <t>Sam Spence</t>
+  </si>
+  <si>
+    <t>A Golden Boy Again</t>
+  </si>
+  <si>
+    <t>Music From NFL Films, Vol. 1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6812,13 +6863,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:B265"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="95.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>381</v>
       </c>
@@ -6826,7 +6877,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>382</v>
       </c>
@@ -6834,7 +6885,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>383</v>
       </c>
@@ -6842,7 +6893,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>377</v>
       </c>
@@ -6850,7 +6901,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -6858,7 +6909,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>262</v>
       </c>
@@ -6866,7 +6917,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -6874,7 +6925,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -6882,7 +6933,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>314</v>
       </c>
@@ -6890,7 +6941,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>433</v>
       </c>
@@ -6898,7 +6949,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>263</v>
       </c>
@@ -6906,7 +6957,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -6914,7 +6965,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>384</v>
       </c>
@@ -6922,7 +6973,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>264</v>
       </c>
@@ -6930,7 +6981,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>212</v>
       </c>
@@ -6938,7 +6989,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>434</v>
       </c>
@@ -6946,7 +6997,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>265</v>
       </c>
@@ -6954,7 +7005,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -6962,7 +7013,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -6970,7 +7021,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>385</v>
       </c>
@@ -6978,7 +7029,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -6986,7 +7037,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>352</v>
       </c>
@@ -6994,7 +7045,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -7002,7 +7053,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>386</v>
       </c>
@@ -7010,7 +7061,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>90</v>
       </c>
@@ -7018,7 +7069,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>353</v>
       </c>
@@ -7026,7 +7077,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>387</v>
       </c>
@@ -7034,7 +7085,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>315</v>
       </c>
@@ -7042,7 +7093,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -7050,7 +7101,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -7058,7 +7109,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>157</v>
       </c>
@@ -7066,7 +7117,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>204</v>
       </c>
@@ -7074,7 +7125,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -7082,7 +7133,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -7090,7 +7141,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -7098,7 +7149,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>231</v>
       </c>
@@ -7106,7 +7157,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>388</v>
       </c>
@@ -7114,7 +7165,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>389</v>
       </c>
@@ -7122,7 +7173,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>316</v>
       </c>
@@ -7130,7 +7181,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>232</v>
       </c>
@@ -7138,7 +7189,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>448</v>
       </c>
@@ -7146,7 +7197,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>354</v>
       </c>
@@ -7154,7 +7205,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -7162,7 +7213,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -7170,7 +7221,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -7178,7 +7229,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>266</v>
       </c>
@@ -7186,7 +7237,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>159</v>
       </c>
@@ -7194,7 +7245,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>415</v>
       </c>
@@ -7202,7 +7253,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>71</v>
       </c>
@@ -7210,7 +7261,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>317</v>
       </c>
@@ -7218,7 +7269,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>435</v>
       </c>
@@ -7226,7 +7277,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>233</v>
       </c>
@@ -7234,7 +7285,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>390</v>
       </c>
@@ -7242,7 +7293,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>160</v>
       </c>
@@ -7250,7 +7301,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -7258,7 +7309,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -7266,7 +7317,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>391</v>
       </c>
@@ -7274,7 +7325,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -7282,7 +7333,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -7290,7 +7341,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -7298,7 +7349,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>163</v>
       </c>
@@ -7306,7 +7357,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -7314,7 +7365,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>416</v>
       </c>
@@ -7322,7 +7373,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>164</v>
       </c>
@@ -7330,7 +7381,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>392</v>
       </c>
@@ -7338,7 +7389,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>449</v>
       </c>
@@ -7346,7 +7397,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>318</v>
       </c>
@@ -7354,7 +7405,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>319</v>
       </c>
@@ -7362,7 +7413,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>320</v>
       </c>
@@ -7370,7 +7421,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>321</v>
       </c>
@@ -7378,7 +7429,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -7386,7 +7437,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -7394,7 +7445,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>322</v>
       </c>
@@ -7402,7 +7453,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>323</v>
       </c>
@@ -7410,7 +7461,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>267</v>
       </c>
@@ -7418,7 +7469,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>450</v>
       </c>
@@ -7426,7 +7477,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>187</v>
       </c>
@@ -7434,7 +7485,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -7442,7 +7493,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -7450,7 +7501,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>393</v>
       </c>
@@ -7458,7 +7509,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -7466,7 +7517,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>47</v>
       </c>
@@ -7474,7 +7525,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>54</v>
       </c>
@@ -7482,7 +7533,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -7490,7 +7541,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>324</v>
       </c>
@@ -7498,7 +7549,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>355</v>
       </c>
@@ -7506,7 +7557,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -7514,7 +7565,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>394</v>
       </c>
@@ -7522,7 +7573,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>68</v>
       </c>
@@ -7530,7 +7581,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>325</v>
       </c>
@@ -7538,7 +7589,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>166</v>
       </c>
@@ -7546,7 +7597,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>417</v>
       </c>
@@ -7554,7 +7605,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>326</v>
       </c>
@@ -7562,7 +7613,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>167</v>
       </c>
@@ -7570,7 +7621,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>436</v>
       </c>
@@ -7578,7 +7629,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -7586,7 +7637,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>327</v>
       </c>
@@ -7594,7 +7645,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -7602,7 +7653,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>328</v>
       </c>
@@ -7610,7 +7661,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -7618,7 +7669,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>418</v>
       </c>
@@ -7626,7 +7677,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>395</v>
       </c>
@@ -7634,7 +7685,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>168</v>
       </c>
@@ -7642,7 +7693,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>169</v>
       </c>
@@ -7650,7 +7701,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -7658,7 +7709,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>329</v>
       </c>
@@ -7666,7 +7717,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>194</v>
       </c>
@@ -7674,7 +7725,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>396</v>
       </c>
@@ -7682,7 +7733,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>451</v>
       </c>
@@ -7690,7 +7741,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -7698,7 +7749,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>437</v>
       </c>
@@ -7706,7 +7757,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>419</v>
       </c>
@@ -7714,7 +7765,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>397</v>
       </c>
@@ -7722,7 +7773,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>20</v>
       </c>
@@ -7730,7 +7781,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>269</v>
       </c>
@@ -7738,7 +7789,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -7746,7 +7797,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>438</v>
       </c>
@@ -7754,7 +7805,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>38</v>
       </c>
@@ -7762,7 +7813,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>398</v>
       </c>
@@ -7770,7 +7821,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>452</v>
       </c>
@@ -7778,7 +7829,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>171</v>
       </c>
@@ -7786,7 +7837,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>235</v>
       </c>
@@ -7794,7 +7845,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>507</v>
       </c>
@@ -7802,7 +7853,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>172</v>
       </c>
@@ -7810,7 +7861,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>439</v>
       </c>
@@ -7818,7 +7869,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -7826,7 +7877,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>330</v>
       </c>
@@ -7834,7 +7885,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -7842,7 +7893,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>440</v>
       </c>
@@ -7850,7 +7901,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>42</v>
       </c>
@@ -7858,7 +7909,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>271</v>
       </c>
@@ -7866,7 +7917,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>399</v>
       </c>
@@ -7874,7 +7925,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>400</v>
       </c>
@@ -7882,7 +7933,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>211</v>
       </c>
@@ -7890,7 +7941,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>401</v>
       </c>
@@ -7898,7 +7949,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>189</v>
       </c>
@@ -7906,7 +7957,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>331</v>
       </c>
@@ -7914,7 +7965,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>402</v>
       </c>
@@ -7922,7 +7973,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>173</v>
       </c>
@@ -7930,7 +7981,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>403</v>
       </c>
@@ -7938,7 +7989,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>420</v>
       </c>
@@ -7946,7 +7997,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>174</v>
       </c>
@@ -7954,7 +8005,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>124</v>
       </c>
@@ -7962,7 +8013,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>111</v>
       </c>
@@ -7970,7 +8021,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>404</v>
       </c>
@@ -7978,7 +8029,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>453</v>
       </c>
@@ -7986,7 +8037,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>356</v>
       </c>
@@ -7994,7 +8045,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>332</v>
       </c>
@@ -8002,7 +8053,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>454</v>
       </c>
@@ -8010,7 +8061,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>441</v>
       </c>
@@ -8018,7 +8069,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>217</v>
       </c>
@@ -8026,7 +8077,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>442</v>
       </c>
@@ -8034,7 +8085,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>272</v>
       </c>
@@ -8042,7 +8093,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>114</v>
       </c>
@@ -8050,7 +8101,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>26</v>
       </c>
@@ -8058,7 +8109,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>30</v>
       </c>
@@ -8066,7 +8117,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -8074,7 +8125,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -8082,7 +8133,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>273</v>
       </c>
@@ -8090,7 +8141,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -8098,7 +8149,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>8</v>
       </c>
@@ -8106,7 +8157,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -8114,7 +8165,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>25</v>
       </c>
@@ -8122,7 +8173,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>27</v>
       </c>
@@ -8130,7 +8181,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -8138,7 +8189,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>64</v>
       </c>
@@ -8146,7 +8197,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>175</v>
       </c>
@@ -8154,7 +8205,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>216</v>
       </c>
@@ -8162,7 +8213,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>61</v>
       </c>
@@ -8170,7 +8221,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -8178,7 +8229,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>63</v>
       </c>
@@ -8186,7 +8237,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>12</v>
       </c>
@@ -8194,7 +8245,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -8202,7 +8253,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -8210,7 +8261,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>201</v>
       </c>
@@ -8218,7 +8269,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>176</v>
       </c>
@@ -8226,7 +8277,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>236</v>
       </c>
@@ -8234,7 +8285,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -8242,7 +8293,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>33</v>
       </c>
@@ -8250,7 +8301,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>56</v>
       </c>
@@ -8258,7 +8309,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>209</v>
       </c>
@@ -8266,7 +8317,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>177</v>
       </c>
@@ -8274,7 +8325,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -8282,7 +8333,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>31</v>
       </c>
@@ -8290,7 +8341,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>67</v>
       </c>
@@ -8298,7 +8349,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>514</v>
       </c>
@@ -8306,7 +8357,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>405</v>
       </c>
@@ -8314,7 +8365,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>29</v>
       </c>
@@ -8322,7 +8373,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -8330,7 +8381,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>100</v>
       </c>
@@ -8338,7 +8389,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>3</v>
       </c>
@@ -8346,7 +8397,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>82</v>
       </c>
@@ -8354,7 +8405,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>406</v>
       </c>
@@ -8362,7 +8413,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>19</v>
       </c>
@@ -8370,7 +8421,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>237</v>
       </c>
@@ -8378,7 +8429,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>407</v>
       </c>
@@ -8386,7 +8437,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -8394,7 +8445,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -8402,7 +8453,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -8410,7 +8461,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>32</v>
       </c>
@@ -8418,7 +8469,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -8426,7 +8477,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>118</v>
       </c>
@@ -8434,7 +8485,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>408</v>
       </c>
@@ -8442,7 +8493,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>28</v>
       </c>
@@ -8450,7 +8501,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>443</v>
       </c>
@@ -8458,7 +8509,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>192</v>
       </c>
@@ -8466,7 +8517,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>409</v>
       </c>
@@ -8474,7 +8525,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>410</v>
       </c>
@@ -8482,7 +8533,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>334</v>
       </c>
@@ -8490,7 +8541,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>238</v>
       </c>
@@ -8498,7 +8549,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>455</v>
       </c>
@@ -8506,7 +8557,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>178</v>
       </c>
@@ -8514,7 +8565,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>87</v>
       </c>
@@ -8522,7 +8573,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>335</v>
       </c>
@@ -8530,7 +8581,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>444</v>
       </c>
@@ -8538,7 +8589,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>456</v>
       </c>
@@ -8546,7 +8597,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>179</v>
       </c>
@@ -8554,7 +8605,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>7</v>
       </c>
@@ -8562,7 +8613,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>24</v>
       </c>
@@ -8570,7 +8621,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>186</v>
       </c>
@@ -8578,7 +8629,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>180</v>
       </c>
@@ -8586,7 +8637,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>86</v>
       </c>
@@ -8594,7 +8645,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>336</v>
       </c>
@@ -8602,7 +8653,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>337</v>
       </c>
@@ -8610,7 +8661,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -8618,7 +8669,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>338</v>
       </c>
@@ -8626,7 +8677,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>120</v>
       </c>
@@ -8634,7 +8685,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>339</v>
       </c>
@@ -8642,7 +8693,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>422</v>
       </c>
@@ -8650,7 +8701,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>181</v>
       </c>
@@ -8658,7 +8709,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>411</v>
       </c>
@@ -8666,7 +8717,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>423</v>
       </c>
@@ -8674,7 +8725,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>457</v>
       </c>
@@ -8682,7 +8733,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>341</v>
       </c>
@@ -8690,7 +8741,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>340</v>
       </c>
@@ -8698,7 +8749,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>182</v>
       </c>
@@ -8706,7 +8757,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>421</v>
       </c>
@@ -8714,7 +8765,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>75</v>
       </c>
@@ -8722,7 +8773,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>445</v>
       </c>
@@ -8730,7 +8781,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>102</v>
       </c>
@@ -8738,7 +8789,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>200</v>
       </c>
@@ -8746,7 +8797,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>458</v>
       </c>
@@ -8754,7 +8805,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>424</v>
       </c>
@@ -8762,7 +8813,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>240</v>
       </c>
@@ -8770,7 +8821,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>342</v>
       </c>
@@ -8778,7 +8829,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>357</v>
       </c>
@@ -8786,7 +8837,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>446</v>
       </c>
@@ -8794,7 +8845,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>412</v>
       </c>
@@ -8802,7 +8853,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>70</v>
       </c>
@@ -8810,7 +8861,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>459</v>
       </c>
@@ -8818,7 +8869,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>358</v>
       </c>
@@ -8826,7 +8877,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>274</v>
       </c>
@@ -8834,7 +8885,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>425</v>
       </c>
@@ -8842,7 +8893,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>413</v>
       </c>
@@ -8850,7 +8901,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>214</v>
       </c>
@@ -8858,7 +8909,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>426</v>
       </c>
@@ -8866,7 +8917,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>414</v>
       </c>
@@ -8874,7 +8925,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>183</v>
       </c>
@@ -8882,7 +8933,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>343</v>
       </c>
@@ -8890,7 +8941,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>460</v>
       </c>
@@ -8898,7 +8949,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>184</v>
       </c>
@@ -8906,7 +8957,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>447</v>
       </c>
@@ -8914,7 +8965,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>23</v>
       </c>
@@ -8922,7 +8973,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>185</v>
       </c>
@@ -8930,7 +8981,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>215</v>
       </c>
@@ -8946,8 +8997,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F594"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:F600"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" bestFit="1" customWidth="1"/>
@@ -8956,7 +9007,7 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>461</v>
       </c>
@@ -8976,7 +9027,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>520</v>
       </c>
@@ -8990,7 +9041,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>523</v>
       </c>
@@ -9004,7 +9055,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>526</v>
       </c>
@@ -9018,7 +9069,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>528</v>
       </c>
@@ -9032,7 +9083,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>299</v>
       </c>
@@ -9046,7 +9097,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>590</v>
       </c>
@@ -9060,7 +9111,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>593</v>
       </c>
@@ -9077,7 +9128,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>596</v>
       </c>
@@ -9091,7 +9142,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -9107,7 +9158,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>620</v>
       </c>
@@ -9125,7 +9176,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>634</v>
       </c>
@@ -9143,7 +9194,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -9158,7 +9209,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>624</v>
       </c>
@@ -9176,7 +9227,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>627</v>
       </c>
@@ -9194,7 +9245,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>630</v>
       </c>
@@ -9214,7 +9265,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>637</v>
       </c>
@@ -9232,7 +9283,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>257</v>
       </c>
@@ -9249,7 +9300,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1">
+    <row r="19" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>405</v>
       </c>
@@ -9263,7 +9314,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="1" customFormat="1">
+    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>646</v>
       </c>
@@ -9283,7 +9334,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>649</v>
       </c>
@@ -9300,7 +9351,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>650</v>
       </c>
@@ -9317,7 +9368,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>655</v>
       </c>
@@ -9334,7 +9385,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="1" customFormat="1">
+    <row r="24" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
@@ -9351,7 +9402,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>658</v>
       </c>
@@ -9369,7 +9420,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="1" customFormat="1">
+    <row r="26" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>222</v>
       </c>
@@ -9386,7 +9437,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="1" customFormat="1">
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>663</v>
       </c>
@@ -9403,7 +9454,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="1" customFormat="1">
+    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>666</v>
       </c>
@@ -9420,7 +9471,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="1" customFormat="1">
+    <row r="29" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>669</v>
       </c>
@@ -9437,7 +9488,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="1" customFormat="1">
+    <row r="30" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>672</v>
       </c>
@@ -9454,7 +9505,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1">
+    <row r="31" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>675</v>
       </c>
@@ -9471,7 +9522,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="1" customFormat="1">
+    <row r="32" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>678</v>
       </c>
@@ -9488,7 +9539,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="1" customFormat="1">
+    <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>228</v>
       </c>
@@ -9505,7 +9556,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="8" customFormat="1">
+    <row r="34" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>685</v>
       </c>
@@ -9523,7 +9574,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="8" customFormat="1">
+    <row r="35" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>688</v>
       </c>
@@ -9541,7 +9592,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="8" customFormat="1">
+    <row r="36" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>689</v>
       </c>
@@ -9559,7 +9610,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="8" customFormat="1">
+    <row r="37" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>692</v>
       </c>
@@ -9577,7 +9628,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="1" customFormat="1">
+    <row r="38" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>698</v>
       </c>
@@ -9594,7 +9645,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="8" customFormat="1">
+    <row r="39" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -9612,7 +9663,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="1" customFormat="1">
+    <row r="40" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>701</v>
       </c>
@@ -9629,7 +9680,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="1" customFormat="1">
+    <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>703</v>
       </c>
@@ -9646,7 +9697,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="1" customFormat="1">
+    <row r="42" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>706</v>
       </c>
@@ -9663,7 +9714,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="1" customFormat="1">
+    <row r="43" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>708</v>
       </c>
@@ -9680,7 +9731,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="44" spans="1:6" s="1" customFormat="1">
+    <row r="44" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>710</v>
       </c>
@@ -9697,7 +9748,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="1" customFormat="1">
+    <row r="45" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>711</v>
       </c>
@@ -9714,7 +9765,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="46" spans="1:6" s="1" customFormat="1">
+    <row r="46" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>235</v>
       </c>
@@ -9731,7 +9782,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="1" customFormat="1">
+    <row r="47" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>289</v>
       </c>
@@ -9748,7 +9799,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="1" customFormat="1">
+    <row r="48" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>718</v>
       </c>
@@ -9765,7 +9816,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="1" customFormat="1">
+    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>719</v>
       </c>
@@ -9782,7 +9833,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="1" customFormat="1">
+    <row r="50" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>720</v>
       </c>
@@ -9799,7 +9850,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="1" customFormat="1">
+    <row r="51" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>721</v>
       </c>
@@ -9816,7 +9867,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="1" customFormat="1">
+    <row r="52" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>722</v>
       </c>
@@ -9833,7 +9884,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>733</v>
       </c>
@@ -9851,7 +9902,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>736</v>
       </c>
@@ -9869,7 +9920,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>737</v>
       </c>
@@ -9887,7 +9938,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>740</v>
       </c>
@@ -9905,7 +9956,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>777</v>
       </c>
@@ -9922,7 +9973,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>778</v>
       </c>
@@ -9939,7 +9990,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>778</v>
       </c>
@@ -9956,7 +10007,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>745</v>
       </c>
@@ -9974,7 +10025,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>748</v>
       </c>
@@ -9992,7 +10043,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>752</v>
       </c>
@@ -10010,7 +10061,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="63" spans="1:6" s="1" customFormat="1">
+    <row r="63" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>755</v>
       </c>
@@ -10027,7 +10078,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="64" spans="1:6" s="1" customFormat="1">
+    <row r="64" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>759</v>
       </c>
@@ -10044,7 +10095,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="1" customFormat="1">
+    <row r="65" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>519</v>
       </c>
@@ -10061,7 +10112,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="1" customFormat="1">
+    <row r="66" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>762</v>
       </c>
@@ -10078,7 +10129,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="1" customFormat="1">
+    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>764</v>
       </c>
@@ -10095,7 +10146,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="1" customFormat="1">
+    <row r="68" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>768</v>
       </c>
@@ -10112,7 +10163,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="1" customFormat="1">
+    <row r="69" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>770</v>
       </c>
@@ -10129,7 +10180,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="1" customFormat="1">
+    <row r="70" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>263</v>
       </c>
@@ -10146,7 +10197,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="1" customFormat="1">
+    <row r="71" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>779</v>
       </c>
@@ -10163,7 +10214,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>782</v>
       </c>
@@ -10181,7 +10232,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>785</v>
       </c>
@@ -10199,7 +10250,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>788</v>
       </c>
@@ -10217,7 +10268,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>256</v>
       </c>
@@ -10235,7 +10286,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>793</v>
       </c>
@@ -10253,7 +10304,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>795</v>
       </c>
@@ -10271,7 +10322,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>798</v>
       </c>
@@ -10289,7 +10340,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>800</v>
       </c>
@@ -10307,7 +10358,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>804</v>
       </c>
@@ -10325,7 +10376,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>192</v>
       </c>
@@ -10343,7 +10394,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>807</v>
       </c>
@@ -10361,7 +10412,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>30</v>
       </c>
@@ -10379,7 +10430,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>367</v>
       </c>
@@ -10397,7 +10448,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>813</v>
       </c>
@@ -10415,7 +10466,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>816</v>
       </c>
@@ -10433,7 +10484,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>819</v>
       </c>
@@ -10451,7 +10502,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>822</v>
       </c>
@@ -10469,7 +10520,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>824</v>
       </c>
@@ -10487,7 +10538,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>827</v>
       </c>
@@ -10505,7 +10556,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>830</v>
       </c>
@@ -10523,7 +10574,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>206</v>
       </c>
@@ -10541,7 +10592,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>835</v>
       </c>
@@ -10559,7 +10610,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>201</v>
       </c>
@@ -10577,7 +10628,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>840</v>
       </c>
@@ -10595,7 +10646,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>368</v>
       </c>
@@ -10613,7 +10664,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>845</v>
       </c>
@@ -10631,7 +10682,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>848</v>
       </c>
@@ -10649,7 +10700,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>164</v>
       </c>
@@ -10667,7 +10718,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>75</v>
       </c>
@@ -10685,7 +10736,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>855</v>
       </c>
@@ -10703,7 +10754,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>858</v>
       </c>
@@ -10721,7 +10772,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>861</v>
       </c>
@@ -10739,7 +10790,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>864</v>
       </c>
@@ -10757,7 +10808,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>867</v>
       </c>
@@ -10775,7 +10826,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>870</v>
       </c>
@@ -10793,7 +10844,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>873</v>
       </c>
@@ -10811,7 +10862,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>876</v>
       </c>
@@ -10829,7 +10880,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>16</v>
       </c>
@@ -10847,7 +10898,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>881</v>
       </c>
@@ -10865,7 +10916,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>884</v>
       </c>
@@ -10883,7 +10934,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>13</v>
       </c>
@@ -10901,7 +10952,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>888</v>
       </c>
@@ -10919,7 +10970,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>890</v>
       </c>
@@ -10937,7 +10988,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>33</v>
       </c>
@@ -10955,7 +11006,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>894</v>
       </c>
@@ -10973,7 +11024,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>897</v>
       </c>
@@ -10991,7 +11042,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>900</v>
       </c>
@@ -11009,7 +11060,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>903</v>
       </c>
@@ -11027,7 +11078,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>15</v>
       </c>
@@ -11045,7 +11096,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>190</v>
       </c>
@@ -11063,7 +11114,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>261</v>
       </c>
@@ -11081,7 +11132,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>911</v>
       </c>
@@ -11099,7 +11150,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>205</v>
       </c>
@@ -11117,7 +11168,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>76</v>
       </c>
@@ -11135,7 +11186,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>50</v>
       </c>
@@ -11153,7 +11204,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>919</v>
       </c>
@@ -11171,7 +11222,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>51</v>
       </c>
@@ -11189,7 +11240,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>0</v>
       </c>
@@ -11207,7 +11258,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>80</v>
       </c>
@@ -11225,7 +11276,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>230</v>
       </c>
@@ -11243,7 +11294,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>233</v>
       </c>
@@ -11261,7 +11312,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>220</v>
       </c>
@@ -11279,7 +11330,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>227</v>
       </c>
@@ -11297,7 +11348,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>364</v>
       </c>
@@ -11315,7 +11366,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>360</v>
       </c>
@@ -11333,7 +11384,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>134</v>
       </c>
@@ -11351,7 +11402,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>135</v>
       </c>
@@ -11369,7 +11420,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -11387,7 +11438,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>146</v>
       </c>
@@ -11405,7 +11456,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>149</v>
       </c>
@@ -11423,7 +11474,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>161</v>
       </c>
@@ -11441,7 +11492,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>184</v>
       </c>
@@ -11459,7 +11510,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>122</v>
       </c>
@@ -11477,7 +11528,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>129</v>
       </c>
@@ -11495,7 +11546,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>130</v>
       </c>
@@ -11513,7 +11564,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>136</v>
       </c>
@@ -11531,7 +11582,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>954</v>
       </c>
@@ -11549,7 +11600,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>957</v>
       </c>
@@ -11567,7 +11618,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>961</v>
       </c>
@@ -11585,7 +11636,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>962</v>
       </c>
@@ -11603,7 +11654,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>965</v>
       </c>
@@ -11621,7 +11672,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>968</v>
       </c>
@@ -11639,7 +11690,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>971</v>
       </c>
@@ -11657,7 +11708,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>141</v>
       </c>
@@ -11675,7 +11726,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>151</v>
       </c>
@@ -11693,7 +11744,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>152</v>
       </c>
@@ -11711,7 +11762,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -11729,7 +11780,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>77</v>
       </c>
@@ -11747,7 +11798,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>45</v>
       </c>
@@ -11765,7 +11816,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>92</v>
       </c>
@@ -11783,7 +11834,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>8</v>
       </c>
@@ -11801,7 +11852,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>144</v>
       </c>
@@ -11819,7 +11870,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>277</v>
       </c>
@@ -11837,7 +11888,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>278</v>
       </c>
@@ -11855,7 +11906,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>283</v>
       </c>
@@ -11873,7 +11924,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>285</v>
       </c>
@@ -11891,7 +11942,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>150</v>
       </c>
@@ -11909,7 +11960,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>153</v>
       </c>
@@ -11927,7 +11978,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>159</v>
       </c>
@@ -11945,7 +11996,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>177</v>
       </c>
@@ -11963,7 +12014,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>1004</v>
       </c>
@@ -11980,7 +12031,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -11998,7 +12049,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>294</v>
       </c>
@@ -12016,7 +12067,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>276</v>
       </c>
@@ -12034,7 +12085,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>279</v>
       </c>
@@ -12052,7 +12103,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>280</v>
       </c>
@@ -12070,7 +12121,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>281</v>
       </c>
@@ -12088,7 +12139,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>1018</v>
       </c>
@@ -12106,7 +12157,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>1021</v>
       </c>
@@ -12124,7 +12175,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>1026</v>
       </c>
@@ -12142,7 +12193,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>290</v>
       </c>
@@ -12160,7 +12211,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12178,7 +12229,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>293</v>
       </c>
@@ -12196,7 +12247,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>1034</v>
       </c>
@@ -12214,7 +12265,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>318</v>
       </c>
@@ -12232,7 +12283,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>320</v>
       </c>
@@ -12250,7 +12301,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>312</v>
       </c>
@@ -12268,7 +12319,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>304</v>
       </c>
@@ -12286,7 +12337,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>1044</v>
       </c>
@@ -12304,7 +12355,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>12</v>
       </c>
@@ -12322,7 +12373,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>1047</v>
       </c>
@@ -12340,7 +12391,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>1050</v>
       </c>
@@ -12358,7 +12409,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>1052</v>
       </c>
@@ -12376,7 +12427,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>1055</v>
       </c>
@@ -12394,7 +12445,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>1058</v>
       </c>
@@ -12411,7 +12462,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>292</v>
       </c>
@@ -12429,7 +12480,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>607</v>
       </c>
@@ -12447,7 +12498,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>39</v>
       </c>
@@ -12465,7 +12516,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>363</v>
       </c>
@@ -12483,7 +12534,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1069</v>
       </c>
@@ -12501,7 +12552,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>297</v>
       </c>
@@ -12519,7 +12570,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1073</v>
       </c>
@@ -12537,7 +12588,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>1076</v>
       </c>
@@ -12555,7 +12606,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>1079</v>
       </c>
@@ -12573,7 +12624,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>295</v>
       </c>
@@ -12591,7 +12642,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>1082</v>
       </c>
@@ -12609,7 +12660,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>1085</v>
       </c>
@@ -12626,7 +12677,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>1087</v>
       </c>
@@ -12644,7 +12695,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>770</v>
       </c>
@@ -12662,7 +12713,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>1092</v>
       </c>
@@ -12680,7 +12731,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>1094</v>
       </c>
@@ -12698,7 +12749,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>1097</v>
       </c>
@@ -12716,7 +12767,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>858</v>
       </c>
@@ -12734,7 +12785,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>1100</v>
       </c>
@@ -12752,7 +12803,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>1102</v>
       </c>
@@ -12770,7 +12821,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>1104</v>
       </c>
@@ -12788,7 +12839,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>1107</v>
       </c>
@@ -12806,7 +12857,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>1110</v>
       </c>
@@ -12824,7 +12875,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>1112</v>
       </c>
@@ -12842,7 +12893,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>398</v>
       </c>
@@ -12860,7 +12911,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>1117</v>
       </c>
@@ -12878,7 +12929,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>1120</v>
       </c>
@@ -12896,7 +12947,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>298</v>
       </c>
@@ -12914,7 +12965,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>300</v>
       </c>
@@ -12932,7 +12983,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>301</v>
       </c>
@@ -12950,7 +13001,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>302</v>
       </c>
@@ -12968,7 +13019,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1129</v>
       </c>
@@ -12986,7 +13037,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>303</v>
       </c>
@@ -13004,7 +13055,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>305</v>
       </c>
@@ -13022,7 +13073,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>306</v>
       </c>
@@ -13040,7 +13091,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>307</v>
       </c>
@@ -13058,7 +13109,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>308</v>
       </c>
@@ -13076,7 +13127,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>309</v>
       </c>
@@ -13094,7 +13145,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>310</v>
       </c>
@@ -13112,7 +13163,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>311</v>
       </c>
@@ -13130,7 +13181,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>316</v>
       </c>
@@ -13148,7 +13199,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>322</v>
       </c>
@@ -13166,7 +13217,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>1156</v>
       </c>
@@ -13184,7 +13235,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>1159</v>
       </c>
@@ -13202,7 +13253,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>1162</v>
       </c>
@@ -13220,7 +13271,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>1165</v>
       </c>
@@ -13238,7 +13289,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>1168</v>
       </c>
@@ -13256,7 +13307,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>1170</v>
       </c>
@@ -13274,7 +13325,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1178</v>
       </c>
@@ -13292,7 +13343,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1173</v>
       </c>
@@ -13310,7 +13361,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>1179</v>
       </c>
@@ -13328,7 +13379,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>1182</v>
       </c>
@@ -13346,7 +13397,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>1185</v>
       </c>
@@ -13364,7 +13415,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>1187</v>
       </c>
@@ -13382,7 +13433,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>1189</v>
       </c>
@@ -13400,7 +13451,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="9" t="s">
         <v>1192</v>
       </c>
@@ -13418,7 +13469,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>94</v>
       </c>
@@ -13436,7 +13487,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>191</v>
       </c>
@@ -13454,7 +13505,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>1197</v>
       </c>
@@ -13472,7 +13523,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>1200</v>
       </c>
@@ -13490,7 +13541,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>1203</v>
       </c>
@@ -13508,7 +13559,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>1203</v>
       </c>
@@ -13526,7 +13577,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>1206</v>
       </c>
@@ -13544,7 +13595,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>1209</v>
       </c>
@@ -13562,7 +13613,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>1212</v>
       </c>
@@ -13580,7 +13631,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>1214</v>
       </c>
@@ -13598,7 +13649,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>1217</v>
       </c>
@@ -13616,7 +13667,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>1220</v>
       </c>
@@ -13634,7 +13685,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>1223</v>
       </c>
@@ -13652,7 +13703,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>1226</v>
       </c>
@@ -13670,7 +13721,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1230</v>
       </c>
@@ -13688,7 +13739,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>1232</v>
       </c>
@@ -13706,7 +13757,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>1235</v>
       </c>
@@ -13724,7 +13775,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>1239</v>
       </c>
@@ -13742,7 +13793,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>1240</v>
       </c>
@@ -13760,7 +13811,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>1243</v>
       </c>
@@ -13778,7 +13829,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>1245</v>
       </c>
@@ -13796,7 +13847,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>1247</v>
       </c>
@@ -13814,7 +13865,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1250</v>
       </c>
@@ -13832,7 +13883,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>1250</v>
       </c>
@@ -13850,7 +13901,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>79</v>
       </c>
@@ -13868,7 +13919,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>1257</v>
       </c>
@@ -13886,7 +13937,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>1260</v>
       </c>
@@ -13904,7 +13955,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>1261</v>
       </c>
@@ -13922,7 +13973,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1263</v>
       </c>
@@ -13940,7 +13991,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>1266</v>
       </c>
@@ -13958,7 +14009,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>1269</v>
       </c>
@@ -13976,7 +14027,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>93</v>
       </c>
@@ -13994,7 +14045,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>1274</v>
       </c>
@@ -14012,7 +14063,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>1277</v>
       </c>
@@ -14030,7 +14081,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>1280</v>
       </c>
@@ -14048,7 +14099,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>1283</v>
       </c>
@@ -14066,7 +14117,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>1286</v>
       </c>
@@ -14084,7 +14135,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>1289</v>
       </c>
@@ -14102,7 +14153,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>1292</v>
       </c>
@@ -14120,7 +14171,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>1295</v>
       </c>
@@ -14138,7 +14189,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>1298</v>
       </c>
@@ -14156,7 +14207,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>367</v>
       </c>
@@ -14174,7 +14225,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>1302</v>
       </c>
@@ -14192,7 +14243,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>1306</v>
       </c>
@@ -14210,7 +14261,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>1309</v>
       </c>
@@ -14228,7 +14279,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>1311</v>
       </c>
@@ -14246,7 +14297,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>127</v>
       </c>
@@ -14264,7 +14315,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>143</v>
       </c>
@@ -14282,7 +14333,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>1318</v>
       </c>
@@ -14300,7 +14351,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>373</v>
       </c>
@@ -14318,7 +14369,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>1323</v>
       </c>
@@ -14336,7 +14387,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>1326</v>
       </c>
@@ -14354,7 +14405,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
         <v>1329</v>
       </c>
@@ -14371,7 +14422,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>172</v>
       </c>
@@ -14389,7 +14440,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>159</v>
       </c>
@@ -14407,7 +14458,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1333</v>
       </c>
@@ -14425,7 +14476,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>1335</v>
       </c>
@@ -14443,7 +14494,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1337</v>
       </c>
@@ -14461,7 +14512,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1341</v>
       </c>
@@ -14479,7 +14530,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>1343</v>
       </c>
@@ -14497,7 +14548,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>1346</v>
       </c>
@@ -14515,7 +14566,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>1349</v>
       </c>
@@ -14533,7 +14584,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1352</v>
       </c>
@@ -14551,7 +14602,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1355</v>
       </c>
@@ -14569,7 +14620,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>752</v>
       </c>
@@ -14587,7 +14638,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>1360</v>
       </c>
@@ -14605,7 +14656,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>31</v>
       </c>
@@ -14623,7 +14674,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>1364</v>
       </c>
@@ -14641,7 +14692,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>1366</v>
       </c>
@@ -14659,7 +14710,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>1370</v>
       </c>
@@ -14677,7 +14728,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>1371</v>
       </c>
@@ -14695,7 +14746,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>1378</v>
       </c>
@@ -14713,7 +14764,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1376</v>
       </c>
@@ -14731,7 +14782,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>1379</v>
       </c>
@@ -14749,7 +14800,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>1382</v>
       </c>
@@ -14767,7 +14818,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>1386</v>
       </c>
@@ -14785,7 +14836,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>1388</v>
       </c>
@@ -14803,7 +14854,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>1391</v>
       </c>
@@ -14821,7 +14872,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>369</v>
       </c>
@@ -14839,7 +14890,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>385</v>
       </c>
@@ -14857,7 +14908,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>588</v>
       </c>
@@ -14875,7 +14926,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1400</v>
       </c>
@@ -14893,7 +14944,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1403</v>
       </c>
@@ -14911,7 +14962,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>84</v>
       </c>
@@ -14929,7 +14980,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>254</v>
       </c>
@@ -14947,7 +14998,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1409</v>
       </c>
@@ -14965,7 +15016,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1412</v>
       </c>
@@ -14983,7 +15034,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
         <v>324</v>
       </c>
@@ -15001,7 +15052,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
         <v>325</v>
       </c>
@@ -15019,7 +15070,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>326</v>
       </c>
@@ -15037,7 +15088,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>327</v>
       </c>
@@ -15055,7 +15106,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
         <v>328</v>
       </c>
@@ -15073,7 +15124,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>330</v>
       </c>
@@ -15091,7 +15142,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>333</v>
       </c>
@@ -15109,7 +15160,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
         <v>335</v>
       </c>
@@ -15127,7 +15178,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
         <v>1426</v>
       </c>
@@ -15145,7 +15196,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>341</v>
       </c>
@@ -15163,7 +15214,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>341</v>
       </c>
@@ -15181,7 +15232,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>343</v>
       </c>
@@ -15199,7 +15250,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
         <v>52</v>
       </c>
@@ -15217,7 +15268,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
         <v>36</v>
       </c>
@@ -15235,7 +15286,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
         <v>59</v>
       </c>
@@ -15253,7 +15304,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
         <v>62</v>
       </c>
@@ -15271,7 +15322,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
         <v>22</v>
       </c>
@@ -15289,7 +15340,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>44</v>
       </c>
@@ -15307,7 +15358,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
         <v>60</v>
       </c>
@@ -15325,7 +15376,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>35</v>
       </c>
@@ -15343,7 +15394,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>37</v>
       </c>
@@ -15361,7 +15412,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1452</v>
       </c>
@@ -15379,7 +15430,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>2</v>
       </c>
@@ -15397,7 +15448,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>47</v>
       </c>
@@ -15415,7 +15466,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>81</v>
       </c>
@@ -15433,7 +15484,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>26</v>
       </c>
@@ -15451,7 +15502,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
         <v>1460</v>
       </c>
@@ -15469,7 +15520,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="17" customHeight="1">
+    <row r="367" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>1460</v>
       </c>
@@ -15487,7 +15538,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
         <v>1</v>
       </c>
@@ -15505,7 +15556,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
         <v>68</v>
       </c>
@@ -15523,7 +15574,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>18</v>
       </c>
@@ -15541,7 +15592,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>18</v>
       </c>
@@ -15559,7 +15610,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
         <v>34</v>
       </c>
@@ -15577,7 +15628,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>3</v>
       </c>
@@ -15595,7 +15646,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -15613,7 +15664,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>17</v>
       </c>
@@ -15631,7 +15682,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>1476</v>
       </c>
@@ -15649,7 +15700,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>1478</v>
       </c>
@@ -15667,7 +15718,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>1483</v>
       </c>
@@ -15685,7 +15736,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="379" spans="1:6">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
         <v>1485</v>
       </c>
@@ -15703,7 +15754,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
         <v>63</v>
       </c>
@@ -15721,7 +15772,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>67</v>
       </c>
@@ -15739,7 +15790,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
         <v>7</v>
       </c>
@@ -15757,7 +15808,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>23</v>
       </c>
@@ -15775,7 +15826,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>21</v>
       </c>
@@ -15793,7 +15844,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>344</v>
       </c>
@@ -15811,7 +15862,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>345</v>
       </c>
@@ -15829,7 +15880,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>346</v>
       </c>
@@ -15847,7 +15898,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>347</v>
       </c>
@@ -15865,7 +15916,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>348</v>
       </c>
@@ -15883,7 +15934,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>349</v>
       </c>
@@ -15901,7 +15952,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>350</v>
       </c>
@@ -15919,7 +15970,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>351</v>
       </c>
@@ -15937,7 +15988,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
         <v>352</v>
       </c>
@@ -15955,7 +16006,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>353</v>
       </c>
@@ -15973,7 +16024,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>1512</v>
       </c>
@@ -15991,7 +16042,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>355</v>
       </c>
@@ -16009,7 +16060,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>356</v>
       </c>
@@ -16027,7 +16078,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>357</v>
       </c>
@@ -16045,7 +16096,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>1515</v>
       </c>
@@ -16063,7 +16114,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>189</v>
       </c>
@@ -16081,7 +16132,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>199</v>
       </c>
@@ -16099,7 +16150,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>359</v>
       </c>
@@ -16117,7 +16168,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
         <v>361</v>
       </c>
@@ -16135,7 +16186,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>362</v>
       </c>
@@ -16153,7 +16204,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
         <v>365</v>
       </c>
@@ -16171,7 +16222,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>366</v>
       </c>
@@ -16189,7 +16240,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1534</v>
       </c>
@@ -16207,7 +16258,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="408" spans="1:6">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1537</v>
       </c>
@@ -16225,7 +16276,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="409" spans="1:6">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
         <v>370</v>
       </c>
@@ -16243,7 +16294,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="410" spans="1:6">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
         <v>371</v>
       </c>
@@ -16261,7 +16312,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="411" spans="1:6">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
         <v>374</v>
       </c>
@@ -16279,7 +16330,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="412" spans="1:6">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
         <v>376</v>
       </c>
@@ -16297,7 +16348,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="413" spans="1:6">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>378</v>
       </c>
@@ -16315,7 +16366,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="414" spans="1:6">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>379</v>
       </c>
@@ -16333,7 +16384,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="415" spans="1:6">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>380</v>
       </c>
@@ -16351,7 +16402,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="416" spans="1:6">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
         <v>382</v>
       </c>
@@ -16369,7 +16420,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="417" spans="1:6">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
         <v>377</v>
       </c>
@@ -16387,7 +16438,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="418" spans="1:6">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
         <v>384</v>
       </c>
@@ -16405,7 +16456,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="419" spans="1:6">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>1559</v>
       </c>
@@ -16423,7 +16474,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="420" spans="1:6">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>388</v>
       </c>
@@ -16441,7 +16492,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="421" spans="1:6">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
         <v>389</v>
       </c>
@@ -16459,7 +16510,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="422" spans="1:6">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
         <v>390</v>
       </c>
@@ -16477,7 +16528,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="423" spans="1:6">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
         <v>391</v>
       </c>
@@ -16495,7 +16546,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="424" spans="1:6">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
         <v>397</v>
       </c>
@@ -16513,7 +16564,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="425" spans="1:6">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
         <v>400</v>
       </c>
@@ -16531,7 +16582,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="426" spans="1:6">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
         <v>402</v>
       </c>
@@ -16549,7 +16600,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="427" spans="1:6">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>403</v>
       </c>
@@ -16567,7 +16618,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="428" spans="1:6">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
         <v>406</v>
       </c>
@@ -16585,7 +16636,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="429" spans="1:6">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>407</v>
       </c>
@@ -16603,7 +16654,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="430" spans="1:6">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
         <v>408</v>
       </c>
@@ -16621,7 +16672,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="431" spans="1:6">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
         <v>411</v>
       </c>
@@ -16639,7 +16690,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="432" spans="1:6">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
         <v>412</v>
       </c>
@@ -16657,7 +16708,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
         <v>413</v>
       </c>
@@ -16675,7 +16726,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="434" spans="1:6">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>414</v>
       </c>
@@ -16693,7 +16744,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="435" spans="1:6">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
         <v>1575</v>
       </c>
@@ -16711,7 +16762,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="436" spans="1:6">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>1599</v>
       </c>
@@ -16729,7 +16780,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="437" spans="1:6">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>218</v>
       </c>
@@ -16746,7 +16797,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="438" spans="1:6">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>428</v>
       </c>
@@ -16763,7 +16814,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="439" spans="1:6">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>128</v>
       </c>
@@ -16780,7 +16831,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="440" spans="1:6">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>241</v>
       </c>
@@ -16797,7 +16848,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="441" spans="1:6">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>195</v>
       </c>
@@ -16814,7 +16865,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="442" spans="1:6">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>131</v>
       </c>
@@ -16831,7 +16882,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="443" spans="1:6">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>219</v>
       </c>
@@ -16848,7 +16899,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="444" spans="1:6">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1613</v>
       </c>
@@ -16865,7 +16916,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="445" spans="1:6">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1616</v>
       </c>
@@ -16882,7 +16933,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="446" spans="1:6">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1618</v>
       </c>
@@ -16902,7 +16953,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="447" spans="1:6">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>242</v>
       </c>
@@ -16919,7 +16970,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="448" spans="1:6">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1624</v>
       </c>
@@ -16936,7 +16987,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="449" spans="1:6">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1625</v>
       </c>
@@ -16953,7 +17004,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="450" spans="1:6">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1627</v>
       </c>
@@ -16970,7 +17021,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="451" spans="1:6">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1629</v>
       </c>
@@ -16987,7 +17038,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="452" spans="1:6">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1632</v>
       </c>
@@ -17004,7 +17055,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="453" spans="1:6">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1635</v>
       </c>
@@ -17021,7 +17072,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="454" spans="1:6">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1631</v>
       </c>
@@ -17038,7 +17089,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="455" spans="1:6">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1638</v>
       </c>
@@ -17055,7 +17106,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="456" spans="1:6">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1641</v>
       </c>
@@ -17072,7 +17123,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="457" spans="1:6">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1644</v>
       </c>
@@ -17089,7 +17140,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="458" spans="1:6">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>220</v>
       </c>
@@ -17106,7 +17157,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="459" spans="1:6">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>429</v>
       </c>
@@ -17123,7 +17174,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="460" spans="1:6">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>132</v>
       </c>
@@ -17140,7 +17191,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="461" spans="1:6">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>110</v>
       </c>
@@ -17157,7 +17208,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="462" spans="1:6">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>89</v>
       </c>
@@ -17174,7 +17225,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="463" spans="1:6">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>133</v>
       </c>
@@ -17191,7 +17242,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="464" spans="1:6">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>243</v>
       </c>
@@ -17208,7 +17259,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="465" spans="1:6">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>1657</v>
       </c>
@@ -17225,7 +17276,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="466" spans="1:6">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>275</v>
       </c>
@@ -17242,7 +17293,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="467" spans="1:6">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1660</v>
       </c>
@@ -17259,7 +17310,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="468" spans="1:6">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>106</v>
       </c>
@@ -17276,7 +17327,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="469" spans="1:6">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>244</v>
       </c>
@@ -17293,7 +17344,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="470" spans="1:6">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>74</v>
       </c>
@@ -17310,7 +17361,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="471" spans="1:6">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>245</v>
       </c>
@@ -17327,7 +17378,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="472" spans="1:6">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>246</v>
       </c>
@@ -17344,7 +17395,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="473" spans="1:6">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>115</v>
       </c>
@@ -17361,7 +17412,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="474" spans="1:6">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>115</v>
       </c>
@@ -17378,7 +17429,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="475" spans="1:6">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>221</v>
       </c>
@@ -17395,7 +17446,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="476" spans="1:6">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>430</v>
       </c>
@@ -17412,7 +17463,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="477" spans="1:6">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>247</v>
       </c>
@@ -17429,7 +17480,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="478" spans="1:6">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1681</v>
       </c>
@@ -17446,7 +17497,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="479" spans="1:6">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1684</v>
       </c>
@@ -17463,7 +17514,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="480" spans="1:6">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1686</v>
       </c>
@@ -17480,7 +17531,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="481" spans="1:6">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1686</v>
       </c>
@@ -17497,7 +17548,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="482" spans="1:6">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>46</v>
       </c>
@@ -17514,7 +17565,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="483" spans="1:6">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1690</v>
       </c>
@@ -17531,7 +17582,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="484" spans="1:6">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>88</v>
       </c>
@@ -17548,7 +17599,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="485" spans="1:6">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1695</v>
       </c>
@@ -17565,7 +17616,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="486" spans="1:6">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>282</v>
       </c>
@@ -17582,7 +17633,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="487" spans="1:6">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>48</v>
       </c>
@@ -17599,7 +17650,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="488" spans="1:6">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>138</v>
       </c>
@@ -17616,7 +17667,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="489" spans="1:6">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>108</v>
       </c>
@@ -17633,7 +17684,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="490" spans="1:6">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>284</v>
       </c>
@@ -17650,7 +17701,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="491" spans="1:6">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>248</v>
       </c>
@@ -17667,7 +17718,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="492" spans="1:6">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>222</v>
       </c>
@@ -17684,7 +17735,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="493" spans="1:6">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>53</v>
       </c>
@@ -17701,7 +17752,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="494" spans="1:6">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1712</v>
       </c>
@@ -17718,7 +17769,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="495" spans="1:6">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1715</v>
       </c>
@@ -17735,7 +17786,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="496" spans="1:6">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1718</v>
       </c>
@@ -17752,7 +17803,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="497" spans="1:6">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>125</v>
       </c>
@@ -17769,7 +17820,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="498" spans="1:6">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>223</v>
       </c>
@@ -17786,7 +17837,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="499" spans="1:6">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1756</v>
       </c>
@@ -17803,7 +17854,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="500" spans="1:6">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1759</v>
       </c>
@@ -17820,7 +17871,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="501" spans="1:6">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1763</v>
       </c>
@@ -17837,7 +17888,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="502" spans="1:6">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1209</v>
       </c>
@@ -17854,7 +17905,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="503" spans="1:6">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>139</v>
       </c>
@@ -17871,7 +17922,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="504" spans="1:6">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>73</v>
       </c>
@@ -17888,7 +17939,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="505" spans="1:6">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>1768</v>
       </c>
@@ -17905,7 +17956,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="506" spans="1:6">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>427</v>
       </c>
@@ -17922,7 +17973,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="507" spans="1:6">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>203</v>
       </c>
@@ -17939,7 +17990,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="508" spans="1:6">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>431</v>
       </c>
@@ -17956,7 +18007,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="509" spans="1:6">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1776</v>
       </c>
@@ -17973,7 +18024,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="510" spans="1:6">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>1779</v>
       </c>
@@ -17990,7 +18041,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="511" spans="1:6">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>1782</v>
       </c>
@@ -18007,7 +18058,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="512" spans="1:6">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>1785</v>
       </c>
@@ -18024,7 +18075,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="513" spans="1:6">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>1788</v>
       </c>
@@ -18041,7 +18092,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="514" spans="1:6">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>1791</v>
       </c>
@@ -18058,7 +18109,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="515" spans="1:6">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>1534</v>
       </c>
@@ -18075,7 +18126,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="516" spans="1:6">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>85</v>
       </c>
@@ -18092,7 +18143,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="517" spans="1:6">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>1795</v>
       </c>
@@ -18109,7 +18160,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="518" spans="1:6">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>206</v>
       </c>
@@ -18126,7 +18177,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="519" spans="1:6">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>1796</v>
       </c>
@@ -18143,7 +18194,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="520" spans="1:6">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>112</v>
       </c>
@@ -18160,7 +18211,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="521" spans="1:6">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>1806</v>
       </c>
@@ -18177,7 +18228,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="522" spans="1:6">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>1349</v>
       </c>
@@ -18194,7 +18245,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="523" spans="1:6">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>249</v>
       </c>
@@ -18211,7 +18262,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="524" spans="1:6">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>250</v>
       </c>
@@ -18228,7 +18279,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="525" spans="1:6">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>251</v>
       </c>
@@ -18245,7 +18296,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="526" spans="1:6">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>140</v>
       </c>
@@ -18262,7 +18313,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="527" spans="1:6">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>286</v>
       </c>
@@ -18279,7 +18330,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="528" spans="1:6">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>287</v>
       </c>
@@ -18296,7 +18347,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="529" spans="1:6">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>252</v>
       </c>
@@ -18313,7 +18364,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="530" spans="1:6">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>66</v>
       </c>
@@ -18330,7 +18381,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="531" spans="1:6">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>288</v>
       </c>
@@ -18347,7 +18398,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="532" spans="1:6">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>49</v>
       </c>
@@ -18364,7 +18415,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="533" spans="1:6">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>116</v>
       </c>
@@ -18381,7 +18432,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="534" spans="1:6">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>349</v>
       </c>
@@ -18398,7 +18449,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="535" spans="1:6">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>1836</v>
       </c>
@@ -18415,7 +18466,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="536" spans="1:6">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>253</v>
       </c>
@@ -18432,7 +18483,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="537" spans="1:6">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>208</v>
       </c>
@@ -18449,7 +18500,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="538" spans="1:6">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>225</v>
       </c>
@@ -18466,7 +18517,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="539" spans="1:6">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>224</v>
       </c>
@@ -18483,7 +18534,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="540" spans="1:6">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>142</v>
       </c>
@@ -18500,7 +18551,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="541" spans="1:6">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>143</v>
       </c>
@@ -18517,7 +18568,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="542" spans="1:6">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>432</v>
       </c>
@@ -18534,7 +18585,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="543" spans="1:6">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>226</v>
       </c>
@@ -18551,7 +18602,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="544" spans="1:6">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>45</v>
       </c>
@@ -18568,7 +18619,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="545" spans="1:6">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>291</v>
       </c>
@@ -18585,7 +18636,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="546" spans="1:6">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>145</v>
       </c>
@@ -18602,7 +18653,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="547" spans="1:6">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>372</v>
       </c>
@@ -18619,7 +18670,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="548" spans="1:6">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>210</v>
       </c>
@@ -18636,7 +18687,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="549" spans="1:6">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>259</v>
       </c>
@@ -18653,7 +18704,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="550" spans="1:6">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>123</v>
       </c>
@@ -18670,7 +18721,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="551" spans="1:6">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>196</v>
       </c>
@@ -18687,7 +18738,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="552" spans="1:6">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>78</v>
       </c>
@@ -18704,7 +18755,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="553" spans="1:6">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>119</v>
       </c>
@@ -18721,7 +18772,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="554" spans="1:6">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>25</v>
       </c>
@@ -18738,7 +18789,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="555" spans="1:6">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>1866</v>
       </c>
@@ -18755,7 +18806,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="556" spans="1:6">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>1878</v>
       </c>
@@ -18772,7 +18823,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="557" spans="1:6">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>1880</v>
       </c>
@@ -18789,7 +18840,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="558" spans="1:6">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>1885</v>
       </c>
@@ -18809,7 +18860,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="559" spans="1:6">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>1887</v>
       </c>
@@ -18826,7 +18877,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="560" spans="1:6">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>1889</v>
       </c>
@@ -18843,7 +18894,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="561" spans="1:6">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>330</v>
       </c>
@@ -18860,7 +18911,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="562" spans="1:6">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>1983</v>
       </c>
@@ -18877,7 +18928,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="563" spans="1:6">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>1984</v>
       </c>
@@ -18894,7 +18945,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="564" spans="1:6">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>1986</v>
       </c>
@@ -18911,7 +18962,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="565" spans="1:6">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>1987</v>
       </c>
@@ -18928,7 +18979,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="566" spans="1:6">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>202</v>
       </c>
@@ -18945,7 +18996,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="567" spans="1:6">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>255</v>
       </c>
@@ -18962,7 +19013,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="568" spans="1:6">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>487</v>
       </c>
@@ -18979,7 +19030,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="569" spans="1:6">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>296</v>
       </c>
@@ -18996,7 +19047,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="570" spans="1:6">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>147</v>
       </c>
@@ -19013,7 +19064,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="571" spans="1:6">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>83</v>
       </c>
@@ -19030,7 +19081,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="572" spans="1:6">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>104</v>
       </c>
@@ -19047,7 +19098,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="573" spans="1:6">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>103</v>
       </c>
@@ -19064,7 +19115,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="574" spans="1:6">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>258</v>
       </c>
@@ -19081,7 +19132,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="575" spans="1:6">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>148</v>
       </c>
@@ -19098,7 +19149,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="576" spans="1:6">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>2032</v>
       </c>
@@ -19115,7 +19166,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="577" spans="1:6">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>198</v>
       </c>
@@ -19132,7 +19183,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="578" spans="1:6">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>72</v>
       </c>
@@ -19149,7 +19200,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="579" spans="1:6">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>375</v>
       </c>
@@ -19166,7 +19217,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="580" spans="1:6">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>213</v>
       </c>
@@ -19183,7 +19234,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="581" spans="1:6">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>260</v>
       </c>
@@ -19200,7 +19251,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="582" spans="1:6">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>107</v>
       </c>
@@ -19217,7 +19268,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="583" spans="1:6">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>2047</v>
       </c>
@@ -19234,7 +19285,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="584" spans="1:6">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>229</v>
       </c>
@@ -19251,7 +19302,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="585" spans="1:6">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>154</v>
       </c>
@@ -19268,7 +19319,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="586" spans="1:6">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>57</v>
       </c>
@@ -19285,7 +19336,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="587" spans="1:6">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>313</v>
       </c>
@@ -19302,7 +19353,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="588" spans="1:6">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>2056</v>
       </c>
@@ -19319,7 +19370,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="589" spans="1:6">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>97</v>
       </c>
@@ -19336,7 +19387,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="590" spans="1:6">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>2059</v>
       </c>
@@ -19353,7 +19404,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="591" spans="1:6">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>2063</v>
       </c>
@@ -19370,7 +19421,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="592" spans="1:6">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>2064</v>
       </c>
@@ -19387,7 +19438,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="593" spans="1:6">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>2066</v>
       </c>
@@ -19404,7 +19455,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="594" spans="1:6">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>2070</v>
       </c>
@@ -19421,6 +19472,108 @@
         <v>2011</v>
       </c>
       <c r="F594" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B595" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C595" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E595">
+        <v>1974</v>
+      </c>
+      <c r="F595" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A596" s="9" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B596" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C596" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E596">
+        <v>2011</v>
+      </c>
+      <c r="F596" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A597" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B597" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C597" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E597">
+        <v>1994</v>
+      </c>
+      <c r="F597" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A598" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B598" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C598" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E598">
+        <v>1967</v>
+      </c>
+      <c r="F598" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A599" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B599" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C599" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E599">
+        <v>1995</v>
+      </c>
+      <c r="F599" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B600" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C600" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E600">
+        <v>1970</v>
+      </c>
+      <c r="F600" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -19446,9 +19599,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EC353B-9472-6C41-B69A-ADB0079B268A}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>461</v>
       </c>
@@ -19468,13 +19621,13 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17">
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="17">
+    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="17">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="C4" s="2"/>
     </row>
   </sheetData>
@@ -19485,7 +19638,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920847D-946C-2D4C-9334-79F517AB3056}">
   <dimension ref="A1:D73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
@@ -19493,7 +19646,7 @@
     <col min="4" max="4" width="136.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>461</v>
       </c>
@@ -19507,7 +19660,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="4" customFormat="1">
+    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>568</v>
       </c>
@@ -19521,12 +19674,12 @@
         <v>607</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>618</v>
       </c>
@@ -19540,22 +19693,22 @@
         <v>607</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>619</v>
       </c>
@@ -19569,72 +19722,72 @@
         <v>607</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C9" s="7" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="4" customFormat="1">
+    <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="4" customFormat="1">
+    <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="4" customFormat="1">
+    <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="4" customFormat="1">
+    <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="4" customFormat="1">
+    <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="4" customFormat="1">
+    <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="4" customFormat="1">
+    <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="4" customFormat="1">
+    <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>568</v>
       </c>
@@ -19642,7 +19795,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="4" customFormat="1">
+    <row r="27" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>568</v>
       </c>
@@ -19650,7 +19803,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="4" customFormat="1">
+    <row r="28" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>568</v>
       </c>
@@ -19658,197 +19811,197 @@
         <v>572</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="4" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" s="4" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" s="4" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" s="4" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B43" s="4" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B46" s="4" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B47" s="4" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" s="4" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B52" s="3" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B53" s="4" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B54" s="4" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B55" s="4" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B56" s="4" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B59" s="3" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="60" spans="2:2">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B60" s="4" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="2:2">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="64" spans="2:2">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="65" spans="2:2">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B65" s="4" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="66" spans="2:2">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" s="4" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="67" spans="2:2">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" s="4" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="68" spans="2:2">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B68" s="4" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="70" spans="2:2">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B70" s="3" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="71" spans="2:2">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B71" s="4" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="72" spans="2:2">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B72" s="4" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="73" spans="2:2">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B73" s="4" t="s">
         <v>586</v>
       </c>
@@ -19866,7 +20019,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61D73BC-D245-FA4B-BDD8-C658F1B5BB4A}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="12"/>
@@ -19874,7 +20027,7 @@
     <col min="4" max="16384" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="13" customFormat="1">
+    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>1723</v>
       </c>
@@ -19882,7 +20035,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>1724</v>
       </c>
@@ -19890,7 +20043,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>1725</v>
       </c>
@@ -19898,7 +20051,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>1726</v>
       </c>
@@ -19906,7 +20059,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>1727</v>
       </c>
@@ -19914,7 +20067,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>1728</v>
       </c>
@@ -19922,7 +20075,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>1729</v>
       </c>
@@ -19930,7 +20083,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>1730</v>
       </c>
@@ -19938,7 +20091,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>1731</v>
       </c>
@@ -19946,7 +20099,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>1732</v>
       </c>
@@ -19954,7 +20107,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>1733</v>
       </c>
@@ -19962,7 +20115,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>1734</v>
       </c>
@@ -19970,7 +20123,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>1735</v>
       </c>
@@ -19978,7 +20131,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>1736</v>
       </c>
@@ -19986,7 +20139,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>1737</v>
       </c>
@@ -19994,7 +20147,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>1738</v>
       </c>
@@ -20010,14 +20163,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
   <dimension ref="A2:E102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>1867</v>
       </c>
@@ -20031,7 +20184,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1940</v>
       </c>
@@ -20048,7 +20201,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>1872</v>
       </c>
@@ -20062,7 +20215,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>1883</v>
       </c>
@@ -20076,7 +20229,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1941</v>
       </c>
@@ -20093,7 +20246,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>1871</v>
       </c>
@@ -20107,7 +20260,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>1872</v>
       </c>
@@ -20121,7 +20274,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1942</v>
       </c>
@@ -20138,7 +20291,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>1893</v>
       </c>
@@ -20152,7 +20305,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>1895</v>
       </c>
@@ -20166,7 +20319,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1943</v>
       </c>
@@ -20183,7 +20336,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>1899</v>
       </c>
@@ -20197,7 +20350,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>1901</v>
       </c>
@@ -20211,7 +20364,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1944</v>
       </c>
@@ -20228,7 +20381,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>1905</v>
       </c>
@@ -20242,7 +20395,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>1910</v>
       </c>
@@ -20253,7 +20406,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1945</v>
       </c>
@@ -20270,7 +20423,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
         <v>1872</v>
       </c>
@@ -20284,7 +20437,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>1917</v>
       </c>
@@ -20298,7 +20451,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1946</v>
       </c>
@@ -20315,7 +20468,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>695</v>
       </c>
@@ -20329,7 +20482,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>1922</v>
       </c>
@@ -20343,7 +20496,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1947</v>
       </c>
@@ -20360,7 +20513,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>1925</v>
       </c>
@@ -20374,7 +20527,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>1927</v>
       </c>
@@ -20388,7 +20541,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1948</v>
       </c>
@@ -20405,7 +20558,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>1907</v>
       </c>
@@ -20419,7 +20572,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>1932</v>
       </c>
@@ -20433,7 +20586,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1949</v>
       </c>
@@ -20450,7 +20603,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>1936</v>
       </c>
@@ -20464,7 +20617,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>1938</v>
       </c>
@@ -20478,7 +20631,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1950</v>
       </c>
@@ -20495,7 +20648,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>1940</v>
       </c>
@@ -20509,7 +20662,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>1872</v>
       </c>
@@ -20523,7 +20676,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1951</v>
       </c>
@@ -20540,7 +20693,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>1947</v>
       </c>
@@ -20554,7 +20707,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>1950</v>
       </c>
@@ -20568,7 +20721,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1952</v>
       </c>
@@ -20585,7 +20738,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>1955</v>
       </c>
@@ -20599,7 +20752,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>1899</v>
       </c>
@@ -20613,7 +20766,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1953</v>
       </c>
@@ -20630,7 +20783,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>1959</v>
       </c>
@@ -20644,7 +20797,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>1962</v>
       </c>
@@ -20658,7 +20811,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1954</v>
       </c>
@@ -20675,7 +20828,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>1966</v>
       </c>
@@ -20689,7 +20842,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
         <v>1968</v>
       </c>
@@ -20703,7 +20856,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1955</v>
       </c>
@@ -20720,7 +20873,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>1972</v>
       </c>
@@ -20734,7 +20887,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
         <v>1974</v>
       </c>
@@ -20745,7 +20898,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1956</v>
       </c>
@@ -20762,7 +20915,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
         <v>0</v>
       </c>
@@ -20776,7 +20929,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
         <v>1979</v>
       </c>
@@ -20790,7 +20943,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>1957</v>
       </c>
@@ -20807,7 +20960,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
         <v>1991</v>
       </c>
@@ -20821,7 +20974,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
         <v>1993</v>
       </c>
@@ -20835,7 +20988,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>1958</v>
       </c>
@@ -20852,7 +21005,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
         <v>1997</v>
       </c>
@@ -20866,7 +21019,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
         <v>2000</v>
       </c>
@@ -20880,7 +21033,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1959</v>
       </c>
@@ -20897,7 +21050,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
         <v>2003</v>
       </c>
@@ -20911,7 +21064,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
         <v>3</v>
       </c>
@@ -20925,7 +21078,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1960</v>
       </c>
@@ -20942,7 +21095,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
         <v>2012</v>
       </c>
@@ -20956,7 +21109,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
         <v>2014</v>
       </c>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C646F27-B53C-B24E-AE84-AB77516D00F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC843B88-D254-6C4A-AAA2-52B5590A0D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="16" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="2075">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -5736,22 +5736,7 @@
     <t>year</t>
   </si>
   <si>
-    <t>The Woodpecker Song</t>
-  </si>
-  <si>
-    <t>Glenn Miller</t>
-  </si>
-  <si>
     <t>The Andrews Sisters</t>
-  </si>
-  <si>
-    <t>Ferryboat Serenade</t>
-  </si>
-  <si>
-    <t>Sammy Kaye</t>
-  </si>
-  <si>
-    <t>Daddy</t>
   </si>
   <si>
     <t>Edelweiss (Reprise)</t>
@@ -5787,9 +5772,6 @@
     <t>Frenesi</t>
   </si>
   <si>
-    <t>Artie Shaw</t>
-  </si>
-  <si>
     <t>The Waltons Theme</t>
   </si>
   <si>
@@ -5814,39 +5796,15 @@
     <t>Stay Awhile/I Only Want to Be With You</t>
   </si>
   <si>
-    <t>Moonlight Cocktail</t>
-  </si>
-  <si>
     <t>Kay Kyser and His Orchestra</t>
   </si>
   <si>
     <t>Jingle Jangle Jingle</t>
   </si>
   <si>
-    <t>Benny Goodman</t>
-  </si>
-  <si>
-    <t>Jersey Bounce</t>
-  </si>
-  <si>
-    <t>Harry James with Helen Forrest</t>
-  </si>
-  <si>
-    <t>I’ve Heard That Song Before</t>
-  </si>
-  <si>
     <t>The Mills Brothers</t>
   </si>
   <si>
-    <t>Paper Doll</t>
-  </si>
-  <si>
-    <t>Duke Ellington</t>
-  </si>
-  <si>
-    <t>Don’t Get Around Much Anymore</t>
-  </si>
-  <si>
     <t>The Merry Macs</t>
   </si>
   <si>
@@ -5877,9 +5835,6 @@
     <t>Decca cast album Meet Me in St. Louis</t>
   </si>
   <si>
-    <t>Rum and Coca‑Cola</t>
-  </si>
-  <si>
     <t>On the Atchison, Topeka and the Santa Fe</t>
   </si>
   <si>
@@ -5968,9 +5923,6 @@
   </si>
   <si>
     <t>Unforgettable</t>
-  </si>
-  <si>
-    <t>I Can Dream, Can’t I?</t>
   </si>
   <si>
     <t>How High the Moon</t>
@@ -6415,6 +6367,12 @@
   </si>
   <si>
     <t>Music From NFL Films, Vol. 1</t>
+  </si>
+  <si>
+    <t>Glenn Miller and His Orchestra</t>
+  </si>
+  <si>
+    <t>Artie Shaw and His Orchestra</t>
   </si>
 </sst>
 </file>
@@ -8997,7 +8955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F600"/>
+  <dimension ref="A1:F607"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -11371,10 +11329,10 @@
         <v>360</v>
       </c>
       <c r="B136" t="s">
-        <v>2045</v>
+        <v>2029</v>
       </c>
       <c r="C136" t="s">
-        <v>2046</v>
+        <v>2030</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1">
@@ -18808,13 +18766,13 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
       <c r="B556" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="C556" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="E556">
         <v>1965</v>
@@ -18825,13 +18783,13 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="B557" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="C557" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
       <c r="E557">
         <v>1955</v>
@@ -18842,16 +18800,16 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="B558" t="s">
-        <v>1884</v>
+        <v>1878</v>
       </c>
       <c r="C558" t="s">
         <v>802</v>
       </c>
       <c r="D558" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="E558">
         <v>1972</v>
@@ -18862,13 +18820,13 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="B559" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="C559" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="E559">
         <v>1964</v>
@@ -18879,13 +18837,13 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="B560" t="s">
-        <v>1890</v>
+        <v>1884</v>
       </c>
       <c r="C560" t="s">
-        <v>1891</v>
+        <v>1885</v>
       </c>
       <c r="E560">
         <v>1964</v>
@@ -18913,13 +18871,13 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1983</v>
+        <v>1967</v>
       </c>
       <c r="B562" t="s">
-        <v>1981</v>
+        <v>1965</v>
       </c>
       <c r="C562" t="s">
-        <v>1982</v>
+        <v>1966</v>
       </c>
       <c r="E562">
         <v>2013</v>
@@ -18930,13 +18888,13 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1984</v>
+        <v>1968</v>
       </c>
       <c r="B563" t="s">
         <v>1819</v>
       </c>
       <c r="C563" t="s">
-        <v>1985</v>
+        <v>1969</v>
       </c>
       <c r="E563">
         <v>1973</v>
@@ -18947,7 +18905,7 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1986</v>
+        <v>1970</v>
       </c>
       <c r="B564" t="s">
         <v>1287</v>
@@ -18964,13 +18922,13 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1987</v>
+        <v>1971</v>
       </c>
       <c r="B565" t="s">
-        <v>1988</v>
+        <v>1972</v>
       </c>
       <c r="C565" t="s">
-        <v>1989</v>
+        <v>1973</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -18984,10 +18942,10 @@
         <v>202</v>
       </c>
       <c r="B566" t="s">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="C566" t="s">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="E566">
         <v>2004</v>
@@ -19001,10 +18959,10 @@
         <v>255</v>
       </c>
       <c r="B567" t="s">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="C567" t="s">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="E567">
         <v>1975</v>
@@ -19035,10 +18993,10 @@
         <v>296</v>
       </c>
       <c r="B569" t="s">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="C569" t="s">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="E569">
         <v>1992</v>
@@ -19052,10 +19010,10 @@
         <v>147</v>
       </c>
       <c r="B570" t="s">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="C570" t="s">
-        <v>2022</v>
+        <v>2006</v>
       </c>
       <c r="E570">
         <v>2008</v>
@@ -19069,10 +19027,10 @@
         <v>83</v>
       </c>
       <c r="B571" t="s">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="C571" t="s">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -19086,10 +19044,10 @@
         <v>104</v>
       </c>
       <c r="B572" t="s">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="C572" t="s">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="E572">
         <v>2010</v>
@@ -19103,10 +19061,10 @@
         <v>103</v>
       </c>
       <c r="B573" t="s">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="C573" t="s">
-        <v>2027</v>
+        <v>2011</v>
       </c>
       <c r="E573">
         <v>2004</v>
@@ -19120,10 +19078,10 @@
         <v>258</v>
       </c>
       <c r="B574" t="s">
-        <v>2028</v>
+        <v>2012</v>
       </c>
       <c r="C574" t="s">
-        <v>2029</v>
+        <v>2013</v>
       </c>
       <c r="E574">
         <v>1984</v>
@@ -19137,10 +19095,10 @@
         <v>148</v>
       </c>
       <c r="B575" t="s">
-        <v>2030</v>
+        <v>2014</v>
       </c>
       <c r="C575" t="s">
-        <v>2031</v>
+        <v>2015</v>
       </c>
       <c r="E575">
         <v>2008</v>
@@ -19151,13 +19109,13 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>2032</v>
+        <v>2016</v>
       </c>
       <c r="B576" t="s">
-        <v>2033</v>
+        <v>2017</v>
       </c>
       <c r="C576" t="s">
-        <v>2034</v>
+        <v>2018</v>
       </c>
       <c r="E576">
         <v>2005</v>
@@ -19171,10 +19129,10 @@
         <v>198</v>
       </c>
       <c r="B577" t="s">
-        <v>2035</v>
+        <v>2019</v>
       </c>
       <c r="C577" t="s">
-        <v>2036</v>
+        <v>2020</v>
       </c>
       <c r="E577">
         <v>2000</v>
@@ -19188,10 +19146,10 @@
         <v>72</v>
       </c>
       <c r="B578" t="s">
-        <v>2037</v>
+        <v>2021</v>
       </c>
       <c r="C578" t="s">
-        <v>2038</v>
+        <v>2022</v>
       </c>
       <c r="E578">
         <v>1983</v>
@@ -19205,10 +19163,10 @@
         <v>375</v>
       </c>
       <c r="B579" t="s">
-        <v>2039</v>
+        <v>2023</v>
       </c>
       <c r="C579" t="s">
-        <v>2040</v>
+        <v>2024</v>
       </c>
       <c r="E579">
         <v>1999</v>
@@ -19222,10 +19180,10 @@
         <v>213</v>
       </c>
       <c r="B580" t="s">
-        <v>2041</v>
+        <v>2025</v>
       </c>
       <c r="C580" t="s">
-        <v>2042</v>
+        <v>2026</v>
       </c>
       <c r="E580">
         <v>2013</v>
@@ -19256,10 +19214,10 @@
         <v>107</v>
       </c>
       <c r="B582" t="s">
-        <v>2043</v>
+        <v>2027</v>
       </c>
       <c r="C582" t="s">
-        <v>2044</v>
+        <v>2028</v>
       </c>
       <c r="E582">
         <v>2002</v>
@@ -19270,10 +19228,10 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>2047</v>
+        <v>2031</v>
       </c>
       <c r="B583" t="s">
-        <v>2048</v>
+        <v>2032</v>
       </c>
       <c r="C583" t="s">
         <v>930</v>
@@ -19290,10 +19248,10 @@
         <v>229</v>
       </c>
       <c r="B584" t="s">
-        <v>2049</v>
+        <v>2033</v>
       </c>
       <c r="C584" t="s">
-        <v>2050</v>
+        <v>2034</v>
       </c>
       <c r="E584">
         <v>1993</v>
@@ -19310,7 +19268,7 @@
         <v>930</v>
       </c>
       <c r="C585" t="s">
-        <v>2051</v>
+        <v>2035</v>
       </c>
       <c r="E585">
         <v>2005</v>
@@ -19324,10 +19282,10 @@
         <v>57</v>
       </c>
       <c r="B586" t="s">
-        <v>2052</v>
+        <v>2036</v>
       </c>
       <c r="C586" t="s">
-        <v>2053</v>
+        <v>2037</v>
       </c>
       <c r="E586">
         <v>1995</v>
@@ -19341,10 +19299,10 @@
         <v>313</v>
       </c>
       <c r="B587" t="s">
-        <v>2054</v>
+        <v>2038</v>
       </c>
       <c r="C587" t="s">
-        <v>2055</v>
+        <v>2039</v>
       </c>
       <c r="E587">
         <v>2011</v>
@@ -19355,13 +19313,13 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>2056</v>
+        <v>2040</v>
       </c>
       <c r="B588" t="s">
-        <v>2057</v>
+        <v>2041</v>
       </c>
       <c r="C588" t="s">
-        <v>2057</v>
+        <v>2041</v>
       </c>
       <c r="E588">
         <v>1972</v>
@@ -19375,7 +19333,7 @@
         <v>97</v>
       </c>
       <c r="B589" t="s">
-        <v>2058</v>
+        <v>2042</v>
       </c>
       <c r="C589" t="s">
         <v>97</v>
@@ -19389,13 +19347,13 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>2059</v>
+        <v>2043</v>
       </c>
       <c r="B590" t="s">
-        <v>2060</v>
+        <v>2044</v>
       </c>
       <c r="C590" t="s">
-        <v>2061</v>
+        <v>2045</v>
       </c>
       <c r="E590">
         <v>1987</v>
@@ -19406,13 +19364,13 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>2063</v>
+        <v>2047</v>
       </c>
       <c r="B591" t="s">
-        <v>2062</v>
+        <v>2046</v>
       </c>
       <c r="C591" t="s">
-        <v>2062</v>
+        <v>2046</v>
       </c>
       <c r="E591">
         <v>1968</v>
@@ -19423,10 +19381,10 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>2064</v>
+        <v>2048</v>
       </c>
       <c r="B592" t="s">
-        <v>2065</v>
+        <v>2049</v>
       </c>
       <c r="C592" t="s">
         <v>802</v>
@@ -19440,10 +19398,10 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>2066</v>
+        <v>2050</v>
       </c>
       <c r="B593" t="s">
-        <v>2067</v>
+        <v>2051</v>
       </c>
       <c r="C593" t="s">
         <v>802</v>
@@ -19457,16 +19415,16 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>2070</v>
+        <v>2054</v>
       </c>
       <c r="B594" t="s">
-        <v>2068</v>
+        <v>2052</v>
       </c>
       <c r="C594" t="s">
-        <v>2069</v>
+        <v>2053</v>
       </c>
       <c r="D594" t="s">
-        <v>2071</v>
+        <v>2055</v>
       </c>
       <c r="E594">
         <v>2011</v>
@@ -19477,13 +19435,13 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>2072</v>
+        <v>2056</v>
       </c>
       <c r="B595" t="s">
-        <v>2073</v>
+        <v>2057</v>
       </c>
       <c r="C595" t="s">
-        <v>2072</v>
+        <v>2056</v>
       </c>
       <c r="E595">
         <v>1974</v>
@@ -19494,13 +19452,13 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A596" s="9" t="s">
-        <v>2074</v>
+        <v>2058</v>
       </c>
       <c r="B596" t="s">
-        <v>2075</v>
+        <v>2059</v>
       </c>
       <c r="C596" t="s">
-        <v>2076</v>
+        <v>2060</v>
       </c>
       <c r="E596">
         <v>2011</v>
@@ -19511,13 +19469,13 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>2077</v>
+        <v>2061</v>
       </c>
       <c r="B597" t="s">
-        <v>2078</v>
+        <v>2062</v>
       </c>
       <c r="C597" t="s">
-        <v>2079</v>
+        <v>2063</v>
       </c>
       <c r="E597">
         <v>1994</v>
@@ -19528,13 +19486,13 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>2081</v>
+        <v>2065</v>
       </c>
       <c r="B598" t="s">
-        <v>2080</v>
+        <v>2064</v>
       </c>
       <c r="C598" t="s">
-        <v>2082</v>
+        <v>2066</v>
       </c>
       <c r="E598">
         <v>1967</v>
@@ -19545,13 +19503,13 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>2083</v>
+        <v>2067</v>
       </c>
       <c r="B599" t="s">
-        <v>2084</v>
+        <v>2068</v>
       </c>
       <c r="C599" t="s">
-        <v>2085</v>
+        <v>2069</v>
       </c>
       <c r="E599">
         <v>1995</v>
@@ -19562,18 +19520,137 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>2086</v>
+        <v>2070</v>
       </c>
       <c r="B600" t="s">
-        <v>2087</v>
+        <v>2071</v>
       </c>
       <c r="C600" t="s">
-        <v>2088</v>
+        <v>2072</v>
       </c>
       <c r="E600">
         <v>1970</v>
       </c>
       <c r="F600" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C601" t="s">
+        <v>802</v>
+      </c>
+      <c r="E601">
+        <v>1941</v>
+      </c>
+      <c r="F601" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A602" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C602" t="s">
+        <v>802</v>
+      </c>
+      <c r="E602">
+        <v>1941</v>
+      </c>
+      <c r="F602" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C603" t="s">
+        <v>802</v>
+      </c>
+      <c r="E603">
+        <v>1940</v>
+      </c>
+      <c r="F603" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A604" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C604" t="s">
+        <v>802</v>
+      </c>
+      <c r="E604">
+        <v>1942</v>
+      </c>
+      <c r="F604" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A605" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C605" t="s">
+        <v>802</v>
+      </c>
+      <c r="E605">
+        <v>1944</v>
+      </c>
+      <c r="F605" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C606" t="s">
+        <v>802</v>
+      </c>
+      <c r="E606">
+        <v>1944</v>
+      </c>
+      <c r="F606" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A607" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E607">
+        <v>1944</v>
+      </c>
+      <c r="F607" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -20162,7 +20239,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E102"/>
+  <dimension ref="A2:E81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
@@ -20184,942 +20261,692 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1940</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1870</v>
-      </c>
-      <c r="D3" t="s">
-        <v>802</v>
-      </c>
-      <c r="E3">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1873</v>
-      </c>
-      <c r="D4" t="s">
-        <v>802</v>
-      </c>
-      <c r="E4">
-        <v>1940</v>
-      </c>
-    </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1945</v>
+      </c>
       <c r="B5" t="s">
-        <v>1883</v>
+        <v>1900</v>
       </c>
       <c r="C5" t="s">
-        <v>1882</v>
+        <v>1899</v>
       </c>
       <c r="D5" t="s">
         <v>802</v>
       </c>
       <c r="E5">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1941</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1874</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1875</v>
-      </c>
-      <c r="D7" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D6" t="s">
         <v>802</v>
       </c>
-      <c r="E7">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D8" t="s">
-        <v>802</v>
-      </c>
-      <c r="E8">
-        <v>1941</v>
+      <c r="E6">
+        <v>1945</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
-        <v>1872</v>
+      <c r="A9">
+        <v>1946</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1904</v>
       </c>
       <c r="C9" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="D9" t="s">
         <v>802</v>
       </c>
       <c r="E9">
-        <v>1941</v>
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>695</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D10" t="s">
+        <v>802</v>
+      </c>
+      <c r="E10">
+        <v>1946</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1942</v>
-      </c>
       <c r="B11" t="s">
-        <v>1871</v>
+        <v>1907</v>
       </c>
       <c r="C11" t="s">
-        <v>1892</v>
+        <v>1906</v>
       </c>
       <c r="D11" t="s">
         <v>802</v>
       </c>
       <c r="E11">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1947</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D14" t="s">
         <v>802</v>
       </c>
-      <c r="E12">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>1895</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1896</v>
-      </c>
-      <c r="D13" t="s">
-        <v>802</v>
-      </c>
-      <c r="E13">
-        <v>1942</v>
+      <c r="E14">
+        <v>1947</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1943</v>
-      </c>
       <c r="B15" t="s">
-        <v>1897</v>
+        <v>1910</v>
       </c>
       <c r="C15" t="s">
-        <v>1898</v>
+        <v>1911</v>
       </c>
       <c r="D15" t="s">
         <v>802</v>
       </c>
       <c r="E15">
-        <v>1943</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>1899</v>
+        <v>1912</v>
       </c>
       <c r="C16" t="s">
-        <v>1900</v>
+        <v>1913</v>
       </c>
       <c r="D16" t="s">
         <v>802</v>
       </c>
       <c r="E16">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>1901</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D17" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1948</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D19" t="s">
         <v>802</v>
       </c>
-      <c r="E17">
-        <v>1943</v>
+      <c r="E19">
+        <v>1948</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>1944</v>
-      </c>
       <c r="B20" t="s">
-        <v>1903</v>
+        <v>1893</v>
       </c>
       <c r="C20" t="s">
-        <v>1904</v>
+        <v>1916</v>
       </c>
       <c r="D20" t="s">
         <v>802</v>
       </c>
       <c r="E20">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>1905</v>
+        <v>1917</v>
       </c>
       <c r="C21" t="s">
-        <v>1906</v>
+        <v>1918</v>
       </c>
       <c r="D21" t="s">
         <v>802</v>
       </c>
       <c r="E21">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>1910</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1911</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1912</v>
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1949</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D24" t="s">
+        <v>802</v>
+      </c>
+      <c r="E24">
+        <v>1949</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>1945</v>
-      </c>
       <c r="B25" t="s">
-        <v>1915</v>
+        <v>1921</v>
       </c>
       <c r="C25" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="D25" t="s">
         <v>802</v>
       </c>
       <c r="E25">
-        <v>1945</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="4" t="s">
-        <v>1872</v>
+      <c r="B26" t="s">
+        <v>1923</v>
       </c>
       <c r="C26" t="s">
-        <v>1913</v>
+        <v>1924</v>
       </c>
       <c r="D26" t="s">
         <v>802</v>
       </c>
       <c r="E26">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>1917</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D27" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1950</v>
+      </c>
+      <c r="B29" t="s">
+        <v>698</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E29">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E30">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1951</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D34" t="s">
         <v>802</v>
       </c>
-      <c r="E27">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>1946</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1919</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D30" t="s">
-        <v>802</v>
-      </c>
-      <c r="E30">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>695</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D31" t="s">
-        <v>802</v>
-      </c>
-      <c r="E31">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>1922</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D32" t="s">
-        <v>802</v>
-      </c>
-      <c r="E32">
-        <v>1946</v>
+      <c r="E34">
+        <v>1951</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>1947</v>
-      </c>
       <c r="B35" t="s">
-        <v>1923</v>
+        <v>1931</v>
       </c>
       <c r="C35" t="s">
-        <v>1924</v>
+        <v>1932</v>
       </c>
       <c r="D35" t="s">
-        <v>802</v>
+        <v>1933</v>
       </c>
       <c r="E35">
-        <v>1947</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>1925</v>
+        <v>1934</v>
       </c>
       <c r="C36" t="s">
-        <v>1926</v>
+        <v>1935</v>
       </c>
       <c r="D36" t="s">
         <v>802</v>
       </c>
       <c r="E36">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>1927</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1928</v>
-      </c>
-      <c r="D37" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>1952</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D39" t="s">
         <v>802</v>
       </c>
-      <c r="E37">
-        <v>1947</v>
+      <c r="E39">
+        <v>1952</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>1948</v>
-      </c>
       <c r="B40" t="s">
-        <v>1930</v>
+        <v>1939</v>
       </c>
       <c r="C40" t="s">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="D40" t="s">
         <v>802</v>
       </c>
       <c r="E40">
-        <v>1948</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>1907</v>
+        <v>1888</v>
       </c>
       <c r="C41" t="s">
-        <v>1931</v>
+        <v>1940</v>
       </c>
       <c r="D41" t="s">
         <v>802</v>
       </c>
       <c r="E41">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D42" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>1953</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D44" t="s">
         <v>802</v>
       </c>
-      <c r="E42">
-        <v>1948</v>
+      <c r="E44">
+        <v>1953</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>1949</v>
-      </c>
       <c r="B45" t="s">
-        <v>1934</v>
+        <v>1943</v>
       </c>
       <c r="C45" t="s">
-        <v>1935</v>
+        <v>1944</v>
       </c>
       <c r="D45" t="s">
         <v>802</v>
       </c>
       <c r="E45">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="C46" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E46">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>1954</v>
+      </c>
+      <c r="B49" t="s">
         <v>1937</v>
       </c>
-      <c r="D46" t="s">
+      <c r="C49" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D49" t="s">
         <v>802</v>
       </c>
-      <c r="E46">
+      <c r="E49">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C50" t="s">
         <v>1949</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1939</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="D50" t="s">
         <v>802</v>
       </c>
-      <c r="E47">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>1950</v>
-      </c>
-      <c r="B50" t="s">
-        <v>698</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1942</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1943</v>
-      </c>
       <c r="E50">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>1940</v>
+        <v>1952</v>
       </c>
       <c r="C51" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="D51" t="s">
-        <v>1941</v>
+        <v>802</v>
       </c>
       <c r="E51">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1944</v>
-      </c>
-      <c r="D52" t="s">
-        <v>802</v>
-      </c>
-      <c r="E52">
-        <v>1950</v>
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>1955</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E54">
+        <v>1955</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>1951</v>
-      </c>
       <c r="B55" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="C55" t="s">
-        <v>1945</v>
+        <v>1956</v>
       </c>
       <c r="D55" t="s">
-        <v>802</v>
+        <v>1956</v>
       </c>
       <c r="E55">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="C56" t="s">
-        <v>1948</v>
+        <v>1957</v>
       </c>
       <c r="D56" t="s">
-        <v>1949</v>
-      </c>
-      <c r="E56">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D57" t="s">
-        <v>802</v>
-      </c>
-      <c r="E57">
-        <v>1951</v>
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1956</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>1956</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>1952</v>
-      </c>
       <c r="B60" t="s">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="D60" t="s">
-        <v>802</v>
+        <v>1961</v>
       </c>
       <c r="E60">
-        <v>1952</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
       <c r="C61" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="D61" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E61">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1957</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D64" t="s">
         <v>802</v>
       </c>
-      <c r="E61">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D62" t="s">
-        <v>802</v>
-      </c>
-      <c r="E62">
-        <v>1952</v>
+      <c r="E64">
+        <v>1957</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>1953</v>
-      </c>
       <c r="B65" t="s">
-        <v>1958</v>
+        <v>1975</v>
       </c>
       <c r="C65" t="s">
-        <v>1957</v>
+        <v>1976</v>
       </c>
       <c r="D65" t="s">
         <v>802</v>
       </c>
       <c r="E65">
-        <v>1953</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>1959</v>
+        <v>1977</v>
       </c>
       <c r="C66" t="s">
-        <v>1960</v>
+        <v>1978</v>
       </c>
       <c r="D66" t="s">
         <v>802</v>
       </c>
       <c r="E66">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E67">
-        <v>1953</v>
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>1958</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D69" t="s">
+        <v>802</v>
+      </c>
+      <c r="E69">
+        <v>1958</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>1954</v>
-      </c>
       <c r="B70" t="s">
-        <v>1953</v>
+        <v>1981</v>
       </c>
       <c r="C70" t="s">
-        <v>1964</v>
+        <v>1982</v>
       </c>
       <c r="D70" t="s">
-        <v>802</v>
+        <v>1983</v>
       </c>
       <c r="E70">
-        <v>1954</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>1966</v>
+        <v>1984</v>
       </c>
       <c r="C71" t="s">
-        <v>1965</v>
+        <v>1985</v>
       </c>
       <c r="D71" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E71">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>1959</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D74" t="s">
         <v>802</v>
       </c>
-      <c r="E71">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>1968</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1967</v>
-      </c>
-      <c r="D72" t="s">
-        <v>802</v>
-      </c>
-      <c r="E72">
-        <v>1954</v>
+      <c r="E74">
+        <v>1959</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>1955</v>
-      </c>
       <c r="B75" t="s">
-        <v>1970</v>
+        <v>1987</v>
       </c>
       <c r="C75" t="s">
-        <v>1969</v>
+        <v>1988</v>
       </c>
       <c r="D75" t="s">
-        <v>1971</v>
+        <v>1989</v>
       </c>
       <c r="E75">
-        <v>1955</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>1972</v>
+        <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>1972</v>
+        <v>1990</v>
       </c>
       <c r="D76" t="s">
-        <v>1972</v>
+        <v>1991</v>
       </c>
       <c r="E76">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B77" t="s">
-        <v>1974</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1975</v>
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>1960</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E79">
+        <v>1960</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>1956</v>
-      </c>
       <c r="B80" t="s">
-        <v>3</v>
+        <v>1996</v>
       </c>
       <c r="C80" t="s">
-        <v>1471</v>
+        <v>1995</v>
       </c>
       <c r="D80" t="s">
-        <v>3</v>
+        <v>1997</v>
       </c>
       <c r="E80">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="C81" t="s">
-        <v>1976</v>
+        <v>1999</v>
       </c>
       <c r="D81" t="s">
-        <v>1977</v>
+        <v>802</v>
       </c>
       <c r="E81">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B82" t="s">
-        <v>1979</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1980</v>
-      </c>
-      <c r="E82">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>1957</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D85" t="s">
-        <v>802</v>
-      </c>
-      <c r="E85">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B86" t="s">
-        <v>1991</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1992</v>
-      </c>
-      <c r="D86" t="s">
-        <v>802</v>
-      </c>
-      <c r="E86">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B87" t="s">
-        <v>1993</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D87" t="s">
-        <v>802</v>
-      </c>
-      <c r="E87">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>1958</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1995</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D90" t="s">
-        <v>802</v>
-      </c>
-      <c r="E90">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B91" t="s">
-        <v>1997</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1998</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1999</v>
-      </c>
-      <c r="E91">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B92" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C92" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D92" t="s">
-        <v>2000</v>
-      </c>
-      <c r="E92">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>1959</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C95" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D95" t="s">
-        <v>802</v>
-      </c>
-      <c r="E95">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B96" t="s">
-        <v>2003</v>
-      </c>
-      <c r="C96" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D96" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E96">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B97" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" t="s">
-        <v>2006</v>
-      </c>
-      <c r="D97" t="s">
-        <v>2007</v>
-      </c>
-      <c r="E97">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>1960</v>
-      </c>
-      <c r="B100" t="s">
-        <v>2008</v>
-      </c>
-      <c r="C100" t="s">
-        <v>2009</v>
-      </c>
-      <c r="D100" t="s">
-        <v>2010</v>
-      </c>
-      <c r="E100">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B101" t="s">
-        <v>2012</v>
-      </c>
-      <c r="C101" t="s">
-        <v>2011</v>
-      </c>
-      <c r="D101" t="s">
-        <v>2013</v>
-      </c>
-      <c r="E101">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B102" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C102" t="s">
-        <v>2015</v>
-      </c>
-      <c r="D102" t="s">
-        <v>802</v>
-      </c>
-      <c r="E102">
         <v>1960</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC843B88-D254-6C4A-AAA2-52B5590A0D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9825C15A-5B96-CB4A-B2F2-E05BB8D9DF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Master" sheetId="16" r:id="rId1"/>
-    <sheet name="Current Playlist" sheetId="17" r:id="rId2"/>
-    <sheet name="Special Playlist" sheetId="18" r:id="rId3"/>
-    <sheet name="Bumpers" sheetId="19" r:id="rId4"/>
-    <sheet name="Broadway" sheetId="21" r:id="rId5"/>
-    <sheet name="1940-1960" sheetId="22" r:id="rId6"/>
+    <sheet name="Music Master" sheetId="16" r:id="rId1"/>
+    <sheet name="Music 1940-1960" sheetId="22" r:id="rId2"/>
+    <sheet name="Music Media Type" sheetId="17" r:id="rId3"/>
+    <sheet name="Talk Media Type" sheetId="23" r:id="rId4"/>
+    <sheet name="Promo Media Type" sheetId="24" r:id="rId5"/>
+    <sheet name="Id Media Type" sheetId="25" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Playlist'!$A$1:$F$436</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Music Media Type'!$A$1:$F$436</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="2044">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -5272,99 +5272,6 @@
     <t>The Time of Our Lives</t>
   </si>
   <si>
-    <t>Classic</t>
-  </si>
-  <si>
-    <t>1. My Fair Lady (1956)</t>
-  </si>
-  <si>
-    <t>2. The Sound of Music (1959)</t>
-  </si>
-  <si>
-    <t>3. Oklahoma! (1943)</t>
-  </si>
-  <si>
-    <t>4. Carousel (1945)</t>
-  </si>
-  <si>
-    <t>5. South Pacific (1949)</t>
-  </si>
-  <si>
-    <t>6. The King and I (1951)</t>
-  </si>
-  <si>
-    <t>7. West Side Story (1957)</t>
-  </si>
-  <si>
-    <t>8. The Music Man (1957)</t>
-  </si>
-  <si>
-    <t>9. Cinderella (1957)</t>
-  </si>
-  <si>
-    <t>10. Paint Your Wagon (1951)</t>
-  </si>
-  <si>
-    <t>11. Li’l Abner (1956)</t>
-  </si>
-  <si>
-    <t>12. Can‑Can (1953)</t>
-  </si>
-  <si>
-    <t>13. Guys and Dolls (1950)</t>
-  </si>
-  <si>
-    <t>14. Brigadoon (1947)</t>
-  </si>
-  <si>
-    <t>15. Kiss Me, Kate (1948)</t>
-  </si>
-  <si>
-    <t>Les Misérables</t>
-  </si>
-  <si>
-    <t>Wicked</t>
-  </si>
-  <si>
-    <t>Cats</t>
-  </si>
-  <si>
-    <t>Hamilton</t>
-  </si>
-  <si>
-    <t>Dear Evan Hansen</t>
-  </si>
-  <si>
-    <t>The Phantom of the Opera</t>
-  </si>
-  <si>
-    <t>The Lion King</t>
-  </si>
-  <si>
-    <t>Mamma Mia!</t>
-  </si>
-  <si>
-    <t>Jersey Boys</t>
-  </si>
-  <si>
-    <t>Aladdin</t>
-  </si>
-  <si>
-    <t>Beauty and the Beast</t>
-  </si>
-  <si>
-    <t>Rent</t>
-  </si>
-  <si>
-    <t>Hairspray</t>
-  </si>
-  <si>
-    <t>The Book of Mormon</t>
-  </si>
-  <si>
-    <t>Fan Favorite</t>
-  </si>
-  <si>
     <t>Thank You</t>
   </si>
   <si>
@@ -6379,7 +6286,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6399,12 +6306,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -6431,19 +6332,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="13.5"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.5"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6465,27 +6353,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8954,8 +8839,715 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
+  <dimension ref="A2:E81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1945</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D5" t="s">
+        <v>802</v>
+      </c>
+      <c r="E5">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D6" t="s">
+        <v>802</v>
+      </c>
+      <c r="E6">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>695</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D10" t="s">
+        <v>802</v>
+      </c>
+      <c r="E10">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D11" t="s">
+        <v>802</v>
+      </c>
+      <c r="E11">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1947</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D14" t="s">
+        <v>802</v>
+      </c>
+      <c r="E14">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D15" t="s">
+        <v>802</v>
+      </c>
+      <c r="E15">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D16" t="s">
+        <v>802</v>
+      </c>
+      <c r="E16">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1948</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D19" t="s">
+        <v>802</v>
+      </c>
+      <c r="E19">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D20" t="s">
+        <v>802</v>
+      </c>
+      <c r="E20">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D21" t="s">
+        <v>802</v>
+      </c>
+      <c r="E21">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1949</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D24" t="s">
+        <v>802</v>
+      </c>
+      <c r="E24">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D25" t="s">
+        <v>802</v>
+      </c>
+      <c r="E25">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D26" t="s">
+        <v>802</v>
+      </c>
+      <c r="E26">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1950</v>
+      </c>
+      <c r="B29" t="s">
+        <v>698</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E29">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E30">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1951</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D34" t="s">
+        <v>802</v>
+      </c>
+      <c r="E34">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1902</v>
+      </c>
+      <c r="E35">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D36" t="s">
+        <v>802</v>
+      </c>
+      <c r="E36">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>1952</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D39" t="s">
+        <v>802</v>
+      </c>
+      <c r="E39">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D40" t="s">
+        <v>802</v>
+      </c>
+      <c r="E40">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D41" t="s">
+        <v>802</v>
+      </c>
+      <c r="E41">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>1953</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D44" t="s">
+        <v>802</v>
+      </c>
+      <c r="E44">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D45" t="s">
+        <v>802</v>
+      </c>
+      <c r="E45">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E46">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>1954</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D49" t="s">
+        <v>802</v>
+      </c>
+      <c r="E49">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D50" t="s">
+        <v>802</v>
+      </c>
+      <c r="E50">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D51" t="s">
+        <v>802</v>
+      </c>
+      <c r="E51">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>1955</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E54">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E55">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1956</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E60">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E61">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1957</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D64" t="s">
+        <v>802</v>
+      </c>
+      <c r="E64">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D65" t="s">
+        <v>802</v>
+      </c>
+      <c r="E65">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D66" t="s">
+        <v>802</v>
+      </c>
+      <c r="E66">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>1958</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D69" t="s">
+        <v>802</v>
+      </c>
+      <c r="E69">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E70">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E71">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>1959</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D74" t="s">
+        <v>802</v>
+      </c>
+      <c r="E74">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E75">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E76">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>1960</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E79">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E80">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D81" t="s">
+        <v>802</v>
+      </c>
+      <c r="E81">
+        <v>1960</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F607"/>
+  <dimension ref="A1:F608"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -8965,23 +9557,23 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>605</v>
       </c>
     </row>
@@ -9514,7 +10106,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>685</v>
       </c>
@@ -9528,11 +10120,11 @@
       <c r="E34" s="1">
         <v>1966</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>688</v>
       </c>
@@ -9550,7 +10142,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>689</v>
       </c>
@@ -9568,7 +10160,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>692</v>
       </c>
@@ -9603,7 +10195,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -9617,7 +10209,7 @@
       <c r="E39" s="1">
         <v>1975</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="7" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -11329,10 +11921,10 @@
         <v>360</v>
       </c>
       <c r="B136" t="s">
-        <v>2029</v>
+        <v>1998</v>
       </c>
       <c r="C136" t="s">
-        <v>2030</v>
+        <v>1999</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1">
@@ -13377,7 +13969,7 @@
       <c r="A250" t="s">
         <v>1187</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B250" s="9" t="s">
         <v>1195</v>
       </c>
       <c r="C250" s="1" t="s">
@@ -13410,7 +14002,7 @@
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A252" s="9" t="s">
+      <c r="A252" s="8" t="s">
         <v>1192</v>
       </c>
       <c r="B252" t="s">
@@ -14364,13 +14956,13 @@
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A305" s="11" t="s">
+      <c r="A305" s="10" t="s">
         <v>1329</v>
       </c>
       <c r="B305" t="s">
         <v>1330</v>
       </c>
-      <c r="C305" s="11" t="s">
+      <c r="C305" s="10" t="s">
         <v>1329</v>
       </c>
       <c r="E305" s="1">
@@ -16472,7 +17064,7 @@
       <c r="A422" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B422" s="10" t="s">
+      <c r="B422" s="9" t="s">
         <v>1566</v>
       </c>
       <c r="C422" t="s">
@@ -16779,7 +17371,7 @@
       <c r="B439" t="s">
         <v>1606</v>
       </c>
-      <c r="C439" s="11" t="s">
+      <c r="C439" s="10" t="s">
         <v>1607</v>
       </c>
       <c r="E439" s="1">
@@ -17578,7 +18170,7 @@
       <c r="A486" t="s">
         <v>282</v>
       </c>
-      <c r="B486" s="11" t="s">
+      <c r="B486" s="10" t="s">
         <v>1698</v>
       </c>
       <c r="C486" t="s">
@@ -17783,10 +18375,10 @@
         <v>223</v>
       </c>
       <c r="B498" t="s">
-        <v>1754</v>
+        <v>1723</v>
       </c>
       <c r="C498" t="s">
-        <v>1755</v>
+        <v>1724</v>
       </c>
       <c r="E498">
         <v>1999</v>
@@ -17797,13 +18389,13 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1756</v>
+        <v>1725</v>
       </c>
       <c r="B499" t="s">
-        <v>1757</v>
+        <v>1726</v>
       </c>
       <c r="C499" t="s">
-        <v>1758</v>
+        <v>1727</v>
       </c>
       <c r="E499" s="1">
         <v>1971</v>
@@ -17814,13 +18406,13 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1759</v>
+        <v>1728</v>
       </c>
       <c r="B500" t="s">
-        <v>1760</v>
+        <v>1729</v>
       </c>
       <c r="C500" t="s">
-        <v>1761</v>
+        <v>1730</v>
       </c>
       <c r="E500" s="1">
         <v>1978</v>
@@ -17831,13 +18423,13 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1763</v>
+        <v>1732</v>
       </c>
       <c r="B501" t="s">
-        <v>1762</v>
+        <v>1731</v>
       </c>
       <c r="C501" t="s">
-        <v>1762</v>
+        <v>1731</v>
       </c>
       <c r="E501" s="1">
         <v>2011</v>
@@ -17851,7 +18443,7 @@
         <v>1209</v>
       </c>
       <c r="B502" t="s">
-        <v>1764</v>
+        <v>1733</v>
       </c>
       <c r="C502" t="s">
         <v>1209</v>
@@ -17871,7 +18463,7 @@
         <v>1703</v>
       </c>
       <c r="C503" t="s">
-        <v>1765</v>
+        <v>1734</v>
       </c>
       <c r="E503" s="1">
         <v>1999</v>
@@ -17885,10 +18477,10 @@
         <v>73</v>
       </c>
       <c r="B504" t="s">
-        <v>1766</v>
+        <v>1735</v>
       </c>
       <c r="C504" t="s">
-        <v>1767</v>
+        <v>1736</v>
       </c>
       <c r="E504" s="1">
         <v>1983</v>
@@ -17899,13 +18491,13 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1768</v>
+        <v>1737</v>
       </c>
       <c r="B505" t="s">
-        <v>1769</v>
+        <v>1738</v>
       </c>
       <c r="C505" t="s">
-        <v>1770</v>
+        <v>1739</v>
       </c>
       <c r="E505" s="1">
         <v>1983</v>
@@ -17919,10 +18511,10 @@
         <v>427</v>
       </c>
       <c r="B506" t="s">
-        <v>1771</v>
+        <v>1740</v>
       </c>
       <c r="C506" t="s">
-        <v>1772</v>
+        <v>1741</v>
       </c>
       <c r="E506" s="1">
         <v>2013</v>
@@ -17936,7 +18528,7 @@
         <v>203</v>
       </c>
       <c r="B507" t="s">
-        <v>1773</v>
+        <v>1742</v>
       </c>
       <c r="C507" t="s">
         <v>203</v>
@@ -17953,10 +18545,10 @@
         <v>431</v>
       </c>
       <c r="B508" t="s">
-        <v>1774</v>
+        <v>1743</v>
       </c>
       <c r="C508" t="s">
-        <v>1775</v>
+        <v>1744</v>
       </c>
       <c r="E508" s="1">
         <v>2014</v>
@@ -17967,13 +18559,13 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1776</v>
+        <v>1745</v>
       </c>
       <c r="B509" t="s">
-        <v>1777</v>
+        <v>1746</v>
       </c>
       <c r="C509" t="s">
-        <v>1778</v>
+        <v>1747</v>
       </c>
       <c r="E509" s="1">
         <v>1992</v>
@@ -17984,13 +18576,13 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1779</v>
+        <v>1748</v>
       </c>
       <c r="B510" t="s">
-        <v>1780</v>
+        <v>1749</v>
       </c>
       <c r="C510" t="s">
-        <v>1781</v>
+        <v>1750</v>
       </c>
       <c r="E510" s="1">
         <v>2004</v>
@@ -18001,13 +18593,13 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1782</v>
+        <v>1751</v>
       </c>
       <c r="B511" t="s">
-        <v>1783</v>
+        <v>1752</v>
       </c>
       <c r="C511" t="s">
-        <v>1784</v>
+        <v>1753</v>
       </c>
       <c r="E511" s="1">
         <v>1952</v>
@@ -18018,13 +18610,13 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1785</v>
+        <v>1754</v>
       </c>
       <c r="B512" t="s">
-        <v>1786</v>
+        <v>1755</v>
       </c>
       <c r="C512" t="s">
-        <v>1787</v>
+        <v>1756</v>
       </c>
       <c r="E512" s="1">
         <v>1961</v>
@@ -18035,13 +18627,13 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1788</v>
+        <v>1757</v>
       </c>
       <c r="B513" t="s">
-        <v>1789</v>
+        <v>1758</v>
       </c>
       <c r="C513" t="s">
-        <v>1790</v>
+        <v>1759</v>
       </c>
       <c r="E513" s="1">
         <v>1980</v>
@@ -18052,13 +18644,13 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1791</v>
+        <v>1760</v>
       </c>
       <c r="B514" t="s">
-        <v>1792</v>
+        <v>1761</v>
       </c>
       <c r="C514" t="s">
-        <v>1793</v>
+        <v>1762</v>
       </c>
       <c r="E514" s="1">
         <v>1989</v>
@@ -18075,7 +18667,7 @@
         <v>1535</v>
       </c>
       <c r="C515" t="s">
-        <v>1794</v>
+        <v>1763</v>
       </c>
       <c r="E515" s="1">
         <v>1997</v>
@@ -18089,10 +18681,10 @@
         <v>85</v>
       </c>
       <c r="B516" t="s">
-        <v>1799</v>
+        <v>1768</v>
       </c>
       <c r="C516" t="s">
-        <v>1798</v>
+        <v>1767</v>
       </c>
       <c r="E516" s="1">
         <v>1980</v>
@@ -18103,13 +18695,13 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1795</v>
+        <v>1764</v>
       </c>
       <c r="B517" t="s">
-        <v>1800</v>
+        <v>1769</v>
       </c>
       <c r="C517" t="s">
-        <v>1801</v>
+        <v>1770</v>
       </c>
       <c r="E517" s="1">
         <v>1988</v>
@@ -18123,10 +18715,10 @@
         <v>206</v>
       </c>
       <c r="B518" t="s">
-        <v>1802</v>
+        <v>1771</v>
       </c>
       <c r="C518" t="s">
-        <v>1803</v>
+        <v>1772</v>
       </c>
       <c r="E518" s="1">
         <v>2002</v>
@@ -18137,13 +18729,13 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1796</v>
+        <v>1765</v>
       </c>
       <c r="B519" t="s">
-        <v>1797</v>
+        <v>1766</v>
       </c>
       <c r="C519" t="s">
-        <v>1804</v>
+        <v>1773</v>
       </c>
       <c r="E519" s="1">
         <v>2012</v>
@@ -18157,10 +18749,10 @@
         <v>112</v>
       </c>
       <c r="B520" t="s">
-        <v>1808</v>
+        <v>1777</v>
       </c>
       <c r="C520" t="s">
-        <v>1809</v>
+        <v>1778</v>
       </c>
       <c r="E520" s="1">
         <v>2012</v>
@@ -18171,13 +18763,13 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1806</v>
+        <v>1775</v>
       </c>
       <c r="B521" t="s">
-        <v>1812</v>
+        <v>1781</v>
       </c>
       <c r="C521" t="s">
-        <v>1813</v>
+        <v>1782</v>
       </c>
       <c r="E521" s="1">
         <v>1982</v>
@@ -18191,7 +18783,7 @@
         <v>1349</v>
       </c>
       <c r="B522" t="s">
-        <v>1810</v>
+        <v>1779</v>
       </c>
       <c r="C522" t="s">
         <v>1351</v>
@@ -18208,10 +18800,10 @@
         <v>249</v>
       </c>
       <c r="B523" t="s">
-        <v>1817</v>
+        <v>1786</v>
       </c>
       <c r="C523" t="s">
-        <v>1814</v>
+        <v>1783</v>
       </c>
       <c r="E523" s="1">
         <v>1985</v>
@@ -18225,10 +18817,10 @@
         <v>250</v>
       </c>
       <c r="B524" t="s">
-        <v>1815</v>
+        <v>1784</v>
       </c>
       <c r="C524" t="s">
-        <v>1816</v>
+        <v>1785</v>
       </c>
       <c r="E524" s="1">
         <v>1998</v>
@@ -18242,7 +18834,7 @@
         <v>251</v>
       </c>
       <c r="B525" t="s">
-        <v>1818</v>
+        <v>1787</v>
       </c>
       <c r="C525" t="s">
         <v>821</v>
@@ -18259,10 +18851,10 @@
         <v>140</v>
       </c>
       <c r="B526" t="s">
-        <v>1819</v>
+        <v>1788</v>
       </c>
       <c r="C526" t="s">
-        <v>1820</v>
+        <v>1789</v>
       </c>
       <c r="E526" s="1">
         <v>1983</v>
@@ -18276,10 +18868,10 @@
         <v>286</v>
       </c>
       <c r="B527" t="s">
-        <v>1829</v>
+        <v>1798</v>
       </c>
       <c r="C527" t="s">
-        <v>1830</v>
+        <v>1799</v>
       </c>
       <c r="E527" s="1">
         <v>2014</v>
@@ -18293,10 +18885,10 @@
         <v>287</v>
       </c>
       <c r="B528" t="s">
-        <v>1821</v>
+        <v>1790</v>
       </c>
       <c r="C528" t="s">
-        <v>1821</v>
+        <v>1790</v>
       </c>
       <c r="E528" s="1">
         <v>1977</v>
@@ -18310,10 +18902,10 @@
         <v>252</v>
       </c>
       <c r="B529" t="s">
-        <v>1822</v>
+        <v>1791</v>
       </c>
       <c r="C529" t="s">
-        <v>1823</v>
+        <v>1792</v>
       </c>
       <c r="E529" s="1">
         <v>1989</v>
@@ -18327,10 +18919,10 @@
         <v>66</v>
       </c>
       <c r="B530" t="s">
-        <v>1807</v>
+        <v>1776</v>
       </c>
       <c r="C530" t="s">
-        <v>1828</v>
+        <v>1797</v>
       </c>
       <c r="E530" s="1">
         <v>1978</v>
@@ -18344,10 +18936,10 @@
         <v>288</v>
       </c>
       <c r="B531" t="s">
-        <v>1842</v>
+        <v>1811</v>
       </c>
       <c r="C531" t="s">
-        <v>1843</v>
+        <v>1812</v>
       </c>
       <c r="E531" s="1">
         <v>2022</v>
@@ -18361,7 +18953,7 @@
         <v>49</v>
       </c>
       <c r="B532" t="s">
-        <v>1826</v>
+        <v>1795</v>
       </c>
       <c r="C532" t="s">
         <v>49</v>
@@ -18378,10 +18970,10 @@
         <v>116</v>
       </c>
       <c r="B533" t="s">
-        <v>1834</v>
+        <v>1803</v>
       </c>
       <c r="C533" t="s">
-        <v>1835</v>
+        <v>1804</v>
       </c>
       <c r="E533" s="1">
         <v>2017</v>
@@ -18409,13 +19001,13 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1836</v>
+        <v>1805</v>
       </c>
       <c r="B535" t="s">
-        <v>1837</v>
+        <v>1806</v>
       </c>
       <c r="C535" t="s">
-        <v>1838</v>
+        <v>1807</v>
       </c>
       <c r="E535" s="1">
         <v>1970</v>
@@ -18429,10 +19021,10 @@
         <v>253</v>
       </c>
       <c r="B536" t="s">
-        <v>1827</v>
+        <v>1796</v>
       </c>
       <c r="C536" t="s">
-        <v>1827</v>
+        <v>1796</v>
       </c>
       <c r="E536">
         <v>1999</v>
@@ -18446,10 +19038,10 @@
         <v>208</v>
       </c>
       <c r="B537" t="s">
-        <v>1824</v>
+        <v>1793</v>
       </c>
       <c r="C537" t="s">
-        <v>1825</v>
+        <v>1794</v>
       </c>
       <c r="E537">
         <v>2006</v>
@@ -18463,10 +19055,10 @@
         <v>225</v>
       </c>
       <c r="B538" t="s">
-        <v>1844</v>
+        <v>1813</v>
       </c>
       <c r="C538" t="s">
-        <v>1845</v>
+        <v>1814</v>
       </c>
       <c r="E538" s="1">
         <v>2010</v>
@@ -18480,10 +19072,10 @@
         <v>224</v>
       </c>
       <c r="B539" t="s">
-        <v>1832</v>
+        <v>1801</v>
       </c>
       <c r="C539" t="s">
-        <v>1833</v>
+        <v>1802</v>
       </c>
       <c r="E539">
         <v>2000</v>
@@ -18497,10 +19089,10 @@
         <v>142</v>
       </c>
       <c r="B540" t="s">
-        <v>1846</v>
+        <v>1815</v>
       </c>
       <c r="C540" t="s">
-        <v>1847</v>
+        <v>1816</v>
       </c>
       <c r="E540">
         <v>2009</v>
@@ -18517,7 +19109,7 @@
         <v>1316</v>
       </c>
       <c r="C541" t="s">
-        <v>1848</v>
+        <v>1817</v>
       </c>
       <c r="E541">
         <v>1999</v>
@@ -18531,10 +19123,10 @@
         <v>432</v>
       </c>
       <c r="B542" t="s">
-        <v>1849</v>
+        <v>1818</v>
       </c>
       <c r="C542" t="s">
-        <v>1850</v>
+        <v>1819</v>
       </c>
       <c r="E542">
         <v>2018</v>
@@ -18548,10 +19140,10 @@
         <v>226</v>
       </c>
       <c r="B543" t="s">
-        <v>1851</v>
+        <v>1820</v>
       </c>
       <c r="C543" t="s">
-        <v>1852</v>
+        <v>1821</v>
       </c>
       <c r="E543">
         <v>2017</v>
@@ -18565,10 +19157,10 @@
         <v>45</v>
       </c>
       <c r="B544" t="s">
-        <v>1839</v>
+        <v>1808</v>
       </c>
       <c r="C544" t="s">
-        <v>1840</v>
+        <v>1809</v>
       </c>
       <c r="E544">
         <v>1970</v>
@@ -18582,10 +19174,10 @@
         <v>291</v>
       </c>
       <c r="B545" t="s">
-        <v>1841</v>
+        <v>1810</v>
       </c>
       <c r="C545" t="s">
-        <v>1841</v>
+        <v>1810</v>
       </c>
       <c r="E545">
         <v>1975</v>
@@ -18599,10 +19191,10 @@
         <v>145</v>
       </c>
       <c r="B546" t="s">
-        <v>1853</v>
+        <v>1822</v>
       </c>
       <c r="C546" t="s">
-        <v>1853</v>
+        <v>1822</v>
       </c>
       <c r="E546">
         <v>2004</v>
@@ -18616,10 +19208,10 @@
         <v>372</v>
       </c>
       <c r="B547" t="s">
-        <v>1854</v>
+        <v>1823</v>
       </c>
       <c r="C547" t="s">
-        <v>1855</v>
+        <v>1824</v>
       </c>
       <c r="E547">
         <v>2021</v>
@@ -18633,10 +19225,10 @@
         <v>210</v>
       </c>
       <c r="B548" t="s">
-        <v>1805</v>
+        <v>1774</v>
       </c>
       <c r="C548" t="s">
-        <v>1811</v>
+        <v>1780</v>
       </c>
       <c r="E548">
         <v>2005</v>
@@ -18650,10 +19242,10 @@
         <v>259</v>
       </c>
       <c r="B549" t="s">
-        <v>1831</v>
+        <v>1800</v>
       </c>
       <c r="C549" t="s">
-        <v>1831</v>
+        <v>1800</v>
       </c>
       <c r="E549">
         <v>2000</v>
@@ -18667,10 +19259,10 @@
         <v>123</v>
       </c>
       <c r="B550" t="s">
-        <v>1856</v>
+        <v>1825</v>
       </c>
       <c r="C550" t="s">
-        <v>1857</v>
+        <v>1826</v>
       </c>
       <c r="E550">
         <v>2022</v>
@@ -18684,10 +19276,10 @@
         <v>196</v>
       </c>
       <c r="B551" t="s">
-        <v>1858</v>
+        <v>1827</v>
       </c>
       <c r="C551" t="s">
-        <v>1859</v>
+        <v>1828</v>
       </c>
       <c r="E551">
         <v>1994</v>
@@ -18701,10 +19293,10 @@
         <v>78</v>
       </c>
       <c r="B552" t="s">
-        <v>1860</v>
+        <v>1829</v>
       </c>
       <c r="C552" t="s">
-        <v>1861</v>
+        <v>1830</v>
       </c>
       <c r="E552">
         <v>1985</v>
@@ -18718,10 +19310,10 @@
         <v>119</v>
       </c>
       <c r="B553" t="s">
-        <v>1862</v>
+        <v>1831</v>
       </c>
       <c r="C553" t="s">
-        <v>1863</v>
+        <v>1832</v>
       </c>
       <c r="E553">
         <v>2012</v>
@@ -18735,10 +19327,10 @@
         <v>25</v>
       </c>
       <c r="B554" t="s">
-        <v>1864</v>
+        <v>1833</v>
       </c>
       <c r="C554" t="s">
-        <v>1865</v>
+        <v>1834</v>
       </c>
       <c r="E554">
         <v>1967</v>
@@ -18749,7 +19341,7 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1866</v>
+        <v>1835</v>
       </c>
       <c r="B555" t="s">
         <v>895</v>
@@ -18766,13 +19358,13 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1873</v>
+        <v>1842</v>
       </c>
       <c r="B556" t="s">
-        <v>1871</v>
+        <v>1840</v>
       </c>
       <c r="C556" t="s">
-        <v>1872</v>
+        <v>1841</v>
       </c>
       <c r="E556">
         <v>1965</v>
@@ -18783,13 +19375,13 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1875</v>
+        <v>1844</v>
       </c>
       <c r="B557" t="s">
-        <v>1874</v>
+        <v>1843</v>
       </c>
       <c r="C557" t="s">
-        <v>1876</v>
+        <v>1845</v>
       </c>
       <c r="E557">
         <v>1955</v>
@@ -18800,16 +19392,16 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1879</v>
+        <v>1848</v>
       </c>
       <c r="B558" t="s">
-        <v>1878</v>
+        <v>1847</v>
       </c>
       <c r="C558" t="s">
         <v>802</v>
       </c>
       <c r="D558" t="s">
-        <v>1880</v>
+        <v>1849</v>
       </c>
       <c r="E558">
         <v>1972</v>
@@ -18820,13 +19412,13 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1881</v>
+        <v>1850</v>
       </c>
       <c r="B559" t="s">
-        <v>1882</v>
+        <v>1851</v>
       </c>
       <c r="C559" t="s">
-        <v>1882</v>
+        <v>1851</v>
       </c>
       <c r="E559">
         <v>1964</v>
@@ -18837,13 +19429,13 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1883</v>
+        <v>1852</v>
       </c>
       <c r="B560" t="s">
-        <v>1884</v>
+        <v>1853</v>
       </c>
       <c r="C560" t="s">
-        <v>1885</v>
+        <v>1854</v>
       </c>
       <c r="E560">
         <v>1964</v>
@@ -18871,13 +19463,13 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1967</v>
+        <v>1936</v>
       </c>
       <c r="B562" t="s">
-        <v>1965</v>
+        <v>1934</v>
       </c>
       <c r="C562" t="s">
-        <v>1966</v>
+        <v>1935</v>
       </c>
       <c r="E562">
         <v>2013</v>
@@ -18888,13 +19480,13 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1968</v>
+        <v>1937</v>
       </c>
       <c r="B563" t="s">
-        <v>1819</v>
+        <v>1788</v>
       </c>
       <c r="C563" t="s">
-        <v>1969</v>
+        <v>1938</v>
       </c>
       <c r="E563">
         <v>1973</v>
@@ -18905,7 +19497,7 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1970</v>
+        <v>1939</v>
       </c>
       <c r="B564" t="s">
         <v>1287</v>
@@ -18922,13 +19514,13 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1971</v>
+        <v>1940</v>
       </c>
       <c r="B565" t="s">
-        <v>1972</v>
+        <v>1941</v>
       </c>
       <c r="C565" t="s">
-        <v>1973</v>
+        <v>1942</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -18942,10 +19534,10 @@
         <v>202</v>
       </c>
       <c r="B566" t="s">
-        <v>2000</v>
+        <v>1969</v>
       </c>
       <c r="C566" t="s">
-        <v>2001</v>
+        <v>1970</v>
       </c>
       <c r="E566">
         <v>2004</v>
@@ -18959,10 +19551,10 @@
         <v>255</v>
       </c>
       <c r="B567" t="s">
-        <v>2002</v>
+        <v>1971</v>
       </c>
       <c r="C567" t="s">
-        <v>2003</v>
+        <v>1972</v>
       </c>
       <c r="E567">
         <v>1975</v>
@@ -18993,10 +19585,10 @@
         <v>296</v>
       </c>
       <c r="B569" t="s">
-        <v>2004</v>
+        <v>1973</v>
       </c>
       <c r="C569" t="s">
-        <v>2004</v>
+        <v>1973</v>
       </c>
       <c r="E569">
         <v>1992</v>
@@ -19010,10 +19602,10 @@
         <v>147</v>
       </c>
       <c r="B570" t="s">
-        <v>2005</v>
+        <v>1974</v>
       </c>
       <c r="C570" t="s">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="E570">
         <v>2008</v>
@@ -19027,10 +19619,10 @@
         <v>83</v>
       </c>
       <c r="B571" t="s">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="C571" t="s">
-        <v>2008</v>
+        <v>1977</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -19044,10 +19636,10 @@
         <v>104</v>
       </c>
       <c r="B572" t="s">
-        <v>2009</v>
+        <v>1978</v>
       </c>
       <c r="C572" t="s">
-        <v>2009</v>
+        <v>1978</v>
       </c>
       <c r="E572">
         <v>2010</v>
@@ -19061,10 +19653,10 @@
         <v>103</v>
       </c>
       <c r="B573" t="s">
-        <v>2010</v>
+        <v>1979</v>
       </c>
       <c r="C573" t="s">
-        <v>2011</v>
+        <v>1980</v>
       </c>
       <c r="E573">
         <v>2004</v>
@@ -19078,10 +19670,10 @@
         <v>258</v>
       </c>
       <c r="B574" t="s">
-        <v>2012</v>
+        <v>1981</v>
       </c>
       <c r="C574" t="s">
-        <v>2013</v>
+        <v>1982</v>
       </c>
       <c r="E574">
         <v>1984</v>
@@ -19095,10 +19687,10 @@
         <v>148</v>
       </c>
       <c r="B575" t="s">
-        <v>2014</v>
+        <v>1983</v>
       </c>
       <c r="C575" t="s">
-        <v>2015</v>
+        <v>1984</v>
       </c>
       <c r="E575">
         <v>2008</v>
@@ -19109,13 +19701,13 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>2016</v>
+        <v>1985</v>
       </c>
       <c r="B576" t="s">
-        <v>2017</v>
+        <v>1986</v>
       </c>
       <c r="C576" t="s">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="E576">
         <v>2005</v>
@@ -19129,10 +19721,10 @@
         <v>198</v>
       </c>
       <c r="B577" t="s">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="C577" t="s">
-        <v>2020</v>
+        <v>1989</v>
       </c>
       <c r="E577">
         <v>2000</v>
@@ -19146,10 +19738,10 @@
         <v>72</v>
       </c>
       <c r="B578" t="s">
-        <v>2021</v>
+        <v>1990</v>
       </c>
       <c r="C578" t="s">
-        <v>2022</v>
+        <v>1991</v>
       </c>
       <c r="E578">
         <v>1983</v>
@@ -19163,10 +19755,10 @@
         <v>375</v>
       </c>
       <c r="B579" t="s">
-        <v>2023</v>
+        <v>1992</v>
       </c>
       <c r="C579" t="s">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="E579">
         <v>1999</v>
@@ -19180,10 +19772,10 @@
         <v>213</v>
       </c>
       <c r="B580" t="s">
-        <v>2025</v>
+        <v>1994</v>
       </c>
       <c r="C580" t="s">
-        <v>2026</v>
+        <v>1995</v>
       </c>
       <c r="E580">
         <v>2013</v>
@@ -19214,10 +19806,10 @@
         <v>107</v>
       </c>
       <c r="B582" t="s">
-        <v>2027</v>
+        <v>1996</v>
       </c>
       <c r="C582" t="s">
-        <v>2028</v>
+        <v>1997</v>
       </c>
       <c r="E582">
         <v>2002</v>
@@ -19228,10 +19820,10 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>2031</v>
+        <v>2000</v>
       </c>
       <c r="B583" t="s">
-        <v>2032</v>
+        <v>2001</v>
       </c>
       <c r="C583" t="s">
         <v>930</v>
@@ -19248,10 +19840,10 @@
         <v>229</v>
       </c>
       <c r="B584" t="s">
-        <v>2033</v>
+        <v>2002</v>
       </c>
       <c r="C584" t="s">
-        <v>2034</v>
+        <v>2003</v>
       </c>
       <c r="E584">
         <v>1993</v>
@@ -19268,7 +19860,7 @@
         <v>930</v>
       </c>
       <c r="C585" t="s">
-        <v>2035</v>
+        <v>2004</v>
       </c>
       <c r="E585">
         <v>2005</v>
@@ -19282,10 +19874,10 @@
         <v>57</v>
       </c>
       <c r="B586" t="s">
-        <v>2036</v>
+        <v>2005</v>
       </c>
       <c r="C586" t="s">
-        <v>2037</v>
+        <v>2006</v>
       </c>
       <c r="E586">
         <v>1995</v>
@@ -19299,10 +19891,10 @@
         <v>313</v>
       </c>
       <c r="B587" t="s">
-        <v>2038</v>
+        <v>2007</v>
       </c>
       <c r="C587" t="s">
-        <v>2039</v>
+        <v>2008</v>
       </c>
       <c r="E587">
         <v>2011</v>
@@ -19313,13 +19905,13 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>2040</v>
+        <v>2009</v>
       </c>
       <c r="B588" t="s">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="C588" t="s">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="E588">
         <v>1972</v>
@@ -19333,7 +19925,7 @@
         <v>97</v>
       </c>
       <c r="B589" t="s">
-        <v>2042</v>
+        <v>2011</v>
       </c>
       <c r="C589" t="s">
         <v>97</v>
@@ -19347,13 +19939,13 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>2043</v>
+        <v>2012</v>
       </c>
       <c r="B590" t="s">
-        <v>2044</v>
+        <v>2013</v>
       </c>
       <c r="C590" t="s">
-        <v>2045</v>
+        <v>2014</v>
       </c>
       <c r="E590">
         <v>1987</v>
@@ -19364,13 +19956,13 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>2047</v>
+        <v>2016</v>
       </c>
       <c r="B591" t="s">
-        <v>2046</v>
+        <v>2015</v>
       </c>
       <c r="C591" t="s">
-        <v>2046</v>
+        <v>2015</v>
       </c>
       <c r="E591">
         <v>1968</v>
@@ -19381,10 +19973,10 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>2048</v>
+        <v>2017</v>
       </c>
       <c r="B592" t="s">
-        <v>2049</v>
+        <v>2018</v>
       </c>
       <c r="C592" t="s">
         <v>802</v>
@@ -19398,10 +19990,10 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>2050</v>
+        <v>2019</v>
       </c>
       <c r="B593" t="s">
-        <v>2051</v>
+        <v>2020</v>
       </c>
       <c r="C593" t="s">
         <v>802</v>
@@ -19415,16 +20007,16 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>2054</v>
+        <v>2023</v>
       </c>
       <c r="B594" t="s">
-        <v>2052</v>
+        <v>2021</v>
       </c>
       <c r="C594" t="s">
-        <v>2053</v>
+        <v>2022</v>
       </c>
       <c r="D594" t="s">
-        <v>2055</v>
+        <v>2024</v>
       </c>
       <c r="E594">
         <v>2011</v>
@@ -19435,13 +20027,13 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>2056</v>
+        <v>2025</v>
       </c>
       <c r="B595" t="s">
-        <v>2057</v>
+        <v>2026</v>
       </c>
       <c r="C595" t="s">
-        <v>2056</v>
+        <v>2025</v>
       </c>
       <c r="E595">
         <v>1974</v>
@@ -19451,14 +20043,14 @@
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A596" s="9" t="s">
-        <v>2058</v>
+      <c r="A596" s="8" t="s">
+        <v>2027</v>
       </c>
       <c r="B596" t="s">
-        <v>2059</v>
+        <v>2028</v>
       </c>
       <c r="C596" t="s">
-        <v>2060</v>
+        <v>2029</v>
       </c>
       <c r="E596">
         <v>2011</v>
@@ -19469,13 +20061,13 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>2061</v>
+        <v>2030</v>
       </c>
       <c r="B597" t="s">
-        <v>2062</v>
+        <v>2031</v>
       </c>
       <c r="C597" t="s">
-        <v>2063</v>
+        <v>2032</v>
       </c>
       <c r="E597">
         <v>1994</v>
@@ -19486,13 +20078,13 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>2065</v>
+        <v>2034</v>
       </c>
       <c r="B598" t="s">
-        <v>2064</v>
+        <v>2033</v>
       </c>
       <c r="C598" t="s">
-        <v>2066</v>
+        <v>2035</v>
       </c>
       <c r="E598">
         <v>1967</v>
@@ -19503,13 +20095,13 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>2067</v>
+        <v>2036</v>
       </c>
       <c r="B599" t="s">
-        <v>2068</v>
+        <v>2037</v>
       </c>
       <c r="C599" t="s">
-        <v>2069</v>
+        <v>2038</v>
       </c>
       <c r="E599">
         <v>1995</v>
@@ -19520,13 +20112,13 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>2070</v>
+        <v>2039</v>
       </c>
       <c r="B600" t="s">
-        <v>2071</v>
+        <v>2040</v>
       </c>
       <c r="C600" t="s">
-        <v>2072</v>
+        <v>2041</v>
       </c>
       <c r="E600">
         <v>1970</v>
@@ -19537,10 +20129,10 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>2073</v>
+        <v>2042</v>
       </c>
       <c r="B601" t="s">
-        <v>1895</v>
+        <v>1864</v>
       </c>
       <c r="C601" t="s">
         <v>802</v>
@@ -19553,11 +20145,11 @@
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A602" s="4" t="s">
-        <v>1870</v>
+      <c r="A602" s="3" t="s">
+        <v>1839</v>
       </c>
       <c r="B602" t="s">
-        <v>1894</v>
+        <v>1863</v>
       </c>
       <c r="C602" t="s">
         <v>802</v>
@@ -19571,10 +20163,10 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>2074</v>
+        <v>2043</v>
       </c>
       <c r="B603" t="s">
-        <v>1877</v>
+        <v>1846</v>
       </c>
       <c r="C603" t="s">
         <v>802</v>
@@ -19588,10 +20180,10 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>1886</v>
+        <v>1855</v>
       </c>
       <c r="B604" t="s">
-        <v>1887</v>
+        <v>1856</v>
       </c>
       <c r="C604" t="s">
         <v>802</v>
@@ -19605,10 +20197,10 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>1889</v>
+        <v>1858</v>
       </c>
       <c r="B605" t="s">
-        <v>1890</v>
+        <v>1859</v>
       </c>
       <c r="C605" t="s">
         <v>802</v>
@@ -19622,10 +20214,10 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>1891</v>
+        <v>1860</v>
       </c>
       <c r="B606" t="s">
-        <v>1892</v>
+        <v>1861</v>
       </c>
       <c r="C606" t="s">
         <v>802</v>
@@ -19639,18 +20231,35 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>1896</v>
+        <v>1865</v>
       </c>
       <c r="B607" t="s">
-        <v>1897</v>
+        <v>1866</v>
       </c>
       <c r="C607" t="s">
-        <v>1898</v>
+        <v>1867</v>
       </c>
       <c r="E607">
         <v>1944</v>
       </c>
       <c r="F607" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C608" t="s">
+        <v>802</v>
+      </c>
+      <c r="E608">
+        <v>1946</v>
+      </c>
+      <c r="F608" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -19673,81 +20282,49 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EC353B-9472-6C41-B69A-ADB0079B268A}">
-  <dimension ref="A1:F4"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18C0A70-D002-0C45-A510-E239EF4FAE1B}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="C4" s="2"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920847D-946C-2D4C-9334-79F517AB3056}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17062239-0C59-4341-B943-F5C1B108BF88}">
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="136.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B2" t="s">
         <v>569</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>607</v>
       </c>
     </row>
@@ -19792,7 +20369,7 @@
       <c r="B8" t="s">
         <v>615</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>617</v>
       </c>
       <c r="D8" t="s">
@@ -19800,7 +20377,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>616</v>
       </c>
     </row>
@@ -19819,1139 +20396,311 @@
         <v>533</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="4" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="4" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="4" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="4" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="4" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B26" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B27" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B28" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B30" s="3" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B31" s="4" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B32" s="4" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="3" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="3" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="3" t="s">
         <v>586</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.bing.com/videos/riverview/relatedvideo?q=plan+9+from+outer+space&amp;&amp;mid=9BE59B27CC3DC29303D29BE59B27CC3DC29303D2&amp;FORM=VRDGAR" xr:uid="{21A364CD-7671-E24D-B8FD-071CD92FB5D6}"/>
-    <hyperlink ref="D4" r:id="rId2" display="https://www.bing.com/videos/riverview/relatedvideo?q=three+stooges+disorder+in+the+court&amp;&amp;mid=1B6D2AB71944253B69D91B6D2AB71944253B69D9&amp;FORM=VAMGZC" xr:uid="{280819EB-2061-354A-A0B5-FC6F999C7B32}"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://www.bing.com/videos/riverview/relatedvideo?q=plan+9+from+outer+space&amp;&amp;mid=9BE59B27CC3DC29303D29BE59B27CC3DC29303D2&amp;FORM=VRDGAR" xr:uid="{FBB698B5-202C-064F-A8C1-A372C73450B7}"/>
+    <hyperlink ref="D4" r:id="rId2" display="https://www.bing.com/videos/riverview/relatedvideo?q=three+stooges+disorder+in+the+court&amp;&amp;mid=1B6D2AB71944253B69D91B6D2AB71944253B69D9&amp;FORM=VAMGZC" xr:uid="{AFBEA9F5-A0C6-174B-904A-472C50C05F34}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61D73BC-D245-FA4B-BDD8-C658F1B5BB4A}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="12"/>
-    <col min="3" max="3" width="22.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>1724</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>1727</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>1728</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>1730</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>1731</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>1732</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>1733</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>1734</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>1735</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>1736</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>1738</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2157E145-3ACC-4C4D-9503-E17E1EFA03F5}">
-  <dimension ref="A2:E81"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EB743D-168A-C34F-BC86-443BFB7A5FF2}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1868</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1945</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1900</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1899</v>
-      </c>
-      <c r="D5" t="s">
-        <v>802</v>
-      </c>
-      <c r="E5">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1901</v>
-      </c>
-      <c r="D6" t="s">
-        <v>802</v>
-      </c>
-      <c r="E6">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1946</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1904</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D9" t="s">
-        <v>802</v>
-      </c>
-      <c r="E9">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>695</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D10" t="s">
-        <v>802</v>
-      </c>
-      <c r="E10">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>1907</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1906</v>
-      </c>
-      <c r="D11" t="s">
-        <v>802</v>
-      </c>
-      <c r="E11">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1947</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D14" t="s">
-        <v>802</v>
-      </c>
-      <c r="E14">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>1910</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1911</v>
-      </c>
-      <c r="D15" t="s">
-        <v>802</v>
-      </c>
-      <c r="E15">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1913</v>
-      </c>
-      <c r="D16" t="s">
-        <v>802</v>
-      </c>
-      <c r="E16">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>1948</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1915</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D19" t="s">
-        <v>802</v>
-      </c>
-      <c r="E19">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D20" t="s">
-        <v>802</v>
-      </c>
-      <c r="E20">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>1917</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D21" t="s">
-        <v>802</v>
-      </c>
-      <c r="E21">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>1949</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1919</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D24" t="s">
-        <v>802</v>
-      </c>
-      <c r="E24">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>1921</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D25" t="s">
-        <v>802</v>
-      </c>
-      <c r="E25">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>1923</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D26" t="s">
-        <v>802</v>
-      </c>
-      <c r="E26">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>1950</v>
-      </c>
-      <c r="B29" t="s">
-        <v>698</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1927</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1928</v>
-      </c>
-      <c r="E29">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>1925</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1926</v>
-      </c>
-      <c r="E30">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>1951</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D34" t="s">
-        <v>802</v>
-      </c>
-      <c r="E34">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>1931</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1933</v>
-      </c>
-      <c r="E35">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>1934</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1935</v>
-      </c>
-      <c r="D36" t="s">
-        <v>802</v>
-      </c>
-      <c r="E36">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>1952</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D39" t="s">
-        <v>802</v>
-      </c>
-      <c r="E39">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>1939</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D40" t="s">
-        <v>802</v>
-      </c>
-      <c r="E40">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>1888</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D41" t="s">
-        <v>802</v>
-      </c>
-      <c r="E41">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>1953</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1941</v>
-      </c>
-      <c r="D44" t="s">
-        <v>802</v>
-      </c>
-      <c r="E44">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1944</v>
-      </c>
-      <c r="D45" t="s">
-        <v>802</v>
-      </c>
-      <c r="E45">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>1946</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E46">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>1954</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D49" t="s">
-        <v>802</v>
-      </c>
-      <c r="E49">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D50" t="s">
-        <v>802</v>
-      </c>
-      <c r="E50">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>1952</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D51" t="s">
-        <v>802</v>
-      </c>
-      <c r="E51">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>1955</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1954</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1953</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1955</v>
-      </c>
-      <c r="E54">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1956</v>
-      </c>
-      <c r="E55">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>1958</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>1956</v>
-      </c>
-      <c r="B59" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1960</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1961</v>
-      </c>
-      <c r="E60">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>1963</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1964</v>
-      </c>
-      <c r="E61">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>1957</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D64" t="s">
-        <v>802</v>
-      </c>
-      <c r="E64">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
-        <v>1975</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1976</v>
-      </c>
-      <c r="D65" t="s">
-        <v>802</v>
-      </c>
-      <c r="E65">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>1977</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D66" t="s">
-        <v>802</v>
-      </c>
-      <c r="E66">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>1958</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1979</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1980</v>
-      </c>
-      <c r="D69" t="s">
-        <v>802</v>
-      </c>
-      <c r="E69">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
-        <v>1981</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1982</v>
-      </c>
-      <c r="D70" t="s">
-        <v>1983</v>
-      </c>
-      <c r="E70">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>1984</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1984</v>
-      </c>
-      <c r="E71">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>1959</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D74" t="s">
-        <v>802</v>
-      </c>
-      <c r="E74">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D75" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E75">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D76" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E76">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>1960</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1992</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1993</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1994</v>
-      </c>
-      <c r="E79">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B80" t="s">
-        <v>1996</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1995</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E80">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B81" t="s">
-        <v>1998</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1999</v>
-      </c>
-      <c r="D81" t="s">
-        <v>802</v>
-      </c>
-      <c r="E81">
-        <v>1960</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7970BF30-B9A3-F44F-A638-FE6B719A79A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65A75A4-CD1B-154C-9F94-F7177853ED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Music Media Type" sheetId="17" r:id="rId1"/>
-    <sheet name="Talk Media Type" sheetId="23" r:id="rId2"/>
-    <sheet name="Promo Media Type" sheetId="24" r:id="rId3"/>
-    <sheet name="Id Media Type" sheetId="25" r:id="rId4"/>
+    <sheet name="List" sheetId="26" r:id="rId1"/>
+    <sheet name="Music Media Type" sheetId="17" r:id="rId2"/>
+    <sheet name="Talk Media Type" sheetId="23" r:id="rId3"/>
+    <sheet name="Promo Media Type" sheetId="24" r:id="rId4"/>
+    <sheet name="Id Media Type" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Music Media Type'!$A$1:$F$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$679</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="1994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="2094">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6128,6 +6129,306 @@
   </si>
   <si>
     <t>Greatest Hits - Orginal Recordings</t>
+  </si>
+  <si>
+    <t>Beyonce</t>
+  </si>
+  <si>
+    <t>Ana Tijoux</t>
+  </si>
+  <si>
+    <t>Pet Shop Boys</t>
+  </si>
+  <si>
+    <t>Radiohead</t>
+  </si>
+  <si>
+    <t>A Tribe Called Quest</t>
+  </si>
+  <si>
+    <t>Suicidal Tendencies</t>
+  </si>
+  <si>
+    <t>Blondie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smashing Pumpkins </t>
+  </si>
+  <si>
+    <t>Ice Cube</t>
+  </si>
+  <si>
+    <t>Wet Leg</t>
+  </si>
+  <si>
+    <t>Joy Division</t>
+  </si>
+  <si>
+    <t>Wolf Alice</t>
+  </si>
+  <si>
+    <t>Nada Surf</t>
+  </si>
+  <si>
+    <t>De La Soul</t>
+  </si>
+  <si>
+    <t>Future Islands</t>
+  </si>
+  <si>
+    <t>Bam Bam</t>
+  </si>
+  <si>
+    <t>Deerhunter</t>
+  </si>
+  <si>
+    <t>Massive Attack</t>
+  </si>
+  <si>
+    <t>Mad Season</t>
+  </si>
+  <si>
+    <t>My Morning Jacket</t>
+  </si>
+  <si>
+    <t>Slowdive</t>
+  </si>
+  <si>
+    <t>George Thorogood</t>
+  </si>
+  <si>
+    <t>Yeah Yeah Yeahs</t>
+  </si>
+  <si>
+    <t>Built To Spill</t>
+  </si>
+  <si>
+    <t>Throwing Muses</t>
+  </si>
+  <si>
+    <t>Hooverphonic</t>
+  </si>
+  <si>
+    <t>Nina Simone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toots and the Maytals </t>
+  </si>
+  <si>
+    <t>Traci Chapman</t>
+  </si>
+  <si>
+    <t>Alexi Murdoch</t>
+  </si>
+  <si>
+    <t>PJ Harvey</t>
+  </si>
+  <si>
+    <t>Frightened Rabbit</t>
+  </si>
+  <si>
+    <t>Portishead</t>
+  </si>
+  <si>
+    <t>Sleater Kinney</t>
+  </si>
+  <si>
+    <t>Sault</t>
+  </si>
+  <si>
+    <t>Fleet Foxes</t>
+  </si>
+  <si>
+    <t>Jeff Buckley</t>
+  </si>
+  <si>
+    <t>Siouxsie and the Banshees</t>
+  </si>
+  <si>
+    <t>Oasis</t>
+  </si>
+  <si>
+    <t>Slint</t>
+  </si>
+  <si>
+    <t>Erykah Badu</t>
+  </si>
+  <si>
+    <t>My Bloody Valentine</t>
+  </si>
+  <si>
+    <t>Franz Ferdinand</t>
+  </si>
+  <si>
+    <t>Eurythmics</t>
+  </si>
+  <si>
+    <t>Tricky</t>
+  </si>
+  <si>
+    <t>Bob Mould</t>
+  </si>
+  <si>
+    <t>Avalanches</t>
+  </si>
+  <si>
+    <t>Run DMC</t>
+  </si>
+  <si>
+    <t>Johnny Cash</t>
+  </si>
+  <si>
+    <t>Kate Bush</t>
+  </si>
+  <si>
+    <t>Sharon Van Etten</t>
+  </si>
+  <si>
+    <t>Iggy and the Stooges</t>
+  </si>
+  <si>
+    <t>George Michael</t>
+  </si>
+  <si>
+    <t>First Aid Kit</t>
+  </si>
+  <si>
+    <t>Talk Talk</t>
+  </si>
+  <si>
+    <t>This Mortal Coil</t>
+  </si>
+  <si>
+    <t>Elbow</t>
+  </si>
+  <si>
+    <t>The War on Drugs</t>
+  </si>
+  <si>
+    <t>Cat Power</t>
+  </si>
+  <si>
+    <t>ZZ Top</t>
+  </si>
+  <si>
+    <t>Joni Mitchell</t>
+  </si>
+  <si>
+    <t>Brandi Carlile</t>
+  </si>
+  <si>
+    <t>Pavement</t>
+  </si>
+  <si>
+    <t>Black Pumas</t>
+  </si>
+  <si>
+    <t>B-52s</t>
+  </si>
+  <si>
+    <t>Anderson. Paak</t>
+  </si>
+  <si>
+    <t>Fiona Apple</t>
+  </si>
+  <si>
+    <t>Gladys Knight &amp; The Pips</t>
+  </si>
+  <si>
+    <t>Tom Tom Club</t>
+  </si>
+  <si>
+    <t>Guns 'n' Roses</t>
+  </si>
+  <si>
+    <t>Jimmy Cliff</t>
+  </si>
+  <si>
+    <t>Beta Band</t>
+  </si>
+  <si>
+    <t>Bill Withers</t>
+  </si>
+  <si>
+    <t>Gary Numan</t>
+  </si>
+  <si>
+    <t>Brad</t>
+  </si>
+  <si>
+    <t>Joan Jett</t>
+  </si>
+  <si>
+    <t>The Replacements</t>
+  </si>
+  <si>
+    <t>Laurie Anderson</t>
+  </si>
+  <si>
+    <t>Janelle Monae</t>
+  </si>
+  <si>
+    <t>Elliott Smith</t>
+  </si>
+  <si>
+    <t>Lauryn Hill</t>
+  </si>
+  <si>
+    <t>Catherine Wheel</t>
+  </si>
+  <si>
+    <t>The Cars</t>
+  </si>
+  <si>
+    <t>Screaming Trees</t>
+  </si>
+  <si>
+    <t>The Cult</t>
+  </si>
+  <si>
+    <t>Arrested Development</t>
+  </si>
+  <si>
+    <t>Kermit the Frog</t>
+  </si>
+  <si>
+    <t>Sufjan Stevens</t>
+  </si>
+  <si>
+    <t>Temple of the Dog</t>
+  </si>
+  <si>
+    <t>Patti Smith</t>
+  </si>
+  <si>
+    <t>The Gits</t>
+  </si>
+  <si>
+    <t>Neutral Milk Hotel</t>
+  </si>
+  <si>
+    <t>Pulp</t>
+  </si>
+  <si>
+    <t>Bob Marley</t>
+  </si>
+  <si>
+    <t>Gnarls Barkley</t>
+  </si>
+  <si>
+    <t>The Specials</t>
+  </si>
+  <si>
+    <t>Grandmaster Flash</t>
+  </si>
+  <si>
+    <t>Idles</t>
+  </si>
+  <si>
+    <t>Motorhead</t>
+  </si>
+  <si>
+    <t>LEFT OFF 268</t>
   </si>
 </sst>
 </file>
@@ -6559,6 +6860,535 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
+  <dimension ref="B1:B103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="1" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2">
+      <c r="B2" s="1" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="1" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="1" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="1" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="1" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="1" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="1" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="1" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="1" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="1" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="1" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="1" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="1" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="1" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="1" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="1" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="1" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="1" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="1" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="1" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
   <dimension ref="A1:F716"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -19131,7 +19961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18C0A70-D002-0C45-A510-E239EF4FAE1B}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -19140,7 +19970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17062239-0C59-4341-B943-F5C1B108BF88}">
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -19545,7 +20375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EB743D-168A-C34F-BC86-443BFB7A5FF2}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65A75A4-CD1B-154C-9F94-F7177853ED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156F834E-741C-4C40-8821-D48CF3022B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="2147">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6428,7 +6428,166 @@
     <t>Motorhead</t>
   </si>
   <si>
-    <t>LEFT OFF 268</t>
+    <t>Childish Gambino</t>
+  </si>
+  <si>
+    <t>Bjork</t>
+  </si>
+  <si>
+    <t>Wolf Parade</t>
+  </si>
+  <si>
+    <t>Black Flag</t>
+  </si>
+  <si>
+    <t>Bomba Estereo</t>
+  </si>
+  <si>
+    <t>Magnetic Fields</t>
+  </si>
+  <si>
+    <t>Cheap Trick</t>
+  </si>
+  <si>
+    <t>Neko Case</t>
+  </si>
+  <si>
+    <t>Public Enemy</t>
+  </si>
+  <si>
+    <t>Bauhaus</t>
+  </si>
+  <si>
+    <t>Lou Reed</t>
+  </si>
+  <si>
+    <t>Christine and the Queens</t>
+  </si>
+  <si>
+    <t>Florence and the Machine</t>
+  </si>
+  <si>
+    <t>Traveling Wilburys</t>
+  </si>
+  <si>
+    <t>Underworld</t>
+  </si>
+  <si>
+    <t>Beastie Boys</t>
+  </si>
+  <si>
+    <t>X Ray Spex</t>
+  </si>
+  <si>
+    <t>Songs: Ohia</t>
+  </si>
+  <si>
+    <t>Big Thief</t>
+  </si>
+  <si>
+    <t>Bon Iver</t>
+  </si>
+  <si>
+    <t>The Sugarcubes</t>
+  </si>
+  <si>
+    <t>Le Tigre</t>
+  </si>
+  <si>
+    <t>Janes Addiction</t>
+  </si>
+  <si>
+    <t>Amy Winehouse</t>
+  </si>
+  <si>
+    <t>The National</t>
+  </si>
+  <si>
+    <t>Cocteau Twins</t>
+  </si>
+  <si>
+    <t>Fela Kuti</t>
+  </si>
+  <si>
+    <t>Al Green</t>
+  </si>
+  <si>
+    <t>The Roots</t>
+  </si>
+  <si>
+    <t>Dee-Lite</t>
+  </si>
+  <si>
+    <t>Blur</t>
+  </si>
+  <si>
+    <t>Iggy Pop</t>
+  </si>
+  <si>
+    <t>Leonard Cohen</t>
+  </si>
+  <si>
+    <t>Stone Roses</t>
+  </si>
+  <si>
+    <t>Violent Femmes</t>
+  </si>
+  <si>
+    <t>The Waterboys</t>
+  </si>
+  <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>Big Star</t>
+  </si>
+  <si>
+    <t>Modern Lovers</t>
+  </si>
+  <si>
+    <t>Parliament</t>
+  </si>
+  <si>
+    <t>Earth Wind and Fire</t>
+  </si>
+  <si>
+    <t>The Knife</t>
+  </si>
+  <si>
+    <t>Animal Collective</t>
+  </si>
+  <si>
+    <t>TV on the Radio</t>
+  </si>
+  <si>
+    <t>Mother Love Bone</t>
+  </si>
+  <si>
+    <t>The Walkmen</t>
+  </si>
+  <si>
+    <t>Robyn</t>
+  </si>
+  <si>
+    <t>The Verve</t>
+  </si>
+  <si>
+    <t>Mountain Goats</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Bikini Kill</t>
+  </si>
+  <si>
+    <t>Television</t>
+  </si>
+  <si>
+    <t>Mazzy Star</t>
+  </si>
+  <si>
+    <t>Fugazi</t>
   </si>
 </sst>
 </file>
@@ -6861,365 +7020,363 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B1:B103"/>
+  <dimension ref="B1:B157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="1" t="s">
-        <v>1994</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="1" t="s">
-        <v>1995</v>
+      <c r="B2" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="1" t="s">
-        <v>1996</v>
+      <c r="B3" t="s">
+        <v>2120</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="1" t="s">
-        <v>1997</v>
+      <c r="B4" t="s">
+        <v>2023</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="1" t="s">
-        <v>1998</v>
+      <c r="B5" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="1" t="s">
-        <v>1999</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="1" t="s">
-        <v>2000</v>
+      <c r="B7" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="1" t="s">
-        <v>2001</v>
+      <c r="B8" t="s">
+        <v>2135</v>
       </c>
     </row>
     <row r="9" spans="2:2">
-      <c r="B9" s="1" t="s">
-        <v>2002</v>
+      <c r="B9" t="s">
+        <v>2079</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="1" t="s">
-        <v>2003</v>
+      <c r="B10" t="s">
+        <v>2040</v>
       </c>
     </row>
     <row r="11" spans="2:2">
-      <c r="B11" s="1" t="s">
-        <v>2004</v>
+      <c r="B11" t="s">
+        <v>2058</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="1" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="13" spans="2:2">
-      <c r="B13" s="1" t="s">
-        <v>2006</v>
+      <c r="B13" t="s">
+        <v>2102</v>
       </c>
     </row>
     <row r="14" spans="2:2">
-      <c r="B14" s="1" t="s">
-        <v>2007</v>
+      <c r="B14" t="s">
+        <v>2108</v>
       </c>
     </row>
     <row r="15" spans="2:2">
-      <c r="B15" s="1" t="s">
-        <v>2008</v>
+      <c r="B15" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="1" t="s">
-        <v>2009</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="1" t="s">
-        <v>2010</v>
+      <c r="B17" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="1" t="s">
-        <v>2011</v>
+      <c r="B18" t="s">
+        <v>2111</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="1" t="s">
-        <v>2012</v>
+      <c r="B19" t="s">
+        <v>2143</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="1" t="s">
-        <v>2013</v>
+      <c r="B20" t="s">
+        <v>2066</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="1" t="s">
-        <v>2014</v>
+      <c r="B21" t="s">
+        <v>2094</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2015</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2016</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>2017</v>
+      <c r="B24" s="1" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2018</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2019</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2020</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2021</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>2022</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2023</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>2024</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2025</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>2026</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2027</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2028</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>2029</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2030</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>2031</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" t="s">
-        <v>2032</v>
+      <c r="B39" s="1" t="s">
+        <v>2007</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2033</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" t="s">
-        <v>2034</v>
+      <c r="B41" s="1" t="s">
+        <v>2010</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2035</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>2036</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2037</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>2038</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2040</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2041</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2043</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>2044</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2045</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2046</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>2047</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" t="s">
-        <v>2048</v>
+      <c r="B55" s="1" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>2049</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>2051</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>2052</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2053</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2054</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>1998</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2055</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64" t="s">
-        <v>2056</v>
+      <c r="B64" s="1" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2057</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2058</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2059</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>2060</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>2061</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2062</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>2063</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="72" spans="2:2">
@@ -7229,32 +7386,32 @@
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2066</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2067</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" t="s">
-        <v>2068</v>
+      <c r="B76" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>2069</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="79" spans="2:2">
@@ -7264,125 +7421,398 @@
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>2073</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>2074</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>2043</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2075</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="85" spans="2:2">
-      <c r="B85" t="s">
-        <v>2076</v>
+      <c r="B85" s="1" t="s">
+        <v>2012</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2077</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" t="s">
-        <v>2078</v>
+      <c r="B87" s="1" t="s">
+        <v>2011</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2079</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2080</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>1577</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2081</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>2083</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>2084</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" t="s">
-        <v>2085</v>
+      <c r="B95" s="1" t="s">
+        <v>2013</v>
       </c>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" t="s">
-        <v>2086</v>
+      <c r="B96" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2087</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>2089</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>2090</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>2091</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>2092</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>2093</v>
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="1" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="1" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="1" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="1" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="1" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" s="1" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="1" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" t="s">
+        <v>2053</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B157">
+    <sortCondition ref="B1:B157"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156F834E-741C-4C40-8821-D48CF3022B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF1525-EB15-A248-AD7D-39BCAFD5483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="2186">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6589,12 +6589,129 @@
   <si>
     <t>Fugazi</t>
   </si>
+  <si>
+    <t>Muddy Waters</t>
+  </si>
+  <si>
+    <t>Ella Fitzgerald</t>
+  </si>
+  <si>
+    <t>Johnnie Ray</t>
+  </si>
+  <si>
+    <t>Dinah Washington</t>
+  </si>
+  <si>
+    <t>Hank Williams</t>
+  </si>
+  <si>
+    <t>Ray Charles</t>
+  </si>
+  <si>
+    <t>Tony Bennett</t>
+  </si>
+  <si>
+    <t>Julie London</t>
+  </si>
+  <si>
+    <t>Buddy Holly</t>
+  </si>
+  <si>
+    <t>Peggy Lee</t>
+  </si>
+  <si>
+    <t>Paul Anka</t>
+  </si>
+  <si>
+    <t>Santo &amp; Johnny</t>
+  </si>
+  <si>
+    <t>The Isley Brothers</t>
+  </si>
+  <si>
+    <t>Etta James</t>
+  </si>
+  <si>
+    <t>Marty Robbins</t>
+  </si>
+  <si>
+    <t>The Chieftains</t>
+  </si>
+  <si>
+    <t>Édith Piaf</t>
+  </si>
+  <si>
+    <t>The Marvelettes</t>
+  </si>
+  <si>
+    <t>Dion</t>
+  </si>
+  <si>
+    <t>Dick Dale</t>
+  </si>
+  <si>
+    <t>The Ronettes</t>
+  </si>
+  <si>
+    <t>Roy Orbison</t>
+  </si>
+  <si>
+    <t>Steppenwolf</t>
+  </si>
+  <si>
+    <t>Led Zepellin</t>
+  </si>
+  <si>
+    <t>Black Sabbath</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Eagles</t>
+  </si>
+  <si>
+    <t>Lynyrd Skynyrd</t>
+  </si>
+  <si>
+    <t>Bob Marley &amp; The Wailers</t>
+  </si>
+  <si>
+    <t>Blue Oyster Cult</t>
+  </si>
+  <si>
+    <t>Ozzy Osbourne</t>
+  </si>
+  <si>
+    <t>Dexys Midnight Runners</t>
+  </si>
+  <si>
+    <t>Cindy Lauper</t>
+  </si>
+  <si>
+    <t>a-ha</t>
+  </si>
+  <si>
+    <t>The Outfield</t>
+  </si>
+  <si>
+    <t>Chris Isaak</t>
+  </si>
+  <si>
+    <t>The Cardigans</t>
+  </si>
+  <si>
+    <t>Smash Mouth</t>
+  </si>
+  <si>
+    <t>Eminem</t>
+  </si>
+  <si>
+    <t>LEFT OFF 2002</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6646,6 +6763,12 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6667,7 +6790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6686,6 +6809,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7020,7 +7144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B1:B157"/>
+  <dimension ref="B1:B200"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
@@ -7807,6 +7931,221 @@
     <row r="157" spans="2:2">
       <c r="B157" t="s">
         <v>2053</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" t="s">
+        <v>2185</v>
       </c>
     </row>
   </sheetData>
@@ -7820,7 +8159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F716"/>
+  <dimension ref="A1:F717"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -17223,7 +17562,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>42</v>
+        <v>2172</v>
       </c>
       <c r="B532" t="s">
         <v>1612</v>
@@ -20371,6 +20710,9 @@
       <c r="F716" t="s">
         <v>970</v>
       </c>
+    </row>
+    <row r="717" spans="1:6" ht="17">
+      <c r="A717" s="12"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A53:E436">

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF1525-EB15-A248-AD7D-39BCAFD5483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4584C1-E457-EC40-BB09-E2FFC9AF2306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="26" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$679</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="2186">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6131,21 +6131,12 @@
     <t>Greatest Hits - Orginal Recordings</t>
   </si>
   <si>
-    <t>Beyonce</t>
-  </si>
-  <si>
-    <t>Ana Tijoux</t>
-  </si>
-  <si>
     <t>Pet Shop Boys</t>
   </si>
   <si>
     <t>Radiohead</t>
   </si>
   <si>
-    <t>A Tribe Called Quest</t>
-  </si>
-  <si>
     <t>Suicidal Tendencies</t>
   </si>
   <si>
@@ -6176,9 +6167,6 @@
     <t>Future Islands</t>
   </si>
   <si>
-    <t>Bam Bam</t>
-  </si>
-  <si>
     <t>Deerhunter</t>
   </si>
   <si>
@@ -6218,9 +6206,6 @@
     <t>Traci Chapman</t>
   </si>
   <si>
-    <t>Alexi Murdoch</t>
-  </si>
-  <si>
     <t>PJ Harvey</t>
   </si>
   <si>
@@ -6269,9 +6254,6 @@
     <t>Bob Mould</t>
   </si>
   <si>
-    <t>Avalanches</t>
-  </si>
-  <si>
     <t>Run DMC</t>
   </si>
   <si>
@@ -6323,12 +6305,6 @@
     <t>Black Pumas</t>
   </si>
   <si>
-    <t>B-52s</t>
-  </si>
-  <si>
-    <t>Anderson. Paak</t>
-  </si>
-  <si>
     <t>Fiona Apple</t>
   </si>
   <si>
@@ -6386,9 +6362,6 @@
     <t>The Cult</t>
   </si>
   <si>
-    <t>Arrested Development</t>
-  </si>
-  <si>
     <t>Kermit the Frog</t>
   </si>
   <si>
@@ -6455,9 +6428,6 @@
     <t>Public Enemy</t>
   </si>
   <si>
-    <t>Bauhaus</t>
-  </si>
-  <si>
     <t>Lou Reed</t>
   </si>
   <si>
@@ -6473,9 +6443,6 @@
     <t>Underworld</t>
   </si>
   <si>
-    <t>Beastie Boys</t>
-  </si>
-  <si>
     <t>X Ray Spex</t>
   </si>
   <si>
@@ -6509,9 +6476,6 @@
     <t>Fela Kuti</t>
   </si>
   <si>
-    <t>Al Green</t>
-  </si>
-  <si>
     <t>The Roots</t>
   </si>
   <si>
@@ -6554,9 +6518,6 @@
     <t>The Knife</t>
   </si>
   <si>
-    <t>Animal Collective</t>
-  </si>
-  <si>
     <t>TV on the Radio</t>
   </si>
   <si>
@@ -6578,9 +6539,6 @@
     <t>MIA</t>
   </si>
   <si>
-    <t>Bikini Kill</t>
-  </si>
-  <si>
     <t>Television</t>
   </si>
   <si>
@@ -6704,14 +6662,56 @@
     <t>Eminem</t>
   </si>
   <si>
-    <t>LEFT OFF 2002</t>
+    <t>Britney Spears</t>
+  </si>
+  <si>
+    <t>Keane</t>
+  </si>
+  <si>
+    <t>Plain White T's</t>
+  </si>
+  <si>
+    <t>Take On Me</t>
+  </si>
+  <si>
+    <t>Hunting High and Low</t>
+  </si>
+  <si>
+    <t>You Know I'm No Good</t>
+  </si>
+  <si>
+    <t>Back to Black</t>
+  </si>
+  <si>
+    <t>Planet Clare</t>
+  </si>
+  <si>
+    <t>The B-52s</t>
+  </si>
+  <si>
+    <t>Dry the Rain</t>
+  </si>
+  <si>
+    <t>The Three Eps</t>
+  </si>
+  <si>
+    <t>September Gurls</t>
+  </si>
+  <si>
+    <t>Radio City</t>
+  </si>
+  <si>
+    <t>Velvet Ring</t>
+  </si>
+  <si>
+    <t>Masterpiece</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6763,12 +6763,6 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6790,7 +6784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6809,7 +6803,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7144,1013 +7137,923 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B1:B200"/>
+  <dimension ref="B2:B183"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="1"/>
-    </row>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>1998</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2120</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2023</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2116</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="1" t="s">
-        <v>1995</v>
+      <c r="B6" t="s">
+        <v>2157</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>2059</v>
+      <c r="B7" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2135</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2079</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2040</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2058</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="12" spans="2:2">
-      <c r="B12" s="1" t="s">
-        <v>2009</v>
+      <c r="B12" t="s">
+        <v>2160</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2102</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2108</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2065</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="16" spans="2:2">
-      <c r="B16" s="1" t="s">
-        <v>1994</v>
+      <c r="B16" t="s">
+        <v>2060</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2130</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2111</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>2066</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2094</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2096</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2057</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="1" t="s">
-        <v>2000</v>
+      <c r="B24" t="s">
+        <v>2084</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2123</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2087</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2039</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" t="s">
-        <v>2112</v>
+      <c r="B29" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2068</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>2055</v>
+      <c r="B31" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2017</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>2052</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2075</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2099</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>2093</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2104</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>2118</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="1" t="s">
-        <v>2007</v>
+      <c r="B39" t="s">
+        <v>2134</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2122</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" s="1" t="s">
-        <v>2010</v>
+      <c r="B41" t="s">
+        <v>2170</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2133</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>2050</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2073</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>2037</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2119</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2060</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2047</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2029</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>2105</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2036</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2025</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="54" spans="2:2">
-      <c r="B54" t="s">
-        <v>2146</v>
+      <c r="B54" s="1" t="s">
+        <v>2005</v>
       </c>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" s="1" t="s">
-        <v>2008</v>
+      <c r="B55" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>2067</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>2046</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>2015</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>2061</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2090</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2063</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" s="1" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2091</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2045</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2124</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2115</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>2064</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2069</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2042</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2054</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="1" t="s">
-        <v>2004</v>
+      <c r="B76" t="s">
+        <v>2048</v>
       </c>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" t="s">
-        <v>2043</v>
+      <c r="B77" s="1" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>2080</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>2071</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2074</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>2114</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>2125</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>2103</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2129</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="85" spans="2:2">
-      <c r="B85" s="1" t="s">
-        <v>2012</v>
+      <c r="B85" t="s">
+        <v>2156</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2098</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" s="1" t="s">
-        <v>2011</v>
+      <c r="B87" t="s">
+        <v>2093</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2145</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2142</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="90" spans="2:2">
-      <c r="B90" t="s">
-        <v>2131</v>
+      <c r="B90" s="1" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2137</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>2092</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="93" spans="2:2">
-      <c r="B93" t="s">
-        <v>2141</v>
+      <c r="B93" s="1" t="s">
+        <v>2007</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>2035</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" s="1" t="s">
-        <v>2013</v>
+      <c r="B95" t="s">
+        <v>2129</v>
       </c>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" s="1" t="s">
-        <v>2006</v>
+      <c r="B96" t="s">
+        <v>2119</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2100</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>2020</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>2032</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>2132</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" t="s">
-        <v>2083</v>
+      <c r="B102" s="1" t="s">
+        <v>2009</v>
       </c>
     </row>
     <row r="103" spans="2:2">
-      <c r="B103" t="s">
-        <v>2056</v>
+      <c r="B103" s="1" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="104" spans="2:2">
-      <c r="B104" s="1" t="s">
-        <v>1996</v>
+      <c r="B104" t="s">
+        <v>2091</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>2024</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>2026</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>2101</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>2086</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="109" spans="2:2">
-      <c r="B109" s="1" t="s">
-        <v>1997</v>
+      <c r="B109" t="s">
+        <v>2162</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>2139</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>2041</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>2028</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>2077</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>2044</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" t="s">
-        <v>2031</v>
+      <c r="B115" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>2027</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>2033</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="1" t="s">
-        <v>2014</v>
+      <c r="B118" t="s">
+        <v>2021</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="1" t="s">
-        <v>2001</v>
+      <c r="B119" t="s">
+        <v>2092</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>2110</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" t="s">
-        <v>2126</v>
+      <c r="B121" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>2081</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="1" t="s">
-        <v>1999</v>
+      <c r="B123" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>2048</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>2144</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>2082</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>999</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>2076</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>2078</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>2084</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>2134</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>2117</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" t="s">
-        <v>2070</v>
+      <c r="B133" s="1" t="s">
+        <v>2010</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>2121</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="135" spans="2:2">
-      <c r="B135" t="s">
-        <v>2089</v>
+      <c r="B135" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>2113</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>2140</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>2138</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>2051</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="140" spans="2:2">
-      <c r="B140" t="s">
-        <v>2128</v>
+      <c r="B140" s="1" t="s">
+        <v>1996</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>2018</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>2062</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>2021</v>
+        <v>999</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>2022</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>2106</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>2038</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>2136</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>2107</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>2127</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="151" spans="2:2">
-      <c r="B151" s="1" t="s">
-        <v>2003</v>
+      <c r="B151" t="s">
+        <v>2145</v>
       </c>
     </row>
     <row r="152" spans="2:2">
-      <c r="B152" s="1" t="s">
-        <v>2005</v>
+      <c r="B152" t="s">
+        <v>2122</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>2095</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>2016</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>1577</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>2053</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>2147</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>2148</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>2149</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>2150</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>2151</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>2152</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>2153</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>2154</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>2155</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>2156</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>2157</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>2158</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>1416</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>2159</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>2160</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>2161</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>2162</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>2163</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="176" spans="2:2">
-      <c r="B176" t="s">
-        <v>2164</v>
+      <c r="B176" s="1" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="177" spans="2:2">
-      <c r="B177" t="s">
-        <v>2165</v>
+      <c r="B177" s="1" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>2166</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>2020</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>2167</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>2168</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>2169</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="183" spans="2:2">
-      <c r="B183" t="s">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="184" spans="2:2">
-      <c r="B184" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2">
-      <c r="B185" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="186" spans="2:2">
-      <c r="B186" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="187" spans="2:2">
-      <c r="B187" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2">
-      <c r="B188" t="s">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="190" spans="2:2">
-      <c r="B190" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="192" spans="2:2">
-      <c r="B192" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" t="s">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" t="s">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="199" spans="2:2">
-      <c r="B199" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" t="s">
-        <v>2185</v>
-      </c>
+      <c r="B183" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B157">
-    <sortCondition ref="B1:B157"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B183">
+    <sortCondition ref="B1:B183"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8159,7 +8062,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F717"/>
+  <dimension ref="A1:F722"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -17562,7 +17465,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2172</v>
+        <v>2158</v>
       </c>
       <c r="B532" t="s">
         <v>1612</v>
@@ -20711,8 +20614,107 @@
         <v>970</v>
       </c>
     </row>
-    <row r="717" spans="1:6" ht="17">
-      <c r="A717" s="12"/>
+    <row r="717" spans="1:6">
+      <c r="A717" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B717" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C717" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E717">
+        <v>1985</v>
+      </c>
+      <c r="F717" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6">
+      <c r="A718" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B718" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C718" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E718">
+        <v>2006</v>
+      </c>
+      <c r="F718" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6">
+      <c r="A719" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B719" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C719" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E719">
+        <v>1979</v>
+      </c>
+      <c r="F719" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6">
+      <c r="A720" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B720" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C720" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E720">
+        <v>1997</v>
+      </c>
+      <c r="F720" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6">
+      <c r="A721" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B721" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C721" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E721">
+        <v>1974</v>
+      </c>
+      <c r="F721" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6">
+      <c r="A722" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B722" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C722" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E722">
+        <v>2016</v>
+      </c>
+      <c r="F722" t="s">
+        <v>969</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A53:E436">

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4584C1-E457-EC40-BB09-E2FFC9AF2306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F152B1E-F8A8-8A46-8B46-C72ABC9A0774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="2204">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -3423,9 +3423,6 @@
     <t>Don’t Dream It’s Over</t>
   </si>
   <si>
-    <t>Blue Öyster Cult</t>
-  </si>
-  <si>
     <t>(Don’t Fear) The Reaper</t>
   </si>
   <si>
@@ -6188,9 +6185,6 @@
     <t>Yeah Yeah Yeahs</t>
   </si>
   <si>
-    <t>Built To Spill</t>
-  </si>
-  <si>
     <t>Throwing Muses</t>
   </si>
   <si>
@@ -6287,9 +6281,6 @@
     <t>The War on Drugs</t>
   </si>
   <si>
-    <t>Cat Power</t>
-  </si>
-  <si>
     <t>ZZ Top</t>
   </si>
   <si>
@@ -6383,9 +6374,6 @@
     <t>Pulp</t>
   </si>
   <si>
-    <t>Bob Marley</t>
-  </si>
-  <si>
     <t>Gnarls Barkley</t>
   </si>
   <si>
@@ -6404,18 +6392,9 @@
     <t>Childish Gambino</t>
   </si>
   <si>
-    <t>Bjork</t>
-  </si>
-  <si>
     <t>Wolf Parade</t>
   </si>
   <si>
-    <t>Black Flag</t>
-  </si>
-  <si>
-    <t>Bomba Estereo</t>
-  </si>
-  <si>
     <t>Magnetic Fields</t>
   </si>
   <si>
@@ -6705,6 +6684,81 @@
   </si>
   <si>
     <t>Masterpiece</t>
+  </si>
+  <si>
+    <t>Lean on Me</t>
+  </si>
+  <si>
+    <t>Still Bill</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Crazy Train</t>
+  </si>
+  <si>
+    <t>Blizzard of Ozz</t>
+  </si>
+  <si>
+    <t>Heart of Glass</t>
+  </si>
+  <si>
+    <t>Parallel Lines</t>
+  </si>
+  <si>
+    <t>Song 2</t>
+  </si>
+  <si>
+    <t>One Love/People Get Ready</t>
+  </si>
+  <si>
+    <t>Exodus</t>
+  </si>
+  <si>
+    <t>See a Little Light</t>
+  </si>
+  <si>
+    <t>Workbook</t>
+  </si>
+  <si>
+    <t>Holocene</t>
+  </si>
+  <si>
+    <t>Bon Iver, Bon Iver 2011</t>
+  </si>
+  <si>
+    <t>The Day Brings</t>
+  </si>
+  <si>
+    <t>Interiors</t>
+  </si>
+  <si>
+    <t>The Story</t>
+  </si>
+  <si>
+    <t>Born to Make You Happy</t>
+  </si>
+  <si>
+    <t>…Baby One More Time</t>
+  </si>
+  <si>
+    <t>Oh Boy!</t>
+  </si>
+  <si>
+    <t>20 Golden Greats</t>
+  </si>
+  <si>
+    <t>Crank</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>The Flame</t>
+  </si>
+  <si>
+    <t>Lap of Luxury</t>
   </si>
 </sst>
 </file>
@@ -7137,30 +7191,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B2:B183"/>
+  <dimension ref="B3:B162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" t="s">
-        <v>2058</v>
-      </c>
-    </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2087</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2051</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -7169,891 +7218,786 @@
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="1" t="s">
-        <v>1997</v>
+      <c r="B7" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>1997</v>
+      <c r="B8" s="1" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2161</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" t="s">
-        <v>2111</v>
+      <c r="B10" s="1" t="s">
+        <v>2005</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2078</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2160</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2034</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2088</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2101</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2060</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2171</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2141</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>2013</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2046</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2067</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2090</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2084</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2167</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2094</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2164</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2107</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" s="1" t="s">
-        <v>2004</v>
+      <c r="B29" t="s">
+        <v>2088</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2110</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" s="1" t="s">
-        <v>2006</v>
+      <c r="B31" t="s">
+        <v>2018</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2163</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" t="s">
-        <v>2152</v>
+      <c r="B33" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2136</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2151</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>2121</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2149</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>2044</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>2134</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2065</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2170</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2029</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="43" spans="2:2">
-      <c r="B43" t="s">
-        <v>2146</v>
+      <c r="B43" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2032</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2052</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2041</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2024</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2095</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>2031</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2020</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2132</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="54" spans="2:2">
-      <c r="B54" s="1" t="s">
-        <v>2005</v>
+      <c r="B54" t="s">
+        <v>2034</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>2059</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" t="s">
-        <v>2040</v>
+      <c r="B56" s="1" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>2011</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>2053</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>2079</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2081</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2055</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2137</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2015</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64" s="1" t="s">
-        <v>1999</v>
+      <c r="B64" t="s">
+        <v>2149</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2082</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2039</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2112</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>2064</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" t="s">
-        <v>2064</v>
+      <c r="B69" s="1" t="s">
+        <v>2007</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2104</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>2025</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" t="s">
-        <v>2056</v>
+      <c r="B72" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2061</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2135</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2036</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>2048</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" s="1" t="s">
-        <v>2001</v>
+      <c r="B77" t="s">
+        <v>2079</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>2140</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>2037</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2172</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" t="s">
-        <v>2071</v>
+      <c r="B81" s="1" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" t="s">
-        <v>2063</v>
+      <c r="B82" s="1" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>2066</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2103</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>2156</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2113</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>2093</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="90" spans="2:2">
-      <c r="B90" s="1" t="s">
-        <v>2008</v>
+      <c r="B90" t="s">
+        <v>2071</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2089</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>2147</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="93" spans="2:2">
-      <c r="B93" s="1" t="s">
-        <v>2007</v>
+      <c r="B93" t="s">
+        <v>2135</v>
       </c>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" t="s">
-        <v>2131</v>
+      <c r="B94" s="1" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>2129</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>2119</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2124</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>2128</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="100" spans="2:2">
-      <c r="B100" t="s">
-        <v>2133</v>
+      <c r="B100" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>2030</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="1" t="s">
-        <v>2009</v>
+      <c r="B102" t="s">
+        <v>2119</v>
       </c>
     </row>
     <row r="103" spans="2:2">
-      <c r="B103" s="1" t="s">
-        <v>2003</v>
+      <c r="B103" t="s">
+        <v>2147</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>2091</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>2076</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>2016</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>2027</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>2162</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>2120</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>2074</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" t="s">
-        <v>2143</v>
+      <c r="B112" s="1" t="s">
+        <v>2009</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>2050</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" t="s">
-        <v>2142</v>
+      <c r="B114" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="1" t="s">
-        <v>1994</v>
+      <c r="B115" t="s">
+        <v>2092</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>2019</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>2173</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>2021</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" t="s">
-        <v>2092</v>
+      <c r="B119" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>2077</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="1" t="s">
-        <v>1995</v>
+      <c r="B121" t="s">
+        <v>2123</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>2138</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>2126</v>
+        <v>999</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>2154</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>2035</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>2023</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>2069</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>2038</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>2026</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>2022</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>2028</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" s="1" t="s">
-        <v>2010</v>
+      <c r="B133" t="s">
+        <v>2099</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>2169</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="135" spans="2:2">
-      <c r="B135" s="1" t="s">
-        <v>1998</v>
+      <c r="B135" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>2099</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>2155</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>2114</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>2072</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="140" spans="2:2">
-      <c r="B140" s="1" t="s">
-        <v>1996</v>
+      <c r="B140" t="s">
+        <v>2120</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>2042</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>2130</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>2073</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>999</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>2168</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>2068</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>2148</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>2070</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>1416</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>2075</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>2145</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>2122</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>2150</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="155" spans="2:2">
-      <c r="B155" t="s">
-        <v>2166</v>
+      <c r="B155" s="1" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="156" spans="2:2">
-      <c r="B156" t="s">
-        <v>2062</v>
+      <c r="B156" s="1" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>2153</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>2109</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>2080</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>2102</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>2127</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2">
-      <c r="B163" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2">
-      <c r="B164" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="165" spans="2:2">
-      <c r="B165" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2">
-      <c r="B166" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2">
-      <c r="B167" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2">
-      <c r="B168" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="169" spans="2:2">
-      <c r="B169" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="170" spans="2:2">
-      <c r="B170" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2">
-      <c r="B173" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2">
-      <c r="B174" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2">
-      <c r="B175" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="1" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="1" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2">
-      <c r="B178" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="179" spans="2:2">
-      <c r="B179" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="180" spans="2:2">
-      <c r="B180" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2">
-      <c r="B181" t="s">
-        <v>1577</v>
-      </c>
-    </row>
-    <row r="182" spans="2:2">
-      <c r="B182" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="183" spans="2:2">
-      <c r="B183" s="1"/>
+      <c r="B162" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B183">
-    <sortCondition ref="B1:B183"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B162">
+    <sortCondition ref="B1:B162"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8062,7 +8006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F722"/>
+  <dimension ref="A1:F736"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -10436,10 +10380,10 @@
         <v>281</v>
       </c>
       <c r="B136" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C136" t="s">
         <v>1795</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1796</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1">
@@ -10454,10 +10398,10 @@
         <v>111</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C137" t="s">
         <v>1411</v>
-      </c>
-      <c r="C137" t="s">
-        <v>1412</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1">
@@ -10508,7 +10452,7 @@
         <v>123</v>
       </c>
       <c r="B140" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C140" t="s">
         <v>759</v>
@@ -10526,10 +10470,10 @@
         <v>126</v>
       </c>
       <c r="B141" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C141" t="s">
         <v>1413</v>
-      </c>
-      <c r="C141" t="s">
-        <v>1414</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1">
@@ -13292,13 +13236,13 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B295" t="s">
         <v>1119</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" s="1" t="s">
         <v>1120</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>1121</v>
       </c>
       <c r="D295" s="1"/>
       <c r="E295" s="1">
@@ -13310,13 +13254,13 @@
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B296" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="D296" s="1"/>
       <c r="E296" s="1">
@@ -13328,13 +13272,13 @@
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C297" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>1127</v>
       </c>
       <c r="D297" s="1"/>
       <c r="E297" s="1">
@@ -13346,13 +13290,13 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B298" t="s">
         <v>1128</v>
       </c>
-      <c r="B298" t="s">
+      <c r="C298" s="1" t="s">
         <v>1129</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>1130</v>
       </c>
       <c r="D298" s="1"/>
       <c r="E298" s="1">
@@ -13367,10 +13311,10 @@
         <v>104</v>
       </c>
       <c r="B299" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C299" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D299" s="1"/>
       <c r="E299" s="1">
@@ -13385,10 +13329,10 @@
         <v>120</v>
       </c>
       <c r="B300" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C300" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="D300" s="1"/>
       <c r="E300" s="1">
@@ -13400,13 +13344,13 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B301" t="s">
         <v>1135</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" s="1" t="s">
         <v>1136</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>1137</v>
       </c>
       <c r="D301" s="1"/>
       <c r="E301" s="1">
@@ -13421,10 +13365,10 @@
         <v>294</v>
       </c>
       <c r="B302" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C302" t="s">
         <v>1138</v>
-      </c>
-      <c r="C302" t="s">
-        <v>1139</v>
       </c>
       <c r="D302" s="1"/>
       <c r="E302" s="1">
@@ -13436,13 +13380,13 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B303" t="s">
         <v>1140</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" t="s">
         <v>1141</v>
-      </c>
-      <c r="C303" t="s">
-        <v>1142</v>
       </c>
       <c r="D303" s="1"/>
       <c r="E303" s="1">
@@ -13454,13 +13398,13 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B304" t="s">
         <v>1143</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C304" t="s">
         <v>1144</v>
-      </c>
-      <c r="C304" t="s">
-        <v>1145</v>
       </c>
       <c r="D304" s="1"/>
       <c r="E304" s="1">
@@ -13472,13 +13416,13 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B305" t="s">
         <v>1146</v>
       </c>
-      <c r="B305" t="s">
-        <v>1147</v>
-      </c>
       <c r="C305" s="10" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E305" s="1">
         <v>1995</v>
@@ -13492,10 +13436,10 @@
         <v>137</v>
       </c>
       <c r="B306" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C306" t="s">
         <v>1148</v>
-      </c>
-      <c r="C306" t="s">
-        <v>1149</v>
       </c>
       <c r="D306" s="1"/>
       <c r="E306" s="1">
@@ -13525,13 +13469,13 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B308" t="s">
         <v>686</v>
       </c>
       <c r="C308" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D308" s="1"/>
       <c r="E308" s="1">
@@ -13543,13 +13487,13 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B309" t="s">
         <v>1152</v>
       </c>
-      <c r="B309" t="s">
-        <v>1153</v>
-      </c>
       <c r="C309" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="1">
@@ -13561,13 +13505,13 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C310" t="s">
         <v>1154</v>
-      </c>
-      <c r="B310" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C310" t="s">
-        <v>1155</v>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="1">
@@ -13579,13 +13523,13 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C311" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="B311" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>1159</v>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="1">
@@ -13597,13 +13541,13 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B312" t="s">
         <v>1160</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C312" t="s">
         <v>1161</v>
-      </c>
-      <c r="C312" t="s">
-        <v>1162</v>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="1">
@@ -13615,13 +13559,13 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B313" t="s">
         <v>1163</v>
       </c>
-      <c r="B313" t="s">
+      <c r="C313" t="s">
         <v>1164</v>
-      </c>
-      <c r="C313" t="s">
-        <v>1165</v>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="1">
@@ -13633,13 +13577,13 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B314" t="s">
         <v>1166</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C314" s="1" t="s">
         <v>1167</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>1168</v>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="1">
@@ -13651,13 +13595,13 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B315" t="s">
         <v>1169</v>
       </c>
-      <c r="B315" t="s">
+      <c r="C315" t="s">
         <v>1170</v>
-      </c>
-      <c r="C315" t="s">
-        <v>1171</v>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="1">
@@ -13669,13 +13613,13 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C316" s="1" t="s">
         <v>1172</v>
-      </c>
-      <c r="B316" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>1173</v>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="1">
@@ -13690,10 +13634,10 @@
         <v>573</v>
       </c>
       <c r="B317" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C317" t="s">
         <v>1174</v>
-      </c>
-      <c r="C317" t="s">
-        <v>1175</v>
       </c>
       <c r="D317" s="1"/>
       <c r="E317" s="1">
@@ -13705,13 +13649,13 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C318" t="s">
         <v>1177</v>
-      </c>
-      <c r="B318" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C318" t="s">
-        <v>1178</v>
       </c>
       <c r="D318" s="1"/>
       <c r="E318" s="1">
@@ -13726,10 +13670,10 @@
         <v>27</v>
       </c>
       <c r="B319" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C319" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="D319" s="1"/>
       <c r="E319" s="1">
@@ -13741,13 +13685,13 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B320" t="s">
         <v>1181</v>
       </c>
-      <c r="B320" t="s">
-        <v>1182</v>
-      </c>
       <c r="C320" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D320" s="1"/>
       <c r="E320" s="1">
@@ -13759,13 +13703,13 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B321" t="s">
         <v>1183</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C321" s="1" t="s">
         <v>1184</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>1185</v>
       </c>
       <c r="D321" s="1"/>
       <c r="E321" s="1">
@@ -13777,13 +13721,13 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B322" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C322" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>1187</v>
       </c>
       <c r="D322" s="1"/>
       <c r="E322" s="1">
@@ -13795,13 +13739,13 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B323" t="s">
         <v>1188</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323" s="1" t="s">
         <v>1189</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>1190</v>
       </c>
       <c r="D323" s="1"/>
       <c r="E323" s="1">
@@ -13813,13 +13757,13 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B324" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C324" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D324" s="1"/>
       <c r="E324" s="1">
@@ -13831,13 +13775,13 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C325" t="s">
         <v>1193</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C325" t="s">
-        <v>1194</v>
       </c>
       <c r="D325" s="1"/>
       <c r="E325" s="1">
@@ -13849,13 +13793,13 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B326" t="s">
         <v>1196</v>
       </c>
-      <c r="B326" t="s">
+      <c r="C326" t="s">
         <v>1197</v>
-      </c>
-      <c r="C326" t="s">
-        <v>1198</v>
       </c>
       <c r="D326" s="1"/>
       <c r="E326" s="1">
@@ -13867,13 +13811,13 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B327" t="s">
         <v>1199</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" t="s">
         <v>1200</v>
-      </c>
-      <c r="C327" t="s">
-        <v>1201</v>
       </c>
       <c r="D327" s="1"/>
       <c r="E327" s="1">
@@ -13885,13 +13829,13 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C328" t="s">
         <v>1203</v>
-      </c>
-      <c r="B328" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C328" t="s">
-        <v>1204</v>
       </c>
       <c r="D328" s="1"/>
       <c r="E328" s="1">
@@ -13903,13 +13847,13 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B329" t="s">
         <v>1205</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C329" t="s">
         <v>1206</v>
-      </c>
-      <c r="C329" t="s">
-        <v>1207</v>
       </c>
       <c r="D329" s="1"/>
       <c r="E329" s="1">
@@ -13921,13 +13865,13 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B330" t="s">
         <v>1208</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C330" s="1" t="s">
         <v>1209</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>1210</v>
       </c>
       <c r="D330" s="1"/>
       <c r="E330" s="1">
@@ -13942,10 +13886,10 @@
         <v>290</v>
       </c>
       <c r="B331" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C331" t="s">
         <v>1211</v>
-      </c>
-      <c r="C331" t="s">
-        <v>1212</v>
       </c>
       <c r="D331" s="1"/>
       <c r="E331" s="1">
@@ -13960,10 +13904,10 @@
         <v>305</v>
       </c>
       <c r="B332" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C332" t="s">
         <v>1213</v>
-      </c>
-      <c r="C332" t="s">
-        <v>1214</v>
       </c>
       <c r="D332" s="1"/>
       <c r="E332" s="1">
@@ -13978,10 +13922,10 @@
         <v>409</v>
       </c>
       <c r="B333" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C333" s="1" t="s">
         <v>1215</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>1216</v>
       </c>
       <c r="D333" s="1"/>
       <c r="E333" s="1">
@@ -13993,13 +13937,13 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B334" t="s">
         <v>1217</v>
       </c>
-      <c r="B334" t="s">
+      <c r="C334" s="1" t="s">
         <v>1218</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>1219</v>
       </c>
       <c r="D334" s="1"/>
       <c r="E334" s="1">
@@ -14011,13 +13955,13 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B335" t="s">
         <v>1220</v>
       </c>
-      <c r="B335" t="s">
+      <c r="C335" s="1" t="s">
         <v>1221</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>1222</v>
       </c>
       <c r="D335" s="1"/>
       <c r="E335" s="1">
@@ -14032,10 +13976,10 @@
         <v>75</v>
       </c>
       <c r="B336" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C336" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>1224</v>
       </c>
       <c r="D336" s="1"/>
       <c r="E336" s="1">
@@ -14050,10 +13994,10 @@
         <v>196</v>
       </c>
       <c r="B337" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C337" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D337" s="1"/>
       <c r="E337" s="1">
@@ -14065,13 +14009,13 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B338" t="s">
         <v>1226</v>
       </c>
-      <c r="B338" t="s">
+      <c r="C338" t="s">
         <v>1227</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1228</v>
       </c>
       <c r="D338" s="1"/>
       <c r="E338" s="1">
@@ -14083,13 +14027,13 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B339" t="s">
         <v>1229</v>
       </c>
-      <c r="B339" t="s">
+      <c r="C339" t="s">
         <v>1230</v>
-      </c>
-      <c r="C339" t="s">
-        <v>1231</v>
       </c>
       <c r="D339" s="1"/>
       <c r="E339" s="1">
@@ -14104,10 +14048,10 @@
         <v>256</v>
       </c>
       <c r="B340" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C340" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D340" s="1"/>
       <c r="E340" s="1">
@@ -14122,10 +14066,10 @@
         <v>257</v>
       </c>
       <c r="B341" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C341" t="s">
         <v>1233</v>
-      </c>
-      <c r="C341" t="s">
-        <v>1234</v>
       </c>
       <c r="D341" s="1"/>
       <c r="E341" s="1">
@@ -14140,10 +14084,10 @@
         <v>258</v>
       </c>
       <c r="B342" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C342" t="s">
         <v>1235</v>
-      </c>
-      <c r="C342" t="s">
-        <v>1236</v>
       </c>
       <c r="D342" s="1"/>
       <c r="E342" s="1">
@@ -14158,10 +14102,10 @@
         <v>259</v>
       </c>
       <c r="B343" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C343" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D343" s="1"/>
       <c r="E343" s="1">
@@ -14176,10 +14120,10 @@
         <v>260</v>
       </c>
       <c r="B344" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C344" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D344" s="1"/>
       <c r="E344" s="1">
@@ -14194,10 +14138,10 @@
         <v>261</v>
       </c>
       <c r="B345" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C345" t="s">
         <v>1239</v>
-      </c>
-      <c r="C345" t="s">
-        <v>1240</v>
       </c>
       <c r="D345" s="1"/>
       <c r="E345" s="1">
@@ -14212,10 +14156,10 @@
         <v>262</v>
       </c>
       <c r="B346" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C346" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D346" s="1"/>
       <c r="E346" s="1">
@@ -14230,7 +14174,7 @@
         <v>263</v>
       </c>
       <c r="B347" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C347" t="s">
         <v>263</v>
@@ -14245,13 +14189,13 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C348" t="s">
         <v>1243</v>
-      </c>
-      <c r="B348" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1244</v>
       </c>
       <c r="D348" s="1"/>
       <c r="E348" s="1">
@@ -14266,10 +14210,10 @@
         <v>265</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D349" s="1"/>
       <c r="E349" s="1">
@@ -14284,10 +14228,10 @@
         <v>265</v>
       </c>
       <c r="B350" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C350" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>1248</v>
       </c>
       <c r="D350" s="1"/>
       <c r="E350" s="1">
@@ -14302,10 +14246,10 @@
         <v>266</v>
       </c>
       <c r="B351" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C351" s="1" t="s">
         <v>1249</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>1250</v>
       </c>
       <c r="D351" s="1"/>
       <c r="E351" s="1">
@@ -14320,10 +14264,10 @@
         <v>45</v>
       </c>
       <c r="B352" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C352" s="1" t="s">
         <v>1251</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>1252</v>
       </c>
       <c r="D352" s="1"/>
       <c r="E352" s="1">
@@ -14338,10 +14282,10 @@
         <v>32</v>
       </c>
       <c r="B353" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C353" t="s">
         <v>1253</v>
-      </c>
-      <c r="C353" t="s">
-        <v>1254</v>
       </c>
       <c r="D353" s="1"/>
       <c r="E353" s="1">
@@ -14356,10 +14300,10 @@
         <v>52</v>
       </c>
       <c r="B354" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C354" s="1" t="s">
         <v>1255</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>1256</v>
       </c>
       <c r="D354" s="1"/>
       <c r="E354" s="1">
@@ -14374,10 +14318,10 @@
         <v>54</v>
       </c>
       <c r="B355" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C355" t="s">
         <v>1257</v>
-      </c>
-      <c r="C355" t="s">
-        <v>1258</v>
       </c>
       <c r="D355" s="1"/>
       <c r="E355" s="1">
@@ -14392,10 +14336,10 @@
         <v>18</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C356" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D356" s="1"/>
       <c r="E356" s="1">
@@ -14410,10 +14354,10 @@
         <v>37</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C357" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D357" s="1"/>
       <c r="E357" s="1">
@@ -14428,10 +14372,10 @@
         <v>53</v>
       </c>
       <c r="B358" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C358" s="1" t="s">
         <v>1262</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>1263</v>
       </c>
       <c r="D358" s="1"/>
       <c r="E358" s="1">
@@ -14446,10 +14390,10 @@
         <v>31</v>
       </c>
       <c r="B359" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C359" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>1265</v>
       </c>
       <c r="D359" s="1"/>
       <c r="E359" s="1">
@@ -14464,10 +14408,10 @@
         <v>33</v>
       </c>
       <c r="B360" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C360" s="1" t="s">
         <v>1267</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="D360" s="1"/>
       <c r="E360" s="1">
@@ -14479,13 +14423,13 @@
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D361" s="1"/>
       <c r="E361" s="1">
@@ -14500,7 +14444,7 @@
         <v>2</v>
       </c>
       <c r="B362" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C362" t="s">
         <v>2</v>
@@ -14518,10 +14462,10 @@
         <v>40</v>
       </c>
       <c r="B363" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C363" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D363" s="1"/>
       <c r="E363" s="1">
@@ -14536,10 +14480,10 @@
         <v>72</v>
       </c>
       <c r="B364" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C364" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>1273</v>
       </c>
       <c r="D364" s="1"/>
       <c r="E364" s="1">
@@ -14554,10 +14498,10 @@
         <v>22</v>
       </c>
       <c r="B365" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C365" t="s">
         <v>1274</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1275</v>
       </c>
       <c r="D365" s="1"/>
       <c r="E365" s="1">
@@ -14569,13 +14513,13 @@
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C366" t="s">
         <v>1277</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1278</v>
       </c>
       <c r="D366" s="1"/>
       <c r="E366" s="1">
@@ -14587,13 +14531,13 @@
     </row>
     <row r="367" spans="1:6" ht="17" customHeight="1">
       <c r="A367" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B367" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C367" t="s">
         <v>1279</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1280</v>
       </c>
       <c r="D367" s="1"/>
       <c r="E367" s="1">
@@ -14608,7 +14552,7 @@
         <v>1</v>
       </c>
       <c r="B368" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>622</v>
@@ -14626,10 +14570,10 @@
         <v>60</v>
       </c>
       <c r="B369" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C369" t="s">
         <v>1282</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1283</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1">
@@ -14644,10 +14588,10 @@
         <v>15</v>
       </c>
       <c r="B370" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C370" s="1" t="s">
         <v>1284</v>
-      </c>
-      <c r="C370" s="1" t="s">
-        <v>1285</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="1">
@@ -14662,10 +14606,10 @@
         <v>15</v>
       </c>
       <c r="B371" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C371" s="1" t="s">
         <v>1298</v>
-      </c>
-      <c r="C371" s="1" t="s">
-        <v>1299</v>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="1">
@@ -14680,10 +14624,10 @@
         <v>30</v>
       </c>
       <c r="B372" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C372" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>1287</v>
       </c>
       <c r="D372" s="1"/>
       <c r="E372" s="1">
@@ -14698,7 +14642,7 @@
         <v>3</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>622</v>
@@ -14716,10 +14660,10 @@
         <v>16</v>
       </c>
       <c r="B374" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C374" t="s">
         <v>1289</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1290</v>
       </c>
       <c r="D374" s="1"/>
       <c r="E374" s="1">
@@ -14734,10 +14678,10 @@
         <v>14</v>
       </c>
       <c r="B375" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C375" t="s">
         <v>1291</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1292</v>
       </c>
       <c r="D375" s="1"/>
       <c r="E375" s="1">
@@ -14749,13 +14693,13 @@
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>1294</v>
-      </c>
       <c r="C376" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D376" s="1"/>
       <c r="E376" s="1">
@@ -14767,13 +14711,13 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="C377" t="s">
         <v>1296</v>
-      </c>
-      <c r="C377" t="s">
-        <v>1297</v>
       </c>
       <c r="D377" s="1"/>
       <c r="E377" s="1">
@@ -14785,13 +14729,13 @@
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>1301</v>
-      </c>
       <c r="C378" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D378" s="1"/>
       <c r="E378" s="1">
@@ -14803,13 +14747,13 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B379" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B379" s="1" t="s">
+      <c r="C379" t="s">
         <v>1303</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1304</v>
       </c>
       <c r="D379" s="1"/>
       <c r="E379" s="1">
@@ -14824,10 +14768,10 @@
         <v>55</v>
       </c>
       <c r="B380" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C380" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="1">
@@ -14842,10 +14786,10 @@
         <v>59</v>
       </c>
       <c r="B381" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C381" t="s">
         <v>1307</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1308</v>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="1">
@@ -14860,10 +14804,10 @@
         <v>7</v>
       </c>
       <c r="B382" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C382" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="1">
@@ -14878,10 +14822,10 @@
         <v>19</v>
       </c>
       <c r="B383" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C383" t="s">
         <v>1310</v>
-      </c>
-      <c r="C383" t="s">
-        <v>1311</v>
       </c>
       <c r="D383" s="1"/>
       <c r="E383" s="1">
@@ -14896,10 +14840,10 @@
         <v>17</v>
       </c>
       <c r="B384" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C384" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="1">
@@ -14914,10 +14858,10 @@
         <v>267</v>
       </c>
       <c r="B385" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C385" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="1">
@@ -14932,10 +14876,10 @@
         <v>268</v>
       </c>
       <c r="B386" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C386" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D386" s="1"/>
       <c r="E386" s="1">
@@ -14950,7 +14894,7 @@
         <v>269</v>
       </c>
       <c r="B387" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>622</v>
@@ -14968,10 +14912,10 @@
         <v>270</v>
       </c>
       <c r="B388" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C388" t="s">
         <v>1316</v>
-      </c>
-      <c r="C388" t="s">
-        <v>1317</v>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="1">
@@ -14986,10 +14930,10 @@
         <v>271</v>
       </c>
       <c r="B389" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C389" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="D389" s="1"/>
       <c r="E389" s="1">
@@ -15004,10 +14948,10 @@
         <v>272</v>
       </c>
       <c r="B390" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C390" t="s">
         <v>1319</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1320</v>
       </c>
       <c r="D390" s="1"/>
       <c r="E390" s="1">
@@ -15022,10 +14966,10 @@
         <v>273</v>
       </c>
       <c r="B391" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C391" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D391" s="1"/>
       <c r="E391" s="1">
@@ -15040,10 +14984,10 @@
         <v>274</v>
       </c>
       <c r="B392" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C392" t="s">
         <v>1322</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1323</v>
       </c>
       <c r="D392" s="1"/>
       <c r="E392" s="1">
@@ -15058,10 +15002,10 @@
         <v>275</v>
       </c>
       <c r="B393" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C393" t="s">
         <v>1324</v>
-      </c>
-      <c r="C393" t="s">
-        <v>1325</v>
       </c>
       <c r="D393" s="1"/>
       <c r="E393" s="1">
@@ -15076,10 +15020,10 @@
         <v>276</v>
       </c>
       <c r="B394" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C394" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="D394" s="1"/>
       <c r="E394" s="1">
@@ -15091,13 +15035,13 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B395" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C395" t="s">
         <v>1327</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1328</v>
       </c>
       <c r="D395" s="1"/>
       <c r="E395" s="1">
@@ -15112,7 +15056,7 @@
         <v>277</v>
       </c>
       <c r="B396" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C396" t="s">
         <v>444</v>
@@ -15130,10 +15074,10 @@
         <v>278</v>
       </c>
       <c r="B397" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C397" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D397" s="1"/>
       <c r="E397" s="1">
@@ -15148,10 +15092,10 @@
         <v>279</v>
       </c>
       <c r="B398" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C398" t="s">
         <v>1335</v>
-      </c>
-      <c r="C398" t="s">
-        <v>1336</v>
       </c>
       <c r="D398" s="1"/>
       <c r="E398" s="1">
@@ -15163,13 +15107,13 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B399" t="s">
         <v>1332</v>
       </c>
-      <c r="B399" t="s">
+      <c r="C399" t="s">
         <v>1333</v>
-      </c>
-      <c r="C399" t="s">
-        <v>1334</v>
       </c>
       <c r="D399" s="1"/>
       <c r="E399" s="1">
@@ -15184,10 +15128,10 @@
         <v>143</v>
       </c>
       <c r="B400" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C400" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1">
@@ -15202,10 +15146,10 @@
         <v>153</v>
       </c>
       <c r="B401" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C401" t="s">
         <v>1339</v>
-      </c>
-      <c r="C401" t="s">
-        <v>1340</v>
       </c>
       <c r="D401" s="1"/>
       <c r="E401" s="1">
@@ -15220,10 +15164,10 @@
         <v>280</v>
       </c>
       <c r="B402" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C402" t="s">
         <v>1341</v>
-      </c>
-      <c r="C402" t="s">
-        <v>1342</v>
       </c>
       <c r="D402" s="1"/>
       <c r="E402" s="1">
@@ -15238,10 +15182,10 @@
         <v>282</v>
       </c>
       <c r="B403" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C403" t="s">
         <v>1343</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1344</v>
       </c>
       <c r="D403" s="1"/>
       <c r="E403" s="1">
@@ -15256,10 +15200,10 @@
         <v>283</v>
       </c>
       <c r="B404" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C404" t="s">
         <v>1345</v>
-      </c>
-      <c r="C404" t="s">
-        <v>1346</v>
       </c>
       <c r="D404" s="1"/>
       <c r="E404" s="1">
@@ -15274,10 +15218,10 @@
         <v>286</v>
       </c>
       <c r="B405" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C405" t="s">
         <v>1347</v>
-      </c>
-      <c r="C405" t="s">
-        <v>1348</v>
       </c>
       <c r="D405" s="1"/>
       <c r="E405" s="1">
@@ -15292,10 +15236,10 @@
         <v>287</v>
       </c>
       <c r="B406" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C406" t="s">
         <v>1349</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1350</v>
       </c>
       <c r="D406" s="1"/>
       <c r="E406" s="1">
@@ -15307,13 +15251,13 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B407" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="B407" s="1" t="s">
+      <c r="C407" s="1" t="s">
         <v>1352</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>1353</v>
       </c>
       <c r="D407" s="1"/>
       <c r="E407" s="1">
@@ -15325,13 +15269,13 @@
     </row>
     <row r="408" spans="1:6">
       <c r="A408" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B408" t="s">
         <v>1354</v>
       </c>
-      <c r="B408" t="s">
+      <c r="C408" t="s">
         <v>1355</v>
-      </c>
-      <c r="C408" t="s">
-        <v>1356</v>
       </c>
       <c r="D408" s="1"/>
       <c r="E408" s="1">
@@ -15346,10 +15290,10 @@
         <v>291</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D409" s="1"/>
       <c r="E409" s="1">
@@ -15364,10 +15308,10 @@
         <v>292</v>
       </c>
       <c r="B410" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C410" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="C410" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="D410" s="1"/>
       <c r="E410" s="1">
@@ -15382,10 +15326,10 @@
         <v>295</v>
       </c>
       <c r="B411" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C411" s="1" t="s">
         <v>1361</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>1362</v>
       </c>
       <c r="D411" s="1"/>
       <c r="E411" s="1">
@@ -15400,10 +15344,10 @@
         <v>297</v>
       </c>
       <c r="B412" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C412" t="s">
         <v>1363</v>
-      </c>
-      <c r="C412" t="s">
-        <v>1364</v>
       </c>
       <c r="D412" s="1"/>
       <c r="E412" s="1">
@@ -15418,7 +15362,7 @@
         <v>299</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>299</v>
@@ -15436,10 +15380,10 @@
         <v>300</v>
       </c>
       <c r="B414" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C414" t="s">
         <v>1366</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1367</v>
       </c>
       <c r="D414" s="1"/>
       <c r="E414" s="1">
@@ -15454,10 +15398,10 @@
         <v>301</v>
       </c>
       <c r="B415" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C415" t="s">
         <v>1368</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1369</v>
       </c>
       <c r="D415" s="1"/>
       <c r="E415" s="1">
@@ -15472,10 +15416,10 @@
         <v>302</v>
       </c>
       <c r="B416" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C416" t="s">
         <v>1370</v>
-      </c>
-      <c r="C416" t="s">
-        <v>1371</v>
       </c>
       <c r="D416" s="1"/>
       <c r="E416" s="1">
@@ -15490,10 +15434,10 @@
         <v>298</v>
       </c>
       <c r="B417" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C417" t="s">
         <v>1372</v>
-      </c>
-      <c r="C417" t="s">
-        <v>1373</v>
       </c>
       <c r="D417" s="1"/>
       <c r="E417" s="1">
@@ -15508,10 +15452,10 @@
         <v>304</v>
       </c>
       <c r="B418" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C418" s="1" t="s">
         <v>1374</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>1375</v>
       </c>
       <c r="D418" s="1"/>
       <c r="E418" s="1">
@@ -15523,13 +15467,13 @@
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B419" t="s">
         <v>1376</v>
       </c>
-      <c r="B419" t="s">
+      <c r="C419" t="s">
         <v>1377</v>
-      </c>
-      <c r="C419" t="s">
-        <v>1378</v>
       </c>
       <c r="D419" s="1"/>
       <c r="E419" s="1">
@@ -15544,10 +15488,10 @@
         <v>306</v>
       </c>
       <c r="B420" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C420" s="1" t="s">
         <v>1379</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>1380</v>
       </c>
       <c r="D420" s="1"/>
       <c r="E420" s="1">
@@ -15562,10 +15506,10 @@
         <v>307</v>
       </c>
       <c r="B421" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C421" s="1" t="s">
         <v>1381</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>1382</v>
       </c>
       <c r="D421" s="1"/>
       <c r="E421" s="1">
@@ -15580,10 +15524,10 @@
         <v>308</v>
       </c>
       <c r="B422" s="9" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C422" t="s">
         <v>1383</v>
-      </c>
-      <c r="C422" t="s">
-        <v>1384</v>
       </c>
       <c r="D422" s="1"/>
       <c r="E422" s="1">
@@ -15598,10 +15542,10 @@
         <v>309</v>
       </c>
       <c r="B423" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C423" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D423" s="1"/>
       <c r="E423" s="1">
@@ -15616,10 +15560,10 @@
         <v>310</v>
       </c>
       <c r="B424" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C424" t="s">
         <v>1387</v>
-      </c>
-      <c r="C424" t="s">
-        <v>1388</v>
       </c>
       <c r="D424" s="1"/>
       <c r="E424" s="1">
@@ -15634,10 +15578,10 @@
         <v>312</v>
       </c>
       <c r="B425" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C425" t="s">
         <v>1389</v>
-      </c>
-      <c r="C425" t="s">
-        <v>1390</v>
       </c>
       <c r="D425" s="1"/>
       <c r="E425" s="1">
@@ -15652,10 +15596,10 @@
         <v>314</v>
       </c>
       <c r="B426" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C426" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D426" s="1"/>
       <c r="E426" s="1">
@@ -15670,10 +15614,10 @@
         <v>315</v>
       </c>
       <c r="B427" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C427" t="s">
         <v>1394</v>
-      </c>
-      <c r="C427" t="s">
-        <v>1395</v>
       </c>
       <c r="D427" s="1"/>
       <c r="E427" s="1">
@@ -15688,10 +15632,10 @@
         <v>318</v>
       </c>
       <c r="B428" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C428" t="s">
         <v>1396</v>
-      </c>
-      <c r="C428" t="s">
-        <v>1397</v>
       </c>
       <c r="D428" s="1"/>
       <c r="E428" s="1">
@@ -15706,10 +15650,10 @@
         <v>319</v>
       </c>
       <c r="B429" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C429" t="s">
         <v>1398</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1399</v>
       </c>
       <c r="D429" s="1"/>
       <c r="E429" s="1">
@@ -15724,10 +15668,10 @@
         <v>320</v>
       </c>
       <c r="B430" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C430" t="s">
         <v>1400</v>
-      </c>
-      <c r="C430" t="s">
-        <v>1401</v>
       </c>
       <c r="D430" s="1"/>
       <c r="E430" s="1">
@@ -15742,10 +15686,10 @@
         <v>321</v>
       </c>
       <c r="B431" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C431" s="1" t="s">
         <v>1402</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>1403</v>
       </c>
       <c r="D431" s="1"/>
       <c r="E431" s="1">
@@ -15760,10 +15704,10 @@
         <v>322</v>
       </c>
       <c r="B432" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C432" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D432" s="1"/>
       <c r="E432" s="1">
@@ -15778,10 +15722,10 @@
         <v>323</v>
       </c>
       <c r="B433" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D433" s="1"/>
       <c r="E433" s="1">
@@ -15796,7 +15740,7 @@
         <v>324</v>
       </c>
       <c r="B434" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C434" t="s">
         <v>324</v>
@@ -15811,13 +15755,13 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B435" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C435" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D435" s="1"/>
       <c r="E435" s="1">
@@ -15829,13 +15773,13 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B436" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="B436" s="1" t="s">
+      <c r="C436" s="1" t="s">
         <v>1417</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>1418</v>
       </c>
       <c r="D436" s="1"/>
       <c r="E436" s="1">
@@ -15850,10 +15794,10 @@
         <v>164</v>
       </c>
       <c r="B437" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C437" t="s">
         <v>1419</v>
-      </c>
-      <c r="C437" t="s">
-        <v>1420</v>
       </c>
       <c r="E437" s="1">
         <v>1999</v>
@@ -15867,10 +15811,10 @@
         <v>326</v>
       </c>
       <c r="B438" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C438" t="s">
         <v>1421</v>
-      </c>
-      <c r="C438" t="s">
-        <v>1422</v>
       </c>
       <c r="E438" s="1">
         <v>2005</v>
@@ -15884,10 +15828,10 @@
         <v>105</v>
       </c>
       <c r="B439" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C439" s="10" t="s">
         <v>1423</v>
-      </c>
-      <c r="C439" s="10" t="s">
-        <v>1424</v>
       </c>
       <c r="E439" s="1">
         <v>2011</v>
@@ -15901,10 +15845,10 @@
         <v>183</v>
       </c>
       <c r="B440" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C440" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E440" s="1">
         <v>1980</v>
@@ -15918,10 +15862,10 @@
         <v>149</v>
       </c>
       <c r="B441" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C441" t="s">
         <v>1426</v>
-      </c>
-      <c r="C441" t="s">
-        <v>1427</v>
       </c>
       <c r="E441" s="1">
         <v>1998</v>
@@ -15935,10 +15879,10 @@
         <v>108</v>
       </c>
       <c r="B442" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C442" t="s">
         <v>1428</v>
-      </c>
-      <c r="C442" t="s">
-        <v>1429</v>
       </c>
       <c r="E442" s="1">
         <v>1990</v>
@@ -15952,10 +15896,10 @@
         <v>165</v>
       </c>
       <c r="B443" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C443" t="s">
         <v>1206</v>
-      </c>
-      <c r="C443" t="s">
-        <v>1207</v>
       </c>
       <c r="E443" s="1">
         <v>2008</v>
@@ -15966,13 +15910,13 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B444" t="s">
         <v>1430</v>
       </c>
-      <c r="B444" t="s">
-        <v>1431</v>
-      </c>
       <c r="C444" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E444" s="1">
         <v>1972</v>
@@ -15983,10 +15927,10 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B445" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C445" t="s">
         <v>622</v>
@@ -16000,16 +15944,16 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B446" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C446" t="s">
         <v>622</v>
       </c>
       <c r="D446" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E446" s="1">
         <v>1973</v>
@@ -16023,10 +15967,10 @@
         <v>184</v>
       </c>
       <c r="B447" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C447" t="s">
         <v>1437</v>
-      </c>
-      <c r="C447" t="s">
-        <v>1438</v>
       </c>
       <c r="E447" s="1">
         <v>1974</v>
@@ -16037,13 +15981,13 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B448" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C448" t="s">
         <v>1439</v>
-      </c>
-      <c r="C448" t="s">
-        <v>1440</v>
       </c>
       <c r="E448" s="1">
         <v>1968</v>
@@ -16054,13 +15998,13 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B449" t="s">
         <v>1442</v>
       </c>
-      <c r="B449" t="s">
-        <v>1443</v>
-      </c>
       <c r="C449" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E449" s="1">
         <v>1962</v>
@@ -16071,13 +16015,13 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B450" t="s">
         <v>1444</v>
       </c>
-      <c r="B450" t="s">
-        <v>1445</v>
-      </c>
       <c r="C450" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E450" s="1">
         <v>1968</v>
@@ -16088,13 +16032,13 @@
     </row>
     <row r="451" spans="1:6">
       <c r="A451" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B451" t="s">
         <v>1446</v>
       </c>
-      <c r="B451" t="s">
-        <v>1447</v>
-      </c>
       <c r="C451" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="E451" s="1">
         <v>1968</v>
@@ -16105,13 +16049,13 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B452" t="s">
         <v>1449</v>
       </c>
-      <c r="B452" t="s">
+      <c r="C452" t="s">
         <v>1450</v>
-      </c>
-      <c r="C452" t="s">
-        <v>1451</v>
       </c>
       <c r="E452" s="1">
         <v>1962</v>
@@ -16122,13 +16066,13 @@
     </row>
     <row r="453" spans="1:6">
       <c r="A453" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B453" t="s">
         <v>1452</v>
       </c>
-      <c r="B453" t="s">
-        <v>1453</v>
-      </c>
       <c r="C453" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E453" s="1">
         <v>1963</v>
@@ -16139,13 +16083,13 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B454" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C454" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="E454" s="1">
         <v>2013</v>
@@ -16156,13 +16100,13 @@
     </row>
     <row r="455" spans="1:6">
       <c r="A455" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B455" t="s">
         <v>1455</v>
       </c>
-      <c r="B455" t="s">
+      <c r="C455" t="s">
         <v>1456</v>
-      </c>
-      <c r="C455" t="s">
-        <v>1457</v>
       </c>
       <c r="E455" s="1">
         <v>1962</v>
@@ -16173,13 +16117,13 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B456" t="s">
         <v>1458</v>
       </c>
-      <c r="B456" t="s">
+      <c r="C456" t="s">
         <v>1459</v>
-      </c>
-      <c r="C456" t="s">
-        <v>1460</v>
       </c>
       <c r="E456" s="1">
         <v>1973</v>
@@ -16190,13 +16134,13 @@
     </row>
     <row r="457" spans="1:6">
       <c r="A457" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B457" t="s">
         <v>1461</v>
       </c>
-      <c r="B457" t="s">
-        <v>1462</v>
-      </c>
       <c r="C457" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="E457" s="1">
         <v>1968</v>
@@ -16227,10 +16171,10 @@
         <v>327</v>
       </c>
       <c r="B459" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C459" t="s">
         <v>1463</v>
-      </c>
-      <c r="C459" t="s">
-        <v>1464</v>
       </c>
       <c r="E459" s="1">
         <v>1991</v>
@@ -16244,10 +16188,10 @@
         <v>109</v>
       </c>
       <c r="B460" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C460" t="s">
         <v>1465</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1466</v>
       </c>
       <c r="E460" s="1">
         <v>1995</v>
@@ -16261,10 +16205,10 @@
         <v>94</v>
       </c>
       <c r="B461" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C461" t="s">
         <v>1467</v>
-      </c>
-      <c r="C461" t="s">
-        <v>1468</v>
       </c>
       <c r="E461" s="1">
         <v>2011</v>
@@ -16278,10 +16222,10 @@
         <v>79</v>
       </c>
       <c r="B462" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C462" t="s">
         <v>1469</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1470</v>
       </c>
       <c r="E462" s="1">
         <v>2000</v>
@@ -16295,10 +16239,10 @@
         <v>110</v>
       </c>
       <c r="B463" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C463" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="E463" s="1">
         <v>1974</v>
@@ -16312,10 +16256,10 @@
         <v>185</v>
       </c>
       <c r="B464" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C464" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="E464" s="1">
         <v>1979</v>
@@ -16326,13 +16270,13 @@
     </row>
     <row r="465" spans="1:6">
       <c r="A465" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B465" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C465" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E465" s="1">
         <v>1964</v>
@@ -16346,10 +16290,10 @@
         <v>210</v>
       </c>
       <c r="B466" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C466" t="s">
         <v>1475</v>
-      </c>
-      <c r="C466" t="s">
-        <v>1476</v>
       </c>
       <c r="E466" s="1">
         <v>2010</v>
@@ -16360,13 +16304,13 @@
     </row>
     <row r="467" spans="1:6">
       <c r="A467" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B467" t="s">
         <v>1477</v>
       </c>
-      <c r="B467" t="s">
+      <c r="C467" t="s">
         <v>1478</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1479</v>
       </c>
       <c r="E467" s="1">
         <v>1977</v>
@@ -16380,10 +16324,10 @@
         <v>90</v>
       </c>
       <c r="B468" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C468" t="s">
         <v>1480</v>
-      </c>
-      <c r="C468" t="s">
-        <v>1481</v>
       </c>
       <c r="E468" s="1">
         <v>2009</v>
@@ -16397,10 +16341,10 @@
         <v>186</v>
       </c>
       <c r="B469" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C469" t="s">
         <v>1482</v>
-      </c>
-      <c r="C469" t="s">
-        <v>1483</v>
       </c>
       <c r="E469" s="1">
         <v>2013</v>
@@ -16414,10 +16358,10 @@
         <v>65</v>
       </c>
       <c r="B470" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C470" t="s">
         <v>1484</v>
-      </c>
-      <c r="C470" t="s">
-        <v>1485</v>
       </c>
       <c r="E470" s="1">
         <v>2013</v>
@@ -16431,10 +16375,10 @@
         <v>187</v>
       </c>
       <c r="B471" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C471" t="s">
         <v>1486</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1487</v>
       </c>
       <c r="E471" s="1">
         <v>1988</v>
@@ -16448,10 +16392,10 @@
         <v>188</v>
       </c>
       <c r="B472" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C472" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="E472" s="1">
         <v>1986</v>
@@ -16465,10 +16409,10 @@
         <v>97</v>
       </c>
       <c r="B473" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C473" t="s">
         <v>1489</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1490</v>
       </c>
       <c r="E473" s="1">
         <v>2010</v>
@@ -16482,10 +16426,10 @@
         <v>97</v>
       </c>
       <c r="B474" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C474" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E474" s="1">
         <v>2010</v>
@@ -16499,10 +16443,10 @@
         <v>167</v>
       </c>
       <c r="B475" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="C475" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E475" s="1">
         <v>1984</v>
@@ -16516,10 +16460,10 @@
         <v>328</v>
       </c>
       <c r="B476" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C476" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="E476" s="1">
         <v>2021</v>
@@ -16533,10 +16477,10 @@
         <v>189</v>
       </c>
       <c r="B477" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C477" t="s">
         <v>1496</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1497</v>
       </c>
       <c r="E477" s="1">
         <v>1972</v>
@@ -16547,10 +16491,10 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B478" t="s">
         <v>1498</v>
-      </c>
-      <c r="B478" t="s">
-        <v>1499</v>
       </c>
       <c r="C478" t="s">
         <v>586</v>
@@ -16564,13 +16508,13 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B479" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C479" t="s">
         <v>1500</v>
-      </c>
-      <c r="C479" t="s">
-        <v>1501</v>
       </c>
       <c r="E479" s="1">
         <v>1972</v>
@@ -16581,13 +16525,13 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C480" t="s">
         <v>1503</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C480" t="s">
-        <v>1504</v>
       </c>
       <c r="E480" s="1">
         <v>1975</v>
@@ -16598,13 +16542,13 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B481" t="s">
         <v>1503</v>
       </c>
-      <c r="B481" t="s">
-        <v>1504</v>
-      </c>
       <c r="C481" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E481" s="1">
         <v>1975</v>
@@ -16618,10 +16562,10 @@
         <v>39</v>
       </c>
       <c r="B482" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C482" t="s">
         <v>1505</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1506</v>
       </c>
       <c r="E482" s="1">
         <v>1971</v>
@@ -16632,13 +16576,13 @@
     </row>
     <row r="483" spans="1:6">
       <c r="A483" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B483" t="s">
         <v>1507</v>
       </c>
-      <c r="B483" t="s">
+      <c r="C483" t="s">
         <v>1508</v>
-      </c>
-      <c r="C483" t="s">
-        <v>1509</v>
       </c>
       <c r="E483" s="1">
         <v>1995</v>
@@ -16652,10 +16596,10 @@
         <v>78</v>
       </c>
       <c r="B484" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C484" t="s">
         <v>1510</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1511</v>
       </c>
       <c r="E484" s="1">
         <v>1997</v>
@@ -16666,13 +16610,13 @@
     </row>
     <row r="485" spans="1:6">
       <c r="A485" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B485" t="s">
         <v>1512</v>
       </c>
-      <c r="B485" t="s">
+      <c r="C485" t="s">
         <v>1513</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1514</v>
       </c>
       <c r="E485" s="1">
         <v>1987</v>
@@ -16686,10 +16630,10 @@
         <v>217</v>
       </c>
       <c r="B486" s="10" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C486" t="s">
         <v>1515</v>
-      </c>
-      <c r="C486" t="s">
-        <v>1516</v>
       </c>
       <c r="E486" s="1">
         <v>2021</v>
@@ -16703,10 +16647,10 @@
         <v>41</v>
       </c>
       <c r="B487" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C487" t="s">
         <v>1517</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1518</v>
       </c>
       <c r="E487" s="1">
         <v>1974</v>
@@ -16720,10 +16664,10 @@
         <v>115</v>
       </c>
       <c r="B488" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C488" t="s">
         <v>1519</v>
-      </c>
-      <c r="C488" t="s">
-        <v>1520</v>
       </c>
       <c r="E488" s="1">
         <v>2023</v>
@@ -16737,10 +16681,10 @@
         <v>92</v>
       </c>
       <c r="B489" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C489" t="s">
         <v>1521</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1522</v>
       </c>
       <c r="E489" s="1">
         <v>2002</v>
@@ -16754,10 +16698,10 @@
         <v>219</v>
       </c>
       <c r="B490" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C490" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="E490" s="1">
         <v>1991</v>
@@ -16771,10 +16715,10 @@
         <v>190</v>
       </c>
       <c r="B491" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C491" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="E491" s="1">
         <v>1985</v>
@@ -16788,7 +16732,7 @@
         <v>168</v>
       </c>
       <c r="B492" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C492" t="s">
         <v>483</v>
@@ -16805,10 +16749,10 @@
         <v>46</v>
       </c>
       <c r="B493" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C493" t="s">
         <v>1527</v>
-      </c>
-      <c r="C493" t="s">
-        <v>1528</v>
       </c>
       <c r="E493" s="1">
         <v>1982</v>
@@ -16819,13 +16763,13 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B494" t="s">
         <v>1529</v>
       </c>
-      <c r="B494" t="s">
+      <c r="C494" t="s">
         <v>1530</v>
-      </c>
-      <c r="C494" t="s">
-        <v>1531</v>
       </c>
       <c r="E494" s="1">
         <v>1991</v>
@@ -16836,13 +16780,13 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B495" t="s">
         <v>1532</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" t="s">
         <v>1533</v>
-      </c>
-      <c r="C495" t="s">
-        <v>1534</v>
       </c>
       <c r="E495" s="1">
         <v>1975</v>
@@ -16853,13 +16797,13 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B496" t="s">
         <v>1535</v>
       </c>
-      <c r="B496" t="s">
+      <c r="C496" t="s">
         <v>1536</v>
-      </c>
-      <c r="C496" t="s">
-        <v>1537</v>
       </c>
       <c r="E496" s="1">
         <v>1965</v>
@@ -16873,10 +16817,10 @@
         <v>103</v>
       </c>
       <c r="B497" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C497" t="s">
         <v>1538</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1539</v>
       </c>
       <c r="E497" s="1">
         <v>2009</v>
@@ -16890,10 +16834,10 @@
         <v>169</v>
       </c>
       <c r="B498" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C498" t="s">
         <v>1540</v>
-      </c>
-      <c r="C498" t="s">
-        <v>1541</v>
       </c>
       <c r="E498">
         <v>1999</v>
@@ -16904,13 +16848,13 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B499" t="s">
         <v>1542</v>
       </c>
-      <c r="B499" t="s">
+      <c r="C499" t="s">
         <v>1543</v>
-      </c>
-      <c r="C499" t="s">
-        <v>1544</v>
       </c>
       <c r="E499" s="1">
         <v>1971</v>
@@ -16921,13 +16865,13 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B500" t="s">
         <v>1545</v>
       </c>
-      <c r="B500" t="s">
+      <c r="C500" t="s">
         <v>1546</v>
-      </c>
-      <c r="C500" t="s">
-        <v>1547</v>
       </c>
       <c r="E500" s="1">
         <v>1978</v>
@@ -16938,13 +16882,13 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B501" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C501" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E501" s="1">
         <v>2011</v>
@@ -16958,7 +16902,7 @@
         <v>1026</v>
       </c>
       <c r="B502" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="C502" t="s">
         <v>1026</v>
@@ -16975,10 +16919,10 @@
         <v>116</v>
       </c>
       <c r="B503" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C503" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="E503" s="1">
         <v>1999</v>
@@ -16992,10 +16936,10 @@
         <v>64</v>
       </c>
       <c r="B504" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C504" t="s">
         <v>1552</v>
-      </c>
-      <c r="C504" t="s">
-        <v>1553</v>
       </c>
       <c r="E504" s="1">
         <v>1983</v>
@@ -17006,13 +16950,13 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B505" t="s">
         <v>1554</v>
       </c>
-      <c r="B505" t="s">
+      <c r="C505" t="s">
         <v>1555</v>
-      </c>
-      <c r="C505" t="s">
-        <v>1556</v>
       </c>
       <c r="E505" s="1">
         <v>1983</v>
@@ -17026,10 +16970,10 @@
         <v>325</v>
       </c>
       <c r="B506" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C506" t="s">
         <v>1557</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1558</v>
       </c>
       <c r="E506" s="1">
         <v>2013</v>
@@ -17043,7 +16987,7 @@
         <v>156</v>
       </c>
       <c r="B507" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C507" t="s">
         <v>156</v>
@@ -17060,10 +17004,10 @@
         <v>329</v>
       </c>
       <c r="B508" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C508" t="s">
         <v>1560</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1561</v>
       </c>
       <c r="E508" s="1">
         <v>2014</v>
@@ -17074,13 +17018,13 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B509" t="s">
         <v>1562</v>
       </c>
-      <c r="B509" t="s">
+      <c r="C509" t="s">
         <v>1563</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1564</v>
       </c>
       <c r="E509" s="1">
         <v>1992</v>
@@ -17091,13 +17035,13 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B510" t="s">
         <v>1565</v>
       </c>
-      <c r="B510" t="s">
+      <c r="C510" t="s">
         <v>1566</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1567</v>
       </c>
       <c r="E510" s="1">
         <v>2004</v>
@@ -17108,13 +17052,13 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B511" t="s">
         <v>1568</v>
       </c>
-      <c r="B511" t="s">
+      <c r="C511" t="s">
         <v>1569</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1570</v>
       </c>
       <c r="E511" s="1">
         <v>1952</v>
@@ -17125,13 +17069,13 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B512" t="s">
         <v>1571</v>
       </c>
-      <c r="B512" t="s">
+      <c r="C512" t="s">
         <v>1572</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1573</v>
       </c>
       <c r="E512" s="1">
         <v>1961</v>
@@ -17142,13 +17086,13 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B513" t="s">
         <v>1574</v>
       </c>
-      <c r="B513" t="s">
+      <c r="C513" t="s">
         <v>1575</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1576</v>
       </c>
       <c r="E513" s="1">
         <v>1980</v>
@@ -17159,13 +17103,13 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B514" t="s">
         <v>1577</v>
       </c>
-      <c r="B514" t="s">
+      <c r="C514" t="s">
         <v>1578</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1579</v>
       </c>
       <c r="E514" s="1">
         <v>1989</v>
@@ -17176,13 +17120,13 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B515" t="s">
         <v>1351</v>
       </c>
-      <c r="B515" t="s">
-        <v>1352</v>
-      </c>
       <c r="C515" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E515" s="1">
         <v>1997</v>
@@ -17196,10 +17140,10 @@
         <v>76</v>
       </c>
       <c r="B516" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C516" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E516" s="1">
         <v>1980</v>
@@ -17210,13 +17154,13 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B517" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C517" t="s">
         <v>1586</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1587</v>
       </c>
       <c r="E517" s="1">
         <v>1988</v>
@@ -17230,10 +17174,10 @@
         <v>159</v>
       </c>
       <c r="B518" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C518" t="s">
         <v>1588</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1589</v>
       </c>
       <c r="E518" s="1">
         <v>2002</v>
@@ -17244,13 +17188,13 @@
     </row>
     <row r="519" spans="1:6">
       <c r="A519" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B519" t="s">
         <v>1582</v>
       </c>
-      <c r="B519" t="s">
-        <v>1583</v>
-      </c>
       <c r="C519" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E519" s="1">
         <v>2012</v>
@@ -17264,10 +17208,10 @@
         <v>95</v>
       </c>
       <c r="B520" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C520" t="s">
         <v>1594</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1595</v>
       </c>
       <c r="E520" s="1">
         <v>2012</v>
@@ -17278,13 +17222,13 @@
     </row>
     <row r="521" spans="1:6">
       <c r="A521" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B521" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C521" t="s">
         <v>1598</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1599</v>
       </c>
       <c r="E521" s="1">
         <v>1982</v>
@@ -17295,13 +17239,13 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B522" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="C522" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E522" s="1">
         <v>1982</v>
@@ -17315,10 +17259,10 @@
         <v>191</v>
       </c>
       <c r="B523" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C523" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E523" s="1">
         <v>1985</v>
@@ -17332,10 +17276,10 @@
         <v>192</v>
       </c>
       <c r="B524" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C524" t="s">
         <v>1601</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1602</v>
       </c>
       <c r="E524" s="1">
         <v>1998</v>
@@ -17349,7 +17293,7 @@
         <v>193</v>
       </c>
       <c r="B525" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="C525" t="s">
         <v>641</v>
@@ -17366,10 +17310,10 @@
         <v>117</v>
       </c>
       <c r="B526" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C526" t="s">
         <v>1605</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1606</v>
       </c>
       <c r="E526" s="1">
         <v>1983</v>
@@ -17383,10 +17327,10 @@
         <v>221</v>
       </c>
       <c r="B527" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C527" t="s">
         <v>1615</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1616</v>
       </c>
       <c r="E527" s="1">
         <v>2014</v>
@@ -17400,10 +17344,10 @@
         <v>222</v>
       </c>
       <c r="B528" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C528" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E528" s="1">
         <v>1977</v>
@@ -17417,10 +17361,10 @@
         <v>194</v>
       </c>
       <c r="B529" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C529" t="s">
         <v>1608</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1609</v>
       </c>
       <c r="E529" s="1">
         <v>1989</v>
@@ -17434,10 +17378,10 @@
         <v>58</v>
       </c>
       <c r="B530" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="C530" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E530" s="1">
         <v>1978</v>
@@ -17451,10 +17395,10 @@
         <v>223</v>
       </c>
       <c r="B531" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C531" t="s">
         <v>1628</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1629</v>
       </c>
       <c r="E531" s="1">
         <v>2022</v>
@@ -17465,10 +17409,10 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2158</v>
+        <v>2151</v>
       </c>
       <c r="B532" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="C532" t="s">
         <v>42</v>
@@ -17485,10 +17429,10 @@
         <v>98</v>
       </c>
       <c r="B533" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C533" t="s">
         <v>1620</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1621</v>
       </c>
       <c r="E533" s="1">
         <v>2017</v>
@@ -17502,10 +17446,10 @@
         <v>272</v>
       </c>
       <c r="B534" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C534" t="s">
         <v>1319</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1320</v>
       </c>
       <c r="E534" s="1">
         <v>1980</v>
@@ -17516,13 +17460,13 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B535" t="s">
         <v>1622</v>
       </c>
-      <c r="B535" t="s">
+      <c r="C535" t="s">
         <v>1623</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1624</v>
       </c>
       <c r="E535" s="1">
         <v>1970</v>
@@ -17536,10 +17480,10 @@
         <v>195</v>
       </c>
       <c r="B536" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C536" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="E536">
         <v>1999</v>
@@ -17553,10 +17497,10 @@
         <v>160</v>
       </c>
       <c r="B537" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C537" t="s">
         <v>1610</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1611</v>
       </c>
       <c r="E537">
         <v>2006</v>
@@ -17570,10 +17514,10 @@
         <v>171</v>
       </c>
       <c r="B538" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C538" t="s">
         <v>1630</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1631</v>
       </c>
       <c r="E538" s="1">
         <v>2010</v>
@@ -17587,10 +17531,10 @@
         <v>170</v>
       </c>
       <c r="B539" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C539" t="s">
         <v>1618</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1619</v>
       </c>
       <c r="E539">
         <v>2000</v>
@@ -17604,10 +17548,10 @@
         <v>119</v>
       </c>
       <c r="B540" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C540" t="s">
         <v>1632</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1633</v>
       </c>
       <c r="E540">
         <v>2009</v>
@@ -17621,10 +17565,10 @@
         <v>120</v>
       </c>
       <c r="B541" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C541" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="E541">
         <v>1999</v>
@@ -17638,10 +17582,10 @@
         <v>330</v>
       </c>
       <c r="B542" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C542" t="s">
         <v>1635</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1636</v>
       </c>
       <c r="E542">
         <v>2018</v>
@@ -17655,10 +17599,10 @@
         <v>172</v>
       </c>
       <c r="B543" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C543" t="s">
         <v>1637</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1638</v>
       </c>
       <c r="E543">
         <v>2017</v>
@@ -17672,10 +17616,10 @@
         <v>38</v>
       </c>
       <c r="B544" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C544" t="s">
         <v>1625</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1626</v>
       </c>
       <c r="E544">
         <v>1970</v>
@@ -17689,10 +17633,10 @@
         <v>226</v>
       </c>
       <c r="B545" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="C545" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="E545">
         <v>1975</v>
@@ -17706,10 +17650,10 @@
         <v>122</v>
       </c>
       <c r="B546" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C546" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="E546">
         <v>2004</v>
@@ -17723,10 +17667,10 @@
         <v>293</v>
       </c>
       <c r="B547" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C547" t="s">
         <v>1640</v>
-      </c>
-      <c r="C547" t="s">
-        <v>1641</v>
       </c>
       <c r="E547">
         <v>2021</v>
@@ -17740,10 +17684,10 @@
         <v>161</v>
       </c>
       <c r="B548" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="C548" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="E548">
         <v>2005</v>
@@ -17757,10 +17701,10 @@
         <v>201</v>
       </c>
       <c r="B549" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C549" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E549">
         <v>2000</v>
@@ -17774,10 +17718,10 @@
         <v>102</v>
       </c>
       <c r="B550" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C550" t="s">
         <v>1642</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1643</v>
       </c>
       <c r="E550">
         <v>2022</v>
@@ -17791,10 +17735,10 @@
         <v>150</v>
       </c>
       <c r="B551" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C551" t="s">
         <v>1644</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1645</v>
       </c>
       <c r="E551">
         <v>1994</v>
@@ -17808,10 +17752,10 @@
         <v>69</v>
       </c>
       <c r="B552" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C552" t="s">
         <v>1646</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1647</v>
       </c>
       <c r="E552">
         <v>1985</v>
@@ -17825,10 +17769,10 @@
         <v>99</v>
       </c>
       <c r="B553" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C553" t="s">
         <v>1648</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1649</v>
       </c>
       <c r="E553">
         <v>2012</v>
@@ -17842,10 +17786,10 @@
         <v>21</v>
       </c>
       <c r="B554" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C554" t="s">
         <v>1650</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1651</v>
       </c>
       <c r="E554">
         <v>1967</v>
@@ -17856,7 +17800,7 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B555" t="s">
         <v>714</v>
@@ -17873,13 +17817,13 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B556" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C556" t="s">
         <v>1654</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1655</v>
       </c>
       <c r="E556">
         <v>1965</v>
@@ -17890,13 +17834,13 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C557" t="s">
         <v>1658</v>
-      </c>
-      <c r="B557" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1659</v>
       </c>
       <c r="E557">
         <v>1955</v>
@@ -17907,16 +17851,16 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B558" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="C558" t="s">
         <v>622</v>
       </c>
       <c r="D558" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E558">
         <v>1972</v>
@@ -17927,13 +17871,13 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B559" t="s">
         <v>1664</v>
       </c>
-      <c r="B559" t="s">
-        <v>1665</v>
-      </c>
       <c r="C559" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="E559">
         <v>1964</v>
@@ -17944,13 +17888,13 @@
     </row>
     <row r="560" spans="1:6">
       <c r="A560" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B560" t="s">
         <v>1666</v>
       </c>
-      <c r="B560" t="s">
+      <c r="C560" t="s">
         <v>1667</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1668</v>
       </c>
       <c r="E560">
         <v>1964</v>
@@ -17964,10 +17908,10 @@
         <v>261</v>
       </c>
       <c r="B561" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C561" t="s">
         <v>1239</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1240</v>
       </c>
       <c r="E561">
         <v>2001</v>
@@ -17978,13 +17922,13 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B562" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C562" t="s">
         <v>1736</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1737</v>
       </c>
       <c r="E562">
         <v>2013</v>
@@ -17995,13 +17939,13 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C563" t="s">
         <v>1739</v>
-      </c>
-      <c r="B563" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1740</v>
       </c>
       <c r="E563">
         <v>1973</v>
@@ -18012,7 +17956,7 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B564" t="s">
         <v>1104</v>
@@ -18029,13 +17973,13 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B565" t="s">
         <v>1742</v>
       </c>
-      <c r="B565" t="s">
+      <c r="C565" t="s">
         <v>1743</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1744</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -18049,10 +17993,10 @@
         <v>155</v>
       </c>
       <c r="B566" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C566" t="s">
         <v>1766</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1767</v>
       </c>
       <c r="E566">
         <v>2004</v>
@@ -18066,10 +18010,10 @@
         <v>197</v>
       </c>
       <c r="B567" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C567" t="s">
         <v>1768</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1769</v>
       </c>
       <c r="E567">
         <v>1975</v>
@@ -18083,10 +18027,10 @@
         <v>338</v>
       </c>
       <c r="B568" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C568" t="s">
         <v>1144</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1145</v>
       </c>
       <c r="E568">
         <v>1990</v>
@@ -18100,10 +18044,10 @@
         <v>231</v>
       </c>
       <c r="B569" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C569" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E569">
         <v>1992</v>
@@ -18117,10 +18061,10 @@
         <v>124</v>
       </c>
       <c r="B570" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C570" t="s">
         <v>1771</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1772</v>
       </c>
       <c r="E570">
         <v>2008</v>
@@ -18134,10 +18078,10 @@
         <v>74</v>
       </c>
       <c r="B571" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C571" t="s">
         <v>1773</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1774</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -18151,10 +18095,10 @@
         <v>88</v>
       </c>
       <c r="B572" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C572" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E572">
         <v>2010</v>
@@ -18168,10 +18112,10 @@
         <v>87</v>
       </c>
       <c r="B573" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C573" t="s">
         <v>1776</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1777</v>
       </c>
       <c r="E573">
         <v>2004</v>
@@ -18185,10 +18129,10 @@
         <v>200</v>
       </c>
       <c r="B574" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C574" t="s">
         <v>1778</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1779</v>
       </c>
       <c r="E574">
         <v>1984</v>
@@ -18202,10 +18146,10 @@
         <v>125</v>
       </c>
       <c r="B575" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C575" t="s">
         <v>1780</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1781</v>
       </c>
       <c r="E575">
         <v>2008</v>
@@ -18216,13 +18160,13 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B576" t="s">
         <v>1782</v>
       </c>
-      <c r="B576" t="s">
+      <c r="C576" t="s">
         <v>1783</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1784</v>
       </c>
       <c r="E576">
         <v>2005</v>
@@ -18236,10 +18180,10 @@
         <v>152</v>
       </c>
       <c r="B577" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C577" t="s">
         <v>1785</v>
-      </c>
-      <c r="C577" t="s">
-        <v>1786</v>
       </c>
       <c r="E577">
         <v>2000</v>
@@ -18253,10 +18197,10 @@
         <v>63</v>
       </c>
       <c r="B578" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C578" t="s">
         <v>1787</v>
-      </c>
-      <c r="C578" t="s">
-        <v>1788</v>
       </c>
       <c r="E578">
         <v>1983</v>
@@ -18270,10 +18214,10 @@
         <v>296</v>
       </c>
       <c r="B579" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C579" t="s">
         <v>1789</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1790</v>
       </c>
       <c r="E579">
         <v>1999</v>
@@ -18287,10 +18231,10 @@
         <v>163</v>
       </c>
       <c r="B580" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C580" t="s">
         <v>1791</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1792</v>
       </c>
       <c r="E580">
         <v>2013</v>
@@ -18304,7 +18248,7 @@
         <v>202</v>
       </c>
       <c r="B581" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="C581" t="s">
         <v>202</v>
@@ -18321,10 +18265,10 @@
         <v>91</v>
       </c>
       <c r="B582" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C582" t="s">
         <v>1793</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1794</v>
       </c>
       <c r="E582">
         <v>2002</v>
@@ -18335,10 +18279,10 @@
     </row>
     <row r="583" spans="1:6">
       <c r="A583" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B583" t="s">
         <v>1797</v>
-      </c>
-      <c r="B583" t="s">
-        <v>1798</v>
       </c>
       <c r="C583" t="s">
         <v>747</v>
@@ -18355,10 +18299,10 @@
         <v>175</v>
       </c>
       <c r="B584" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C584" t="s">
         <v>1799</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1800</v>
       </c>
       <c r="E584">
         <v>1993</v>
@@ -18375,7 +18319,7 @@
         <v>747</v>
       </c>
       <c r="C585" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E585">
         <v>2005</v>
@@ -18389,10 +18333,10 @@
         <v>50</v>
       </c>
       <c r="B586" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C586" t="s">
         <v>1802</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1803</v>
       </c>
       <c r="E586">
         <v>1995</v>
@@ -18406,10 +18350,10 @@
         <v>248</v>
       </c>
       <c r="B587" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C587" t="s">
         <v>1804</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1805</v>
       </c>
       <c r="E587">
         <v>2011</v>
@@ -18420,13 +18364,13 @@
     </row>
     <row r="588" spans="1:6">
       <c r="A588" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B588" t="s">
         <v>1806</v>
       </c>
-      <c r="B588" t="s">
-        <v>1807</v>
-      </c>
       <c r="C588" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E588">
         <v>1972</v>
@@ -18440,7 +18384,7 @@
         <v>85</v>
       </c>
       <c r="B589" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C589" t="s">
         <v>85</v>
@@ -18454,13 +18398,13 @@
     </row>
     <row r="590" spans="1:6">
       <c r="A590" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B590" t="s">
         <v>1809</v>
       </c>
-      <c r="B590" t="s">
+      <c r="C590" t="s">
         <v>1810</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1811</v>
       </c>
       <c r="E590">
         <v>1987</v>
@@ -18471,13 +18415,13 @@
     </row>
     <row r="591" spans="1:6">
       <c r="A591" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B591" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C591" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E591">
         <v>1968</v>
@@ -18488,10 +18432,10 @@
     </row>
     <row r="592" spans="1:6">
       <c r="A592" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B592" t="s">
         <v>1814</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1815</v>
       </c>
       <c r="C592" t="s">
         <v>622</v>
@@ -18505,10 +18449,10 @@
     </row>
     <row r="593" spans="1:6">
       <c r="A593" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B593" t="s">
         <v>1816</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1817</v>
       </c>
       <c r="C593" t="s">
         <v>622</v>
@@ -18522,16 +18466,16 @@
     </row>
     <row r="594" spans="1:6">
       <c r="A594" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C594" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D594" t="s">
         <v>1820</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1818</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1819</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1821</v>
       </c>
       <c r="E594">
         <v>2011</v>
@@ -18542,13 +18486,13 @@
     </row>
     <row r="595" spans="1:6">
       <c r="A595" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B595" t="s">
         <v>1822</v>
       </c>
-      <c r="B595" t="s">
-        <v>1823</v>
-      </c>
       <c r="C595" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E595">
         <v>1974</v>
@@ -18559,13 +18503,13 @@
     </row>
     <row r="596" spans="1:6">
       <c r="A596" s="8" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B596" t="s">
         <v>1824</v>
       </c>
-      <c r="B596" t="s">
+      <c r="C596" t="s">
         <v>1825</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1826</v>
       </c>
       <c r="E596">
         <v>2011</v>
@@ -18576,13 +18520,13 @@
     </row>
     <row r="597" spans="1:6">
       <c r="A597" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B597" t="s">
         <v>1827</v>
       </c>
-      <c r="B597" t="s">
+      <c r="C597" t="s">
         <v>1828</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1829</v>
       </c>
       <c r="E597">
         <v>1994</v>
@@ -18593,13 +18537,13 @@
     </row>
     <row r="598" spans="1:6">
       <c r="A598" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C598" t="s">
         <v>1831</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1830</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1832</v>
       </c>
       <c r="E598">
         <v>1967</v>
@@ -18610,13 +18554,13 @@
     </row>
     <row r="599" spans="1:6">
       <c r="A599" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B599" t="s">
         <v>1833</v>
       </c>
-      <c r="B599" t="s">
+      <c r="C599" t="s">
         <v>1834</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1835</v>
       </c>
       <c r="E599">
         <v>1995</v>
@@ -18627,13 +18571,13 @@
     </row>
     <row r="600" spans="1:6">
       <c r="A600" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B600" t="s">
         <v>1836</v>
       </c>
-      <c r="B600" t="s">
+      <c r="C600" t="s">
         <v>1837</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1838</v>
       </c>
       <c r="E600">
         <v>1970</v>
@@ -18644,10 +18588,10 @@
     </row>
     <row r="601" spans="1:6">
       <c r="A601" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B601" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C601" t="s">
         <v>622</v>
@@ -18661,10 +18605,10 @@
     </row>
     <row r="602" spans="1:6">
       <c r="A602" s="3" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B602" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="C602" t="s">
         <v>622</v>
@@ -18678,10 +18622,10 @@
     </row>
     <row r="603" spans="1:6">
       <c r="A603" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B603" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="C603" t="s">
         <v>622</v>
@@ -18695,10 +18639,10 @@
     </row>
     <row r="604" spans="1:6">
       <c r="A604" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B604" t="s">
         <v>1669</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1670</v>
       </c>
       <c r="C604" t="s">
         <v>622</v>
@@ -18712,10 +18656,10 @@
     </row>
     <row r="605" spans="1:6">
       <c r="A605" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B605" t="s">
         <v>1672</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1673</v>
       </c>
       <c r="C605" t="s">
         <v>622</v>
@@ -18729,10 +18673,10 @@
     </row>
     <row r="606" spans="1:6">
       <c r="A606" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B606" t="s">
         <v>1674</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1675</v>
       </c>
       <c r="C606" t="s">
         <v>622</v>
@@ -18746,13 +18690,13 @@
     </row>
     <row r="607" spans="1:6">
       <c r="A607" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B607" t="s">
         <v>1679</v>
       </c>
-      <c r="B607" t="s">
+      <c r="C607" t="s">
         <v>1680</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1681</v>
       </c>
       <c r="E607">
         <v>1944</v>
@@ -18763,10 +18707,10 @@
     </row>
     <row r="608" spans="1:6">
       <c r="A608" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B608" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C608" t="s">
         <v>622</v>
@@ -18780,13 +18724,13 @@
     </row>
     <row r="609" spans="1:6">
       <c r="A609" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B609" t="s">
         <v>1841</v>
       </c>
-      <c r="B609" t="s">
+      <c r="C609" t="s">
         <v>1842</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1843</v>
       </c>
       <c r="E609">
         <v>1980</v>
@@ -18797,13 +18741,13 @@
     </row>
     <row r="610" spans="1:6">
       <c r="A610" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B610" t="s">
         <v>1844</v>
       </c>
-      <c r="B610" t="s">
+      <c r="C610" t="s">
         <v>1845</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1846</v>
       </c>
       <c r="E610">
         <v>1979</v>
@@ -18814,13 +18758,13 @@
     </row>
     <row r="611" spans="1:6">
       <c r="A611" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B611" t="s">
         <v>1847</v>
       </c>
-      <c r="B611" t="s">
+      <c r="C611" t="s">
         <v>1848</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1849</v>
       </c>
       <c r="E611">
         <v>1974</v>
@@ -18834,10 +18778,10 @@
         <v>68</v>
       </c>
       <c r="B612" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C612" t="s">
         <v>1850</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1851</v>
       </c>
       <c r="E612">
         <v>1985</v>
@@ -18848,13 +18792,13 @@
     </row>
     <row r="613" spans="1:6">
       <c r="A613" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C613" t="s">
         <v>1852</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1854</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1853</v>
       </c>
       <c r="E613">
         <v>1988</v>
@@ -18868,10 +18812,10 @@
         <v>303</v>
       </c>
       <c r="B614" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C614" t="s">
         <v>1855</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1856</v>
       </c>
       <c r="E614">
         <v>2006</v>
@@ -18885,10 +18829,10 @@
         <v>298</v>
       </c>
       <c r="B615" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C615" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E615">
         <v>2017</v>
@@ -18902,10 +18846,10 @@
         <v>147</v>
       </c>
       <c r="B616" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C616" t="s">
         <v>1858</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1859</v>
       </c>
       <c r="E616">
         <v>1997</v>
@@ -18919,7 +18863,7 @@
         <v>249</v>
       </c>
       <c r="B617" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="C617" t="s">
         <v>444</v>
@@ -18936,10 +18880,10 @@
         <v>205</v>
       </c>
       <c r="B618" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C618" t="s">
         <v>1861</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1862</v>
       </c>
       <c r="E618">
         <v>1990</v>
@@ -18953,10 +18897,10 @@
         <v>162</v>
       </c>
       <c r="B619" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C619" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="E619">
         <v>2022</v>
@@ -18970,10 +18914,10 @@
         <v>331</v>
       </c>
       <c r="B620" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C620" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="E620">
         <v>2000</v>
@@ -18987,10 +18931,10 @@
         <v>93</v>
       </c>
       <c r="B621" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C621" t="s">
         <v>1866</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1867</v>
       </c>
       <c r="E621">
         <v>2001</v>
@@ -19004,10 +18948,10 @@
         <v>86</v>
       </c>
       <c r="B622" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C622" t="s">
         <v>1868</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1869</v>
       </c>
       <c r="E622">
         <v>2001</v>
@@ -19021,10 +18965,10 @@
         <v>80</v>
       </c>
       <c r="B623" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C623" t="s">
         <v>1870</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1871</v>
       </c>
       <c r="E623">
         <v>2002</v>
@@ -19038,10 +18982,10 @@
         <v>250</v>
       </c>
       <c r="B624" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C624" t="s">
         <v>1872</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1873</v>
       </c>
       <c r="E624">
         <v>2016</v>
@@ -19055,10 +18999,10 @@
         <v>57</v>
       </c>
       <c r="B625" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C625" t="s">
         <v>1874</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1875</v>
       </c>
       <c r="E625">
         <v>1974</v>
@@ -19069,13 +19013,13 @@
     </row>
     <row r="626" spans="1:6">
       <c r="A626" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B626" t="s">
         <v>1876</v>
       </c>
-      <c r="B626" t="s">
+      <c r="C626" t="s">
         <v>1877</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1878</v>
       </c>
       <c r="E626">
         <v>1978</v>
@@ -19089,10 +19033,10 @@
         <v>100</v>
       </c>
       <c r="B627" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C627" t="s">
         <v>1879</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1880</v>
       </c>
       <c r="E627">
         <v>2021</v>
@@ -19106,10 +19050,10 @@
         <v>132</v>
       </c>
       <c r="B628" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C628" t="s">
         <v>1881</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1882</v>
       </c>
       <c r="E628">
         <v>2014</v>
@@ -19123,10 +19067,10 @@
         <v>157</v>
       </c>
       <c r="B629" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C629" t="s">
         <v>1883</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1884</v>
       </c>
       <c r="E629">
         <v>2013</v>
@@ -19140,10 +19084,10 @@
         <v>89</v>
       </c>
       <c r="B630" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C630" t="s">
         <v>1885</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1886</v>
       </c>
       <c r="E630">
         <v>2003</v>
@@ -19157,10 +19101,10 @@
         <v>177</v>
       </c>
       <c r="B631" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C631" t="s">
         <v>1887</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1888</v>
       </c>
       <c r="E631">
         <v>2012</v>
@@ -19188,13 +19132,13 @@
     </row>
     <row r="633" spans="1:6">
       <c r="A633" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C633" t="s">
         <v>1889</v>
-      </c>
-      <c r="B633" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1890</v>
       </c>
       <c r="E633">
         <v>1977</v>
@@ -19208,10 +19152,10 @@
         <v>62</v>
       </c>
       <c r="B634" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C634" t="s">
         <v>1892</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1893</v>
       </c>
       <c r="E634">
         <v>1985</v>
@@ -19225,10 +19169,10 @@
         <v>332</v>
       </c>
       <c r="B635" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C635" t="s">
         <v>1894</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1895</v>
       </c>
       <c r="E635">
         <v>2013</v>
@@ -19239,13 +19183,13 @@
     </row>
     <row r="636" spans="1:6">
       <c r="A636" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B636" t="s">
         <v>1896</v>
       </c>
-      <c r="B636" t="s">
+      <c r="C636" t="s">
         <v>1897</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1898</v>
       </c>
       <c r="E636">
         <v>2024</v>
@@ -19256,13 +19200,13 @@
     </row>
     <row r="637" spans="1:6">
       <c r="A637" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B637" t="s">
         <v>1899</v>
       </c>
-      <c r="B637" t="s">
+      <c r="C637" t="s">
         <v>1900</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1901</v>
       </c>
       <c r="E637">
         <v>1959</v>
@@ -19273,13 +19217,13 @@
     </row>
     <row r="638" spans="1:6">
       <c r="A638" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B638" t="s">
         <v>1902</v>
       </c>
-      <c r="B638" t="s">
+      <c r="C638" t="s">
         <v>1903</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1904</v>
       </c>
       <c r="E638">
         <v>1975</v>
@@ -19293,7 +19237,7 @@
         <v>180</v>
       </c>
       <c r="B639" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="C639" t="s">
         <v>180</v>
@@ -19307,13 +19251,13 @@
     </row>
     <row r="640" spans="1:6">
       <c r="A640" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B640" t="s">
         <v>1906</v>
       </c>
-      <c r="B640" t="s">
+      <c r="C640" t="s">
         <v>1907</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1908</v>
       </c>
       <c r="E640">
         <v>1998</v>
@@ -19324,13 +19268,13 @@
     </row>
     <row r="641" spans="1:6">
       <c r="A641" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B641" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="C641" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="E641">
         <v>1991</v>
@@ -19344,10 +19288,10 @@
         <v>253</v>
       </c>
       <c r="B642" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C642" t="s">
         <v>1911</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1912</v>
       </c>
       <c r="E642">
         <v>2020</v>
@@ -19361,10 +19305,10 @@
         <v>47</v>
       </c>
       <c r="B643" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C643" t="s">
         <v>1913</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1914</v>
       </c>
       <c r="E643">
         <v>1971</v>
@@ -19378,10 +19322,10 @@
         <v>206</v>
       </c>
       <c r="B644" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C644" t="s">
         <v>1915</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1916</v>
       </c>
       <c r="E644">
         <v>1988</v>
@@ -19395,10 +19339,10 @@
         <v>333</v>
       </c>
       <c r="B645" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C645" t="s">
         <v>1917</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1918</v>
       </c>
       <c r="E645">
         <v>2010</v>
@@ -19412,7 +19356,7 @@
         <v>84</v>
       </c>
       <c r="B646" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C646" t="s">
         <v>84</v>
@@ -19429,10 +19373,10 @@
         <v>136</v>
       </c>
       <c r="B647" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C647" t="s">
         <v>1935</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1936</v>
       </c>
       <c r="E647">
         <v>2002</v>
@@ -19446,7 +19390,7 @@
         <v>148</v>
       </c>
       <c r="B648" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C648" t="s">
         <v>148</v>
@@ -19463,10 +19407,10 @@
         <v>207</v>
       </c>
       <c r="B649" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C649" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="E649">
         <v>1991</v>
@@ -19480,10 +19424,10 @@
         <v>334</v>
       </c>
       <c r="B650" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C650" t="s">
         <v>1921</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1922</v>
       </c>
       <c r="E650">
         <v>2009</v>
@@ -19497,10 +19441,10 @@
         <v>36</v>
       </c>
       <c r="B651" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C651" t="s">
         <v>1923</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1924</v>
       </c>
       <c r="E651">
         <v>1976</v>
@@ -19514,10 +19458,10 @@
         <v>208</v>
       </c>
       <c r="B652" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C652" t="s">
         <v>1925</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1926</v>
       </c>
       <c r="E652">
         <v>1993</v>
@@ -19531,10 +19475,10 @@
         <v>313</v>
       </c>
       <c r="B653" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C653" t="s">
         <v>1927</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1928</v>
       </c>
       <c r="E653">
         <v>2011</v>
@@ -19548,10 +19492,10 @@
         <v>143</v>
       </c>
       <c r="B654" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C654" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E654">
         <v>1997</v>
@@ -19565,10 +19509,10 @@
         <v>315</v>
       </c>
       <c r="B655" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C655" t="s">
         <v>1929</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1930</v>
       </c>
       <c r="E655">
         <v>2003</v>
@@ -19582,10 +19526,10 @@
         <v>138</v>
       </c>
       <c r="B656" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C656" t="s">
         <v>1931</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1932</v>
       </c>
       <c r="E656">
         <v>2001</v>
@@ -19599,10 +19543,10 @@
         <v>316</v>
       </c>
       <c r="B657" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C657" t="s">
         <v>1933</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1934</v>
       </c>
       <c r="E657">
         <v>2002</v>
@@ -19616,10 +19560,10 @@
         <v>96</v>
       </c>
       <c r="B658" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C658" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E658">
         <v>2012</v>
@@ -19633,10 +19577,10 @@
         <v>11</v>
       </c>
       <c r="B659" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C659" t="s">
         <v>1937</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1938</v>
       </c>
       <c r="E659">
         <v>1967</v>
@@ -19650,10 +19594,10 @@
         <v>209</v>
       </c>
       <c r="B660" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C660" t="s">
         <v>1939</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1940</v>
       </c>
       <c r="E660">
         <v>1988</v>
@@ -19667,10 +19611,10 @@
         <v>23</v>
       </c>
       <c r="B661" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C661" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E661">
         <v>1967</v>
@@ -19684,10 +19628,10 @@
         <v>56</v>
       </c>
       <c r="B662" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C662" t="s">
         <v>1942</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1943</v>
       </c>
       <c r="E662">
         <v>1972</v>
@@ -19698,13 +19642,13 @@
     </row>
     <row r="663" spans="1:6">
       <c r="A663" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B663" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C663" t="s">
         <v>1944</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1945</v>
       </c>
       <c r="E663">
         <v>2017</v>
@@ -19715,13 +19659,13 @@
     </row>
     <row r="664" spans="1:6">
       <c r="A664" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B664" t="s">
         <v>1947</v>
       </c>
-      <c r="B664" t="s">
+      <c r="C664" t="s">
         <v>1948</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1949</v>
       </c>
       <c r="E664">
         <v>2010</v>
@@ -19732,13 +19676,13 @@
     </row>
     <row r="665" spans="1:6">
       <c r="A665" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B665" t="s">
         <v>1950</v>
       </c>
-      <c r="B665" t="s">
-        <v>1951</v>
-      </c>
       <c r="C665" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E665">
         <v>1976</v>
@@ -19752,10 +19696,10 @@
         <v>4</v>
       </c>
       <c r="B666" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C666" t="s">
         <v>1952</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1953</v>
       </c>
       <c r="E666">
         <v>1962</v>
@@ -19769,10 +19713,10 @@
         <v>73</v>
       </c>
       <c r="B667" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C667" t="s">
         <v>1954</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1955</v>
       </c>
       <c r="E667">
         <v>1979</v>
@@ -19786,10 +19730,10 @@
         <v>6</v>
       </c>
       <c r="B668" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C668" t="s">
         <v>1956</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1957</v>
       </c>
       <c r="E668">
         <v>1958</v>
@@ -19803,10 +19747,10 @@
         <v>28</v>
       </c>
       <c r="B669" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C669" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E669">
         <v>1966</v>
@@ -19820,10 +19764,10 @@
         <v>24</v>
       </c>
       <c r="B670" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C670" t="s">
         <v>1959</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1960</v>
       </c>
       <c r="E670">
         <v>1969</v>
@@ -19837,10 +19781,10 @@
         <v>140</v>
       </c>
       <c r="B671" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C671" t="s">
         <v>1961</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1962</v>
       </c>
       <c r="E671">
         <v>1984</v>
@@ -19854,10 +19798,10 @@
         <v>77</v>
       </c>
       <c r="B672" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C672" t="s">
         <v>1963</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1964</v>
       </c>
       <c r="E672">
         <v>1982</v>
@@ -19871,10 +19815,10 @@
         <v>264</v>
       </c>
       <c r="B673" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C673" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="E673">
         <v>1996</v>
@@ -19888,10 +19832,10 @@
         <v>181</v>
       </c>
       <c r="B674" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C674" t="s">
         <v>1966</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1967</v>
       </c>
       <c r="E674">
         <v>2001</v>
@@ -19905,10 +19849,10 @@
         <v>182</v>
       </c>
       <c r="B675" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C675" t="s">
         <v>1968</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1969</v>
       </c>
       <c r="E675">
         <v>2014</v>
@@ -19922,7 +19866,7 @@
         <v>61</v>
       </c>
       <c r="B676" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C676" t="s">
         <v>61</v>
@@ -19939,10 +19883,10 @@
         <v>335</v>
       </c>
       <c r="B677" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C677" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="E677">
         <v>2016</v>
@@ -19956,10 +19900,10 @@
         <v>19</v>
       </c>
       <c r="B678" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C678" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E678">
         <v>1969</v>
@@ -19973,7 +19917,7 @@
         <v>142</v>
       </c>
       <c r="B679" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C679" t="s">
         <v>622</v>
@@ -19987,13 +19931,13 @@
     </row>
     <row r="680" spans="1:6">
       <c r="A680" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B680" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="C680" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="E680">
         <v>1945</v>
@@ -20007,10 +19951,10 @@
         <v>516</v>
       </c>
       <c r="B681" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C681" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="E681">
         <v>1945</v>
@@ -20024,10 +19968,10 @@
         <v>519</v>
       </c>
       <c r="B682" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="C682" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E682">
         <v>1965</v>
@@ -20038,13 +19982,13 @@
     </row>
     <row r="683" spans="1:6">
       <c r="A683" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B683" t="s">
         <v>1687</v>
       </c>
-      <c r="B683" t="s">
-        <v>1688</v>
-      </c>
       <c r="C683" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E683">
         <v>1947</v>
@@ -20055,13 +19999,13 @@
     </row>
     <row r="684" spans="1:6">
       <c r="A684" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B684" t="s">
         <v>1689</v>
       </c>
-      <c r="B684" t="s">
-        <v>1690</v>
-      </c>
       <c r="C684" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E684">
         <v>1947</v>
@@ -20072,13 +20016,13 @@
     </row>
     <row r="685" spans="1:6">
       <c r="A685" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B685" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="C685" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E685">
         <v>1948</v>
@@ -20089,10 +20033,10 @@
     </row>
     <row r="686" spans="1:6">
       <c r="A686" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B686" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="C686" t="s">
         <v>622</v>
@@ -20106,10 +20050,10 @@
     </row>
     <row r="687" spans="1:6">
       <c r="A687" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B687" t="s">
         <v>1694</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1695</v>
       </c>
       <c r="C687" t="s">
         <v>622</v>
@@ -20123,13 +20067,13 @@
     </row>
     <row r="688" spans="1:6">
       <c r="A688" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B688" t="s">
         <v>1696</v>
       </c>
-      <c r="B688" t="s">
-        <v>1697</v>
-      </c>
       <c r="C688" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="E688">
         <v>1949</v>
@@ -20140,13 +20084,13 @@
     </row>
     <row r="689" spans="1:6">
       <c r="A689" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B689" t="s">
         <v>1698</v>
       </c>
-      <c r="B689" t="s">
-        <v>1699</v>
-      </c>
       <c r="C689" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E689">
         <v>1949</v>
@@ -20157,13 +20101,13 @@
     </row>
     <row r="690" spans="1:6">
       <c r="A690" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B690" t="s">
         <v>1700</v>
       </c>
-      <c r="B690" t="s">
-        <v>1701</v>
-      </c>
       <c r="C690" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E690">
         <v>1949</v>
@@ -20174,13 +20118,13 @@
     </row>
     <row r="691" spans="1:6">
       <c r="A691" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B691" t="s">
         <v>1702</v>
       </c>
-      <c r="B691" t="s">
-        <v>1703</v>
-      </c>
       <c r="C691" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E691">
         <v>1950</v>
@@ -20191,13 +20135,13 @@
     </row>
     <row r="692" spans="1:6">
       <c r="A692" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B692" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C692" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E692">
         <v>1951</v>
@@ -20208,13 +20152,13 @@
     </row>
     <row r="693" spans="1:6">
       <c r="A693" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B693" t="s">
         <v>1706</v>
       </c>
-      <c r="B693" t="s">
+      <c r="C693" t="s">
         <v>1707</v>
-      </c>
-      <c r="C693" t="s">
-        <v>1708</v>
       </c>
       <c r="E693">
         <v>1951</v>
@@ -20225,13 +20169,13 @@
     </row>
     <row r="694" spans="1:6">
       <c r="A694" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B694" t="s">
         <v>1709</v>
       </c>
-      <c r="B694" t="s">
-        <v>1710</v>
-      </c>
       <c r="C694" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E694">
         <v>1951</v>
@@ -20242,13 +20186,13 @@
     </row>
     <row r="695" spans="1:6">
       <c r="A695" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B695" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C695" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="E695">
         <v>1952</v>
@@ -20259,13 +20203,13 @@
     </row>
     <row r="696" spans="1:6">
       <c r="A696" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B696" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C696" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E696">
         <v>1952</v>
@@ -20276,13 +20220,13 @@
     </row>
     <row r="697" spans="1:6">
       <c r="A697" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B697" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C697" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="E697">
         <v>1952</v>
@@ -20293,13 +20237,13 @@
     </row>
     <row r="698" spans="1:6">
       <c r="A698" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B698" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="C698" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="E698">
         <v>1953</v>
@@ -20310,13 +20254,13 @@
     </row>
     <row r="699" spans="1:6">
       <c r="A699" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B699" t="s">
         <v>1718</v>
       </c>
-      <c r="B699" t="s">
-        <v>1719</v>
-      </c>
       <c r="C699" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="E699">
         <v>1953</v>
@@ -20327,13 +20271,13 @@
     </row>
     <row r="700" spans="1:6">
       <c r="A700" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C700" t="s">
         <v>1721</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1720</v>
-      </c>
-      <c r="C700" t="s">
-        <v>1722</v>
       </c>
       <c r="E700">
         <v>1953</v>
@@ -20344,13 +20288,13 @@
     </row>
     <row r="701" spans="1:6">
       <c r="A701" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B701" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C701" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E701">
         <v>1954</v>
@@ -20361,13 +20305,13 @@
     </row>
     <row r="702" spans="1:6">
       <c r="A702" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B702" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="C702" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="E702">
         <v>1954</v>
@@ -20378,13 +20322,13 @@
     </row>
     <row r="703" spans="1:6">
       <c r="A703" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C703" t="s">
         <v>1727</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1726</v>
-      </c>
-      <c r="C703" t="s">
-        <v>1728</v>
       </c>
       <c r="E703">
         <v>1955</v>
@@ -20395,13 +20339,13 @@
     </row>
     <row r="704" spans="1:6">
       <c r="A704" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B704" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="C704" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E704">
         <v>1955</v>
@@ -20412,13 +20356,13 @@
     </row>
     <row r="705" spans="1:6">
       <c r="A705" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C705" t="s">
         <v>1731</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1730</v>
-      </c>
-      <c r="C705" t="s">
-        <v>1732</v>
       </c>
       <c r="E705">
         <v>1955</v>
@@ -20432,7 +20376,7 @@
         <v>3</v>
       </c>
       <c r="B706" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C706" t="s">
         <v>3</v>
@@ -20446,13 +20390,13 @@
     </row>
     <row r="707" spans="1:6">
       <c r="A707" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C707" t="s">
         <v>1734</v>
-      </c>
-      <c r="B707" t="s">
-        <v>1733</v>
-      </c>
-      <c r="C707" t="s">
-        <v>1735</v>
       </c>
       <c r="E707">
         <v>1956</v>
@@ -20463,13 +20407,13 @@
     </row>
     <row r="708" spans="1:6">
       <c r="A708" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B708" t="s">
         <v>1745</v>
       </c>
-      <c r="B708" t="s">
-        <v>1746</v>
-      </c>
       <c r="C708" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E708">
         <v>1957</v>
@@ -20480,13 +20424,13 @@
     </row>
     <row r="709" spans="1:6">
       <c r="A709" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B709" s="11" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C709" s="11" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="E709">
         <v>1958</v>
@@ -20497,13 +20441,13 @@
     </row>
     <row r="710" spans="1:6">
       <c r="A710" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B710" t="s">
         <v>1748</v>
       </c>
-      <c r="B710" t="s">
-        <v>1749</v>
-      </c>
       <c r="C710" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="E710">
         <v>1958</v>
@@ -20514,13 +20458,13 @@
     </row>
     <row r="711" spans="1:6">
       <c r="A711" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B711" t="s">
         <v>1750</v>
       </c>
-      <c r="B711" t="s">
+      <c r="C711" t="s">
         <v>1751</v>
-      </c>
-      <c r="C711" t="s">
-        <v>1752</v>
       </c>
       <c r="E711">
         <v>1958</v>
@@ -20531,13 +20475,13 @@
     </row>
     <row r="712" spans="1:6">
       <c r="A712" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B712" t="s">
         <v>1753</v>
       </c>
-      <c r="B712" t="s">
-        <v>1754</v>
-      </c>
       <c r="C712" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E712">
         <v>1958</v>
@@ -20548,13 +20492,13 @@
     </row>
     <row r="713" spans="1:6">
       <c r="A713" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B713" t="s">
         <v>1755</v>
       </c>
-      <c r="B713" t="s">
+      <c r="C713" t="s">
         <v>1756</v>
-      </c>
-      <c r="C713" t="s">
-        <v>1757</v>
       </c>
       <c r="E713">
         <v>1959</v>
@@ -20565,13 +20509,13 @@
     </row>
     <row r="714" spans="1:6">
       <c r="A714" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B714" t="s">
         <v>1758</v>
       </c>
-      <c r="B714" t="s">
+      <c r="C714" t="s">
         <v>1759</v>
-      </c>
-      <c r="C714" t="s">
-        <v>1760</v>
       </c>
       <c r="E714">
         <v>1960</v>
@@ -20582,13 +20526,13 @@
     </row>
     <row r="715" spans="1:6">
       <c r="A715" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C715" t="s">
         <v>1762</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1761</v>
-      </c>
-      <c r="C715" t="s">
-        <v>1763</v>
       </c>
       <c r="E715">
         <v>1960</v>
@@ -20599,13 +20543,13 @@
     </row>
     <row r="716" spans="1:6">
       <c r="A716" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B716" t="s">
         <v>1764</v>
       </c>
-      <c r="B716" t="s">
-        <v>1765</v>
-      </c>
       <c r="C716" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="E716">
         <v>1960</v>
@@ -20616,13 +20560,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="B717" t="s">
-        <v>2174</v>
+        <v>2167</v>
       </c>
       <c r="C717" t="s">
-        <v>2175</v>
+        <v>2168</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20633,13 +20577,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2105</v>
+        <v>2098</v>
       </c>
       <c r="B718" t="s">
-        <v>2176</v>
+        <v>2169</v>
       </c>
       <c r="C718" t="s">
-        <v>2177</v>
+        <v>2170</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20650,13 +20594,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2179</v>
+        <v>2172</v>
       </c>
       <c r="B719" t="s">
-        <v>2178</v>
+        <v>2171</v>
       </c>
       <c r="C719" t="s">
-        <v>2179</v>
+        <v>2172</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20667,13 +20611,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="B720" t="s">
-        <v>2180</v>
+        <v>2173</v>
       </c>
       <c r="C720" t="s">
-        <v>2181</v>
+        <v>2174</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20684,13 +20628,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2118</v>
+        <v>2111</v>
       </c>
       <c r="B721" t="s">
-        <v>2182</v>
+        <v>2175</v>
       </c>
       <c r="C721" t="s">
-        <v>2183</v>
+        <v>2176</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20701,19 +20645,257 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2100</v>
+        <v>2093</v>
       </c>
       <c r="B722" t="s">
-        <v>2184</v>
+        <v>2177</v>
       </c>
       <c r="C722" t="s">
-        <v>2185</v>
+        <v>2178</v>
       </c>
       <c r="E722">
         <v>2016</v>
       </c>
       <c r="F722" t="s">
         <v>969</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6">
+      <c r="A723" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B723" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C723" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E723">
+        <v>1972</v>
+      </c>
+      <c r="F723" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6">
+      <c r="A724" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B724" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C724" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E724">
+        <v>2019</v>
+      </c>
+      <c r="F724" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6">
+      <c r="A725" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B725" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C725" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E725">
+        <v>1980</v>
+      </c>
+      <c r="F725" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6">
+      <c r="A726" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B726" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C726" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E726">
+        <v>1979</v>
+      </c>
+      <c r="F726" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6">
+      <c r="A727" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B727" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C727" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E727">
+        <v>1997</v>
+      </c>
+      <c r="F727" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6">
+      <c r="A728" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B728" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C728" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E728">
+        <v>1977</v>
+      </c>
+      <c r="F728" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6">
+      <c r="A729" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B729" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C729" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E729">
+        <v>1988</v>
+      </c>
+      <c r="F729" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6">
+      <c r="A730" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B730" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C730" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E730">
+        <v>2011</v>
+      </c>
+      <c r="F730" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6">
+      <c r="A731" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B731" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C731" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E731">
+        <v>1997</v>
+      </c>
+      <c r="F731" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6">
+      <c r="A732" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B732" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C732" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E732">
+        <v>2007</v>
+      </c>
+      <c r="F732" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6">
+      <c r="A733" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B733" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C733" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E733">
+        <v>1999</v>
+      </c>
+      <c r="F733" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6">
+      <c r="A734" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B734" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C734" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E734">
+        <v>1957</v>
+      </c>
+      <c r="F734" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6">
+      <c r="A735" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B735" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C735" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E735">
+        <v>1993</v>
+      </c>
+      <c r="F735" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6">
+      <c r="A736" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B736" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C736" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E736">
+        <v>1988</v>
+      </c>
+      <c r="F736" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F152B1E-F8A8-8A46-8B46-C72ABC9A0774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA0EBAF-6EF3-EF41-A8D1-4D09CAB1C3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="2204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="2216">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6158,15 +6158,9 @@
     <t>Nada Surf</t>
   </si>
   <si>
-    <t>De La Soul</t>
-  </si>
-  <si>
     <t>Future Islands</t>
   </si>
   <si>
-    <t>Deerhunter</t>
-  </si>
-  <si>
     <t>Massive Attack</t>
   </si>
   <si>
@@ -6389,9 +6383,6 @@
     <t>Motorhead</t>
   </si>
   <si>
-    <t>Childish Gambino</t>
-  </si>
-  <si>
     <t>Wolf Parade</t>
   </si>
   <si>
@@ -6491,9 +6482,6 @@
     <t>Parliament</t>
   </si>
   <si>
-    <t>Earth Wind and Fire</t>
-  </si>
-  <si>
     <t>The Knife</t>
   </si>
   <si>
@@ -6536,9 +6524,6 @@
     <t>Johnnie Ray</t>
   </si>
   <si>
-    <t>Dinah Washington</t>
-  </si>
-  <si>
     <t>Hank Williams</t>
   </si>
   <si>
@@ -6759,6 +6744,57 @@
   </si>
   <si>
     <t>Lap of Luxury</t>
+  </si>
+  <si>
+    <t>Wicked Game</t>
+  </si>
+  <si>
+    <t>Heart Shaped World</t>
+  </si>
+  <si>
+    <t>Chris de Burgh</t>
+  </si>
+  <si>
+    <t>The Lady in Red</t>
+  </si>
+  <si>
+    <t>Into the Light</t>
+  </si>
+  <si>
+    <t>Tilted</t>
+  </si>
+  <si>
+    <t>Chaleur humaine</t>
+  </si>
+  <si>
+    <t>Girls Just Want to Have Fun</t>
+  </si>
+  <si>
+    <t>She’s So Unusual</t>
+  </si>
+  <si>
+    <t>Heaven or Las Vegas</t>
+  </si>
+  <si>
+    <t>Groove Is in the Heart</t>
+  </si>
+  <si>
+    <t>World Clique</t>
+  </si>
+  <si>
+    <t>Come On Eileen</t>
+  </si>
+  <si>
+    <t>Too‑Rye‑Ay</t>
+  </si>
+  <si>
+    <t>Misirlou</t>
+  </si>
+  <si>
+    <t>Surfers’ Choice (1962)</t>
+  </si>
+  <si>
+    <t>Dion (1969)</t>
   </si>
 </sst>
 </file>
@@ -7191,7 +7227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B162"/>
+  <dimension ref="B3:B149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7199,805 +7235,740 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2080</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2160</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2087</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2157</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2100</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="1" t="s">
-        <v>2003</v>
+      <c r="B8" t="s">
+        <v>2025</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2103</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="1" t="s">
-        <v>2005</v>
+      <c r="B10" t="s">
+        <v>2028</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2156</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2145</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2129</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2144</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2114</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2142</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2042</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2127</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2062</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>2163</v>
+      <c r="B20" s="1" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2027</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2139</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2030</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2030</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2101</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2049</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2039</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2022</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>2088</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" t="s">
-        <v>2029</v>
+      <c r="B30" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>2018</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2125</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="1" t="s">
-        <v>2004</v>
+      <c r="B33" t="s">
+        <v>2102</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2038</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>2010</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2050</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>2075</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>2077</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2052</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2130</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2013</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="1" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2078</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>2105</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2061</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2097</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2023</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>2053</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2058</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2128</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>2034</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>2045</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="1" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>2133</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>2035</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="59" spans="2:2">
-      <c r="B59" t="s">
-        <v>2165</v>
+      <c r="B59" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2068</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2060</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2063</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2096</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>2149</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2106</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2086</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2152</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" t="s">
-        <v>2110</v>
+      <c r="B68" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="1" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>2140</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="1" t="s">
-        <v>2006</v>
+      <c r="B72" t="s">
+        <v>2012</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2124</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2122</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2112</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>2117</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>2126</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2028</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="1" t="s">
-        <v>2008</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="1" t="s">
-        <v>2002</v>
+      <c r="B82" t="s">
+        <v>2015</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>2084</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2073</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>2014</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2014</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" t="s">
-        <v>2025</v>
+      <c r="B87" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2155</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>2071</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2136</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>2047</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>2135</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="1" t="s">
-        <v>1993</v>
+      <c r="B94" t="s">
+        <v>2064</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>2017</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>2166</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2085</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="99" spans="2:2">
-      <c r="B99" t="s">
-        <v>2074</v>
+      <c r="B99" s="1" t="s">
+        <v>2007</v>
       </c>
     </row>
     <row r="100" spans="2:2">
-      <c r="B100" s="1" t="s">
-        <v>1994</v>
+      <c r="B100" t="s">
+        <v>2157</v>
       </c>
     </row>
     <row r="101" spans="2:2">
-      <c r="B101" t="s">
-        <v>2131</v>
+      <c r="B101" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>2119</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>2033</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>2137</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" t="s">
-        <v>2021</v>
+      <c r="B106" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>2066</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>2036</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>2024</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>2020</v>
+        <v>999</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>2026</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="1" t="s">
-        <v>2009</v>
+      <c r="B112" t="s">
+        <v>2063</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>2162</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" s="1" t="s">
-        <v>1997</v>
+      <c r="B114" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>2092</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>2148</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>2107</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>2069</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="1" t="s">
-        <v>1995</v>
+      <c r="B119" t="s">
+        <v>2138</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>2040</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>2123</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>2070</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>999</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>2161</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>2065</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>2141</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>2067</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>1415</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>2072</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>2138</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>2115</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>2143</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>2099</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>2159</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>2059</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>2146</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>2102</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>2076</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>2095</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>2120</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>2118</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="142" spans="2:2">
-      <c r="B142" t="s">
-        <v>2043</v>
+      <c r="B142" s="1" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="143" spans="2:2">
-      <c r="B143" t="s">
-        <v>2109</v>
+      <c r="B143" s="1" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>2041</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>2012</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>2051</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>2132</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>2015</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="149" spans="2:2">
-      <c r="B149" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2">
-      <c r="B150" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2">
-      <c r="B151" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="1" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="1" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="1"/>
+      <c r="B149" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B162">
-    <sortCondition ref="B1:B162"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B149">
+    <sortCondition ref="B1:B149"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8006,7 +7977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F736"/>
+  <dimension ref="A1:F745"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -13236,7 +13207,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17409,7 +17380,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20560,13 +20531,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="B717" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="C717" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20577,13 +20548,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="B718" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="C718" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20594,13 +20565,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="B719" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="C719" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20611,13 +20582,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="B720" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="C720" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20628,13 +20599,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="B721" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="C721" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20645,13 +20616,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="B722" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="C722" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20662,13 +20633,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="B723" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="C723" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20679,13 +20650,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="B724" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="C724" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20696,13 +20667,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="B725" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="C725" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20716,10 +20687,10 @@
         <v>1996</v>
       </c>
       <c r="B726" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="C726" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20730,13 +20701,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="B727" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="C727" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20747,13 +20718,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="B728" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="C728" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20764,13 +20735,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B729" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="C729" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20781,13 +20752,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="B730" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="C730" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20798,13 +20769,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="B731" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="C731" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20815,13 +20786,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="B732" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
       <c r="C732" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20832,13 +20803,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="B733" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="C733" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20849,13 +20820,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="B734" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="C734" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20866,13 +20837,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="B735" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="C735" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20883,18 +20854,171 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="B736" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="C736" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="E736">
         <v>1988</v>
       </c>
       <c r="F736" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6">
+      <c r="A737" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B737" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C737" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E737">
+        <v>1989</v>
+      </c>
+      <c r="F737" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6">
+      <c r="A738" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B738" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C738" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E738">
+        <v>1986</v>
+      </c>
+      <c r="F738" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6">
+      <c r="A739" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B739" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C739" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E739">
+        <v>2016</v>
+      </c>
+      <c r="F739" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6">
+      <c r="A740" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B740" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C740" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E740">
+        <v>1983</v>
+      </c>
+      <c r="F740" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6">
+      <c r="A741" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B741" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C741" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E741">
+        <v>1990</v>
+      </c>
+      <c r="F741" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6">
+      <c r="A742" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B742" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C742" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E742">
+        <v>1990</v>
+      </c>
+      <c r="F742" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6">
+      <c r="A743" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B743" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C743" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E743">
+        <v>1982</v>
+      </c>
+      <c r="F743" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6">
+      <c r="A744" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B744" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C744" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E744">
+        <v>1962</v>
+      </c>
+      <c r="F744" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6">
+      <c r="A745" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B745" t="s">
+        <v>621</v>
+      </c>
+      <c r="C745" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E745">
+        <v>1969</v>
+      </c>
+      <c r="F745" t="s">
         <v>970</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA0EBAF-6EF3-EF41-A8D1-4D09CAB1C3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DE091F-4FB1-7B49-B157-B4E86CC49669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="2216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="2236">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6173,9 +6173,6 @@
     <t>Slowdive</t>
   </si>
   <si>
-    <t>George Thorogood</t>
-  </si>
-  <si>
     <t>Yeah Yeah Yeahs</t>
   </si>
   <si>
@@ -6224,15 +6221,9 @@
     <t>Slint</t>
   </si>
   <si>
-    <t>Erykah Badu</t>
-  </si>
-  <si>
     <t>My Bloody Valentine</t>
   </si>
   <si>
-    <t>Franz Ferdinand</t>
-  </si>
-  <si>
     <t>Eurythmics</t>
   </si>
   <si>
@@ -6257,9 +6248,6 @@
     <t>Iggy and the Stooges</t>
   </si>
   <si>
-    <t>George Michael</t>
-  </si>
-  <si>
     <t>First Aid Kit</t>
   </si>
   <si>
@@ -6404,9 +6392,6 @@
     <t>Christine and the Queens</t>
   </si>
   <si>
-    <t>Florence and the Machine</t>
-  </si>
-  <si>
     <t>Traveling Wilburys</t>
   </si>
   <si>
@@ -6443,9 +6428,6 @@
     <t>Cocteau Twins</t>
   </si>
   <si>
-    <t>Fela Kuti</t>
-  </si>
-  <si>
     <t>The Roots</t>
   </si>
   <si>
@@ -6518,9 +6500,6 @@
     <t>Muddy Waters</t>
   </si>
   <si>
-    <t>Ella Fitzgerald</t>
-  </si>
-  <si>
     <t>Johnnie Ray</t>
   </si>
   <si>
@@ -6560,9 +6539,6 @@
     <t>The Chieftains</t>
   </si>
   <si>
-    <t>Édith Piaf</t>
-  </si>
-  <si>
     <t>The Marvelettes</t>
   </si>
   <si>
@@ -6623,9 +6599,6 @@
     <t>Smash Mouth</t>
   </si>
   <si>
-    <t>Eminem</t>
-  </si>
-  <si>
     <t>Britney Spears</t>
   </si>
   <si>
@@ -6795,6 +6768,93 @@
   </si>
   <si>
     <t>Dion (1969)</t>
+  </si>
+  <si>
+    <t>One Day Like This</t>
+  </si>
+  <si>
+    <t>The Seldom Seen Kid</t>
+  </si>
+  <si>
+    <t>Ella Fitzgerald &amp; Louis Armstrong</t>
+  </si>
+  <si>
+    <t>Dream a Little Dream of Me</t>
+  </si>
+  <si>
+    <t>Ella and Louis</t>
+  </si>
+  <si>
+    <t>Waltz #2 (XO)</t>
+  </si>
+  <si>
+    <t>XO</t>
+  </si>
+  <si>
+    <t>At Last</t>
+  </si>
+  <si>
+    <t>At Last!</t>
+  </si>
+  <si>
+    <t>Here Comes the Rain Again</t>
+  </si>
+  <si>
+    <t>Touch</t>
+  </si>
+  <si>
+    <t>Criminal</t>
+  </si>
+  <si>
+    <t>Tidal</t>
+  </si>
+  <si>
+    <t>Emmylou</t>
+  </si>
+  <si>
+    <t>The Lion's Roar</t>
+  </si>
+  <si>
+    <t>Helplessness Blues</t>
+  </si>
+  <si>
+    <t>The Modern Leper</t>
+  </si>
+  <si>
+    <t>The Midnight Organ Fight</t>
+  </si>
+  <si>
+    <t>Waiting Room</t>
+  </si>
+  <si>
+    <t>13 Songs</t>
+  </si>
+  <si>
+    <t>Seasons (Waiting on You)</t>
+  </si>
+  <si>
+    <t>Singles</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>The Pleasure Principle</t>
+  </si>
+  <si>
+    <t>Move it on Over</t>
+  </si>
+  <si>
+    <t>George Thorogood &amp; The Destroyers</t>
+  </si>
+  <si>
+    <t>Best Thing that Ever Happened to Me</t>
+  </si>
+  <si>
+    <t>Imagination</t>
+  </si>
+  <si>
+    <t>St. Elsewhere</t>
   </si>
 </sst>
 </file>
@@ -7227,7 +7287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B149"/>
+  <dimension ref="B3:B126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7235,740 +7295,625 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2137</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2060</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>2158</v>
+      <c r="B7" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2025</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2134</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2028</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2028</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2098</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2047</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2037</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2020</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2085</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2027</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2016</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2121</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="1" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2054</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2036</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2008</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2048</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2073</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2075</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2050</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2125</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>2011</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" s="1" t="s">
-        <v>1998</v>
+      <c r="B30" t="s">
+        <v>2079</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>2076</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2035</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" t="s">
-        <v>2102</v>
+      <c r="B33" s="1" t="s">
+        <v>2005</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2059</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2059</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>2094</v>
+      <c r="B36" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2021</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>2051</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>2056</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2124</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2032</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2043</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="43" spans="2:2">
-      <c r="B43" s="1" t="s">
-        <v>2000</v>
+      <c r="B43" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2128</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" t="s">
-        <v>2033</v>
+      <c r="B45" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" t="s">
-        <v>2160</v>
+      <c r="B46" s="1" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2066</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2058</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2061</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2093</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>2144</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2103</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2083</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>2147</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>2107</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" s="1" t="s">
-        <v>2005</v>
+      <c r="B56" t="s">
+        <v>2041</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>2079</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" t="s">
-        <v>2135</v>
+      <c r="B58" s="1" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="59" spans="2:2">
-      <c r="B59" s="1" t="s">
-        <v>2004</v>
+      <c r="B59" t="s">
+        <v>2014</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2120</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2118</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2109</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2113</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64" t="s">
-        <v>2077</v>
+      <c r="B64" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2122</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2026</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="1" t="s">
-        <v>2006</v>
+      <c r="B68" t="s">
+        <v>2028</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="1" t="s">
-        <v>2002</v>
+      <c r="B69" t="s">
+        <v>2125</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2081</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>2071</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>2012</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2012</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2150</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" t="s">
-        <v>2110</v>
+      <c r="B76" s="1" t="s">
+        <v>2007</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>2069</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" t="s">
-        <v>2131</v>
+      <c r="B78" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>2045</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2130</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="1" t="s">
-        <v>1993</v>
+      <c r="B81" t="s">
+        <v>2098</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>2015</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" t="s">
-        <v>2161</v>
+      <c r="B83" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2017</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>2082</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" s="1" t="s">
-        <v>1994</v>
+      <c r="B87" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2126</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2115</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>2142</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2031</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>2132</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>2019</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>2064</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>2034</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>2022</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2018</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2024</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="99" spans="2:2">
-      <c r="B99" s="1" t="s">
-        <v>2007</v>
+      <c r="B99" t="s">
+        <v>2053</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>2157</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="101" spans="2:2">
-      <c r="B101" s="1" t="s">
-        <v>1997</v>
+      <c r="B101" t="s">
+        <v>2093</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>2089</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>2143</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>2104</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>2067</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="1" t="s">
-        <v>1995</v>
+      <c r="B106" t="s">
+        <v>2037</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>2038</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>2119</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>2068</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>999</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>2156</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>2063</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>2136</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>2065</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>1415</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>2070</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>2133</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>2111</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" t="s">
-        <v>2138</v>
+      <c r="B119" s="1" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" t="s">
-        <v>2096</v>
+      <c r="B120" s="1" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>2154</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>2057</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>2141</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>2099</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>2074</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="126" spans="2:2">
-      <c r="B126" t="s">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" t="s">
-        <v>2106</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2">
-      <c r="B131" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="137" spans="2:2">
-      <c r="B137" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2">
-      <c r="B138" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2">
-      <c r="B139" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2">
-      <c r="B140" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="141" spans="2:2">
-      <c r="B141" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2">
-      <c r="B142" s="1" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" s="1" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2">
-      <c r="B144" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2">
-      <c r="B145" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2">
-      <c r="B146" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2">
-      <c r="B147" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2">
-      <c r="B148" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2">
-      <c r="B149" s="1"/>
+      <c r="B126" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B149">
-    <sortCondition ref="B1:B149"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B126">
+    <sortCondition ref="B1:B126"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7977,7 +7922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F745"/>
+  <dimension ref="A1:F760"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -13207,7 +13152,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2149</v>
+        <v>2141</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17380,7 +17325,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2146</v>
+        <v>2138</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20531,13 +20476,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B717" t="s">
         <v>2153</v>
       </c>
-      <c r="B717" t="s">
-        <v>2162</v>
-      </c>
       <c r="C717" t="s">
-        <v>2163</v>
+        <v>2154</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20548,13 +20493,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="B718" t="s">
-        <v>2164</v>
+        <v>2155</v>
       </c>
       <c r="C718" t="s">
-        <v>2165</v>
+        <v>2156</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20565,13 +20510,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2167</v>
+        <v>2158</v>
       </c>
       <c r="B719" t="s">
-        <v>2166</v>
+        <v>2157</v>
       </c>
       <c r="C719" t="s">
-        <v>2167</v>
+        <v>2158</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20582,13 +20527,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="B720" t="s">
-        <v>2168</v>
+        <v>2159</v>
       </c>
       <c r="C720" t="s">
-        <v>2169</v>
+        <v>2160</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20599,13 +20544,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2108</v>
+        <v>2102</v>
       </c>
       <c r="B721" t="s">
-        <v>2170</v>
+        <v>2161</v>
       </c>
       <c r="C721" t="s">
-        <v>2171</v>
+        <v>2162</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20616,13 +20561,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="B722" t="s">
-        <v>2172</v>
+        <v>2163</v>
       </c>
       <c r="C722" t="s">
-        <v>2173</v>
+        <v>2164</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20633,13 +20578,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="B723" t="s">
-        <v>2174</v>
+        <v>2165</v>
       </c>
       <c r="C723" t="s">
-        <v>2175</v>
+        <v>2166</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20650,13 +20595,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="B724" t="s">
-        <v>2176</v>
+        <v>2167</v>
       </c>
       <c r="C724" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20667,13 +20612,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2145</v>
+        <v>2137</v>
       </c>
       <c r="B725" t="s">
-        <v>2177</v>
+        <v>2168</v>
       </c>
       <c r="C725" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20687,10 +20632,10 @@
         <v>1996</v>
       </c>
       <c r="B726" t="s">
-        <v>2179</v>
+        <v>2170</v>
       </c>
       <c r="C726" t="s">
-        <v>2180</v>
+        <v>2171</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20701,13 +20646,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
       <c r="B727" t="s">
-        <v>2181</v>
+        <v>2172</v>
       </c>
       <c r="C727" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20718,13 +20663,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2148</v>
+        <v>2140</v>
       </c>
       <c r="B728" t="s">
-        <v>2182</v>
+        <v>2173</v>
       </c>
       <c r="C728" t="s">
-        <v>2183</v>
+        <v>2174</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20735,13 +20680,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="B729" t="s">
-        <v>2184</v>
+        <v>2175</v>
       </c>
       <c r="C729" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20752,13 +20697,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="B730" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="C730" t="s">
-        <v>2187</v>
+        <v>2178</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20769,13 +20714,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="B731" t="s">
-        <v>2188</v>
+        <v>2179</v>
       </c>
       <c r="C731" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20786,13 +20731,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="B732" t="s">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="C732" t="s">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20803,13 +20748,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2159</v>
+        <v>2150</v>
       </c>
       <c r="B733" t="s">
-        <v>2191</v>
+        <v>2182</v>
       </c>
       <c r="C733" t="s">
-        <v>2192</v>
+        <v>2183</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20820,13 +20765,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2129</v>
+        <v>2122</v>
       </c>
       <c r="B734" t="s">
-        <v>2193</v>
+        <v>2184</v>
       </c>
       <c r="C734" t="s">
-        <v>2194</v>
+        <v>2185</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20837,13 +20782,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="B735" t="s">
-        <v>2195</v>
+        <v>2186</v>
       </c>
       <c r="C735" t="s">
-        <v>2196</v>
+        <v>2187</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20854,13 +20799,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="B736" t="s">
-        <v>2197</v>
+        <v>2188</v>
       </c>
       <c r="C736" t="s">
-        <v>2198</v>
+        <v>2189</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20871,13 +20816,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2155</v>
+        <v>2147</v>
       </c>
       <c r="B737" t="s">
-        <v>2199</v>
+        <v>2190</v>
       </c>
       <c r="C737" t="s">
-        <v>2200</v>
+        <v>2191</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20888,13 +20833,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2201</v>
+        <v>2192</v>
       </c>
       <c r="B738" t="s">
-        <v>2202</v>
+        <v>2193</v>
       </c>
       <c r="C738" t="s">
-        <v>2203</v>
+        <v>2194</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20905,13 +20850,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="B739" t="s">
-        <v>2204</v>
+        <v>2195</v>
       </c>
       <c r="C739" t="s">
-        <v>2205</v>
+        <v>2196</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20922,13 +20867,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2152</v>
+        <v>2144</v>
       </c>
       <c r="B740" t="s">
-        <v>2206</v>
+        <v>2197</v>
       </c>
       <c r="C740" t="s">
-        <v>2207</v>
+        <v>2198</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20939,13 +20884,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="B741" t="s">
-        <v>2208</v>
+        <v>2199</v>
       </c>
       <c r="C741" t="s">
-        <v>2208</v>
+        <v>2199</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20956,13 +20901,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2100</v>
+        <v>2094</v>
       </c>
       <c r="B742" t="s">
-        <v>2209</v>
+        <v>2200</v>
       </c>
       <c r="C742" t="s">
-        <v>2210</v>
+        <v>2201</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20973,13 +20918,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2151</v>
+        <v>2143</v>
       </c>
       <c r="B743" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="C743" t="s">
-        <v>2212</v>
+        <v>2203</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20990,13 +20935,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2140</v>
+        <v>2132</v>
       </c>
       <c r="B744" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="C744" t="s">
-        <v>2214</v>
+        <v>2205</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -21007,19 +20952,274 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2139</v>
+        <v>2131</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2215</v>
+        <v>2206</v>
       </c>
       <c r="E745">
         <v>1969</v>
       </c>
       <c r="F745" t="s">
         <v>970</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6">
+      <c r="A746" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B746" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C746" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E746">
+        <v>2008</v>
+      </c>
+      <c r="F746" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6">
+      <c r="A747" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B747" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C747" t="s">
+        <v>2211</v>
+      </c>
+      <c r="E747">
+        <v>1956</v>
+      </c>
+      <c r="F747" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6">
+      <c r="A748" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B748" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C748" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E748">
+        <v>1998</v>
+      </c>
+      <c r="F748" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6">
+      <c r="A749" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B749" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C749" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E749">
+        <v>1960</v>
+      </c>
+      <c r="F749" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6">
+      <c r="A750" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B750" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C750" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E750">
+        <v>1983</v>
+      </c>
+      <c r="F750" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6">
+      <c r="A751" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B751" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C751" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E751">
+        <v>1996</v>
+      </c>
+      <c r="F751" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6">
+      <c r="A752" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B752" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C752" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E752">
+        <v>2012</v>
+      </c>
+      <c r="F752" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6">
+      <c r="A753" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B753" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C753" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E753">
+        <v>2011</v>
+      </c>
+      <c r="F753" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6">
+      <c r="A754" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B754" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C754" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E754">
+        <v>2008</v>
+      </c>
+      <c r="F754" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6">
+      <c r="A755" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B755" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C755" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E755">
+        <v>1989</v>
+      </c>
+      <c r="F755" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6">
+      <c r="A756" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B756" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C756" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E756">
+        <v>2014</v>
+      </c>
+      <c r="F756" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6">
+      <c r="A757" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B757" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C757" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E757">
+        <v>1979</v>
+      </c>
+      <c r="F757" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6">
+      <c r="A758" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B758" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C758" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E758">
+        <v>1978</v>
+      </c>
+      <c r="F758" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6">
+      <c r="A759" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B759" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C759" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E759">
+        <v>1973</v>
+      </c>
+      <c r="F759" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6">
+      <c r="A760" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B760" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C760" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E760">
+        <v>2006</v>
+      </c>
+      <c r="F760" t="s">
+        <v>969</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DE091F-4FB1-7B49-B157-B4E86CC49669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80993FF7-C060-DD41-9F62-9F7334D53AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="2236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="2242">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6143,9 +6143,6 @@
     <t xml:space="preserve">Smashing Pumpkins </t>
   </si>
   <si>
-    <t>Ice Cube</t>
-  </si>
-  <si>
     <t>Wet Leg</t>
   </si>
   <si>
@@ -6362,9 +6359,6 @@
     <t>The Specials</t>
   </si>
   <si>
-    <t>Grandmaster Flash</t>
-  </si>
-  <si>
     <t>Idles</t>
   </si>
   <si>
@@ -6855,6 +6849,30 @@
   </si>
   <si>
     <t>St. Elsewhere</t>
+  </si>
+  <si>
+    <t>Welcome to the Jungle</t>
+  </si>
+  <si>
+    <t>Appetite for Destruction</t>
+  </si>
+  <si>
+    <t>Jambalaya (On the Bayou)</t>
+  </si>
+  <si>
+    <t>40 Greatest Hits</t>
+  </si>
+  <si>
+    <t>Mad About You</t>
+  </si>
+  <si>
+    <t>The Magnificant Tree</t>
+  </si>
+  <si>
+    <t>Danny Nedelko</t>
+  </si>
+  <si>
+    <t>Joy as an Act of Resistance</t>
   </si>
 </sst>
 </file>
@@ -7287,7 +7305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B126"/>
+  <dimension ref="B3:B119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7295,147 +7313,147 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2071</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2046</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2118</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2010</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="1" t="s">
-        <v>1998</v>
+      <c r="B7" t="s">
+        <v>2019</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2072</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2032</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2096</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2055</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2055</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>2089</v>
+      <c r="B13" s="1" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2020</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2047</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2052</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2117</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2029</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2039</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="1" t="s">
-        <v>2000</v>
+      <c r="B20" t="s">
+        <v>2086</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2121</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2030</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2151</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2062</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2054</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" t="s">
-        <v>2057</v>
+      <c r="B26" s="1" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2088</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2136</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" t="s">
-        <v>2097</v>
+      <c r="B29" s="1" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2079</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>2139</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="32" spans="2:2">
@@ -7444,476 +7462,441 @@
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="1" t="s">
-        <v>2005</v>
+      <c r="B33" t="s">
+        <v>2105</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2128</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="1" t="s">
-        <v>2004</v>
+      <c r="B36" t="s">
+        <v>2114</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2114</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" t="s">
-        <v>2112</v>
+      <c r="B38" s="1" t="s">
+        <v>2005</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" t="s">
-        <v>2103</v>
+      <c r="B39" s="1" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2107</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2111</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>2116</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" s="1" t="s">
-        <v>2006</v>
+      <c r="B45" t="s">
+        <v>2140</v>
       </c>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="1" t="s">
-        <v>2002</v>
+      <c r="B46" t="s">
+        <v>2102</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2077</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2067</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2011</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2011</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" t="s">
-        <v>2022</v>
+      <c r="B51" s="1" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2142</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2104</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>2065</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>2124</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>2041</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" t="s">
-        <v>2123</v>
+      <c r="B57" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="1" t="s">
-        <v>1993</v>
+      <c r="B58" t="s">
+        <v>2117</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>2014</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2152</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2016</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2078</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2068</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64" s="1" t="s">
-        <v>1994</v>
+      <c r="B64" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2119</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2109</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2134</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>2028</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" t="s">
-        <v>2125</v>
+      <c r="B69" s="1" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2018</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" t="s">
-        <v>2060</v>
+      <c r="B71" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>2031</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>2021</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2017</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2023</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="1" t="s">
-        <v>2007</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>2149</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="1" t="s">
-        <v>1997</v>
+      <c r="B78" t="s">
+        <v>2111</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>2084</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>2135</v>
+        <v>999</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>2098</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="1" t="s">
-        <v>1995</v>
+      <c r="B83" t="s">
+        <v>2127</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>2034</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>2113</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>999</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>2148</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>2059</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>2129</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>2061</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>1415</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>2066</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>2126</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>2105</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>2130</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>2091</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>2146</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>2053</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>2133</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>2093</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>2070</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>2087</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>2110</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>2108</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>2037</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>2100</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>2035</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>2009</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>2045</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>2120</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" t="s">
-        <v>2012</v>
+      <c r="B112" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" t="s">
-        <v>2013</v>
+      <c r="B113" s="1" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>2081</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>2026</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>2106</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>2082</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>2099</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="1" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="1" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2">
-      <c r="B122" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="1"/>
+      <c r="B119" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B126">
-    <sortCondition ref="B1:B126"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B119">
+    <sortCondition ref="B1:B119"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7922,7 +7905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F760"/>
+  <dimension ref="A1:F764"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -13152,7 +13135,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17325,7 +17308,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20476,13 +20459,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="B717" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="C717" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20493,13 +20476,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="B718" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C718" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20510,13 +20493,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="B719" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C719" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20527,13 +20510,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B720" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C720" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20544,13 +20527,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="B721" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C721" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20561,13 +20544,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="B722" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C722" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20578,13 +20561,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B723" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C723" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20595,13 +20578,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B724" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C724" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20612,13 +20595,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="B725" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="C725" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20632,10 +20615,10 @@
         <v>1996</v>
       </c>
       <c r="B726" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C726" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20646,13 +20629,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="B727" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="C727" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20663,13 +20646,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="B728" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="C728" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20680,13 +20663,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B729" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C729" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20697,13 +20680,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="B730" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="C730" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20714,13 +20697,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B731" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C731" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20731,13 +20714,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B732" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C732" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20748,13 +20731,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B733" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C733" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20765,13 +20748,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="B734" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="C734" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20782,13 +20765,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B735" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="C735" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20799,13 +20782,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="B736" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="C736" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20816,13 +20799,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B737" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="C737" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20833,13 +20816,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B738" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C738" t="s">
         <v>2192</v>
-      </c>
-      <c r="B738" t="s">
-        <v>2193</v>
-      </c>
-      <c r="C738" t="s">
-        <v>2194</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20850,13 +20833,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="B739" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C739" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20867,13 +20850,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="B740" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C740" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20884,13 +20867,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="B741" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C741" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20901,13 +20884,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="B742" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C742" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20918,13 +20901,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="B743" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C743" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20935,13 +20918,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="B744" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C744" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20952,13 +20935,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20969,13 +20952,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B746" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C746" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20986,13 +20969,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B747" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C747" t="s">
         <v>2209</v>
-      </c>
-      <c r="B747" t="s">
-        <v>2210</v>
-      </c>
-      <c r="C747" t="s">
-        <v>2211</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -21003,13 +20986,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B748" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C748" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -21020,13 +21003,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B749" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C749" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -21037,13 +21020,13 @@
     </row>
     <row r="750" spans="1:6">
       <c r="A750" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B750" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C750" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -21054,13 +21037,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B751" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C751" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -21071,13 +21054,13 @@
     </row>
     <row r="752" spans="1:6">
       <c r="A752" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B752" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="C752" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -21088,13 +21071,13 @@
     </row>
     <row r="753" spans="1:6">
       <c r="A753" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B753" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="C753" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -21105,13 +21088,13 @@
     </row>
     <row r="754" spans="1:6">
       <c r="A754" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B754" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C754" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -21122,13 +21105,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="B755" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C755" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -21139,13 +21122,13 @@
     </row>
     <row r="756" spans="1:6">
       <c r="A756" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B756" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C756" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -21156,13 +21139,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B757" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="C757" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -21173,13 +21156,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="B758" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="C758" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -21190,13 +21173,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B759" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="C759" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -21207,18 +21190,86 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="E760">
         <v>2006</v>
       </c>
       <c r="F760" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6">
+      <c r="A761" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B761" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C761" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E761">
+        <v>1987</v>
+      </c>
+      <c r="F761" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6">
+      <c r="A762" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B762" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C762" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E762">
+        <v>1952</v>
+      </c>
+      <c r="F762" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6">
+      <c r="A763" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B763" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C763" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E763">
+        <v>2000</v>
+      </c>
+      <c r="F763" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6">
+      <c r="A764" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B764" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C764" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E764">
+        <v>2018</v>
+      </c>
+      <c r="F764" t="s">
         <v>969</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80993FF7-C060-DD41-9F62-9F7334D53AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF2768C-EDD3-3149-9879-15F633D346FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3284" uniqueCount="2249">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6146,9 +6146,6 @@
     <t>Wet Leg</t>
   </si>
   <si>
-    <t>Joy Division</t>
-  </si>
-  <si>
     <t>Wolf Alice</t>
   </si>
   <si>
@@ -6158,9 +6155,6 @@
     <t>Future Islands</t>
   </si>
   <si>
-    <t>Massive Attack</t>
-  </si>
-  <si>
     <t>Mad Season</t>
   </si>
   <si>
@@ -6179,9 +6173,6 @@
     <t>Hooverphonic</t>
   </si>
   <si>
-    <t>Nina Simone</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toots and the Maytals </t>
   </si>
   <si>
@@ -6218,9 +6209,6 @@
     <t>Slint</t>
   </si>
   <si>
-    <t>My Bloody Valentine</t>
-  </si>
-  <si>
     <t>Eurythmics</t>
   </si>
   <si>
@@ -6242,9 +6230,6 @@
     <t>Sharon Van Etten</t>
   </si>
   <si>
-    <t>Iggy and the Stooges</t>
-  </si>
-  <si>
     <t>First Aid Kit</t>
   </si>
   <si>
@@ -6302,24 +6287,12 @@
     <t>Brad</t>
   </si>
   <si>
-    <t>Joan Jett</t>
-  </si>
-  <si>
     <t>The Replacements</t>
   </si>
   <si>
-    <t>Laurie Anderson</t>
-  </si>
-  <si>
-    <t>Janelle Monae</t>
-  </si>
-  <si>
     <t>Elliott Smith</t>
   </si>
   <si>
-    <t>Lauryn Hill</t>
-  </si>
-  <si>
     <t>Catherine Wheel</t>
   </si>
   <si>
@@ -6347,9 +6320,6 @@
     <t>The Gits</t>
   </si>
   <si>
-    <t>Neutral Milk Hotel</t>
-  </si>
-  <si>
     <t>Pulp</t>
   </si>
   <si>
@@ -6362,21 +6332,12 @@
     <t>Idles</t>
   </si>
   <si>
-    <t>Motorhead</t>
-  </si>
-  <si>
     <t>Wolf Parade</t>
   </si>
   <si>
-    <t>Magnetic Fields</t>
-  </si>
-  <si>
     <t>Cheap Trick</t>
   </si>
   <si>
-    <t>Neko Case</t>
-  </si>
-  <si>
     <t>Public Enemy</t>
   </si>
   <si>
@@ -6407,12 +6368,6 @@
     <t>The Sugarcubes</t>
   </si>
   <si>
-    <t>Le Tigre</t>
-  </si>
-  <si>
-    <t>Janes Addiction</t>
-  </si>
-  <si>
     <t>Amy Winehouse</t>
   </si>
   <si>
@@ -6434,9 +6389,6 @@
     <t>Iggy Pop</t>
   </si>
   <si>
-    <t>Leonard Cohen</t>
-  </si>
-  <si>
     <t>Stone Roses</t>
   </si>
   <si>
@@ -6452,9 +6404,6 @@
     <t>Big Star</t>
   </si>
   <si>
-    <t>Modern Lovers</t>
-  </si>
-  <si>
     <t>Parliament</t>
   </si>
   <si>
@@ -6464,9 +6413,6 @@
     <t>TV on the Radio</t>
   </si>
   <si>
-    <t>Mother Love Bone</t>
-  </si>
-  <si>
     <t>The Walkmen</t>
   </si>
   <si>
@@ -6476,12 +6422,6 @@
     <t>The Verve</t>
   </si>
   <si>
-    <t>Mountain Goats</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
     <t>Television</t>
   </si>
   <si>
@@ -6491,12 +6431,6 @@
     <t>Fugazi</t>
   </si>
   <si>
-    <t>Muddy Waters</t>
-  </si>
-  <si>
-    <t>Johnnie Ray</t>
-  </si>
-  <si>
     <t>Hank Williams</t>
   </si>
   <si>
@@ -6506,9 +6440,6 @@
     <t>Tony Bennett</t>
   </si>
   <si>
-    <t>Julie London</t>
-  </si>
-  <si>
     <t>Buddy Holly</t>
   </si>
   <si>
@@ -6527,9 +6458,6 @@
     <t>Etta James</t>
   </si>
   <si>
-    <t>Marty Robbins</t>
-  </si>
-  <si>
     <t>The Chieftains</t>
   </si>
   <si>
@@ -6551,9 +6479,6 @@
     <t>Steppenwolf</t>
   </si>
   <si>
-    <t>Led Zepellin</t>
-  </si>
-  <si>
     <t>Black Sabbath</t>
   </si>
   <si>
@@ -6873,6 +6798,102 @@
   </si>
   <si>
     <t>Joy as an Act of Resistance</t>
+  </si>
+  <si>
+    <t>Lust for Life</t>
+  </si>
+  <si>
+    <t>Hallelujah</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>The Harder They Come</t>
+  </si>
+  <si>
+    <t>The Man Comes Around</t>
+  </si>
+  <si>
+    <t>Help Me</t>
+  </si>
+  <si>
+    <t>Court and Spark</t>
+  </si>
+  <si>
+    <t>The Kick Inside</t>
+  </si>
+  <si>
+    <t>Wuthering Heights</t>
+  </si>
+  <si>
+    <t>Somewhere Only We Know</t>
+  </si>
+  <si>
+    <t>Hopes And Fears</t>
+  </si>
+  <si>
+    <t>Rainbow Connection</t>
+  </si>
+  <si>
+    <t>The Muppet Movie Soundtrack</t>
+  </si>
+  <si>
+    <t>I Love You, Suzanne</t>
+  </si>
+  <si>
+    <t>New Sensations</t>
+  </si>
+  <si>
+    <t>Sweet Home Alabama</t>
+  </si>
+  <si>
+    <t>Second Helping</t>
+  </si>
+  <si>
+    <t>Midnight City</t>
+  </si>
+  <si>
+    <t>Hurry Up, We’re Dreaming</t>
+  </si>
+  <si>
+    <t>River of Deceit</t>
+  </si>
+  <si>
+    <t>This Sky</t>
+  </si>
+  <si>
+    <t>The Derek Trucks</t>
+  </si>
+  <si>
+    <t>Songlines</t>
+  </si>
+  <si>
+    <t>The Champs</t>
+  </si>
+  <si>
+    <t>Taquila</t>
+  </si>
+  <si>
+    <t>Go, Champs, Go!</t>
+  </si>
+  <si>
+    <t>So Tonight That I Might See</t>
+  </si>
+  <si>
+    <t>Fade Into You</t>
+  </si>
+  <si>
+    <t>I’m Amazed</t>
+  </si>
+  <si>
+    <t>Evil Urges</t>
+  </si>
+  <si>
+    <t>Always Love</t>
+  </si>
+  <si>
+    <t>The Weight Is A Gift</t>
   </si>
 </sst>
 </file>
@@ -7305,598 +7326,393 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B119"/>
+  <dimension ref="B4:B79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>2031</v>
-      </c>
-    </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2094</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2054</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2019</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2046</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2051</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2115</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>2028</v>
+      <c r="B11" s="1" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2038</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="13" spans="2:2">
-      <c r="B13" s="1" t="s">
-        <v>1999</v>
+      <c r="B13" t="s">
+        <v>2125</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2119</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2029</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2149</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" t="s">
-        <v>2061</v>
+      <c r="B17" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2053</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2056</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>2086</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2134</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2095</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2077</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2137</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2099</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="1" t="s">
-        <v>2004</v>
+      <c r="B26" t="s">
+        <v>2017</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2073</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2126</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="1" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>2110</v>
+      <c r="B31" s="1" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2101</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2071</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2109</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>2114</v>
+      <c r="B36" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="1" t="s">
-        <v>2005</v>
+      <c r="B38" t="s">
+        <v>2091</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="1" t="s">
-        <v>2001</v>
+      <c r="B39" t="s">
+        <v>2054</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>2075</v>
+        <v>999</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2066</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2010</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>2010</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2021</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>2140</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>2102</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>2064</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>2122</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>2040</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>2121</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="1" t="s">
-        <v>1993</v>
+      <c r="B51" t="s">
+        <v>2119</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>2013</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>2150</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>2015</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>2076</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" s="1" t="s">
-        <v>1994</v>
+      <c r="B57" t="s">
+        <v>2090</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>2117</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>2107</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>2132</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>2123</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>2017</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>2059</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>2030</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>2020</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>2016</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="1" t="s">
-        <v>2006</v>
+      <c r="B69" t="s">
+        <v>2087</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>2147</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="1" t="s">
-        <v>1997</v>
+      <c r="B71" t="s">
+        <v>2081</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" t="s">
-        <v>2082</v>
+      <c r="B72" s="1" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" t="s">
-        <v>2133</v>
+      <c r="B73" s="1" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>2096</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="1" t="s">
-        <v>1995</v>
+      <c r="B76" t="s">
+        <v>2005</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>2033</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>2111</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2">
-      <c r="B87" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2">
-      <c r="B88" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2">
-      <c r="B89" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2">
-      <c r="B92" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" t="s">
-        <v>2106</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2">
-      <c r="B108" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" t="s">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="1" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="1" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="1"/>
+      <c r="B79" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B119">
-    <sortCondition ref="B1:B119"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B79">
+    <sortCondition ref="B1:B79"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7905,7 +7721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F764"/>
+  <dimension ref="A1:F781"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -13135,7 +12951,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2139</v>
+        <v>2114</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17308,7 +17124,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2136</v>
+        <v>2111</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20459,13 +20275,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2143</v>
+        <v>2118</v>
       </c>
       <c r="B717" t="s">
-        <v>2151</v>
+        <v>2126</v>
       </c>
       <c r="C717" t="s">
-        <v>2152</v>
+        <v>2127</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20476,13 +20292,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2088</v>
+        <v>2073</v>
       </c>
       <c r="B718" t="s">
-        <v>2153</v>
+        <v>2128</v>
       </c>
       <c r="C718" t="s">
-        <v>2154</v>
+        <v>2129</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20493,13 +20309,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2156</v>
+        <v>2131</v>
       </c>
       <c r="B719" t="s">
-        <v>2155</v>
+        <v>2130</v>
       </c>
       <c r="C719" t="s">
-        <v>2156</v>
+        <v>2131</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20510,13 +20326,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B720" t="s">
-        <v>2157</v>
+        <v>2132</v>
       </c>
       <c r="C720" t="s">
-        <v>2158</v>
+        <v>2133</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20527,13 +20343,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2100</v>
+        <v>2084</v>
       </c>
       <c r="B721" t="s">
-        <v>2159</v>
+        <v>2134</v>
       </c>
       <c r="C721" t="s">
-        <v>2160</v>
+        <v>2135</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20544,13 +20360,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2083</v>
+        <v>2070</v>
       </c>
       <c r="B722" t="s">
-        <v>2161</v>
+        <v>2136</v>
       </c>
       <c r="C722" t="s">
-        <v>2162</v>
+        <v>2137</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20561,13 +20377,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B723" t="s">
-        <v>2163</v>
+        <v>2138</v>
       </c>
       <c r="C723" t="s">
-        <v>2164</v>
+        <v>2139</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20578,13 +20394,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B724" t="s">
-        <v>2165</v>
+        <v>2140</v>
       </c>
       <c r="C724" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20595,13 +20411,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2135</v>
+        <v>2110</v>
       </c>
       <c r="B725" t="s">
-        <v>2166</v>
+        <v>2141</v>
       </c>
       <c r="C725" t="s">
-        <v>2167</v>
+        <v>2142</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20615,10 +20431,10 @@
         <v>1996</v>
       </c>
       <c r="B726" t="s">
-        <v>2168</v>
+        <v>2143</v>
       </c>
       <c r="C726" t="s">
-        <v>2169</v>
+        <v>2144</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20629,13 +20445,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2093</v>
+        <v>2078</v>
       </c>
       <c r="B727" t="s">
-        <v>2170</v>
+        <v>2145</v>
       </c>
       <c r="C727" t="s">
-        <v>2093</v>
+        <v>2078</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20646,13 +20462,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2138</v>
+        <v>2113</v>
       </c>
       <c r="B728" t="s">
-        <v>2171</v>
+        <v>2146</v>
       </c>
       <c r="C728" t="s">
-        <v>2172</v>
+        <v>2147</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20663,13 +20479,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="B729" t="s">
-        <v>2173</v>
+        <v>2148</v>
       </c>
       <c r="C729" t="s">
-        <v>2174</v>
+        <v>2149</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20680,13 +20496,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2084</v>
+        <v>2071</v>
       </c>
       <c r="B730" t="s">
-        <v>2175</v>
+        <v>2150</v>
       </c>
       <c r="C730" t="s">
-        <v>2176</v>
+        <v>2151</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20697,13 +20513,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B731" t="s">
-        <v>2177</v>
+        <v>2152</v>
       </c>
       <c r="C731" t="s">
-        <v>2178</v>
+        <v>2153</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20714,13 +20530,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B732" t="s">
-        <v>2179</v>
+        <v>2154</v>
       </c>
       <c r="C732" t="s">
-        <v>2179</v>
+        <v>2154</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20731,13 +20547,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2148</v>
+        <v>2123</v>
       </c>
       <c r="B733" t="s">
-        <v>2180</v>
+        <v>2155</v>
       </c>
       <c r="C733" t="s">
-        <v>2181</v>
+        <v>2156</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20748,13 +20564,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2120</v>
+        <v>2097</v>
       </c>
       <c r="B734" t="s">
-        <v>2182</v>
+        <v>2157</v>
       </c>
       <c r="C734" t="s">
-        <v>2183</v>
+        <v>2158</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20765,13 +20581,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2057</v>
+        <v>2048</v>
       </c>
       <c r="B735" t="s">
-        <v>2184</v>
+        <v>2159</v>
       </c>
       <c r="C735" t="s">
-        <v>2185</v>
+        <v>2160</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20782,13 +20598,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2074</v>
+        <v>2062</v>
       </c>
       <c r="B736" t="s">
-        <v>2186</v>
+        <v>2161</v>
       </c>
       <c r="C736" t="s">
-        <v>2187</v>
+        <v>2162</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20799,13 +20615,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2145</v>
+        <v>2120</v>
       </c>
       <c r="B737" t="s">
-        <v>2188</v>
+        <v>2163</v>
       </c>
       <c r="C737" t="s">
-        <v>2189</v>
+        <v>2164</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20816,13 +20632,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2190</v>
+        <v>2165</v>
       </c>
       <c r="B738" t="s">
-        <v>2191</v>
+        <v>2166</v>
       </c>
       <c r="C738" t="s">
-        <v>2192</v>
+        <v>2167</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20833,13 +20649,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2078</v>
+        <v>2065</v>
       </c>
       <c r="B739" t="s">
-        <v>2193</v>
+        <v>2168</v>
       </c>
       <c r="C739" t="s">
-        <v>2194</v>
+        <v>2169</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20850,13 +20666,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2142</v>
+        <v>2117</v>
       </c>
       <c r="B740" t="s">
-        <v>2195</v>
+        <v>2170</v>
       </c>
       <c r="C740" t="s">
-        <v>2196</v>
+        <v>2171</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20867,13 +20683,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2090</v>
+        <v>2075</v>
       </c>
       <c r="B741" t="s">
-        <v>2197</v>
+        <v>2172</v>
       </c>
       <c r="C741" t="s">
-        <v>2197</v>
+        <v>2172</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20884,13 +20700,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2092</v>
+        <v>2077</v>
       </c>
       <c r="B742" t="s">
-        <v>2198</v>
+        <v>2173</v>
       </c>
       <c r="C742" t="s">
-        <v>2199</v>
+        <v>2174</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20901,13 +20717,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2141</v>
+        <v>2116</v>
       </c>
       <c r="B743" t="s">
-        <v>2200</v>
+        <v>2175</v>
       </c>
       <c r="C743" t="s">
-        <v>2201</v>
+        <v>2176</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20918,13 +20734,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2130</v>
+        <v>2106</v>
       </c>
       <c r="B744" t="s">
-        <v>2202</v>
+        <v>2177</v>
       </c>
       <c r="C744" t="s">
-        <v>2203</v>
+        <v>2178</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20935,13 +20751,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2129</v>
+        <v>2105</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2204</v>
+        <v>2179</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20952,13 +20768,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B746" t="s">
-        <v>2205</v>
+        <v>2180</v>
       </c>
       <c r="C746" t="s">
-        <v>2206</v>
+        <v>2181</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20969,13 +20785,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
-        <v>2207</v>
+        <v>2182</v>
       </c>
       <c r="B747" t="s">
-        <v>2208</v>
+        <v>2183</v>
       </c>
       <c r="C747" t="s">
-        <v>2209</v>
+        <v>2184</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -20986,13 +20802,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2055</v>
+        <v>2047</v>
       </c>
       <c r="B748" t="s">
-        <v>2210</v>
+        <v>2185</v>
       </c>
       <c r="C748" t="s">
-        <v>2211</v>
+        <v>2186</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -21003,13 +20819,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2125</v>
+        <v>2102</v>
       </c>
       <c r="B749" t="s">
-        <v>2212</v>
+        <v>2187</v>
       </c>
       <c r="C749" t="s">
-        <v>2213</v>
+        <v>2188</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -21020,13 +20836,13 @@
     </row>
     <row r="750" spans="1:6">
       <c r="A750" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B750" t="s">
-        <v>2214</v>
+        <v>2189</v>
       </c>
       <c r="C750" t="s">
-        <v>2215</v>
+        <v>2190</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -21037,13 +20853,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B751" t="s">
-        <v>2216</v>
+        <v>2191</v>
       </c>
       <c r="C751" t="s">
-        <v>2217</v>
+        <v>2192</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -21054,13 +20870,13 @@
     </row>
     <row r="752" spans="1:6">
       <c r="A752" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B752" t="s">
-        <v>2218</v>
+        <v>2193</v>
       </c>
       <c r="C752" t="s">
-        <v>2219</v>
+        <v>2194</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -21071,13 +20887,13 @@
     </row>
     <row r="753" spans="1:6">
       <c r="A753" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B753" t="s">
-        <v>2220</v>
+        <v>2195</v>
       </c>
       <c r="C753" t="s">
-        <v>2220</v>
+        <v>2195</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -21088,13 +20904,13 @@
     </row>
     <row r="754" spans="1:6">
       <c r="A754" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B754" t="s">
-        <v>2221</v>
+        <v>2196</v>
       </c>
       <c r="C754" t="s">
-        <v>2222</v>
+        <v>2197</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -21105,13 +20921,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2113</v>
+        <v>2093</v>
       </c>
       <c r="B755" t="s">
-        <v>2223</v>
+        <v>2198</v>
       </c>
       <c r="C755" t="s">
-        <v>2224</v>
+        <v>2199</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -21122,13 +20938,13 @@
     </row>
     <row r="756" spans="1:6">
       <c r="A756" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B756" t="s">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="C756" t="s">
-        <v>2226</v>
+        <v>2201</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -21139,13 +20955,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B757" t="s">
-        <v>2227</v>
+        <v>2202</v>
       </c>
       <c r="C757" t="s">
-        <v>2228</v>
+        <v>2203</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -21156,13 +20972,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2230</v>
+        <v>2205</v>
       </c>
       <c r="B758" t="s">
-        <v>2229</v>
+        <v>2204</v>
       </c>
       <c r="C758" t="s">
-        <v>2229</v>
+        <v>2204</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -21173,13 +20989,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B759" t="s">
-        <v>2231</v>
+        <v>2206</v>
       </c>
       <c r="C759" t="s">
-        <v>2232</v>
+        <v>2207</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -21190,13 +21006,13 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2068</v>
+        <v>2058</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2233</v>
+        <v>2208</v>
       </c>
       <c r="E760">
         <v>2006</v>
@@ -21207,13 +21023,13 @@
     </row>
     <row r="761" spans="1:6">
       <c r="A761" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B761" t="s">
-        <v>2234</v>
+        <v>2209</v>
       </c>
       <c r="C761" t="s">
-        <v>2235</v>
+        <v>2210</v>
       </c>
       <c r="E761">
         <v>1987</v>
@@ -21224,13 +21040,13 @@
     </row>
     <row r="762" spans="1:6">
       <c r="A762" t="s">
-        <v>2116</v>
+        <v>2094</v>
       </c>
       <c r="B762" t="s">
-        <v>2236</v>
+        <v>2211</v>
       </c>
       <c r="C762" t="s">
-        <v>2237</v>
+        <v>2212</v>
       </c>
       <c r="E762">
         <v>1952</v>
@@ -21241,13 +21057,13 @@
     </row>
     <row r="763" spans="1:6">
       <c r="A763" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B763" t="s">
-        <v>2238</v>
+        <v>2213</v>
       </c>
       <c r="C763" t="s">
-        <v>2239</v>
+        <v>2214</v>
       </c>
       <c r="E763">
         <v>2000</v>
@@ -21258,18 +21074,307 @@
     </row>
     <row r="764" spans="1:6">
       <c r="A764" t="s">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B764" t="s">
-        <v>2240</v>
+        <v>2215</v>
       </c>
       <c r="C764" t="s">
-        <v>2241</v>
+        <v>2216</v>
       </c>
       <c r="E764">
         <v>2018</v>
       </c>
       <c r="F764" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6">
+      <c r="A765" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B765" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C765" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E765">
+        <v>1977</v>
+      </c>
+      <c r="F765" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6">
+      <c r="A766" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B766" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C766" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E766">
+        <v>1994</v>
+      </c>
+      <c r="F766" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6">
+      <c r="A767" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B767" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C767" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E767">
+        <v>1972</v>
+      </c>
+      <c r="F767" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6">
+      <c r="A768" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B768" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C768" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E768">
+        <v>2002</v>
+      </c>
+      <c r="F768" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6">
+      <c r="A769" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B769" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C769" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E769">
+        <v>1974</v>
+      </c>
+      <c r="F769" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6">
+      <c r="A770" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B770" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C770" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E770">
+        <v>1978</v>
+      </c>
+      <c r="F770" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6">
+      <c r="A771" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B771" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C771" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E771">
+        <v>2004</v>
+      </c>
+      <c r="F771" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6">
+      <c r="A772" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B772" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C772" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E772">
+        <v>1979</v>
+      </c>
+      <c r="F772" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6">
+      <c r="A773" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B773" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C773" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E773">
+        <v>1984</v>
+      </c>
+      <c r="F773" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6">
+      <c r="A774" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B774" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C774" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E774">
+        <v>1974</v>
+      </c>
+      <c r="F774" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6">
+      <c r="A775" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B775" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C775" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E775">
+        <v>2011</v>
+      </c>
+      <c r="F775" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6">
+      <c r="A776" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B776" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C776" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E776">
+        <v>1995</v>
+      </c>
+      <c r="F776" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6">
+      <c r="A777" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B777" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C777" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E777">
+        <v>2006</v>
+      </c>
+      <c r="F777" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6">
+      <c r="A778" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B778" s="8" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C778" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E778">
+        <v>1958</v>
+      </c>
+      <c r="F778" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6">
+      <c r="A779" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B779" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C779" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E779">
+        <v>1993</v>
+      </c>
+      <c r="F779" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6">
+      <c r="A780" s="1" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B780" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C780" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E780">
+        <v>2008</v>
+      </c>
+      <c r="F780" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6">
+      <c r="A781" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B781" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C781" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E781">
+        <v>2005</v>
+      </c>
+      <c r="F781" t="s">
         <v>969</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF2768C-EDD3-3149-9879-15F633D346FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AC1EA0-F814-1B47-90DF-8C1B7D01214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Id Media Type" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$801</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3284" uniqueCount="2249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="2273">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6128,21 +6128,12 @@
     <t>Greatest Hits - Orginal Recordings</t>
   </si>
   <si>
-    <t>Pet Shop Boys</t>
-  </si>
-  <si>
     <t>Radiohead</t>
   </si>
   <si>
-    <t>Suicidal Tendencies</t>
-  </si>
-  <si>
     <t>Blondie</t>
   </si>
   <si>
-    <t xml:space="preserve">Smashing Pumpkins </t>
-  </si>
-  <si>
     <t>Wet Leg</t>
   </si>
   <si>
@@ -6161,9 +6152,6 @@
     <t>My Morning Jacket</t>
   </si>
   <si>
-    <t>Slowdive</t>
-  </si>
-  <si>
     <t>Yeah Yeah Yeahs</t>
   </si>
   <si>
@@ -6179,21 +6167,9 @@
     <t>Traci Chapman</t>
   </si>
   <si>
-    <t>PJ Harvey</t>
-  </si>
-  <si>
     <t>Frightened Rabbit</t>
   </si>
   <si>
-    <t>Portishead</t>
-  </si>
-  <si>
-    <t>Sleater Kinney</t>
-  </si>
-  <si>
-    <t>Sault</t>
-  </si>
-  <si>
     <t>Fleet Foxes</t>
   </si>
   <si>
@@ -6206,9 +6182,6 @@
     <t>Oasis</t>
   </si>
   <si>
-    <t>Slint</t>
-  </si>
-  <si>
     <t>Eurythmics</t>
   </si>
   <si>
@@ -6218,18 +6191,12 @@
     <t>Bob Mould</t>
   </si>
   <si>
-    <t>Run DMC</t>
-  </si>
-  <si>
     <t>Johnny Cash</t>
   </si>
   <si>
     <t>Kate Bush</t>
   </si>
   <si>
-    <t>Sharon Van Etten</t>
-  </si>
-  <si>
     <t>First Aid Kit</t>
   </si>
   <si>
@@ -6254,9 +6221,6 @@
     <t>Brandi Carlile</t>
   </si>
   <si>
-    <t>Pavement</t>
-  </si>
-  <si>
     <t>Black Pumas</t>
   </si>
   <si>
@@ -6308,9 +6272,6 @@
     <t>Kermit the Frog</t>
   </si>
   <si>
-    <t>Sufjan Stevens</t>
-  </si>
-  <si>
     <t>Temple of the Dog</t>
   </si>
   <si>
@@ -6320,9 +6281,6 @@
     <t>The Gits</t>
   </si>
   <si>
-    <t>Pulp</t>
-  </si>
-  <si>
     <t>Gnarls Barkley</t>
   </si>
   <si>
@@ -6338,9 +6296,6 @@
     <t>Cheap Trick</t>
   </si>
   <si>
-    <t>Public Enemy</t>
-  </si>
-  <si>
     <t>Lou Reed</t>
   </si>
   <si>
@@ -6356,9 +6311,6 @@
     <t>X Ray Spex</t>
   </si>
   <si>
-    <t>Songs: Ohia</t>
-  </si>
-  <si>
     <t>Big Thief</t>
   </si>
   <si>
@@ -6404,9 +6356,6 @@
     <t>Big Star</t>
   </si>
   <si>
-    <t>Parliament</t>
-  </si>
-  <si>
     <t>The Knife</t>
   </si>
   <si>
@@ -6416,9 +6365,6 @@
     <t>The Walkmen</t>
   </si>
   <si>
-    <t>Robyn</t>
-  </si>
-  <si>
     <t>The Verve</t>
   </si>
   <si>
@@ -6479,9 +6425,6 @@
     <t>Steppenwolf</t>
   </si>
   <si>
-    <t>Black Sabbath</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Eagles</t>
   </si>
   <si>
@@ -6894,6 +6837,135 @@
   </si>
   <si>
     <t>The Weight Is A Gift</t>
+  </si>
+  <si>
+    <t>(What’s the Story) Morning Glory?</t>
+  </si>
+  <si>
+    <t>Wonderwall</t>
+  </si>
+  <si>
+    <t>Because the Night</t>
+  </si>
+  <si>
+    <t>Easter</t>
+  </si>
+  <si>
+    <t>Anka</t>
+  </si>
+  <si>
+    <t>(You’re) Having My Baby (feat. Odia Coates)</t>
+  </si>
+  <si>
+    <t>I'm a Woman</t>
+  </si>
+  <si>
+    <t>Hey There Delilah</t>
+  </si>
+  <si>
+    <t>All That We Needed</t>
+  </si>
+  <si>
+    <t>Peter Tosh</t>
+  </si>
+  <si>
+    <t>Wanted Dread or Alive</t>
+  </si>
+  <si>
+    <t>Bush Doctor</t>
+  </si>
+  <si>
+    <t>Jay Ferguson</t>
+  </si>
+  <si>
+    <t>Thunder Island</t>
+  </si>
+  <si>
+    <t>Human League</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>Martha and the Vandellas</t>
+  </si>
+  <si>
+    <t>Nowhere to Run</t>
+  </si>
+  <si>
+    <t>Dance Party</t>
+  </si>
+  <si>
+    <t>The Thrills</t>
+  </si>
+  <si>
+    <t>One Horse Town</t>
+  </si>
+  <si>
+    <t>So Much For The City</t>
+  </si>
+  <si>
+    <t>Karma Police</t>
+  </si>
+  <si>
+    <t>OK Computer OKNOTOK</t>
+  </si>
+  <si>
+    <t>What’d I Say Pt. 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>Pure Genius- The Complete Atlantic Recordings (1952-1959)</t>
+  </si>
+  <si>
+    <t>House of Pain</t>
+  </si>
+  <si>
+    <t>Jump Around</t>
+  </si>
+  <si>
+    <t>House of Pain (Fine Malt Lyrics)</t>
+  </si>
+  <si>
+    <t>You Got It</t>
+  </si>
+  <si>
+    <t>Mystery Girl</t>
+  </si>
+  <si>
+    <t>Sleep Walk</t>
+  </si>
+  <si>
+    <t>Nearly Lost You</t>
+  </si>
+  <si>
+    <t>Sweet Oblivion</t>
+  </si>
+  <si>
+    <t>Kiss Them For Me</t>
+  </si>
+  <si>
+    <t>Superstition</t>
+  </si>
+  <si>
+    <t>All Star</t>
+  </si>
+  <si>
+    <t>Astro Lounge</t>
+  </si>
+  <si>
+    <t>Magic Carpet Ride</t>
+  </si>
+  <si>
+    <t>The Second</t>
+  </si>
+  <si>
+    <t>Love Spreads</t>
+  </si>
+  <si>
+    <t>Second Coming</t>
   </si>
 </sst>
 </file>
@@ -7326,85 +7398,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B4:B79"/>
+  <dimension ref="B3:B45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>2017</v>
+      </c>
+    </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2018</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2115</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2085</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2055</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2099</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2035</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2098</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="11" spans="2:2">
-      <c r="B11" s="1" t="s">
-        <v>1993</v>
+      <c r="B11" t="s">
+        <v>1415</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2010</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2125</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2012</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2063</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="1" t="s">
-        <v>1994</v>
+      <c r="B17" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2095</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="19" spans="2:2">
@@ -7414,305 +7491,135 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>2108</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>2023</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2100</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2014</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2050</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2017</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>2019</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" s="1" t="s">
-        <v>2004</v>
+      <c r="B29" t="s">
+        <v>2027</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>2122</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" s="1" t="s">
-        <v>1997</v>
+      <c r="B31" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>2069</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>2109</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>2080</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>2053</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="1" t="s">
-        <v>1995</v>
+      <c r="B36" t="s">
+        <v>2052</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>2028</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" t="s">
-        <v>2091</v>
+      <c r="B38" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" t="s">
-        <v>2054</v>
+      <c r="B39" s="1" t="s">
+        <v>1996</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>999</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>2121</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>2049</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>2103</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>2051</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" t="s">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="1" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="1" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="1"/>
+      <c r="B45" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B79">
-    <sortCondition ref="B1:B79"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B45">
+    <sortCondition ref="B1:B45"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7721,7 +7628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F781"/>
+  <dimension ref="A1:F801"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -12951,7 +12858,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2114</v>
+        <v>2095</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17124,7 +17031,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2111</v>
+        <v>2092</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20275,13 +20182,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2118</v>
+        <v>2099</v>
       </c>
       <c r="B717" t="s">
-        <v>2126</v>
+        <v>2107</v>
       </c>
       <c r="C717" t="s">
-        <v>2127</v>
+        <v>2108</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20292,13 +20199,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2073</v>
+        <v>2057</v>
       </c>
       <c r="B718" t="s">
-        <v>2128</v>
+        <v>2109</v>
       </c>
       <c r="C718" t="s">
-        <v>2129</v>
+        <v>2110</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20309,13 +20216,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2131</v>
+        <v>2112</v>
       </c>
       <c r="B719" t="s">
-        <v>2130</v>
+        <v>2111</v>
       </c>
       <c r="C719" t="s">
-        <v>2131</v>
+        <v>2112</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20326,13 +20233,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2042</v>
+        <v>2030</v>
       </c>
       <c r="B720" t="s">
-        <v>2132</v>
+        <v>2113</v>
       </c>
       <c r="C720" t="s">
-        <v>2133</v>
+        <v>2114</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20343,13 +20250,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2084</v>
+        <v>2068</v>
       </c>
       <c r="B721" t="s">
-        <v>2134</v>
+        <v>2115</v>
       </c>
       <c r="C721" t="s">
-        <v>2135</v>
+        <v>2116</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20360,13 +20267,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2070</v>
+        <v>2054</v>
       </c>
       <c r="B722" t="s">
-        <v>2136</v>
+        <v>2117</v>
       </c>
       <c r="C722" t="s">
-        <v>2137</v>
+        <v>2118</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20377,13 +20284,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2043</v>
+        <v>2031</v>
       </c>
       <c r="B723" t="s">
-        <v>2138</v>
+        <v>2119</v>
       </c>
       <c r="C723" t="s">
-        <v>2139</v>
+        <v>2120</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20394,13 +20301,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="B724" t="s">
-        <v>2140</v>
+        <v>2121</v>
       </c>
       <c r="C724" t="s">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20411,13 +20318,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2110</v>
+        <v>2096</v>
       </c>
       <c r="B725" t="s">
-        <v>2141</v>
+        <v>2122</v>
       </c>
       <c r="C725" t="s">
-        <v>2142</v>
+        <v>2123</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20428,13 +20335,13 @@
     </row>
     <row r="726" spans="1:6">
       <c r="A726" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B726" t="s">
-        <v>2143</v>
+        <v>2124</v>
       </c>
       <c r="C726" t="s">
-        <v>2144</v>
+        <v>2125</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20445,13 +20352,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2078</v>
+        <v>2062</v>
       </c>
       <c r="B727" t="s">
-        <v>2145</v>
+        <v>2126</v>
       </c>
       <c r="C727" t="s">
-        <v>2078</v>
+        <v>2062</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20462,13 +20369,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2113</v>
+        <v>2094</v>
       </c>
       <c r="B728" t="s">
-        <v>2146</v>
+        <v>2127</v>
       </c>
       <c r="C728" t="s">
-        <v>2147</v>
+        <v>2128</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20479,13 +20386,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="B729" t="s">
-        <v>2148</v>
+        <v>2129</v>
       </c>
       <c r="C729" t="s">
-        <v>2149</v>
+        <v>2130</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20496,13 +20403,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2071</v>
+        <v>2055</v>
       </c>
       <c r="B730" t="s">
-        <v>2150</v>
+        <v>2131</v>
       </c>
       <c r="C730" t="s">
-        <v>2151</v>
+        <v>2132</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20513,13 +20420,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2045</v>
+        <v>2033</v>
       </c>
       <c r="B731" t="s">
-        <v>2152</v>
+        <v>2133</v>
       </c>
       <c r="C731" t="s">
-        <v>2153</v>
+        <v>2134</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20530,13 +20437,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2034</v>
+        <v>2023</v>
       </c>
       <c r="B732" t="s">
-        <v>2154</v>
+        <v>2135</v>
       </c>
       <c r="C732" t="s">
-        <v>2154</v>
+        <v>2135</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20547,13 +20454,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2123</v>
+        <v>2104</v>
       </c>
       <c r="B733" t="s">
-        <v>2155</v>
+        <v>2136</v>
       </c>
       <c r="C733" t="s">
-        <v>2156</v>
+        <v>2137</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20564,13 +20471,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2097</v>
+        <v>2079</v>
       </c>
       <c r="B734" t="s">
-        <v>2157</v>
+        <v>2138</v>
       </c>
       <c r="C734" t="s">
-        <v>2158</v>
+        <v>2139</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20581,13 +20488,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="B735" t="s">
-        <v>2159</v>
+        <v>2140</v>
       </c>
       <c r="C735" t="s">
-        <v>2160</v>
+        <v>2141</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20598,13 +20505,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2062</v>
+        <v>2048</v>
       </c>
       <c r="B736" t="s">
-        <v>2161</v>
+        <v>2142</v>
       </c>
       <c r="C736" t="s">
-        <v>2162</v>
+        <v>2143</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20615,13 +20522,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2120</v>
+        <v>2101</v>
       </c>
       <c r="B737" t="s">
-        <v>2163</v>
+        <v>2144</v>
       </c>
       <c r="C737" t="s">
-        <v>2164</v>
+        <v>2145</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20632,13 +20539,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2165</v>
+        <v>2146</v>
       </c>
       <c r="B738" t="s">
-        <v>2166</v>
+        <v>2147</v>
       </c>
       <c r="C738" t="s">
-        <v>2167</v>
+        <v>2148</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20649,13 +20556,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2065</v>
+        <v>2050</v>
       </c>
       <c r="B739" t="s">
-        <v>2168</v>
+        <v>2149</v>
       </c>
       <c r="C739" t="s">
-        <v>2169</v>
+        <v>2150</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20666,13 +20573,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2117</v>
+        <v>2098</v>
       </c>
       <c r="B740" t="s">
-        <v>2170</v>
+        <v>2151</v>
       </c>
       <c r="C740" t="s">
-        <v>2171</v>
+        <v>2152</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20683,13 +20590,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2075</v>
+        <v>2059</v>
       </c>
       <c r="B741" t="s">
-        <v>2172</v>
+        <v>2153</v>
       </c>
       <c r="C741" t="s">
-        <v>2172</v>
+        <v>2153</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20700,13 +20607,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2077</v>
+        <v>2061</v>
       </c>
       <c r="B742" t="s">
-        <v>2173</v>
+        <v>2154</v>
       </c>
       <c r="C742" t="s">
-        <v>2174</v>
+        <v>2155</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20717,13 +20624,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2116</v>
+        <v>2097</v>
       </c>
       <c r="B743" t="s">
-        <v>2175</v>
+        <v>2156</v>
       </c>
       <c r="C743" t="s">
-        <v>2176</v>
+        <v>2157</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20734,13 +20641,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2106</v>
+        <v>2088</v>
       </c>
       <c r="B744" t="s">
-        <v>2177</v>
+        <v>2158</v>
       </c>
       <c r="C744" t="s">
-        <v>2178</v>
+        <v>2159</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20751,13 +20658,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2105</v>
+        <v>2087</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2179</v>
+        <v>2160</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20768,13 +20675,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2030</v>
+        <v>2019</v>
       </c>
       <c r="B746" t="s">
-        <v>2180</v>
+        <v>2161</v>
       </c>
       <c r="C746" t="s">
-        <v>2181</v>
+        <v>2162</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20785,13 +20692,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
-        <v>2182</v>
+        <v>2163</v>
       </c>
       <c r="B747" t="s">
-        <v>2183</v>
+        <v>2164</v>
       </c>
       <c r="C747" t="s">
-        <v>2184</v>
+        <v>2165</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -20802,13 +20709,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2047</v>
+        <v>2035</v>
       </c>
       <c r="B748" t="s">
-        <v>2185</v>
+        <v>2166</v>
       </c>
       <c r="C748" t="s">
-        <v>2186</v>
+        <v>2167</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -20819,13 +20726,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2102</v>
+        <v>2084</v>
       </c>
       <c r="B749" t="s">
-        <v>2187</v>
+        <v>2168</v>
       </c>
       <c r="C749" t="s">
-        <v>2188</v>
+        <v>2169</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -20836,13 +20743,13 @@
     </row>
     <row r="750" spans="1:6">
       <c r="A750" t="s">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="B750" t="s">
-        <v>2189</v>
+        <v>2170</v>
       </c>
       <c r="C750" t="s">
-        <v>2190</v>
+        <v>2171</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -20853,13 +20760,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2037</v>
+        <v>2025</v>
       </c>
       <c r="B751" t="s">
-        <v>2191</v>
+        <v>2172</v>
       </c>
       <c r="C751" t="s">
-        <v>2192</v>
+        <v>2173</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -20870,13 +20777,13 @@
     </row>
     <row r="752" spans="1:6">
       <c r="A752" t="s">
-        <v>2027</v>
+        <v>2016</v>
       </c>
       <c r="B752" t="s">
-        <v>2193</v>
+        <v>2174</v>
       </c>
       <c r="C752" t="s">
-        <v>2194</v>
+        <v>2175</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -20887,13 +20794,13 @@
     </row>
     <row r="753" spans="1:6">
       <c r="A753" t="s">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B753" t="s">
-        <v>2195</v>
+        <v>2176</v>
       </c>
       <c r="C753" t="s">
-        <v>2195</v>
+        <v>2176</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -20904,13 +20811,13 @@
     </row>
     <row r="754" spans="1:6">
       <c r="A754" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B754" t="s">
-        <v>2196</v>
+        <v>2177</v>
       </c>
       <c r="C754" t="s">
-        <v>2197</v>
+        <v>2178</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -20921,13 +20828,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2093</v>
+        <v>2075</v>
       </c>
       <c r="B755" t="s">
-        <v>2198</v>
+        <v>2179</v>
       </c>
       <c r="C755" t="s">
-        <v>2199</v>
+        <v>2180</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -20938,13 +20845,13 @@
     </row>
     <row r="756" spans="1:6">
       <c r="A756" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="B756" t="s">
-        <v>2200</v>
+        <v>2181</v>
       </c>
       <c r="C756" t="s">
-        <v>2201</v>
+        <v>2182</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -20955,13 +20862,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2044</v>
+        <v>2032</v>
       </c>
       <c r="B757" t="s">
-        <v>2202</v>
+        <v>2183</v>
       </c>
       <c r="C757" t="s">
-        <v>2203</v>
+        <v>2184</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -20972,13 +20879,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2205</v>
+        <v>2186</v>
       </c>
       <c r="B758" t="s">
-        <v>2204</v>
+        <v>2185</v>
       </c>
       <c r="C758" t="s">
-        <v>2204</v>
+        <v>2185</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -20989,13 +20896,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2038</v>
+        <v>2026</v>
       </c>
       <c r="B759" t="s">
-        <v>2206</v>
+        <v>2187</v>
       </c>
       <c r="C759" t="s">
-        <v>2207</v>
+        <v>2188</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -21006,13 +20913,13 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2058</v>
+        <v>2044</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2208</v>
+        <v>2189</v>
       </c>
       <c r="E760">
         <v>2006</v>
@@ -21023,13 +20930,13 @@
     </row>
     <row r="761" spans="1:6">
       <c r="A761" t="s">
-        <v>2040</v>
+        <v>2028</v>
       </c>
       <c r="B761" t="s">
-        <v>2209</v>
+        <v>2190</v>
       </c>
       <c r="C761" t="s">
-        <v>2210</v>
+        <v>2191</v>
       </c>
       <c r="E761">
         <v>1987</v>
@@ -21040,13 +20947,13 @@
     </row>
     <row r="762" spans="1:6">
       <c r="A762" t="s">
-        <v>2094</v>
+        <v>2076</v>
       </c>
       <c r="B762" t="s">
-        <v>2211</v>
+        <v>2192</v>
       </c>
       <c r="C762" t="s">
-        <v>2212</v>
+        <v>2193</v>
       </c>
       <c r="E762">
         <v>1952</v>
@@ -21057,13 +20964,13 @@
     </row>
     <row r="763" spans="1:6">
       <c r="A763" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B763" t="s">
-        <v>2213</v>
+        <v>2194</v>
       </c>
       <c r="C763" t="s">
-        <v>2214</v>
+        <v>2195</v>
       </c>
       <c r="E763">
         <v>2000</v>
@@ -21074,13 +20981,13 @@
     </row>
     <row r="764" spans="1:6">
       <c r="A764" t="s">
-        <v>2060</v>
+        <v>2046</v>
       </c>
       <c r="B764" t="s">
-        <v>2215</v>
+        <v>2196</v>
       </c>
       <c r="C764" t="s">
-        <v>2216</v>
+        <v>2197</v>
       </c>
       <c r="E764">
         <v>2018</v>
@@ -21091,13 +20998,13 @@
     </row>
     <row r="765" spans="1:6">
       <c r="A765" t="s">
-        <v>2079</v>
+        <v>2063</v>
       </c>
       <c r="B765" t="s">
-        <v>2217</v>
+        <v>2198</v>
       </c>
       <c r="C765" t="s">
-        <v>2217</v>
+        <v>2198</v>
       </c>
       <c r="E765">
         <v>1977</v>
@@ -21108,13 +21015,13 @@
     </row>
     <row r="766" spans="1:6">
       <c r="A766" t="s">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B766" t="s">
-        <v>2218</v>
+        <v>2199</v>
       </c>
       <c r="C766" t="s">
-        <v>2219</v>
+        <v>2200</v>
       </c>
       <c r="E766">
         <v>1994</v>
@@ -21125,13 +21032,13 @@
     </row>
     <row r="767" spans="1:6">
       <c r="A767" t="s">
-        <v>2041</v>
+        <v>2029</v>
       </c>
       <c r="B767" t="s">
-        <v>2220</v>
+        <v>2201</v>
       </c>
       <c r="C767" t="s">
-        <v>2220</v>
+        <v>2201</v>
       </c>
       <c r="E767">
         <v>1972</v>
@@ -21142,13 +21049,13 @@
     </row>
     <row r="768" spans="1:6">
       <c r="A768" t="s">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B768" t="s">
         <v>1212</v>
       </c>
       <c r="C768" t="s">
-        <v>2221</v>
+        <v>2202</v>
       </c>
       <c r="E768">
         <v>2002</v>
@@ -21159,13 +21066,13 @@
     </row>
     <row r="769" spans="1:6">
       <c r="A769" t="s">
-        <v>2033</v>
+        <v>2022</v>
       </c>
       <c r="B769" t="s">
-        <v>2222</v>
+        <v>2203</v>
       </c>
       <c r="C769" t="s">
-        <v>2223</v>
+        <v>2204</v>
       </c>
       <c r="E769">
         <v>1974</v>
@@ -21176,13 +21083,13 @@
     </row>
     <row r="770" spans="1:6">
       <c r="A770" t="s">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B770" t="s">
-        <v>2225</v>
+        <v>2206</v>
       </c>
       <c r="C770" t="s">
-        <v>2224</v>
+        <v>2205</v>
       </c>
       <c r="E770">
         <v>1978</v>
@@ -21193,13 +21100,13 @@
     </row>
     <row r="771" spans="1:6">
       <c r="A771" t="s">
-        <v>2124</v>
+        <v>2105</v>
       </c>
       <c r="B771" t="s">
-        <v>2226</v>
+        <v>2207</v>
       </c>
       <c r="C771" t="s">
-        <v>2227</v>
+        <v>2208</v>
       </c>
       <c r="E771">
         <v>2004</v>
@@ -21210,13 +21117,13 @@
     </row>
     <row r="772" spans="1:6">
       <c r="A772" t="s">
-        <v>2052</v>
+        <v>2040</v>
       </c>
       <c r="B772" t="s">
-        <v>2228</v>
+        <v>2209</v>
       </c>
       <c r="C772" t="s">
-        <v>2229</v>
+        <v>2210</v>
       </c>
       <c r="E772">
         <v>1979</v>
@@ -21227,13 +21134,13 @@
     </row>
     <row r="773" spans="1:6">
       <c r="A773" t="s">
-        <v>2064</v>
+        <v>2049</v>
       </c>
       <c r="B773" t="s">
-        <v>2230</v>
+        <v>2211</v>
       </c>
       <c r="C773" t="s">
-        <v>2231</v>
+        <v>2212</v>
       </c>
       <c r="E773">
         <v>1984</v>
@@ -21244,13 +21151,13 @@
     </row>
     <row r="774" spans="1:6">
       <c r="A774" t="s">
-        <v>2112</v>
+        <v>2093</v>
       </c>
       <c r="B774" t="s">
-        <v>2232</v>
+        <v>2213</v>
       </c>
       <c r="C774" t="s">
-        <v>2233</v>
+        <v>2214</v>
       </c>
       <c r="E774">
         <v>1974</v>
@@ -21261,13 +21168,13 @@
     </row>
     <row r="775" spans="1:6">
       <c r="A775" t="s">
-        <v>2083</v>
+        <v>2067</v>
       </c>
       <c r="B775" t="s">
-        <v>2234</v>
+        <v>2215</v>
       </c>
       <c r="C775" t="s">
-        <v>2235</v>
+        <v>2216</v>
       </c>
       <c r="E775">
         <v>2011</v>
@@ -21278,13 +21185,13 @@
     </row>
     <row r="776" spans="1:6">
       <c r="A776" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B776" t="s">
-        <v>2236</v>
+        <v>2217</v>
       </c>
       <c r="C776" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="E776">
         <v>1995</v>
@@ -21295,13 +21202,13 @@
     </row>
     <row r="777" spans="1:6">
       <c r="A777" t="s">
-        <v>2238</v>
+        <v>2219</v>
       </c>
       <c r="B777" t="s">
-        <v>2237</v>
+        <v>2218</v>
       </c>
       <c r="C777" t="s">
-        <v>2239</v>
+        <v>2220</v>
       </c>
       <c r="E777">
         <v>2006</v>
@@ -21312,13 +21219,13 @@
     </row>
     <row r="778" spans="1:6">
       <c r="A778" t="s">
-        <v>2240</v>
+        <v>2221</v>
       </c>
       <c r="B778" s="8" t="s">
-        <v>2241</v>
+        <v>2222</v>
       </c>
       <c r="C778" t="s">
-        <v>2242</v>
+        <v>2223</v>
       </c>
       <c r="E778">
         <v>1958</v>
@@ -21329,13 +21236,13 @@
     </row>
     <row r="779" spans="1:6">
       <c r="A779" t="s">
-        <v>2092</v>
+        <v>2074</v>
       </c>
       <c r="B779" t="s">
-        <v>2244</v>
+        <v>2225</v>
       </c>
       <c r="C779" t="s">
-        <v>2243</v>
+        <v>2224</v>
       </c>
       <c r="E779">
         <v>1993</v>
@@ -21346,13 +21253,13 @@
     </row>
     <row r="780" spans="1:6">
       <c r="A780" s="1" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B780" t="s">
-        <v>2245</v>
+        <v>2226</v>
       </c>
       <c r="C780" t="s">
-        <v>2246</v>
+        <v>2227</v>
       </c>
       <c r="E780">
         <v>2008</v>
@@ -21363,19 +21270,359 @@
     </row>
     <row r="781" spans="1:6">
       <c r="A781" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B781" t="s">
-        <v>2247</v>
+        <v>2228</v>
       </c>
       <c r="C781" t="s">
-        <v>2248</v>
+        <v>2229</v>
       </c>
       <c r="E781">
         <v>2005</v>
       </c>
       <c r="F781" t="s">
         <v>969</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6">
+      <c r="A782" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B782" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C782" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E782">
+        <v>1995</v>
+      </c>
+      <c r="F782" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6">
+      <c r="A783" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B783" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C783" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E783">
+        <v>1978</v>
+      </c>
+      <c r="F783" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6">
+      <c r="A784" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B784" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C784" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E784">
+        <v>1974</v>
+      </c>
+      <c r="F784" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6">
+      <c r="A785" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B785" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C785" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E785">
+        <v>1963</v>
+      </c>
+      <c r="F785" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6">
+      <c r="A786" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B786" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C786" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E786">
+        <v>2005</v>
+      </c>
+      <c r="F786" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6">
+      <c r="A787" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B787" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C787" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E787">
+        <v>1978</v>
+      </c>
+      <c r="F787" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6">
+      <c r="A788" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B788" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C788" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E788">
+        <v>1977</v>
+      </c>
+      <c r="F788" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6">
+      <c r="A789" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B789" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C789" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E789">
+        <v>1986</v>
+      </c>
+      <c r="F789" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6">
+      <c r="A790" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B790" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C790" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E790">
+        <v>1965</v>
+      </c>
+      <c r="F790" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6">
+      <c r="A791" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B791" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C791" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E791">
+        <v>2003</v>
+      </c>
+      <c r="F791" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6">
+      <c r="A792" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B792" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C792" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E792">
+        <v>1997</v>
+      </c>
+      <c r="F792" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6">
+      <c r="A793" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B793" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C793" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E793">
+        <v>1959</v>
+      </c>
+      <c r="F793" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6">
+      <c r="A794" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B794" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C794" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E794">
+        <v>1992</v>
+      </c>
+      <c r="F794" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6">
+      <c r="A795" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B795" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C795" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E795">
+        <v>1989</v>
+      </c>
+      <c r="F795" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6">
+      <c r="A796" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B796" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C796" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E796">
+        <v>1959</v>
+      </c>
+      <c r="F796" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6">
+      <c r="A797" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B797" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C797" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E797">
+        <v>1991</v>
+      </c>
+      <c r="F797" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6">
+      <c r="A798" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B798" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C798" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E798">
+        <v>1991</v>
+      </c>
+      <c r="F798" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6">
+      <c r="A799" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B799" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C799" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E799">
+        <v>1999</v>
+      </c>
+      <c r="F799" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6">
+      <c r="A800" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B800" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C800" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E800">
+        <v>1968</v>
+      </c>
+      <c r="F800" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6">
+      <c r="A801" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B801" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C801" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E801">
+        <v>1994</v>
+      </c>
+      <c r="F801" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AC1EA0-F814-1B47-90DF-8C1B7D01214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AB4DB7-A8AE-B748-8BE2-CA58FC8FEA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="2273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="2278">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6200,9 +6200,6 @@
     <t>First Aid Kit</t>
   </si>
   <si>
-    <t>Talk Talk</t>
-  </si>
-  <si>
     <t>This Mortal Coil</t>
   </si>
   <si>
@@ -6251,9 +6248,6 @@
     <t>Brad</t>
   </si>
   <si>
-    <t>The Replacements</t>
-  </si>
-  <si>
     <t>Elliott Smith</t>
   </si>
   <si>
@@ -6266,21 +6260,12 @@
     <t>Screaming Trees</t>
   </si>
   <si>
-    <t>The Cult</t>
-  </si>
-  <si>
     <t>Kermit the Frog</t>
   </si>
   <si>
-    <t>Temple of the Dog</t>
-  </si>
-  <si>
     <t>Patti Smith</t>
   </si>
   <si>
-    <t>The Gits</t>
-  </si>
-  <si>
     <t>Gnarls Barkley</t>
   </si>
   <si>
@@ -6329,9 +6314,6 @@
     <t>Cocteau Twins</t>
   </si>
   <si>
-    <t>The Roots</t>
-  </si>
-  <si>
     <t>Dee-Lite</t>
   </si>
   <si>
@@ -6356,9 +6338,6 @@
     <t>Big Star</t>
   </si>
   <si>
-    <t>The Knife</t>
-  </si>
-  <si>
     <t>TV on the Radio</t>
   </si>
   <si>
@@ -6368,9 +6347,6 @@
     <t>The Verve</t>
   </si>
   <si>
-    <t>Television</t>
-  </si>
-  <si>
     <t>Mazzy Star</t>
   </si>
   <si>
@@ -6404,12 +6380,6 @@
     <t>Etta James</t>
   </si>
   <si>
-    <t>The Chieftains</t>
-  </si>
-  <si>
-    <t>The Marvelettes</t>
-  </si>
-  <si>
     <t>Dion</t>
   </si>
   <si>
@@ -6449,9 +6419,6 @@
     <t>a-ha</t>
   </si>
   <si>
-    <t>The Outfield</t>
-  </si>
-  <si>
     <t>Chris Isaak</t>
   </si>
   <si>
@@ -6966,6 +6933,54 @@
   </si>
   <si>
     <t>Second Coming</t>
+  </si>
+  <si>
+    <t>The Verve Pipe</t>
+  </si>
+  <si>
+    <t>The Freshmen</t>
+  </si>
+  <si>
+    <t>Villains</t>
+  </si>
+  <si>
+    <t>Last  Splash</t>
+  </si>
+  <si>
+    <t>My Favourite Game</t>
+  </si>
+  <si>
+    <t>Gran Turismo</t>
+  </si>
+  <si>
+    <t>Since You’re Gone</t>
+  </si>
+  <si>
+    <t>Complete Greatest Hits</t>
+  </si>
+  <si>
+    <t>The Gifts</t>
+  </si>
+  <si>
+    <t>Second Skin</t>
+  </si>
+  <si>
+    <t>Frenching the Bully</t>
+  </si>
+  <si>
+    <t>Shout!</t>
+  </si>
+  <si>
+    <t>Bloodbuzz Ohio</t>
+  </si>
+  <si>
+    <t>High Violet</t>
+  </si>
+  <si>
+    <t>By My Baby</t>
+  </si>
+  <si>
+    <t>The Best of</t>
   </si>
 </sst>
 </file>
@@ -7398,7 +7413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B45"/>
+  <dimension ref="B3:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7406,220 +7421,130 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2017</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2073</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2041</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>999</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2102</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2037</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2085</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2039</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>1415</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2043</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2083</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2069</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>2086</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>2058</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>2100</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>2034</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>2089</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>2060</v>
+      <c r="B20" s="1" t="s">
+        <v>1995</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>2045</v>
+      <c r="B21" s="1" t="s">
+        <v>1996</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>2056</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>2072</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>2071</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>2020</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>2066</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="27" spans="2:2">
-      <c r="B27" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="1" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="1" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="1"/>
+      <c r="B27" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B45">
-    <sortCondition ref="B1:B45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B27">
+    <sortCondition ref="B1:B27"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7628,7 +7553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F801"/>
+  <dimension ref="A1:F810"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -12858,7 +12783,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -17031,7 +16956,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2092</v>
+        <v>2082</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -20182,13 +20107,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="B717" t="s">
-        <v>2107</v>
+        <v>2096</v>
       </c>
       <c r="C717" t="s">
-        <v>2108</v>
+        <v>2097</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20199,13 +20124,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="B718" t="s">
-        <v>2109</v>
+        <v>2098</v>
       </c>
       <c r="C718" t="s">
-        <v>2110</v>
+        <v>2099</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20216,13 +20141,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2112</v>
+        <v>2101</v>
       </c>
       <c r="B719" t="s">
-        <v>2111</v>
+        <v>2100</v>
       </c>
       <c r="C719" t="s">
-        <v>2112</v>
+        <v>2101</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20233,13 +20158,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B720" t="s">
-        <v>2113</v>
+        <v>2102</v>
       </c>
       <c r="C720" t="s">
-        <v>2114</v>
+        <v>2103</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20250,13 +20175,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
       <c r="B721" t="s">
-        <v>2115</v>
+        <v>2104</v>
       </c>
       <c r="C721" t="s">
-        <v>2116</v>
+        <v>2105</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20267,13 +20192,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B722" t="s">
-        <v>2117</v>
+        <v>2106</v>
       </c>
       <c r="C722" t="s">
-        <v>2118</v>
+        <v>2107</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20284,13 +20209,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B723" t="s">
-        <v>2119</v>
+        <v>2108</v>
       </c>
       <c r="C723" t="s">
-        <v>2120</v>
+        <v>2109</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20301,13 +20226,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B724" t="s">
-        <v>2121</v>
+        <v>2110</v>
       </c>
       <c r="C724" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20318,13 +20243,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2096</v>
+        <v>2086</v>
       </c>
       <c r="B725" t="s">
-        <v>2122</v>
+        <v>2111</v>
       </c>
       <c r="C725" t="s">
-        <v>2123</v>
+        <v>2112</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20338,10 +20263,10 @@
         <v>1994</v>
       </c>
       <c r="B726" t="s">
-        <v>2124</v>
+        <v>2113</v>
       </c>
       <c r="C726" t="s">
-        <v>2125</v>
+        <v>2114</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20352,13 +20277,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
       <c r="B727" t="s">
-        <v>2126</v>
+        <v>2115</v>
       </c>
       <c r="C727" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20369,13 +20294,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2094</v>
+        <v>2084</v>
       </c>
       <c r="B728" t="s">
-        <v>2127</v>
+        <v>2116</v>
       </c>
       <c r="C728" t="s">
-        <v>2128</v>
+        <v>2117</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20389,10 +20314,10 @@
         <v>2013</v>
       </c>
       <c r="B729" t="s">
-        <v>2129</v>
+        <v>2118</v>
       </c>
       <c r="C729" t="s">
-        <v>2130</v>
+        <v>2119</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20403,13 +20328,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="B730" t="s">
-        <v>2131</v>
+        <v>2120</v>
       </c>
       <c r="C730" t="s">
-        <v>2132</v>
+        <v>2121</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20420,13 +20345,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B731" t="s">
-        <v>2133</v>
+        <v>2122</v>
       </c>
       <c r="C731" t="s">
-        <v>2134</v>
+        <v>2123</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20437,13 +20362,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B732" t="s">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="C732" t="s">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20454,13 +20379,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="B733" t="s">
-        <v>2136</v>
+        <v>2125</v>
       </c>
       <c r="C733" t="s">
-        <v>2137</v>
+        <v>2126</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20471,13 +20396,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="B734" t="s">
-        <v>2138</v>
+        <v>2127</v>
       </c>
       <c r="C734" t="s">
-        <v>2139</v>
+        <v>2128</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20488,13 +20413,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="B735" t="s">
-        <v>2140</v>
+        <v>2129</v>
       </c>
       <c r="C735" t="s">
-        <v>2141</v>
+        <v>2130</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20505,13 +20430,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B736" t="s">
-        <v>2142</v>
+        <v>2131</v>
       </c>
       <c r="C736" t="s">
-        <v>2143</v>
+        <v>2132</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20522,13 +20447,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2101</v>
+        <v>2090</v>
       </c>
       <c r="B737" t="s">
-        <v>2144</v>
+        <v>2133</v>
       </c>
       <c r="C737" t="s">
-        <v>2145</v>
+        <v>2134</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20539,13 +20464,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2146</v>
+        <v>2135</v>
       </c>
       <c r="B738" t="s">
-        <v>2147</v>
+        <v>2136</v>
       </c>
       <c r="C738" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20556,13 +20481,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B739" t="s">
-        <v>2149</v>
+        <v>2138</v>
       </c>
       <c r="C739" t="s">
-        <v>2150</v>
+        <v>2139</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20573,13 +20498,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2098</v>
+        <v>2088</v>
       </c>
       <c r="B740" t="s">
-        <v>2151</v>
+        <v>2140</v>
       </c>
       <c r="C740" t="s">
-        <v>2152</v>
+        <v>2141</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20590,13 +20515,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="B741" t="s">
-        <v>2153</v>
+        <v>2142</v>
       </c>
       <c r="C741" t="s">
-        <v>2153</v>
+        <v>2142</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20607,13 +20532,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2061</v>
+        <v>2055</v>
       </c>
       <c r="B742" t="s">
-        <v>2154</v>
+        <v>2143</v>
       </c>
       <c r="C742" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20624,13 +20549,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2097</v>
+        <v>2087</v>
       </c>
       <c r="B743" t="s">
-        <v>2156</v>
+        <v>2145</v>
       </c>
       <c r="C743" t="s">
-        <v>2157</v>
+        <v>2146</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20641,13 +20566,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2088</v>
+        <v>2078</v>
       </c>
       <c r="B744" t="s">
-        <v>2158</v>
+        <v>2147</v>
       </c>
       <c r="C744" t="s">
-        <v>2159</v>
+        <v>2148</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20658,13 +20583,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2087</v>
+        <v>2077</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2160</v>
+        <v>2149</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20675,13 +20600,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B746" t="s">
-        <v>2161</v>
+        <v>2150</v>
       </c>
       <c r="C746" t="s">
-        <v>2162</v>
+        <v>2151</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20692,13 +20617,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
-        <v>2163</v>
+        <v>2152</v>
       </c>
       <c r="B747" t="s">
-        <v>2164</v>
+        <v>2153</v>
       </c>
       <c r="C747" t="s">
-        <v>2165</v>
+        <v>2154</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -20709,13 +20634,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="B748" t="s">
-        <v>2166</v>
+        <v>2155</v>
       </c>
       <c r="C748" t="s">
-        <v>2167</v>
+        <v>2156</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -20726,13 +20651,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="B749" t="s">
-        <v>2168</v>
+        <v>2157</v>
       </c>
       <c r="C749" t="s">
-        <v>2169</v>
+        <v>2158</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -20746,10 +20671,10 @@
         <v>2011</v>
       </c>
       <c r="B750" t="s">
-        <v>2170</v>
+        <v>2159</v>
       </c>
       <c r="C750" t="s">
-        <v>2171</v>
+        <v>2160</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -20760,13 +20685,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B751" t="s">
-        <v>2172</v>
+        <v>2161</v>
       </c>
       <c r="C751" t="s">
-        <v>2173</v>
+        <v>2162</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -20780,10 +20705,10 @@
         <v>2016</v>
       </c>
       <c r="B752" t="s">
-        <v>2174</v>
+        <v>2163</v>
       </c>
       <c r="C752" t="s">
-        <v>2175</v>
+        <v>2164</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -20797,10 +20722,10 @@
         <v>2007</v>
       </c>
       <c r="B753" t="s">
-        <v>2176</v>
+        <v>2165</v>
       </c>
       <c r="C753" t="s">
-        <v>2176</v>
+        <v>2165</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -20814,10 +20739,10 @@
         <v>2006</v>
       </c>
       <c r="B754" t="s">
-        <v>2177</v>
+        <v>2166</v>
       </c>
       <c r="C754" t="s">
-        <v>2178</v>
+        <v>2167</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -20828,13 +20753,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
       <c r="B755" t="s">
-        <v>2179</v>
+        <v>2168</v>
       </c>
       <c r="C755" t="s">
-        <v>2180</v>
+        <v>2169</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -20848,10 +20773,10 @@
         <v>1998</v>
       </c>
       <c r="B756" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="C756" t="s">
-        <v>2182</v>
+        <v>2171</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -20862,13 +20787,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B757" t="s">
-        <v>2183</v>
+        <v>2172</v>
       </c>
       <c r="C757" t="s">
-        <v>2184</v>
+        <v>2173</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -20879,13 +20804,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="B758" t="s">
-        <v>2185</v>
+        <v>2174</v>
       </c>
       <c r="C758" t="s">
-        <v>2185</v>
+        <v>2174</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -20896,13 +20821,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B759" t="s">
-        <v>2187</v>
+        <v>2176</v>
       </c>
       <c r="C759" t="s">
-        <v>2188</v>
+        <v>2177</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -20913,13 +20838,13 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2189</v>
+        <v>2178</v>
       </c>
       <c r="E760">
         <v>2006</v>
@@ -20930,13 +20855,13 @@
     </row>
     <row r="761" spans="1:6">
       <c r="A761" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B761" t="s">
-        <v>2190</v>
+        <v>2179</v>
       </c>
       <c r="C761" t="s">
-        <v>2191</v>
+        <v>2180</v>
       </c>
       <c r="E761">
         <v>1987</v>
@@ -20947,13 +20872,13 @@
     </row>
     <row r="762" spans="1:6">
       <c r="A762" t="s">
-        <v>2076</v>
+        <v>2068</v>
       </c>
       <c r="B762" t="s">
-        <v>2192</v>
+        <v>2181</v>
       </c>
       <c r="C762" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="E762">
         <v>1952</v>
@@ -20967,10 +20892,10 @@
         <v>2003</v>
       </c>
       <c r="B763" t="s">
-        <v>2194</v>
+        <v>2183</v>
       </c>
       <c r="C763" t="s">
-        <v>2195</v>
+        <v>2184</v>
       </c>
       <c r="E763">
         <v>2000</v>
@@ -20981,13 +20906,13 @@
     </row>
     <row r="764" spans="1:6">
       <c r="A764" t="s">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B764" t="s">
-        <v>2196</v>
+        <v>2185</v>
       </c>
       <c r="C764" t="s">
-        <v>2197</v>
+        <v>2186</v>
       </c>
       <c r="E764">
         <v>2018</v>
@@ -20998,13 +20923,13 @@
     </row>
     <row r="765" spans="1:6">
       <c r="A765" t="s">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="B765" t="s">
-        <v>2198</v>
+        <v>2187</v>
       </c>
       <c r="C765" t="s">
-        <v>2198</v>
+        <v>2187</v>
       </c>
       <c r="E765">
         <v>1977</v>
@@ -21018,10 +20943,10 @@
         <v>2008</v>
       </c>
       <c r="B766" t="s">
-        <v>2199</v>
+        <v>2188</v>
       </c>
       <c r="C766" t="s">
-        <v>2200</v>
+        <v>2189</v>
       </c>
       <c r="E766">
         <v>1994</v>
@@ -21032,13 +20957,13 @@
     </row>
     <row r="767" spans="1:6">
       <c r="A767" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B767" t="s">
-        <v>2201</v>
+        <v>2190</v>
       </c>
       <c r="C767" t="s">
-        <v>2201</v>
+        <v>2190</v>
       </c>
       <c r="E767">
         <v>1972</v>
@@ -21055,7 +20980,7 @@
         <v>1212</v>
       </c>
       <c r="C768" t="s">
-        <v>2202</v>
+        <v>2191</v>
       </c>
       <c r="E768">
         <v>2002</v>
@@ -21066,13 +20991,13 @@
     </row>
     <row r="769" spans="1:6">
       <c r="A769" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B769" t="s">
-        <v>2203</v>
+        <v>2192</v>
       </c>
       <c r="C769" t="s">
-        <v>2204</v>
+        <v>2193</v>
       </c>
       <c r="E769">
         <v>1974</v>
@@ -21086,10 +21011,10 @@
         <v>2015</v>
       </c>
       <c r="B770" t="s">
-        <v>2206</v>
+        <v>2195</v>
       </c>
       <c r="C770" t="s">
-        <v>2205</v>
+        <v>2194</v>
       </c>
       <c r="E770">
         <v>1978</v>
@@ -21100,13 +21025,13 @@
     </row>
     <row r="771" spans="1:6">
       <c r="A771" t="s">
-        <v>2105</v>
+        <v>2094</v>
       </c>
       <c r="B771" t="s">
-        <v>2207</v>
+        <v>2196</v>
       </c>
       <c r="C771" t="s">
-        <v>2208</v>
+        <v>2197</v>
       </c>
       <c r="E771">
         <v>2004</v>
@@ -21117,13 +21042,13 @@
     </row>
     <row r="772" spans="1:6">
       <c r="A772" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="B772" t="s">
-        <v>2209</v>
+        <v>2198</v>
       </c>
       <c r="C772" t="s">
-        <v>2210</v>
+        <v>2199</v>
       </c>
       <c r="E772">
         <v>1979</v>
@@ -21134,13 +21059,13 @@
     </row>
     <row r="773" spans="1:6">
       <c r="A773" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B773" t="s">
-        <v>2211</v>
+        <v>2200</v>
       </c>
       <c r="C773" t="s">
-        <v>2212</v>
+        <v>2201</v>
       </c>
       <c r="E773">
         <v>1984</v>
@@ -21151,13 +21076,13 @@
     </row>
     <row r="774" spans="1:6">
       <c r="A774" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="B774" t="s">
-        <v>2213</v>
+        <v>2202</v>
       </c>
       <c r="C774" t="s">
-        <v>2214</v>
+        <v>2203</v>
       </c>
       <c r="E774">
         <v>1974</v>
@@ -21168,13 +21093,13 @@
     </row>
     <row r="775" spans="1:6">
       <c r="A775" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="B775" t="s">
-        <v>2215</v>
+        <v>2204</v>
       </c>
       <c r="C775" t="s">
-        <v>2216</v>
+        <v>2205</v>
       </c>
       <c r="E775">
         <v>2011</v>
@@ -21188,7 +21113,7 @@
         <v>1999</v>
       </c>
       <c r="B776" t="s">
-        <v>2217</v>
+        <v>2206</v>
       </c>
       <c r="C776" t="s">
         <v>1999</v>
@@ -21202,13 +21127,13 @@
     </row>
     <row r="777" spans="1:6">
       <c r="A777" t="s">
-        <v>2219</v>
+        <v>2208</v>
       </c>
       <c r="B777" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="C777" t="s">
-        <v>2220</v>
+        <v>2209</v>
       </c>
       <c r="E777">
         <v>2006</v>
@@ -21219,13 +21144,13 @@
     </row>
     <row r="778" spans="1:6">
       <c r="A778" t="s">
-        <v>2221</v>
+        <v>2210</v>
       </c>
       <c r="B778" s="8" t="s">
-        <v>2222</v>
+        <v>2211</v>
       </c>
       <c r="C778" t="s">
-        <v>2223</v>
+        <v>2212</v>
       </c>
       <c r="E778">
         <v>1958</v>
@@ -21236,13 +21161,13 @@
     </row>
     <row r="779" spans="1:6">
       <c r="A779" t="s">
-        <v>2074</v>
+        <v>2066</v>
       </c>
       <c r="B779" t="s">
-        <v>2225</v>
+        <v>2214</v>
       </c>
       <c r="C779" t="s">
-        <v>2224</v>
+        <v>2213</v>
       </c>
       <c r="E779">
         <v>1993</v>
@@ -21256,10 +21181,10 @@
         <v>2000</v>
       </c>
       <c r="B780" t="s">
-        <v>2226</v>
+        <v>2215</v>
       </c>
       <c r="C780" t="s">
-        <v>2227</v>
+        <v>2216</v>
       </c>
       <c r="E780">
         <v>2008</v>
@@ -21273,10 +21198,10 @@
         <v>1997</v>
       </c>
       <c r="B781" t="s">
-        <v>2228</v>
+        <v>2217</v>
       </c>
       <c r="C781" t="s">
-        <v>2229</v>
+        <v>2218</v>
       </c>
       <c r="E781">
         <v>2005</v>
@@ -21290,10 +21215,10 @@
         <v>2010</v>
       </c>
       <c r="B782" t="s">
-        <v>2231</v>
+        <v>2220</v>
       </c>
       <c r="C782" t="s">
-        <v>2230</v>
+        <v>2219</v>
       </c>
       <c r="E782">
         <v>1995</v>
@@ -21304,13 +21229,13 @@
     </row>
     <row r="783" spans="1:6">
       <c r="A783" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="B783" t="s">
-        <v>2232</v>
+        <v>2221</v>
       </c>
       <c r="C783" t="s">
-        <v>2233</v>
+        <v>2222</v>
       </c>
       <c r="E783">
         <v>1978</v>
@@ -21321,13 +21246,13 @@
     </row>
     <row r="784" spans="1:6">
       <c r="A784" t="s">
-        <v>2081</v>
+        <v>2073</v>
       </c>
       <c r="B784" t="s">
-        <v>2235</v>
+        <v>2224</v>
       </c>
       <c r="C784" t="s">
-        <v>2234</v>
+        <v>2223</v>
       </c>
       <c r="E784">
         <v>1974</v>
@@ -21338,13 +21263,13 @@
     </row>
     <row r="785" spans="1:6">
       <c r="A785" t="s">
-        <v>2080</v>
+        <v>2072</v>
       </c>
       <c r="B785" t="s">
-        <v>2236</v>
+        <v>2225</v>
       </c>
       <c r="C785" t="s">
-        <v>2236</v>
+        <v>2225</v>
       </c>
       <c r="E785">
         <v>1963</v>
@@ -21355,13 +21280,13 @@
     </row>
     <row r="786" spans="1:6">
       <c r="A786" t="s">
-        <v>2106</v>
+        <v>2095</v>
       </c>
       <c r="B786" t="s">
-        <v>2237</v>
+        <v>2226</v>
       </c>
       <c r="C786" t="s">
-        <v>2238</v>
+        <v>2227</v>
       </c>
       <c r="E786">
         <v>2005</v>
@@ -21372,13 +21297,13 @@
     </row>
     <row r="787" spans="1:6">
       <c r="A787" t="s">
-        <v>2239</v>
+        <v>2228</v>
       </c>
       <c r="B787" t="s">
-        <v>2240</v>
+        <v>2229</v>
       </c>
       <c r="C787" t="s">
-        <v>2241</v>
+        <v>2230</v>
       </c>
       <c r="E787">
         <v>1978</v>
@@ -21389,13 +21314,13 @@
     </row>
     <row r="788" spans="1:6">
       <c r="A788" t="s">
-        <v>2242</v>
+        <v>2231</v>
       </c>
       <c r="B788" t="s">
-        <v>2243</v>
+        <v>2232</v>
       </c>
       <c r="C788" t="s">
-        <v>2243</v>
+        <v>2232</v>
       </c>
       <c r="E788">
         <v>1977</v>
@@ -21406,13 +21331,13 @@
     </row>
     <row r="789" spans="1:6">
       <c r="A789" t="s">
-        <v>2244</v>
+        <v>2233</v>
       </c>
       <c r="B789" t="s">
-        <v>2245</v>
+        <v>2234</v>
       </c>
       <c r="C789" t="s">
-        <v>2246</v>
+        <v>2235</v>
       </c>
       <c r="E789">
         <v>1986</v>
@@ -21423,13 +21348,13 @@
     </row>
     <row r="790" spans="1:6">
       <c r="A790" t="s">
-        <v>2247</v>
+        <v>2236</v>
       </c>
       <c r="B790" t="s">
-        <v>2248</v>
+        <v>2237</v>
       </c>
       <c r="C790" t="s">
-        <v>2249</v>
+        <v>2238</v>
       </c>
       <c r="E790">
         <v>1965</v>
@@ -21440,13 +21365,13 @@
     </row>
     <row r="791" spans="1:6">
       <c r="A791" t="s">
-        <v>2250</v>
+        <v>2239</v>
       </c>
       <c r="B791" t="s">
-        <v>2251</v>
+        <v>2240</v>
       </c>
       <c r="C791" t="s">
-        <v>2252</v>
+        <v>2241</v>
       </c>
       <c r="E791">
         <v>2003</v>
@@ -21460,10 +21385,10 @@
         <v>1993</v>
       </c>
       <c r="B792" t="s">
-        <v>2253</v>
+        <v>2242</v>
       </c>
       <c r="C792" t="s">
-        <v>2254</v>
+        <v>2243</v>
       </c>
       <c r="E792">
         <v>1997</v>
@@ -21474,13 +21399,13 @@
     </row>
     <row r="793" spans="1:6">
       <c r="A793" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
       <c r="B793" t="s">
-        <v>2255</v>
+        <v>2244</v>
       </c>
       <c r="C793" t="s">
-        <v>2256</v>
+        <v>2245</v>
       </c>
       <c r="E793">
         <v>1959</v>
@@ -21491,13 +21416,13 @@
     </row>
     <row r="794" spans="1:6">
       <c r="A794" t="s">
-        <v>2257</v>
+        <v>2246</v>
       </c>
       <c r="B794" t="s">
-        <v>2258</v>
+        <v>2247</v>
       </c>
       <c r="C794" t="s">
-        <v>2259</v>
+        <v>2248</v>
       </c>
       <c r="E794">
         <v>1992</v>
@@ -21508,13 +21433,13 @@
     </row>
     <row r="795" spans="1:6">
       <c r="A795" t="s">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B795" t="s">
-        <v>2260</v>
+        <v>2249</v>
       </c>
       <c r="C795" t="s">
-        <v>2261</v>
+        <v>2250</v>
       </c>
       <c r="E795">
         <v>1989</v>
@@ -21525,13 +21450,13 @@
     </row>
     <row r="796" spans="1:6">
       <c r="A796" t="s">
-        <v>2082</v>
+        <v>2074</v>
       </c>
       <c r="B796" t="s">
-        <v>2262</v>
+        <v>2251</v>
       </c>
       <c r="C796" t="s">
-        <v>2082</v>
+        <v>2074</v>
       </c>
       <c r="E796">
         <v>1959</v>
@@ -21542,13 +21467,13 @@
     </row>
     <row r="797" spans="1:6">
       <c r="A797" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="B797" t="s">
-        <v>2263</v>
+        <v>2252</v>
       </c>
       <c r="C797" t="s">
-        <v>2264</v>
+        <v>2253</v>
       </c>
       <c r="E797">
         <v>1991</v>
@@ -21562,10 +21487,10 @@
         <v>2009</v>
       </c>
       <c r="B798" t="s">
-        <v>2265</v>
+        <v>2254</v>
       </c>
       <c r="C798" t="s">
-        <v>2266</v>
+        <v>2255</v>
       </c>
       <c r="E798">
         <v>1991</v>
@@ -21576,13 +21501,13 @@
     </row>
     <row r="799" spans="1:6">
       <c r="A799" t="s">
-        <v>2103</v>
+        <v>2092</v>
       </c>
       <c r="B799" t="s">
-        <v>2267</v>
+        <v>2256</v>
       </c>
       <c r="C799" t="s">
-        <v>2268</v>
+        <v>2257</v>
       </c>
       <c r="E799">
         <v>1999</v>
@@ -21593,13 +21518,13 @@
     </row>
     <row r="800" spans="1:6">
       <c r="A800" t="s">
-        <v>2091</v>
+        <v>2081</v>
       </c>
       <c r="B800" t="s">
-        <v>2269</v>
+        <v>2258</v>
       </c>
       <c r="C800" t="s">
-        <v>2270</v>
+        <v>2259</v>
       </c>
       <c r="E800">
         <v>1968</v>
@@ -21610,19 +21535,172 @@
     </row>
     <row r="801" spans="1:6">
       <c r="A801" t="s">
-        <v>2064</v>
+        <v>2058</v>
       </c>
       <c r="B801" t="s">
-        <v>2271</v>
+        <v>2260</v>
       </c>
       <c r="C801" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E801">
         <v>1994</v>
       </c>
       <c r="F801" t="s">
         <v>970</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6">
+      <c r="A802" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B802" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C802" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E802">
+        <v>1996</v>
+      </c>
+      <c r="F802" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6">
+      <c r="A803" t="s">
+        <v>999</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C803" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E803">
+        <v>1993</v>
+      </c>
+      <c r="F803" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6">
+      <c r="A804" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B804" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C804" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E804">
+        <v>1998</v>
+      </c>
+      <c r="F804" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6">
+      <c r="A805" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B805" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C805" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E805">
+        <v>1981</v>
+      </c>
+      <c r="F805" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6">
+      <c r="A806" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C806" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E806">
+        <v>1959</v>
+      </c>
+      <c r="F806" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6">
+      <c r="A807" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B807" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C807" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E807">
+        <v>1992</v>
+      </c>
+      <c r="F807" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6">
+      <c r="A808" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B808" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C808" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E808">
+        <v>1959</v>
+      </c>
+      <c r="F808" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6">
+      <c r="A809" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B809" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C809" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E809">
+        <v>2010</v>
+      </c>
+      <c r="F809" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6">
+      <c r="A810" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B810" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C810" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E810">
+        <v>1964</v>
+      </c>
+      <c r="F810" t="s">
+        <v>969</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AB4DB7-A8AE-B748-8BE2-CA58FC8FEA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EE335C-387B-7045-8301-9F8B520CCBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="2278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="2293">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -5192,9 +5192,6 @@
     <t>Louis Jordan</t>
   </si>
   <si>
-    <t>Five Minutes More</t>
-  </si>
-  <si>
     <t>Francis Craig</t>
   </si>
   <si>
@@ -6074,9 +6071,6 @@
     <t>Patriotic Songs &amp; Marches</t>
   </si>
   <si>
-    <t>The Columbia Years (1943-1952): The Complete Recordings: Volume 4</t>
-  </si>
-  <si>
     <t>American Songbook</t>
   </si>
   <si>
@@ -6155,9 +6149,6 @@
     <t>Yeah Yeah Yeahs</t>
   </si>
   <si>
-    <t>Throwing Muses</t>
-  </si>
-  <si>
     <t>Hooverphonic</t>
   </si>
   <si>
@@ -6200,9 +6191,6 @@
     <t>First Aid Kit</t>
   </si>
   <si>
-    <t>This Mortal Coil</t>
-  </si>
-  <si>
     <t>Elbow</t>
   </si>
   <si>
@@ -6227,9 +6215,6 @@
     <t>Gladys Knight &amp; The Pips</t>
   </si>
   <si>
-    <t>Tom Tom Club</t>
-  </si>
-  <si>
     <t>Guns 'n' Roses</t>
   </si>
   <si>
@@ -6302,9 +6287,6 @@
     <t>Bon Iver</t>
   </si>
   <si>
-    <t>The Sugarcubes</t>
-  </si>
-  <si>
     <t>Amy Winehouse</t>
   </si>
   <si>
@@ -6341,9 +6323,6 @@
     <t>TV on the Radio</t>
   </si>
   <si>
-    <t>The Walkmen</t>
-  </si>
-  <si>
     <t>The Verve</t>
   </si>
   <si>
@@ -6981,6 +6960,72 @@
   </si>
   <si>
     <t>The Best of</t>
+  </si>
+  <si>
+    <t>Rat Race</t>
+  </si>
+  <si>
+    <t>More Specials</t>
+  </si>
+  <si>
+    <t>The Sundays</t>
+  </si>
+  <si>
+    <t>Here's Where the Story Ends</t>
+  </si>
+  <si>
+    <t>Reading, Writing and Arithmetic</t>
+  </si>
+  <si>
+    <t>Bitter Sweet Symphony</t>
+  </si>
+  <si>
+    <t>Urban Hymns</t>
+  </si>
+  <si>
+    <t>MGMT</t>
+  </si>
+  <si>
+    <t>Oracular Spectacular</t>
+  </si>
+  <si>
+    <t>Time to Pretend</t>
+  </si>
+  <si>
+    <t>Red Eyes</t>
+  </si>
+  <si>
+    <t>Lost in the Dream</t>
+  </si>
+  <si>
+    <t>Fisherman’s Blues</t>
+  </si>
+  <si>
+    <t>I Left My Heart in San Francisco</t>
+  </si>
+  <si>
+    <t>The Way You Look Tonight</t>
+  </si>
+  <si>
+    <t>Sinatra Sings of Love and Things</t>
+  </si>
+  <si>
+    <t>Pressure Drop</t>
+  </si>
+  <si>
+    <t>Funky Kingston</t>
+  </si>
+  <si>
+    <t>Talkin’ Bout a Revolution</t>
+  </si>
+  <si>
+    <t>Tracy Chapman</t>
+  </si>
+  <si>
+    <t>End of the Line</t>
+  </si>
+  <si>
+    <t>Traveling Wilburys Vol. 1</t>
   </si>
 </sst>
 </file>
@@ -7413,138 +7458,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B3:B27"/>
+  <dimension ref="B4:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>2040</v>
-      </c>
-    </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2051</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2065</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2064</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2019</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>2060</v>
+      <c r="B8" s="1" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="9" spans="2:2">
-      <c r="B9" t="s">
-        <v>2017</v>
+      <c r="B9" s="1" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2002</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2026</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2070</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2004</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>2005</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="15" spans="2:2">
-      <c r="B15" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="1" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="1" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="1"/>
+      <c r="B15" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B27">
-    <sortCondition ref="B1:B27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B15">
+    <sortCondition ref="B1:B15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7553,7 +7533,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F810"/>
+  <dimension ref="A1:F820"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -9927,10 +9907,10 @@
         <v>281</v>
       </c>
       <c r="B136" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C136" t="s">
         <v>1794</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1795</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1">
@@ -12783,7 +12763,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2085</v>
+        <v>2078</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -16956,7 +16936,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2082</v>
+        <v>2075</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -17469,13 +17449,13 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B562" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C562" t="s">
         <v>1735</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1736</v>
       </c>
       <c r="E562">
         <v>2013</v>
@@ -17486,13 +17466,13 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B563" t="s">
         <v>1604</v>
       </c>
       <c r="C563" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E563">
         <v>1973</v>
@@ -17503,7 +17483,7 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B564" t="s">
         <v>1104</v>
@@ -17520,13 +17500,13 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B565" t="s">
         <v>1741</v>
       </c>
-      <c r="B565" t="s">
+      <c r="C565" t="s">
         <v>1742</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1743</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -17540,10 +17520,10 @@
         <v>155</v>
       </c>
       <c r="B566" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C566" t="s">
         <v>1765</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1766</v>
       </c>
       <c r="E566">
         <v>2004</v>
@@ -17557,10 +17537,10 @@
         <v>197</v>
       </c>
       <c r="B567" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C567" t="s">
         <v>1767</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1768</v>
       </c>
       <c r="E567">
         <v>1975</v>
@@ -17591,10 +17571,10 @@
         <v>231</v>
       </c>
       <c r="B569" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="C569" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E569">
         <v>1992</v>
@@ -17608,10 +17588,10 @@
         <v>124</v>
       </c>
       <c r="B570" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C570" t="s">
         <v>1770</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1771</v>
       </c>
       <c r="E570">
         <v>2008</v>
@@ -17625,10 +17605,10 @@
         <v>74</v>
       </c>
       <c r="B571" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C571" t="s">
         <v>1772</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1773</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -17642,10 +17622,10 @@
         <v>88</v>
       </c>
       <c r="B572" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C572" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E572">
         <v>2010</v>
@@ -17659,10 +17639,10 @@
         <v>87</v>
       </c>
       <c r="B573" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C573" t="s">
         <v>1775</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1776</v>
       </c>
       <c r="E573">
         <v>2004</v>
@@ -17676,10 +17656,10 @@
         <v>200</v>
       </c>
       <c r="B574" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C574" t="s">
         <v>1777</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1778</v>
       </c>
       <c r="E574">
         <v>1984</v>
@@ -17693,10 +17673,10 @@
         <v>125</v>
       </c>
       <c r="B575" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C575" t="s">
         <v>1779</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1780</v>
       </c>
       <c r="E575">
         <v>2008</v>
@@ -17707,13 +17687,13 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B576" t="s">
         <v>1781</v>
       </c>
-      <c r="B576" t="s">
+      <c r="C576" t="s">
         <v>1782</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1783</v>
       </c>
       <c r="E576">
         <v>2005</v>
@@ -17727,10 +17707,10 @@
         <v>152</v>
       </c>
       <c r="B577" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C577" t="s">
         <v>1784</v>
-      </c>
-      <c r="C577" t="s">
-        <v>1785</v>
       </c>
       <c r="E577">
         <v>2000</v>
@@ -17744,10 +17724,10 @@
         <v>63</v>
       </c>
       <c r="B578" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C578" t="s">
         <v>1786</v>
-      </c>
-      <c r="C578" t="s">
-        <v>1787</v>
       </c>
       <c r="E578">
         <v>1983</v>
@@ -17761,10 +17741,10 @@
         <v>296</v>
       </c>
       <c r="B579" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C579" t="s">
         <v>1788</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1789</v>
       </c>
       <c r="E579">
         <v>1999</v>
@@ -17778,10 +17758,10 @@
         <v>163</v>
       </c>
       <c r="B580" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C580" t="s">
         <v>1790</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1791</v>
       </c>
       <c r="E580">
         <v>2013</v>
@@ -17812,10 +17792,10 @@
         <v>91</v>
       </c>
       <c r="B582" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C582" t="s">
         <v>1792</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1793</v>
       </c>
       <c r="E582">
         <v>2002</v>
@@ -17826,10 +17806,10 @@
     </row>
     <row r="583" spans="1:6">
       <c r="A583" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B583" t="s">
         <v>1796</v>
-      </c>
-      <c r="B583" t="s">
-        <v>1797</v>
       </c>
       <c r="C583" t="s">
         <v>747</v>
@@ -17846,10 +17826,10 @@
         <v>175</v>
       </c>
       <c r="B584" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C584" t="s">
         <v>1798</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1799</v>
       </c>
       <c r="E584">
         <v>1993</v>
@@ -17866,7 +17846,7 @@
         <v>747</v>
       </c>
       <c r="C585" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E585">
         <v>2005</v>
@@ -17880,10 +17860,10 @@
         <v>50</v>
       </c>
       <c r="B586" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C586" t="s">
         <v>1801</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1802</v>
       </c>
       <c r="E586">
         <v>1995</v>
@@ -17897,10 +17877,10 @@
         <v>248</v>
       </c>
       <c r="B587" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C587" t="s">
         <v>1803</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1804</v>
       </c>
       <c r="E587">
         <v>2011</v>
@@ -17911,13 +17891,13 @@
     </row>
     <row r="588" spans="1:6">
       <c r="A588" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B588" t="s">
         <v>1805</v>
       </c>
-      <c r="B588" t="s">
-        <v>1806</v>
-      </c>
       <c r="C588" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E588">
         <v>1972</v>
@@ -17931,7 +17911,7 @@
         <v>85</v>
       </c>
       <c r="B589" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C589" t="s">
         <v>85</v>
@@ -17945,13 +17925,13 @@
     </row>
     <row r="590" spans="1:6">
       <c r="A590" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B590" t="s">
         <v>1808</v>
       </c>
-      <c r="B590" t="s">
+      <c r="C590" t="s">
         <v>1809</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1810</v>
       </c>
       <c r="E590">
         <v>1987</v>
@@ -17962,13 +17942,13 @@
     </row>
     <row r="591" spans="1:6">
       <c r="A591" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B591" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C591" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E591">
         <v>1968</v>
@@ -17979,10 +17959,10 @@
     </row>
     <row r="592" spans="1:6">
       <c r="A592" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B592" t="s">
         <v>1813</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1814</v>
       </c>
       <c r="C592" t="s">
         <v>622</v>
@@ -17996,10 +17976,10 @@
     </row>
     <row r="593" spans="1:6">
       <c r="A593" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B593" t="s">
         <v>1815</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1816</v>
       </c>
       <c r="C593" t="s">
         <v>622</v>
@@ -18013,16 +17993,16 @@
     </row>
     <row r="594" spans="1:6">
       <c r="A594" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C594" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D594" t="s">
         <v>1819</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1817</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1818</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1820</v>
       </c>
       <c r="E594">
         <v>2011</v>
@@ -18033,13 +18013,13 @@
     </row>
     <row r="595" spans="1:6">
       <c r="A595" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B595" t="s">
         <v>1821</v>
       </c>
-      <c r="B595" t="s">
-        <v>1822</v>
-      </c>
       <c r="C595" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E595">
         <v>1974</v>
@@ -18050,13 +18030,13 @@
     </row>
     <row r="596" spans="1:6">
       <c r="A596" s="8" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B596" t="s">
         <v>1823</v>
       </c>
-      <c r="B596" t="s">
+      <c r="C596" t="s">
         <v>1824</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1825</v>
       </c>
       <c r="E596">
         <v>2011</v>
@@ -18067,13 +18047,13 @@
     </row>
     <row r="597" spans="1:6">
       <c r="A597" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B597" t="s">
         <v>1826</v>
       </c>
-      <c r="B597" t="s">
+      <c r="C597" t="s">
         <v>1827</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1828</v>
       </c>
       <c r="E597">
         <v>1994</v>
@@ -18084,13 +18064,13 @@
     </row>
     <row r="598" spans="1:6">
       <c r="A598" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C598" t="s">
         <v>1830</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1829</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1831</v>
       </c>
       <c r="E598">
         <v>1967</v>
@@ -18101,13 +18081,13 @@
     </row>
     <row r="599" spans="1:6">
       <c r="A599" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B599" t="s">
         <v>1832</v>
       </c>
-      <c r="B599" t="s">
+      <c r="C599" t="s">
         <v>1833</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1834</v>
       </c>
       <c r="E599">
         <v>1995</v>
@@ -18118,13 +18098,13 @@
     </row>
     <row r="600" spans="1:6">
       <c r="A600" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B600" t="s">
         <v>1835</v>
       </c>
-      <c r="B600" t="s">
+      <c r="C600" t="s">
         <v>1836</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1837</v>
       </c>
       <c r="E600">
         <v>1970</v>
@@ -18135,7 +18115,7 @@
     </row>
     <row r="601" spans="1:6">
       <c r="A601" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B601" t="s">
         <v>1677</v>
@@ -18169,7 +18149,7 @@
     </row>
     <row r="603" spans="1:6">
       <c r="A603" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B603" t="s">
         <v>1659</v>
@@ -18271,13 +18251,13 @@
     </row>
     <row r="609" spans="1:6">
       <c r="A609" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B609" t="s">
         <v>1840</v>
       </c>
-      <c r="B609" t="s">
+      <c r="C609" t="s">
         <v>1841</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1842</v>
       </c>
       <c r="E609">
         <v>1980</v>
@@ -18288,13 +18268,13 @@
     </row>
     <row r="610" spans="1:6">
       <c r="A610" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B610" t="s">
         <v>1843</v>
       </c>
-      <c r="B610" t="s">
+      <c r="C610" t="s">
         <v>1844</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1845</v>
       </c>
       <c r="E610">
         <v>1979</v>
@@ -18305,13 +18285,13 @@
     </row>
     <row r="611" spans="1:6">
       <c r="A611" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B611" t="s">
         <v>1846</v>
       </c>
-      <c r="B611" t="s">
+      <c r="C611" t="s">
         <v>1847</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1848</v>
       </c>
       <c r="E611">
         <v>1974</v>
@@ -18325,10 +18305,10 @@
         <v>68</v>
       </c>
       <c r="B612" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C612" t="s">
         <v>1849</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1850</v>
       </c>
       <c r="E612">
         <v>1985</v>
@@ -18339,13 +18319,13 @@
     </row>
     <row r="613" spans="1:6">
       <c r="A613" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C613" t="s">
         <v>1851</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1853</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1852</v>
       </c>
       <c r="E613">
         <v>1988</v>
@@ -18359,10 +18339,10 @@
         <v>303</v>
       </c>
       <c r="B614" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C614" t="s">
         <v>1854</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1855</v>
       </c>
       <c r="E614">
         <v>2006</v>
@@ -18376,7 +18356,7 @@
         <v>298</v>
       </c>
       <c r="B615" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="C615" t="s">
         <v>1372</v>
@@ -18393,10 +18373,10 @@
         <v>147</v>
       </c>
       <c r="B616" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C616" t="s">
         <v>1857</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1858</v>
       </c>
       <c r="E616">
         <v>1997</v>
@@ -18410,7 +18390,7 @@
         <v>249</v>
       </c>
       <c r="B617" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C617" t="s">
         <v>444</v>
@@ -18427,10 +18407,10 @@
         <v>205</v>
       </c>
       <c r="B618" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C618" t="s">
         <v>1860</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1861</v>
       </c>
       <c r="E618">
         <v>1990</v>
@@ -18444,10 +18424,10 @@
         <v>162</v>
       </c>
       <c r="B619" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C619" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E619">
         <v>2022</v>
@@ -18464,7 +18444,7 @@
         <v>1430</v>
       </c>
       <c r="C620" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E620">
         <v>2000</v>
@@ -18478,10 +18458,10 @@
         <v>93</v>
       </c>
       <c r="B621" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C621" t="s">
         <v>1865</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1866</v>
       </c>
       <c r="E621">
         <v>2001</v>
@@ -18495,10 +18475,10 @@
         <v>86</v>
       </c>
       <c r="B622" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C622" t="s">
         <v>1867</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1868</v>
       </c>
       <c r="E622">
         <v>2001</v>
@@ -18512,10 +18492,10 @@
         <v>80</v>
       </c>
       <c r="B623" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C623" t="s">
         <v>1869</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1870</v>
       </c>
       <c r="E623">
         <v>2002</v>
@@ -18529,10 +18509,10 @@
         <v>250</v>
       </c>
       <c r="B624" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C624" t="s">
         <v>1871</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1872</v>
       </c>
       <c r="E624">
         <v>2016</v>
@@ -18546,10 +18526,10 @@
         <v>57</v>
       </c>
       <c r="B625" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C625" t="s">
         <v>1873</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1874</v>
       </c>
       <c r="E625">
         <v>1974</v>
@@ -18560,13 +18540,13 @@
     </row>
     <row r="626" spans="1:6">
       <c r="A626" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B626" t="s">
         <v>1875</v>
       </c>
-      <c r="B626" t="s">
+      <c r="C626" t="s">
         <v>1876</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1877</v>
       </c>
       <c r="E626">
         <v>1978</v>
@@ -18580,10 +18560,10 @@
         <v>100</v>
       </c>
       <c r="B627" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C627" t="s">
         <v>1878</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1879</v>
       </c>
       <c r="E627">
         <v>2021</v>
@@ -18597,10 +18577,10 @@
         <v>132</v>
       </c>
       <c r="B628" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C628" t="s">
         <v>1880</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1881</v>
       </c>
       <c r="E628">
         <v>2014</v>
@@ -18614,10 +18594,10 @@
         <v>157</v>
       </c>
       <c r="B629" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C629" t="s">
         <v>1882</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1883</v>
       </c>
       <c r="E629">
         <v>2013</v>
@@ -18631,10 +18611,10 @@
         <v>89</v>
       </c>
       <c r="B630" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C630" t="s">
         <v>1884</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1885</v>
       </c>
       <c r="E630">
         <v>2003</v>
@@ -18648,10 +18628,10 @@
         <v>177</v>
       </c>
       <c r="B631" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C631" t="s">
         <v>1886</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1887</v>
       </c>
       <c r="E631">
         <v>2012</v>
@@ -18679,13 +18659,13 @@
     </row>
     <row r="633" spans="1:6">
       <c r="A633" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C633" t="s">
         <v>1888</v>
-      </c>
-      <c r="B633" t="s">
-        <v>1890</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1889</v>
       </c>
       <c r="E633">
         <v>1977</v>
@@ -18699,10 +18679,10 @@
         <v>62</v>
       </c>
       <c r="B634" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C634" t="s">
         <v>1891</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1892</v>
       </c>
       <c r="E634">
         <v>1985</v>
@@ -18716,10 +18696,10 @@
         <v>332</v>
       </c>
       <c r="B635" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C635" t="s">
         <v>1893</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1894</v>
       </c>
       <c r="E635">
         <v>2013</v>
@@ -18730,13 +18710,13 @@
     </row>
     <row r="636" spans="1:6">
       <c r="A636" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B636" t="s">
         <v>1895</v>
       </c>
-      <c r="B636" t="s">
+      <c r="C636" t="s">
         <v>1896</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1897</v>
       </c>
       <c r="E636">
         <v>2024</v>
@@ -18747,13 +18727,13 @@
     </row>
     <row r="637" spans="1:6">
       <c r="A637" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B637" t="s">
         <v>1898</v>
       </c>
-      <c r="B637" t="s">
+      <c r="C637" t="s">
         <v>1899</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1900</v>
       </c>
       <c r="E637">
         <v>1959</v>
@@ -18764,13 +18744,13 @@
     </row>
     <row r="638" spans="1:6">
       <c r="A638" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B638" t="s">
         <v>1901</v>
       </c>
-      <c r="B638" t="s">
+      <c r="C638" t="s">
         <v>1902</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1903</v>
       </c>
       <c r="E638">
         <v>1975</v>
@@ -18784,7 +18764,7 @@
         <v>180</v>
       </c>
       <c r="B639" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="C639" t="s">
         <v>180</v>
@@ -18798,13 +18778,13 @@
     </row>
     <row r="640" spans="1:6">
       <c r="A640" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B640" t="s">
         <v>1905</v>
       </c>
-      <c r="B640" t="s">
+      <c r="C640" t="s">
         <v>1906</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1907</v>
       </c>
       <c r="E640">
         <v>1998</v>
@@ -18815,13 +18795,13 @@
     </row>
     <row r="641" spans="1:6">
       <c r="A641" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B641" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C641" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E641">
         <v>1991</v>
@@ -18835,10 +18815,10 @@
         <v>253</v>
       </c>
       <c r="B642" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C642" t="s">
         <v>1910</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1911</v>
       </c>
       <c r="E642">
         <v>2020</v>
@@ -18852,10 +18832,10 @@
         <v>47</v>
       </c>
       <c r="B643" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C643" t="s">
         <v>1912</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1913</v>
       </c>
       <c r="E643">
         <v>1971</v>
@@ -18869,10 +18849,10 @@
         <v>206</v>
       </c>
       <c r="B644" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C644" t="s">
         <v>1914</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1915</v>
       </c>
       <c r="E644">
         <v>1988</v>
@@ -18886,10 +18866,10 @@
         <v>333</v>
       </c>
       <c r="B645" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C645" t="s">
         <v>1916</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1917</v>
       </c>
       <c r="E645">
         <v>2010</v>
@@ -18920,10 +18900,10 @@
         <v>136</v>
       </c>
       <c r="B647" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C647" t="s">
         <v>1934</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1935</v>
       </c>
       <c r="E647">
         <v>2002</v>
@@ -18937,7 +18917,7 @@
         <v>148</v>
       </c>
       <c r="B648" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C648" t="s">
         <v>148</v>
@@ -18954,10 +18934,10 @@
         <v>207</v>
       </c>
       <c r="B649" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C649" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="E649">
         <v>1991</v>
@@ -18971,10 +18951,10 @@
         <v>334</v>
       </c>
       <c r="B650" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C650" t="s">
         <v>1920</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1921</v>
       </c>
       <c r="E650">
         <v>2009</v>
@@ -18988,10 +18968,10 @@
         <v>36</v>
       </c>
       <c r="B651" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C651" t="s">
         <v>1922</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1923</v>
       </c>
       <c r="E651">
         <v>1976</v>
@@ -19005,10 +18985,10 @@
         <v>208</v>
       </c>
       <c r="B652" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C652" t="s">
         <v>1924</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1925</v>
       </c>
       <c r="E652">
         <v>1993</v>
@@ -19022,10 +19002,10 @@
         <v>313</v>
       </c>
       <c r="B653" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C653" t="s">
         <v>1926</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1927</v>
       </c>
       <c r="E653">
         <v>2011</v>
@@ -19056,10 +19036,10 @@
         <v>315</v>
       </c>
       <c r="B655" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C655" t="s">
         <v>1928</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1929</v>
       </c>
       <c r="E655">
         <v>2003</v>
@@ -19073,10 +19053,10 @@
         <v>138</v>
       </c>
       <c r="B656" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C656" t="s">
         <v>1930</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1931</v>
       </c>
       <c r="E656">
         <v>2001</v>
@@ -19090,10 +19070,10 @@
         <v>316</v>
       </c>
       <c r="B657" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C657" t="s">
         <v>1932</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1933</v>
       </c>
       <c r="E657">
         <v>2002</v>
@@ -19124,10 +19104,10 @@
         <v>11</v>
       </c>
       <c r="B659" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C659" t="s">
         <v>1936</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1937</v>
       </c>
       <c r="E659">
         <v>1967</v>
@@ -19141,10 +19121,10 @@
         <v>209</v>
       </c>
       <c r="B660" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C660" t="s">
         <v>1938</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1939</v>
       </c>
       <c r="E660">
         <v>1988</v>
@@ -19158,10 +19138,10 @@
         <v>23</v>
       </c>
       <c r="B661" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C661" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E661">
         <v>1967</v>
@@ -19175,10 +19155,10 @@
         <v>56</v>
       </c>
       <c r="B662" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C662" t="s">
         <v>1941</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1942</v>
       </c>
       <c r="E662">
         <v>1972</v>
@@ -19189,13 +19169,13 @@
     </row>
     <row r="663" spans="1:6">
       <c r="A663" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B663" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C663" t="s">
         <v>1943</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1944</v>
       </c>
       <c r="E663">
         <v>2017</v>
@@ -19206,13 +19186,13 @@
     </row>
     <row r="664" spans="1:6">
       <c r="A664" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B664" t="s">
         <v>1946</v>
       </c>
-      <c r="B664" t="s">
+      <c r="C664" t="s">
         <v>1947</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1948</v>
       </c>
       <c r="E664">
         <v>2010</v>
@@ -19223,13 +19203,13 @@
     </row>
     <row r="665" spans="1:6">
       <c r="A665" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B665" t="s">
         <v>1949</v>
       </c>
-      <c r="B665" t="s">
-        <v>1950</v>
-      </c>
       <c r="C665" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="E665">
         <v>1976</v>
@@ -19243,10 +19223,10 @@
         <v>4</v>
       </c>
       <c r="B666" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C666" t="s">
         <v>1951</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1952</v>
       </c>
       <c r="E666">
         <v>1962</v>
@@ -19260,10 +19240,10 @@
         <v>73</v>
       </c>
       <c r="B667" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C667" t="s">
         <v>1953</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1954</v>
       </c>
       <c r="E667">
         <v>1979</v>
@@ -19277,10 +19257,10 @@
         <v>6</v>
       </c>
       <c r="B668" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C668" t="s">
         <v>1955</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1956</v>
       </c>
       <c r="E668">
         <v>1958</v>
@@ -19294,10 +19274,10 @@
         <v>28</v>
       </c>
       <c r="B669" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C669" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E669">
         <v>1966</v>
@@ -19311,10 +19291,10 @@
         <v>24</v>
       </c>
       <c r="B670" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C670" t="s">
         <v>1958</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1959</v>
       </c>
       <c r="E670">
         <v>1969</v>
@@ -19328,10 +19308,10 @@
         <v>140</v>
       </c>
       <c r="B671" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C671" t="s">
         <v>1960</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1961</v>
       </c>
       <c r="E671">
         <v>1984</v>
@@ -19345,10 +19325,10 @@
         <v>77</v>
       </c>
       <c r="B672" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C672" t="s">
         <v>1962</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1963</v>
       </c>
       <c r="E672">
         <v>1982</v>
@@ -19362,10 +19342,10 @@
         <v>264</v>
       </c>
       <c r="B673" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C673" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E673">
         <v>1996</v>
@@ -19379,10 +19359,10 @@
         <v>181</v>
       </c>
       <c r="B674" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C674" t="s">
         <v>1965</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1966</v>
       </c>
       <c r="E674">
         <v>2001</v>
@@ -19396,10 +19376,10 @@
         <v>182</v>
       </c>
       <c r="B675" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C675" t="s">
         <v>1967</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1968</v>
       </c>
       <c r="E675">
         <v>2014</v>
@@ -19413,7 +19393,7 @@
         <v>61</v>
       </c>
       <c r="B676" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="C676" t="s">
         <v>61</v>
@@ -19430,10 +19410,10 @@
         <v>335</v>
       </c>
       <c r="B677" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C677" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E677">
         <v>2016</v>
@@ -19464,7 +19444,7 @@
         <v>142</v>
       </c>
       <c r="B679" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C679" t="s">
         <v>622</v>
@@ -19484,7 +19464,7 @@
         <v>1681</v>
       </c>
       <c r="C680" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E680">
         <v>1945</v>
@@ -19498,13 +19478,13 @@
         <v>516</v>
       </c>
       <c r="B681" t="s">
-        <v>1685</v>
+        <v>2285</v>
       </c>
       <c r="C681" t="s">
-        <v>1975</v>
+        <v>2286</v>
       </c>
       <c r="E681">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="F681" t="s">
         <v>970</v>
@@ -19515,10 +19495,10 @@
         <v>519</v>
       </c>
       <c r="B682" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C682" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E682">
         <v>1965</v>
@@ -19529,13 +19509,13 @@
     </row>
     <row r="683" spans="1:6">
       <c r="A683" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B683" t="s">
         <v>1686</v>
       </c>
-      <c r="B683" t="s">
-        <v>1687</v>
-      </c>
       <c r="C683" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="E683">
         <v>1947</v>
@@ -19546,13 +19526,13 @@
     </row>
     <row r="684" spans="1:6">
       <c r="A684" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B684" t="s">
         <v>1688</v>
       </c>
-      <c r="B684" t="s">
-        <v>1689</v>
-      </c>
       <c r="C684" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="E684">
         <v>1947</v>
@@ -19563,13 +19543,13 @@
     </row>
     <row r="685" spans="1:6">
       <c r="A685" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="B685" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="C685" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="E685">
         <v>1948</v>
@@ -19583,7 +19563,7 @@
         <v>1675</v>
       </c>
       <c r="B686" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="C686" t="s">
         <v>622</v>
@@ -19597,10 +19577,10 @@
     </row>
     <row r="687" spans="1:6">
       <c r="A687" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B687" t="s">
         <v>1693</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1694</v>
       </c>
       <c r="C687" t="s">
         <v>622</v>
@@ -19614,13 +19594,13 @@
     </row>
     <row r="688" spans="1:6">
       <c r="A688" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B688" t="s">
         <v>1695</v>
       </c>
-      <c r="B688" t="s">
-        <v>1696</v>
-      </c>
       <c r="C688" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="E688">
         <v>1949</v>
@@ -19631,13 +19611,13 @@
     </row>
     <row r="689" spans="1:6">
       <c r="A689" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B689" t="s">
         <v>1697</v>
       </c>
-      <c r="B689" t="s">
-        <v>1698</v>
-      </c>
       <c r="C689" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="E689">
         <v>1949</v>
@@ -19648,13 +19628,13 @@
     </row>
     <row r="690" spans="1:6">
       <c r="A690" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B690" t="s">
         <v>1699</v>
       </c>
-      <c r="B690" t="s">
-        <v>1700</v>
-      </c>
       <c r="C690" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="E690">
         <v>1949</v>
@@ -19665,13 +19645,13 @@
     </row>
     <row r="691" spans="1:6">
       <c r="A691" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B691" t="s">
         <v>1701</v>
       </c>
-      <c r="B691" t="s">
-        <v>1702</v>
-      </c>
       <c r="C691" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E691">
         <v>1950</v>
@@ -19682,13 +19662,13 @@
     </row>
     <row r="692" spans="1:6">
       <c r="A692" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B692" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C692" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E692">
         <v>1951</v>
@@ -19699,13 +19679,13 @@
     </row>
     <row r="693" spans="1:6">
       <c r="A693" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B693" t="s">
         <v>1705</v>
       </c>
-      <c r="B693" t="s">
+      <c r="C693" t="s">
         <v>1706</v>
-      </c>
-      <c r="C693" t="s">
-        <v>1707</v>
       </c>
       <c r="E693">
         <v>1951</v>
@@ -19716,13 +19696,13 @@
     </row>
     <row r="694" spans="1:6">
       <c r="A694" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B694" t="s">
         <v>1708</v>
       </c>
-      <c r="B694" t="s">
-        <v>1709</v>
-      </c>
       <c r="C694" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="E694">
         <v>1951</v>
@@ -19733,13 +19713,13 @@
     </row>
     <row r="695" spans="1:6">
       <c r="A695" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B695" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C695" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="E695">
         <v>1952</v>
@@ -19750,13 +19730,13 @@
     </row>
     <row r="696" spans="1:6">
       <c r="A696" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B696" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C696" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="E696">
         <v>1952</v>
@@ -19770,10 +19750,10 @@
         <v>1670</v>
       </c>
       <c r="B697" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C697" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="E697">
         <v>1952</v>
@@ -19784,13 +19764,13 @@
     </row>
     <row r="698" spans="1:6">
       <c r="A698" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B698" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C698" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="E698">
         <v>1953</v>
@@ -19801,13 +19781,13 @@
     </row>
     <row r="699" spans="1:6">
       <c r="A699" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B699" t="s">
         <v>1717</v>
       </c>
-      <c r="B699" t="s">
-        <v>1718</v>
-      </c>
       <c r="C699" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="E699">
         <v>1953</v>
@@ -19818,13 +19798,13 @@
     </row>
     <row r="700" spans="1:6">
       <c r="A700" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C700" t="s">
         <v>1720</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1719</v>
-      </c>
-      <c r="C700" t="s">
-        <v>1721</v>
       </c>
       <c r="E700">
         <v>1953</v>
@@ -19835,13 +19815,13 @@
     </row>
     <row r="701" spans="1:6">
       <c r="A701" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B701" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="C701" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="E701">
         <v>1954</v>
@@ -19852,13 +19832,13 @@
     </row>
     <row r="702" spans="1:6">
       <c r="A702" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B702" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="C702" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="E702">
         <v>1954</v>
@@ -19869,13 +19849,13 @@
     </row>
     <row r="703" spans="1:6">
       <c r="A703" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C703" t="s">
         <v>1726</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C703" t="s">
-        <v>1727</v>
       </c>
       <c r="E703">
         <v>1955</v>
@@ -19886,13 +19866,13 @@
     </row>
     <row r="704" spans="1:6">
       <c r="A704" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B704" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="C704" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="E704">
         <v>1955</v>
@@ -19903,13 +19883,13 @@
     </row>
     <row r="705" spans="1:6">
       <c r="A705" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C705" t="s">
         <v>1730</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C705" t="s">
-        <v>1731</v>
       </c>
       <c r="E705">
         <v>1955</v>
@@ -19937,13 +19917,13 @@
     </row>
     <row r="707" spans="1:6">
       <c r="A707" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C707" t="s">
         <v>1733</v>
-      </c>
-      <c r="B707" t="s">
-        <v>1732</v>
-      </c>
-      <c r="C707" t="s">
-        <v>1734</v>
       </c>
       <c r="E707">
         <v>1956</v>
@@ -19954,13 +19934,13 @@
     </row>
     <row r="708" spans="1:6">
       <c r="A708" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B708" t="s">
         <v>1744</v>
       </c>
-      <c r="B708" t="s">
-        <v>1745</v>
-      </c>
       <c r="C708" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="E708">
         <v>1957</v>
@@ -19971,13 +19951,13 @@
     </row>
     <row r="709" spans="1:6">
       <c r="A709" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B709" s="11" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C709" s="11" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="E709">
         <v>1958</v>
@@ -19988,13 +19968,13 @@
     </row>
     <row r="710" spans="1:6">
       <c r="A710" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B710" t="s">
         <v>1747</v>
       </c>
-      <c r="B710" t="s">
-        <v>1748</v>
-      </c>
       <c r="C710" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E710">
         <v>1958</v>
@@ -20005,13 +19985,13 @@
     </row>
     <row r="711" spans="1:6">
       <c r="A711" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B711" t="s">
         <v>1749</v>
       </c>
-      <c r="B711" t="s">
+      <c r="C711" t="s">
         <v>1750</v>
-      </c>
-      <c r="C711" t="s">
-        <v>1751</v>
       </c>
       <c r="E711">
         <v>1958</v>
@@ -20022,13 +20002,13 @@
     </row>
     <row r="712" spans="1:6">
       <c r="A712" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B712" t="s">
         <v>1752</v>
       </c>
-      <c r="B712" t="s">
-        <v>1753</v>
-      </c>
       <c r="C712" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E712">
         <v>1958</v>
@@ -20039,13 +20019,13 @@
     </row>
     <row r="713" spans="1:6">
       <c r="A713" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B713" t="s">
         <v>1754</v>
       </c>
-      <c r="B713" t="s">
+      <c r="C713" t="s">
         <v>1755</v>
-      </c>
-      <c r="C713" t="s">
-        <v>1756</v>
       </c>
       <c r="E713">
         <v>1959</v>
@@ -20056,13 +20036,13 @@
     </row>
     <row r="714" spans="1:6">
       <c r="A714" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B714" t="s">
         <v>1757</v>
       </c>
-      <c r="B714" t="s">
+      <c r="C714" t="s">
         <v>1758</v>
-      </c>
-      <c r="C714" t="s">
-        <v>1759</v>
       </c>
       <c r="E714">
         <v>1960</v>
@@ -20073,13 +20053,13 @@
     </row>
     <row r="715" spans="1:6">
       <c r="A715" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C715" t="s">
         <v>1761</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1760</v>
-      </c>
-      <c r="C715" t="s">
-        <v>1762</v>
       </c>
       <c r="E715">
         <v>1960</v>
@@ -20090,13 +20070,13 @@
     </row>
     <row r="716" spans="1:6">
       <c r="A716" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B716" t="s">
         <v>1763</v>
       </c>
-      <c r="B716" t="s">
-        <v>1764</v>
-      </c>
       <c r="C716" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="E716">
         <v>1960</v>
@@ -20107,13 +20087,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B717" t="s">
         <v>2089</v>
       </c>
-      <c r="B717" t="s">
-        <v>2096</v>
-      </c>
       <c r="C717" t="s">
-        <v>2097</v>
+        <v>2090</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20124,13 +20104,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="B718" t="s">
-        <v>2098</v>
+        <v>2091</v>
       </c>
       <c r="C718" t="s">
-        <v>2099</v>
+        <v>2092</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20141,13 +20121,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2101</v>
+        <v>2094</v>
       </c>
       <c r="B719" t="s">
-        <v>2100</v>
+        <v>2093</v>
       </c>
       <c r="C719" t="s">
-        <v>2101</v>
+        <v>2094</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20158,13 +20138,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="B720" t="s">
-        <v>2102</v>
+        <v>2095</v>
       </c>
       <c r="C720" t="s">
-        <v>2103</v>
+        <v>2096</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20175,13 +20155,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
       <c r="B721" t="s">
-        <v>2104</v>
+        <v>2097</v>
       </c>
       <c r="C721" t="s">
-        <v>2105</v>
+        <v>2098</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20192,13 +20172,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B722" t="s">
-        <v>2106</v>
+        <v>2099</v>
       </c>
       <c r="C722" t="s">
-        <v>2107</v>
+        <v>2100</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20209,13 +20189,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="B723" t="s">
-        <v>2108</v>
+        <v>2101</v>
       </c>
       <c r="C723" t="s">
-        <v>2109</v>
+        <v>2102</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20226,13 +20206,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B724" t="s">
-        <v>2110</v>
+        <v>2103</v>
       </c>
       <c r="C724" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20243,13 +20223,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2086</v>
+        <v>2079</v>
       </c>
       <c r="B725" t="s">
-        <v>2111</v>
+        <v>2104</v>
       </c>
       <c r="C725" t="s">
-        <v>2112</v>
+        <v>2105</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20260,13 +20240,13 @@
     </row>
     <row r="726" spans="1:6">
       <c r="A726" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B726" t="s">
-        <v>2113</v>
+        <v>2106</v>
       </c>
       <c r="C726" t="s">
-        <v>2114</v>
+        <v>2107</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20277,13 +20257,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="B727" t="s">
-        <v>2115</v>
+        <v>2108</v>
       </c>
       <c r="C727" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20294,13 +20274,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2084</v>
+        <v>2077</v>
       </c>
       <c r="B728" t="s">
-        <v>2116</v>
+        <v>2109</v>
       </c>
       <c r="C728" t="s">
-        <v>2117</v>
+        <v>2110</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20311,13 +20291,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B729" t="s">
-        <v>2118</v>
+        <v>2111</v>
       </c>
       <c r="C729" t="s">
-        <v>2119</v>
+        <v>2112</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20328,13 +20308,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B730" t="s">
-        <v>2120</v>
+        <v>2113</v>
       </c>
       <c r="C730" t="s">
-        <v>2121</v>
+        <v>2114</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20345,13 +20325,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B731" t="s">
-        <v>2122</v>
+        <v>2115</v>
       </c>
       <c r="C731" t="s">
-        <v>2123</v>
+        <v>2116</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20362,13 +20342,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B732" t="s">
-        <v>2124</v>
+        <v>2117</v>
       </c>
       <c r="C732" t="s">
-        <v>2124</v>
+        <v>2117</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20379,13 +20359,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="B733" t="s">
-        <v>2125</v>
+        <v>2118</v>
       </c>
       <c r="C733" t="s">
-        <v>2126</v>
+        <v>2119</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20396,13 +20376,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2071</v>
+        <v>2064</v>
       </c>
       <c r="B734" t="s">
-        <v>2127</v>
+        <v>2120</v>
       </c>
       <c r="C734" t="s">
-        <v>2128</v>
+        <v>2121</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20413,13 +20393,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B735" t="s">
-        <v>2129</v>
+        <v>2122</v>
       </c>
       <c r="C735" t="s">
-        <v>2130</v>
+        <v>2123</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20430,13 +20410,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B736" t="s">
-        <v>2131</v>
+        <v>2124</v>
       </c>
       <c r="C736" t="s">
-        <v>2132</v>
+        <v>2125</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20447,13 +20427,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2090</v>
+        <v>2083</v>
       </c>
       <c r="B737" t="s">
-        <v>2133</v>
+        <v>2126</v>
       </c>
       <c r="C737" t="s">
-        <v>2134</v>
+        <v>2127</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20464,13 +20444,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2135</v>
+        <v>2128</v>
       </c>
       <c r="B738" t="s">
-        <v>2136</v>
+        <v>2129</v>
       </c>
       <c r="C738" t="s">
-        <v>2137</v>
+        <v>2130</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20481,13 +20461,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B739" t="s">
-        <v>2138</v>
+        <v>2131</v>
       </c>
       <c r="C739" t="s">
-        <v>2139</v>
+        <v>2132</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20498,13 +20478,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="B740" t="s">
-        <v>2140</v>
+        <v>2133</v>
       </c>
       <c r="C740" t="s">
-        <v>2141</v>
+        <v>2134</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20515,13 +20495,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="B741" t="s">
-        <v>2142</v>
+        <v>2135</v>
       </c>
       <c r="C741" t="s">
-        <v>2142</v>
+        <v>2135</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20532,13 +20512,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2055</v>
+        <v>2049</v>
       </c>
       <c r="B742" t="s">
-        <v>2143</v>
+        <v>2136</v>
       </c>
       <c r="C742" t="s">
-        <v>2144</v>
+        <v>2137</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20549,13 +20529,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2087</v>
+        <v>2080</v>
       </c>
       <c r="B743" t="s">
-        <v>2145</v>
+        <v>2138</v>
       </c>
       <c r="C743" t="s">
-        <v>2146</v>
+        <v>2139</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20566,13 +20546,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2078</v>
+        <v>2071</v>
       </c>
       <c r="B744" t="s">
-        <v>2147</v>
+        <v>2140</v>
       </c>
       <c r="C744" t="s">
-        <v>2148</v>
+        <v>2141</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20583,13 +20563,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2077</v>
+        <v>2070</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2149</v>
+        <v>2142</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20600,13 +20580,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B746" t="s">
-        <v>2150</v>
+        <v>2143</v>
       </c>
       <c r="C746" t="s">
-        <v>2151</v>
+        <v>2144</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20617,13 +20597,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
-        <v>2152</v>
+        <v>2145</v>
       </c>
       <c r="B747" t="s">
-        <v>2153</v>
+        <v>2146</v>
       </c>
       <c r="C747" t="s">
-        <v>2154</v>
+        <v>2147</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -20634,13 +20614,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B748" t="s">
-        <v>2155</v>
+        <v>2148</v>
       </c>
       <c r="C748" t="s">
-        <v>2156</v>
+        <v>2149</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -20651,13 +20631,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2076</v>
+        <v>2069</v>
       </c>
       <c r="B749" t="s">
-        <v>2157</v>
+        <v>2150</v>
       </c>
       <c r="C749" t="s">
-        <v>2158</v>
+        <v>2151</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -20668,13 +20648,13 @@
     </row>
     <row r="750" spans="1:6">
       <c r="A750" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B750" t="s">
-        <v>2159</v>
+        <v>2152</v>
       </c>
       <c r="C750" t="s">
-        <v>2160</v>
+        <v>2153</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -20685,13 +20665,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B751" t="s">
-        <v>2161</v>
+        <v>2154</v>
       </c>
       <c r="C751" t="s">
-        <v>2162</v>
+        <v>2155</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -20702,13 +20682,13 @@
     </row>
     <row r="752" spans="1:6">
       <c r="A752" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B752" t="s">
-        <v>2163</v>
+        <v>2156</v>
       </c>
       <c r="C752" t="s">
-        <v>2164</v>
+        <v>2157</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -20719,13 +20699,13 @@
     </row>
     <row r="753" spans="1:6">
       <c r="A753" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B753" t="s">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="C753" t="s">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -20736,13 +20716,13 @@
     </row>
     <row r="754" spans="1:6">
       <c r="A754" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B754" t="s">
-        <v>2166</v>
+        <v>2159</v>
       </c>
       <c r="C754" t="s">
-        <v>2167</v>
+        <v>2160</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -20753,13 +20733,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2067</v>
+        <v>2060</v>
       </c>
       <c r="B755" t="s">
-        <v>2168</v>
+        <v>2161</v>
       </c>
       <c r="C755" t="s">
-        <v>2169</v>
+        <v>2162</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -20770,13 +20750,13 @@
     </row>
     <row r="756" spans="1:6">
       <c r="A756" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B756" t="s">
-        <v>2170</v>
+        <v>2163</v>
       </c>
       <c r="C756" t="s">
-        <v>2171</v>
+        <v>2164</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -20787,13 +20767,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B757" t="s">
-        <v>2172</v>
+        <v>2165</v>
       </c>
       <c r="C757" t="s">
-        <v>2173</v>
+        <v>2166</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -20804,13 +20784,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2175</v>
+        <v>2168</v>
       </c>
       <c r="B758" t="s">
-        <v>2174</v>
+        <v>2167</v>
       </c>
       <c r="C758" t="s">
-        <v>2174</v>
+        <v>2167</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -20821,13 +20801,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B759" t="s">
-        <v>2176</v>
+        <v>2169</v>
       </c>
       <c r="C759" t="s">
-        <v>2177</v>
+        <v>2170</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -20838,13 +20818,13 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2178</v>
+        <v>2171</v>
       </c>
       <c r="E760">
         <v>2006</v>
@@ -20855,13 +20835,13 @@
     </row>
     <row r="761" spans="1:6">
       <c r="A761" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="B761" t="s">
-        <v>2179</v>
+        <v>2172</v>
       </c>
       <c r="C761" t="s">
-        <v>2180</v>
+        <v>2173</v>
       </c>
       <c r="E761">
         <v>1987</v>
@@ -20872,13 +20852,13 @@
     </row>
     <row r="762" spans="1:6">
       <c r="A762" t="s">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="B762" t="s">
-        <v>2181</v>
+        <v>2174</v>
       </c>
       <c r="C762" t="s">
-        <v>2182</v>
+        <v>2175</v>
       </c>
       <c r="E762">
         <v>1952</v>
@@ -20889,13 +20869,13 @@
     </row>
     <row r="763" spans="1:6">
       <c r="A763" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B763" t="s">
-        <v>2183</v>
+        <v>2176</v>
       </c>
       <c r="C763" t="s">
-        <v>2184</v>
+        <v>2177</v>
       </c>
       <c r="E763">
         <v>2000</v>
@@ -20906,13 +20886,13 @@
     </row>
     <row r="764" spans="1:6">
       <c r="A764" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B764" t="s">
-        <v>2185</v>
+        <v>2178</v>
       </c>
       <c r="C764" t="s">
-        <v>2186</v>
+        <v>2179</v>
       </c>
       <c r="E764">
         <v>2018</v>
@@ -20923,13 +20903,13 @@
     </row>
     <row r="765" spans="1:6">
       <c r="A765" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="B765" t="s">
-        <v>2187</v>
+        <v>2180</v>
       </c>
       <c r="C765" t="s">
-        <v>2187</v>
+        <v>2180</v>
       </c>
       <c r="E765">
         <v>1977</v>
@@ -20940,13 +20920,13 @@
     </row>
     <row r="766" spans="1:6">
       <c r="A766" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B766" t="s">
-        <v>2188</v>
+        <v>2181</v>
       </c>
       <c r="C766" t="s">
-        <v>2189</v>
+        <v>2182</v>
       </c>
       <c r="E766">
         <v>1994</v>
@@ -20957,13 +20937,13 @@
     </row>
     <row r="767" spans="1:6">
       <c r="A767" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="B767" t="s">
-        <v>2190</v>
+        <v>2183</v>
       </c>
       <c r="C767" t="s">
-        <v>2190</v>
+        <v>2183</v>
       </c>
       <c r="E767">
         <v>1972</v>
@@ -20974,13 +20954,13 @@
     </row>
     <row r="768" spans="1:6">
       <c r="A768" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B768" t="s">
         <v>1212</v>
       </c>
       <c r="C768" t="s">
-        <v>2191</v>
+        <v>2184</v>
       </c>
       <c r="E768">
         <v>2002</v>
@@ -20991,13 +20971,13 @@
     </row>
     <row r="769" spans="1:6">
       <c r="A769" t="s">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B769" t="s">
-        <v>2192</v>
+        <v>2185</v>
       </c>
       <c r="C769" t="s">
-        <v>2193</v>
+        <v>2186</v>
       </c>
       <c r="E769">
         <v>1974</v>
@@ -21008,13 +20988,13 @@
     </row>
     <row r="770" spans="1:6">
       <c r="A770" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B770" t="s">
-        <v>2195</v>
+        <v>2188</v>
       </c>
       <c r="C770" t="s">
-        <v>2194</v>
+        <v>2187</v>
       </c>
       <c r="E770">
         <v>1978</v>
@@ -21025,13 +21005,13 @@
     </row>
     <row r="771" spans="1:6">
       <c r="A771" t="s">
-        <v>2094</v>
+        <v>2087</v>
       </c>
       <c r="B771" t="s">
-        <v>2196</v>
+        <v>2189</v>
       </c>
       <c r="C771" t="s">
-        <v>2197</v>
+        <v>2190</v>
       </c>
       <c r="E771">
         <v>2004</v>
@@ -21042,13 +21022,13 @@
     </row>
     <row r="772" spans="1:6">
       <c r="A772" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B772" t="s">
-        <v>2198</v>
+        <v>2191</v>
       </c>
       <c r="C772" t="s">
-        <v>2199</v>
+        <v>2192</v>
       </c>
       <c r="E772">
         <v>1979</v>
@@ -21059,13 +21039,13 @@
     </row>
     <row r="773" spans="1:6">
       <c r="A773" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B773" t="s">
-        <v>2200</v>
+        <v>2193</v>
       </c>
       <c r="C773" t="s">
-        <v>2201</v>
+        <v>2194</v>
       </c>
       <c r="E773">
         <v>1984</v>
@@ -21076,13 +21056,13 @@
     </row>
     <row r="774" spans="1:6">
       <c r="A774" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="B774" t="s">
-        <v>2202</v>
+        <v>2195</v>
       </c>
       <c r="C774" t="s">
-        <v>2203</v>
+        <v>2196</v>
       </c>
       <c r="E774">
         <v>1974</v>
@@ -21093,13 +21073,13 @@
     </row>
     <row r="775" spans="1:6">
       <c r="A775" t="s">
-        <v>2061</v>
+        <v>2055</v>
       </c>
       <c r="B775" t="s">
-        <v>2204</v>
+        <v>2197</v>
       </c>
       <c r="C775" t="s">
-        <v>2205</v>
+        <v>2198</v>
       </c>
       <c r="E775">
         <v>2011</v>
@@ -21110,13 +21090,13 @@
     </row>
     <row r="776" spans="1:6">
       <c r="A776" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B776" t="s">
-        <v>2206</v>
+        <v>2199</v>
       </c>
       <c r="C776" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="E776">
         <v>1995</v>
@@ -21127,13 +21107,13 @@
     </row>
     <row r="777" spans="1:6">
       <c r="A777" t="s">
-        <v>2208</v>
+        <v>2201</v>
       </c>
       <c r="B777" t="s">
-        <v>2207</v>
+        <v>2200</v>
       </c>
       <c r="C777" t="s">
-        <v>2209</v>
+        <v>2202</v>
       </c>
       <c r="E777">
         <v>2006</v>
@@ -21144,13 +21124,13 @@
     </row>
     <row r="778" spans="1:6">
       <c r="A778" t="s">
-        <v>2210</v>
+        <v>2203</v>
       </c>
       <c r="B778" s="8" t="s">
-        <v>2211</v>
+        <v>2204</v>
       </c>
       <c r="C778" t="s">
-        <v>2212</v>
+        <v>2205</v>
       </c>
       <c r="E778">
         <v>1958</v>
@@ -21161,13 +21141,13 @@
     </row>
     <row r="779" spans="1:6">
       <c r="A779" t="s">
-        <v>2066</v>
+        <v>2059</v>
       </c>
       <c r="B779" t="s">
-        <v>2214</v>
+        <v>2207</v>
       </c>
       <c r="C779" t="s">
-        <v>2213</v>
+        <v>2206</v>
       </c>
       <c r="E779">
         <v>1993</v>
@@ -21178,13 +21158,13 @@
     </row>
     <row r="780" spans="1:6">
       <c r="A780" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B780" t="s">
-        <v>2215</v>
+        <v>2208</v>
       </c>
       <c r="C780" t="s">
-        <v>2216</v>
+        <v>2209</v>
       </c>
       <c r="E780">
         <v>2008</v>
@@ -21195,13 +21175,13 @@
     </row>
     <row r="781" spans="1:6">
       <c r="A781" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B781" t="s">
-        <v>2217</v>
+        <v>2210</v>
       </c>
       <c r="C781" t="s">
-        <v>2218</v>
+        <v>2211</v>
       </c>
       <c r="E781">
         <v>2005</v>
@@ -21212,13 +21192,13 @@
     </row>
     <row r="782" spans="1:6">
       <c r="A782" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B782" t="s">
-        <v>2220</v>
+        <v>2213</v>
       </c>
       <c r="C782" t="s">
-        <v>2219</v>
+        <v>2212</v>
       </c>
       <c r="E782">
         <v>1995</v>
@@ -21229,13 +21209,13 @@
     </row>
     <row r="783" spans="1:6">
       <c r="A783" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B783" t="s">
-        <v>2221</v>
+        <v>2214</v>
       </c>
       <c r="C783" t="s">
-        <v>2222</v>
+        <v>2215</v>
       </c>
       <c r="E783">
         <v>1978</v>
@@ -21246,13 +21226,13 @@
     </row>
     <row r="784" spans="1:6">
       <c r="A784" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
       <c r="B784" t="s">
-        <v>2224</v>
+        <v>2217</v>
       </c>
       <c r="C784" t="s">
-        <v>2223</v>
+        <v>2216</v>
       </c>
       <c r="E784">
         <v>1974</v>
@@ -21263,13 +21243,13 @@
     </row>
     <row r="785" spans="1:6">
       <c r="A785" t="s">
-        <v>2072</v>
+        <v>2065</v>
       </c>
       <c r="B785" t="s">
-        <v>2225</v>
+        <v>2218</v>
       </c>
       <c r="C785" t="s">
-        <v>2225</v>
+        <v>2218</v>
       </c>
       <c r="E785">
         <v>1963</v>
@@ -21280,13 +21260,13 @@
     </row>
     <row r="786" spans="1:6">
       <c r="A786" t="s">
-        <v>2095</v>
+        <v>2088</v>
       </c>
       <c r="B786" t="s">
-        <v>2226</v>
+        <v>2219</v>
       </c>
       <c r="C786" t="s">
-        <v>2227</v>
+        <v>2220</v>
       </c>
       <c r="E786">
         <v>2005</v>
@@ -21297,13 +21277,13 @@
     </row>
     <row r="787" spans="1:6">
       <c r="A787" t="s">
-        <v>2228</v>
+        <v>2221</v>
       </c>
       <c r="B787" t="s">
-        <v>2229</v>
+        <v>2222</v>
       </c>
       <c r="C787" t="s">
-        <v>2230</v>
+        <v>2223</v>
       </c>
       <c r="E787">
         <v>1978</v>
@@ -21314,13 +21294,13 @@
     </row>
     <row r="788" spans="1:6">
       <c r="A788" t="s">
-        <v>2231</v>
+        <v>2224</v>
       </c>
       <c r="B788" t="s">
-        <v>2232</v>
+        <v>2225</v>
       </c>
       <c r="C788" t="s">
-        <v>2232</v>
+        <v>2225</v>
       </c>
       <c r="E788">
         <v>1977</v>
@@ -21331,13 +21311,13 @@
     </row>
     <row r="789" spans="1:6">
       <c r="A789" t="s">
-        <v>2233</v>
+        <v>2226</v>
       </c>
       <c r="B789" t="s">
-        <v>2234</v>
+        <v>2227</v>
       </c>
       <c r="C789" t="s">
-        <v>2235</v>
+        <v>2228</v>
       </c>
       <c r="E789">
         <v>1986</v>
@@ -21348,13 +21328,13 @@
     </row>
     <row r="790" spans="1:6">
       <c r="A790" t="s">
-        <v>2236</v>
+        <v>2229</v>
       </c>
       <c r="B790" t="s">
-        <v>2237</v>
+        <v>2230</v>
       </c>
       <c r="C790" t="s">
-        <v>2238</v>
+        <v>2231</v>
       </c>
       <c r="E790">
         <v>1965</v>
@@ -21365,13 +21345,13 @@
     </row>
     <row r="791" spans="1:6">
       <c r="A791" t="s">
-        <v>2239</v>
+        <v>2232</v>
       </c>
       <c r="B791" t="s">
-        <v>2240</v>
+        <v>2233</v>
       </c>
       <c r="C791" t="s">
-        <v>2241</v>
+        <v>2234</v>
       </c>
       <c r="E791">
         <v>2003</v>
@@ -21382,13 +21362,13 @@
     </row>
     <row r="792" spans="1:6">
       <c r="A792" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B792" t="s">
-        <v>2242</v>
+        <v>2235</v>
       </c>
       <c r="C792" t="s">
-        <v>2243</v>
+        <v>2236</v>
       </c>
       <c r="E792">
         <v>1997</v>
@@ -21399,13 +21379,13 @@
     </row>
     <row r="793" spans="1:6">
       <c r="A793" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="B793" t="s">
-        <v>2244</v>
+        <v>2237</v>
       </c>
       <c r="C793" t="s">
-        <v>2245</v>
+        <v>2238</v>
       </c>
       <c r="E793">
         <v>1959</v>
@@ -21416,13 +21396,13 @@
     </row>
     <row r="794" spans="1:6">
       <c r="A794" t="s">
-        <v>2246</v>
+        <v>2239</v>
       </c>
       <c r="B794" t="s">
-        <v>2247</v>
+        <v>2240</v>
       </c>
       <c r="C794" t="s">
-        <v>2248</v>
+        <v>2241</v>
       </c>
       <c r="E794">
         <v>1992</v>
@@ -21433,13 +21413,13 @@
     </row>
     <row r="795" spans="1:6">
       <c r="A795" t="s">
-        <v>2080</v>
+        <v>2073</v>
       </c>
       <c r="B795" t="s">
-        <v>2249</v>
+        <v>2242</v>
       </c>
       <c r="C795" t="s">
-        <v>2250</v>
+        <v>2243</v>
       </c>
       <c r="E795">
         <v>1989</v>
@@ -21450,13 +21430,13 @@
     </row>
     <row r="796" spans="1:6">
       <c r="A796" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
       <c r="B796" t="s">
-        <v>2251</v>
+        <v>2244</v>
       </c>
       <c r="C796" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
       <c r="E796">
         <v>1959</v>
@@ -21467,13 +21447,13 @@
     </row>
     <row r="797" spans="1:6">
       <c r="A797" t="s">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B797" t="s">
-        <v>2252</v>
+        <v>2245</v>
       </c>
       <c r="C797" t="s">
-        <v>2253</v>
+        <v>2246</v>
       </c>
       <c r="E797">
         <v>1991</v>
@@ -21484,13 +21464,13 @@
     </row>
     <row r="798" spans="1:6">
       <c r="A798" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B798" t="s">
-        <v>2254</v>
+        <v>2247</v>
       </c>
       <c r="C798" t="s">
-        <v>2255</v>
+        <v>2248</v>
       </c>
       <c r="E798">
         <v>1991</v>
@@ -21501,13 +21481,13 @@
     </row>
     <row r="799" spans="1:6">
       <c r="A799" t="s">
-        <v>2092</v>
+        <v>2085</v>
       </c>
       <c r="B799" t="s">
-        <v>2256</v>
+        <v>2249</v>
       </c>
       <c r="C799" t="s">
-        <v>2257</v>
+        <v>2250</v>
       </c>
       <c r="E799">
         <v>1999</v>
@@ -21518,13 +21498,13 @@
     </row>
     <row r="800" spans="1:6">
       <c r="A800" t="s">
-        <v>2081</v>
+        <v>2074</v>
       </c>
       <c r="B800" t="s">
-        <v>2258</v>
+        <v>2251</v>
       </c>
       <c r="C800" t="s">
-        <v>2259</v>
+        <v>2252</v>
       </c>
       <c r="E800">
         <v>1968</v>
@@ -21535,13 +21515,13 @@
     </row>
     <row r="801" spans="1:6">
       <c r="A801" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
       <c r="B801" t="s">
-        <v>2260</v>
+        <v>2253</v>
       </c>
       <c r="C801" t="s">
-        <v>2261</v>
+        <v>2254</v>
       </c>
       <c r="E801">
         <v>1994</v>
@@ -21552,13 +21532,13 @@
     </row>
     <row r="802" spans="1:6">
       <c r="A802" t="s">
-        <v>2262</v>
+        <v>2255</v>
       </c>
       <c r="B802" t="s">
-        <v>2263</v>
+        <v>2256</v>
       </c>
       <c r="C802" t="s">
-        <v>2264</v>
+        <v>2257</v>
       </c>
       <c r="E802">
         <v>1996</v>
@@ -21575,7 +21555,7 @@
         <v>1000</v>
       </c>
       <c r="C803" t="s">
-        <v>2265</v>
+        <v>2258</v>
       </c>
       <c r="E803">
         <v>1993</v>
@@ -21586,13 +21566,13 @@
     </row>
     <row r="804" spans="1:6">
       <c r="A804" t="s">
-        <v>2091</v>
+        <v>2084</v>
       </c>
       <c r="B804" t="s">
-        <v>2266</v>
+        <v>2259</v>
       </c>
       <c r="C804" t="s">
-        <v>2267</v>
+        <v>2260</v>
       </c>
       <c r="E804">
         <v>1998</v>
@@ -21603,13 +21583,13 @@
     </row>
     <row r="805" spans="1:6">
       <c r="A805" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B805" t="s">
-        <v>2268</v>
+        <v>2261</v>
       </c>
       <c r="C805" t="s">
-        <v>2269</v>
+        <v>2262</v>
       </c>
       <c r="E805">
         <v>1981</v>
@@ -21637,13 +21617,13 @@
     </row>
     <row r="807" spans="1:6">
       <c r="A807" t="s">
-        <v>2270</v>
+        <v>2263</v>
       </c>
       <c r="B807" t="s">
-        <v>2271</v>
+        <v>2264</v>
       </c>
       <c r="C807" t="s">
-        <v>2272</v>
+        <v>2265</v>
       </c>
       <c r="E807">
         <v>1992</v>
@@ -21654,13 +21634,13 @@
     </row>
     <row r="808" spans="1:6">
       <c r="A808" t="s">
-        <v>2075</v>
+        <v>2068</v>
       </c>
       <c r="B808" t="s">
-        <v>2273</v>
+        <v>2266</v>
       </c>
       <c r="C808" t="s">
-        <v>2273</v>
+        <v>2266</v>
       </c>
       <c r="E808">
         <v>1959</v>
@@ -21671,13 +21651,13 @@
     </row>
     <row r="809" spans="1:6">
       <c r="A809" t="s">
-        <v>2053</v>
+        <v>2047</v>
       </c>
       <c r="B809" t="s">
-        <v>2274</v>
+        <v>2267</v>
       </c>
       <c r="C809" t="s">
-        <v>2275</v>
+        <v>2268</v>
       </c>
       <c r="E809">
         <v>2010</v>
@@ -21688,18 +21668,188 @@
     </row>
     <row r="810" spans="1:6">
       <c r="A810" t="s">
-        <v>2079</v>
+        <v>2072</v>
       </c>
       <c r="B810" t="s">
-        <v>2276</v>
+        <v>2269</v>
       </c>
       <c r="C810" t="s">
-        <v>2277</v>
+        <v>2270</v>
       </c>
       <c r="E810">
         <v>1964</v>
       </c>
       <c r="F810" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6">
+      <c r="A811" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B811" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C811" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E811">
+        <v>1980</v>
+      </c>
+      <c r="F811" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6">
+      <c r="A812" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B812" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C812" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E812">
+        <v>1990</v>
+      </c>
+      <c r="F812" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6">
+      <c r="A813" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B813" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C813" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E813">
+        <v>1997</v>
+      </c>
+      <c r="F813" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6">
+      <c r="A814" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B814" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C814" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E814">
+        <v>2007</v>
+      </c>
+      <c r="F814" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6">
+      <c r="A815" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B815" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C815" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E815">
+        <v>2014</v>
+      </c>
+      <c r="F815" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6">
+      <c r="A816" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B816" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C816" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E816">
+        <v>1988</v>
+      </c>
+      <c r="F816" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6">
+      <c r="A817" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B817" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C817" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E817">
+        <v>1962</v>
+      </c>
+      <c r="F817" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6">
+      <c r="A818" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B818" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C818" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E818">
+        <v>1972</v>
+      </c>
+      <c r="F818" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6">
+      <c r="A819" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B819" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C819" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E819">
+        <v>1988</v>
+      </c>
+      <c r="F819" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6">
+      <c r="A820" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B820" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C820" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E820">
+        <v>1988</v>
+      </c>
+      <c r="F820" t="s">
         <v>969</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EE335C-387B-7045-8301-9F8B520CCBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2940C610-8F13-5B46-AE6D-E900F79A30C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="2293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="2308">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6128,12 +6128,6 @@
     <t>Blondie</t>
   </si>
   <si>
-    <t>Wet Leg</t>
-  </si>
-  <si>
-    <t>Wolf Alice</t>
-  </si>
-  <si>
     <t>Nada Surf</t>
   </si>
   <si>
@@ -6146,9 +6140,6 @@
     <t>My Morning Jacket</t>
   </si>
   <si>
-    <t>Yeah Yeah Yeahs</t>
-  </si>
-  <si>
     <t>Hooverphonic</t>
   </si>
   <si>
@@ -6176,9 +6167,6 @@
     <t>Eurythmics</t>
   </si>
   <si>
-    <t>Tricky</t>
-  </si>
-  <si>
     <t>Bob Mould</t>
   </si>
   <si>
@@ -6260,9 +6248,6 @@
     <t>Idles</t>
   </si>
   <si>
-    <t>Wolf Parade</t>
-  </si>
-  <si>
     <t>Cheap Trick</t>
   </si>
   <si>
@@ -6275,12 +6260,6 @@
     <t>Traveling Wilburys</t>
   </si>
   <si>
-    <t>Underworld</t>
-  </si>
-  <si>
-    <t>X Ray Spex</t>
-  </si>
-  <si>
     <t>Big Thief</t>
   </si>
   <si>
@@ -6320,9 +6299,6 @@
     <t>Big Star</t>
   </si>
   <si>
-    <t>TV on the Radio</t>
-  </si>
-  <si>
     <t>The Verve</t>
   </si>
   <si>
@@ -7026,6 +7002,75 @@
   </si>
   <si>
     <t>Traveling Wilburys Vol. 1</t>
+  </si>
+  <si>
+    <t>Blister in the Sun</t>
+  </si>
+  <si>
+    <t>Ride the Tiger</t>
+  </si>
+  <si>
+    <t>La Grange</t>
+  </si>
+  <si>
+    <t>Tres Hombres</t>
+  </si>
+  <si>
+    <t>Canned Heat</t>
+  </si>
+  <si>
+    <t>Going Up the Country</t>
+  </si>
+  <si>
+    <t>Living the Blues</t>
+  </si>
+  <si>
+    <t>Wake Me Up</t>
+  </si>
+  <si>
+    <t>Avicii</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>The Yard Birds</t>
+  </si>
+  <si>
+    <t>Shapes of Things</t>
+  </si>
+  <si>
+    <t>Mission: Impossible (feat. San Diego Symphony Pops)</t>
+  </si>
+  <si>
+    <t>Lalo Schifrin</t>
+  </si>
+  <si>
+    <t>Music From Mission: Impossible (Original Television Soundtrack)</t>
+  </si>
+  <si>
+    <t>Gary Portnoy</t>
+  </si>
+  <si>
+    <t>Cheers Theme Song (TV Version)</t>
+  </si>
+  <si>
+    <t>The Rembrandts</t>
+  </si>
+  <si>
+    <t>Ja’Net DuBois</t>
+  </si>
+  <si>
+    <t>Larry Marks</t>
+  </si>
+  <si>
+    <t>Friends Theme Song (TV Version)</t>
+  </si>
+  <si>
+    <t>Jeffersons Theme Song (TV Version)</t>
+  </si>
+  <si>
+    <t>Scooby‑Doo Theme Song (TV Version)</t>
   </si>
 </sst>
 </file>
@@ -7458,73 +7503,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="B4:B15"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.83203125" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="1" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="1" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="1"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B15">
-    <sortCondition ref="B1:B15"/>
+  <sheetData/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B3">
+    <sortCondition ref="B1:B3"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7533,7 +7519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F820"/>
+  <dimension ref="A1:F831"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -12763,7 +12749,7 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>2078</v>
+        <v>2070</v>
       </c>
       <c r="B295" t="s">
         <v>1119</v>
@@ -16936,7 +16922,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
       <c r="B532" t="s">
         <v>1611</v>
@@ -19478,10 +19464,10 @@
         <v>516</v>
       </c>
       <c r="B681" t="s">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="C681" t="s">
-        <v>2286</v>
+        <v>2278</v>
       </c>
       <c r="E681">
         <v>1961</v>
@@ -20087,13 +20073,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B717" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C717" t="s">
         <v>2082</v>
-      </c>
-      <c r="B717" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C717" t="s">
-        <v>2090</v>
       </c>
       <c r="E717">
         <v>1985</v>
@@ -20104,13 +20090,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
       <c r="B718" t="s">
-        <v>2091</v>
+        <v>2083</v>
       </c>
       <c r="C718" t="s">
-        <v>2092</v>
+        <v>2084</v>
       </c>
       <c r="E718">
         <v>2006</v>
@@ -20121,13 +20107,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="B719" t="s">
-        <v>2093</v>
+        <v>2085</v>
       </c>
       <c r="C719" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="E719">
         <v>1979</v>
@@ -20138,13 +20124,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B720" t="s">
-        <v>2095</v>
+        <v>2087</v>
       </c>
       <c r="C720" t="s">
-        <v>2096</v>
+        <v>2088</v>
       </c>
       <c r="E720">
         <v>1997</v>
@@ -20155,13 +20141,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
       <c r="B721" t="s">
-        <v>2097</v>
+        <v>2089</v>
       </c>
       <c r="C721" t="s">
-        <v>2098</v>
+        <v>2090</v>
       </c>
       <c r="E721">
         <v>1974</v>
@@ -20172,13 +20158,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
       <c r="B722" t="s">
-        <v>2099</v>
+        <v>2091</v>
       </c>
       <c r="C722" t="s">
-        <v>2100</v>
+        <v>2092</v>
       </c>
       <c r="E722">
         <v>2016</v>
@@ -20189,13 +20175,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B723" t="s">
-        <v>2101</v>
+        <v>2093</v>
       </c>
       <c r="C723" t="s">
-        <v>2102</v>
+        <v>2094</v>
       </c>
       <c r="E723">
         <v>1972</v>
@@ -20206,13 +20192,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B724" t="s">
-        <v>2103</v>
+        <v>2095</v>
       </c>
       <c r="C724" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E724">
         <v>2019</v>
@@ -20223,13 +20209,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" t="s">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="B725" t="s">
-        <v>2104</v>
+        <v>2096</v>
       </c>
       <c r="C725" t="s">
-        <v>2105</v>
+        <v>2097</v>
       </c>
       <c r="E725">
         <v>1980</v>
@@ -20243,10 +20229,10 @@
         <v>1992</v>
       </c>
       <c r="B726" t="s">
-        <v>2106</v>
+        <v>2098</v>
       </c>
       <c r="C726" t="s">
-        <v>2107</v>
+        <v>2099</v>
       </c>
       <c r="E726">
         <v>1979</v>
@@ -20257,13 +20243,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="B727" t="s">
-        <v>2108</v>
+        <v>2100</v>
       </c>
       <c r="C727" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="E727">
         <v>1997</v>
@@ -20274,13 +20260,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
       <c r="B728" t="s">
-        <v>2109</v>
+        <v>2101</v>
       </c>
       <c r="C728" t="s">
-        <v>2110</v>
+        <v>2102</v>
       </c>
       <c r="E728">
         <v>1977</v>
@@ -20291,13 +20277,13 @@
     </row>
     <row r="729" spans="1:6">
       <c r="A729" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B729" t="s">
-        <v>2111</v>
+        <v>2103</v>
       </c>
       <c r="C729" t="s">
-        <v>2112</v>
+        <v>2104</v>
       </c>
       <c r="E729">
         <v>1988</v>
@@ -20308,13 +20294,13 @@
     </row>
     <row r="730" spans="1:6">
       <c r="A730" t="s">
-        <v>2045</v>
+        <v>2038</v>
       </c>
       <c r="B730" t="s">
-        <v>2113</v>
+        <v>2105</v>
       </c>
       <c r="C730" t="s">
-        <v>2114</v>
+        <v>2106</v>
       </c>
       <c r="E730">
         <v>2011</v>
@@ -20325,13 +20311,13 @@
     </row>
     <row r="731" spans="1:6">
       <c r="A731" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="B731" t="s">
-        <v>2115</v>
+        <v>2107</v>
       </c>
       <c r="C731" t="s">
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="E731">
         <v>1997</v>
@@ -20342,13 +20328,13 @@
     </row>
     <row r="732" spans="1:6">
       <c r="A732" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B732" t="s">
-        <v>2117</v>
+        <v>2109</v>
       </c>
       <c r="C732" t="s">
-        <v>2117</v>
+        <v>2109</v>
       </c>
       <c r="E732">
         <v>2007</v>
@@ -20359,13 +20345,13 @@
     </row>
     <row r="733" spans="1:6">
       <c r="A733" t="s">
-        <v>2086</v>
+        <v>2078</v>
       </c>
       <c r="B733" t="s">
-        <v>2118</v>
+        <v>2110</v>
       </c>
       <c r="C733" t="s">
-        <v>2119</v>
+        <v>2111</v>
       </c>
       <c r="E733">
         <v>1999</v>
@@ -20376,13 +20362,13 @@
     </row>
     <row r="734" spans="1:6">
       <c r="A734" t="s">
-        <v>2064</v>
+        <v>2056</v>
       </c>
       <c r="B734" t="s">
-        <v>2120</v>
+        <v>2112</v>
       </c>
       <c r="C734" t="s">
-        <v>2121</v>
+        <v>2113</v>
       </c>
       <c r="E734">
         <v>1957</v>
@@ -20393,13 +20379,13 @@
     </row>
     <row r="735" spans="1:6">
       <c r="A735" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="B735" t="s">
-        <v>2122</v>
+        <v>2114</v>
       </c>
       <c r="C735" t="s">
-        <v>2123</v>
+        <v>2115</v>
       </c>
       <c r="E735">
         <v>1993</v>
@@ -20410,13 +20396,13 @@
     </row>
     <row r="736" spans="1:6">
       <c r="A736" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B736" t="s">
-        <v>2124</v>
+        <v>2116</v>
       </c>
       <c r="C736" t="s">
-        <v>2125</v>
+        <v>2117</v>
       </c>
       <c r="E736">
         <v>1988</v>
@@ -20427,13 +20413,13 @@
     </row>
     <row r="737" spans="1:6">
       <c r="A737" t="s">
-        <v>2083</v>
+        <v>2075</v>
       </c>
       <c r="B737" t="s">
-        <v>2126</v>
+        <v>2118</v>
       </c>
       <c r="C737" t="s">
-        <v>2127</v>
+        <v>2119</v>
       </c>
       <c r="E737">
         <v>1989</v>
@@ -20444,13 +20430,13 @@
     </row>
     <row r="738" spans="1:6">
       <c r="A738" t="s">
-        <v>2128</v>
+        <v>2120</v>
       </c>
       <c r="B738" t="s">
-        <v>2129</v>
+        <v>2121</v>
       </c>
       <c r="C738" t="s">
-        <v>2130</v>
+        <v>2122</v>
       </c>
       <c r="E738">
         <v>1986</v>
@@ -20461,13 +20447,13 @@
     </row>
     <row r="739" spans="1:6">
       <c r="A739" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B739" t="s">
-        <v>2131</v>
+        <v>2123</v>
       </c>
       <c r="C739" t="s">
-        <v>2132</v>
+        <v>2124</v>
       </c>
       <c r="E739">
         <v>2016</v>
@@ -20478,13 +20464,13 @@
     </row>
     <row r="740" spans="1:6">
       <c r="A740" t="s">
-        <v>2081</v>
+        <v>2073</v>
       </c>
       <c r="B740" t="s">
-        <v>2133</v>
+        <v>2125</v>
       </c>
       <c r="C740" t="s">
-        <v>2134</v>
+        <v>2126</v>
       </c>
       <c r="E740">
         <v>1983</v>
@@ -20495,13 +20481,13 @@
     </row>
     <row r="741" spans="1:6">
       <c r="A741" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
       <c r="B741" t="s">
-        <v>2135</v>
+        <v>2127</v>
       </c>
       <c r="C741" t="s">
-        <v>2135</v>
+        <v>2127</v>
       </c>
       <c r="E741">
         <v>1990</v>
@@ -20512,13 +20498,13 @@
     </row>
     <row r="742" spans="1:6">
       <c r="A742" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
       <c r="B742" t="s">
-        <v>2136</v>
+        <v>2128</v>
       </c>
       <c r="C742" t="s">
-        <v>2137</v>
+        <v>2129</v>
       </c>
       <c r="E742">
         <v>1990</v>
@@ -20529,13 +20515,13 @@
     </row>
     <row r="743" spans="1:6">
       <c r="A743" t="s">
-        <v>2080</v>
+        <v>2072</v>
       </c>
       <c r="B743" t="s">
-        <v>2138</v>
+        <v>2130</v>
       </c>
       <c r="C743" t="s">
-        <v>2139</v>
+        <v>2131</v>
       </c>
       <c r="E743">
         <v>1982</v>
@@ -20546,13 +20532,13 @@
     </row>
     <row r="744" spans="1:6">
       <c r="A744" t="s">
-        <v>2071</v>
+        <v>2063</v>
       </c>
       <c r="B744" t="s">
-        <v>2140</v>
+        <v>2132</v>
       </c>
       <c r="C744" t="s">
-        <v>2141</v>
+        <v>2133</v>
       </c>
       <c r="E744">
         <v>1962</v>
@@ -20563,13 +20549,13 @@
     </row>
     <row r="745" spans="1:6">
       <c r="A745" t="s">
-        <v>2070</v>
+        <v>2062</v>
       </c>
       <c r="B745" t="s">
         <v>621</v>
       </c>
       <c r="C745" t="s">
-        <v>2142</v>
+        <v>2134</v>
       </c>
       <c r="E745">
         <v>1969</v>
@@ -20580,13 +20566,13 @@
     </row>
     <row r="746" spans="1:6">
       <c r="A746" t="s">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B746" t="s">
-        <v>2143</v>
+        <v>2135</v>
       </c>
       <c r="C746" t="s">
-        <v>2144</v>
+        <v>2136</v>
       </c>
       <c r="E746">
         <v>2008</v>
@@ -20597,13 +20583,13 @@
     </row>
     <row r="747" spans="1:6">
       <c r="A747" t="s">
-        <v>2145</v>
+        <v>2137</v>
       </c>
       <c r="B747" t="s">
-        <v>2146</v>
+        <v>2138</v>
       </c>
       <c r="C747" t="s">
-        <v>2147</v>
+        <v>2139</v>
       </c>
       <c r="E747">
         <v>1956</v>
@@ -20614,13 +20600,13 @@
     </row>
     <row r="748" spans="1:6">
       <c r="A748" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="B748" t="s">
-        <v>2148</v>
+        <v>2140</v>
       </c>
       <c r="C748" t="s">
-        <v>2149</v>
+        <v>2141</v>
       </c>
       <c r="E748">
         <v>1998</v>
@@ -20631,13 +20617,13 @@
     </row>
     <row r="749" spans="1:6">
       <c r="A749" t="s">
-        <v>2069</v>
+        <v>2061</v>
       </c>
       <c r="B749" t="s">
-        <v>2150</v>
+        <v>2142</v>
       </c>
       <c r="C749" t="s">
-        <v>2151</v>
+        <v>2143</v>
       </c>
       <c r="E749">
         <v>1960</v>
@@ -20648,13 +20634,13 @@
     </row>
     <row r="750" spans="1:6">
       <c r="A750" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B750" t="s">
-        <v>2152</v>
+        <v>2144</v>
       </c>
       <c r="C750" t="s">
-        <v>2153</v>
+        <v>2145</v>
       </c>
       <c r="E750">
         <v>1983</v>
@@ -20665,13 +20651,13 @@
     </row>
     <row r="751" spans="1:6">
       <c r="A751" t="s">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="B751" t="s">
-        <v>2154</v>
+        <v>2146</v>
       </c>
       <c r="C751" t="s">
-        <v>2155</v>
+        <v>2147</v>
       </c>
       <c r="E751">
         <v>1996</v>
@@ -20682,13 +20668,13 @@
     </row>
     <row r="752" spans="1:6">
       <c r="A752" t="s">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="B752" t="s">
-        <v>2156</v>
+        <v>2148</v>
       </c>
       <c r="C752" t="s">
-        <v>2157</v>
+        <v>2149</v>
       </c>
       <c r="E752">
         <v>2012</v>
@@ -20699,13 +20685,13 @@
     </row>
     <row r="753" spans="1:6">
       <c r="A753" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B753" t="s">
-        <v>2158</v>
+        <v>2150</v>
       </c>
       <c r="C753" t="s">
-        <v>2158</v>
+        <v>2150</v>
       </c>
       <c r="E753">
         <v>2011</v>
@@ -20716,13 +20702,13 @@
     </row>
     <row r="754" spans="1:6">
       <c r="A754" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B754" t="s">
-        <v>2159</v>
+        <v>2151</v>
       </c>
       <c r="C754" t="s">
-        <v>2160</v>
+        <v>2152</v>
       </c>
       <c r="E754">
         <v>2008</v>
@@ -20733,13 +20719,13 @@
     </row>
     <row r="755" spans="1:6">
       <c r="A755" t="s">
-        <v>2060</v>
+        <v>2052</v>
       </c>
       <c r="B755" t="s">
-        <v>2161</v>
+        <v>2153</v>
       </c>
       <c r="C755" t="s">
-        <v>2162</v>
+        <v>2154</v>
       </c>
       <c r="E755">
         <v>1989</v>
@@ -20750,13 +20736,13 @@
     </row>
     <row r="756" spans="1:6">
       <c r="A756" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B756" t="s">
-        <v>2163</v>
+        <v>2155</v>
       </c>
       <c r="C756" t="s">
-        <v>2164</v>
+        <v>2156</v>
       </c>
       <c r="E756">
         <v>2014</v>
@@ -20767,13 +20753,13 @@
     </row>
     <row r="757" spans="1:6">
       <c r="A757" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="B757" t="s">
-        <v>2165</v>
+        <v>2157</v>
       </c>
       <c r="C757" t="s">
-        <v>2166</v>
+        <v>2158</v>
       </c>
       <c r="E757">
         <v>1979</v>
@@ -20784,13 +20770,13 @@
     </row>
     <row r="758" spans="1:6">
       <c r="A758" t="s">
-        <v>2168</v>
+        <v>2160</v>
       </c>
       <c r="B758" t="s">
-        <v>2167</v>
+        <v>2159</v>
       </c>
       <c r="C758" t="s">
-        <v>2167</v>
+        <v>2159</v>
       </c>
       <c r="E758">
         <v>1978</v>
@@ -20801,13 +20787,13 @@
     </row>
     <row r="759" spans="1:6">
       <c r="A759" t="s">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B759" t="s">
-        <v>2169</v>
+        <v>2161</v>
       </c>
       <c r="C759" t="s">
-        <v>2170</v>
+        <v>2162</v>
       </c>
       <c r="E759">
         <v>1973</v>
@@ -20818,13 +20804,13 @@
     </row>
     <row r="760" spans="1:6">
       <c r="A760" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B760" t="s">
         <v>1326</v>
       </c>
       <c r="C760" t="s">
-        <v>2171</v>
+        <v>2163</v>
       </c>
       <c r="E760">
         <v>2006</v>
@@ -20835,13 +20821,13 @@
     </row>
     <row r="761" spans="1:6">
       <c r="A761" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B761" t="s">
-        <v>2172</v>
+        <v>2164</v>
       </c>
       <c r="C761" t="s">
-        <v>2173</v>
+        <v>2165</v>
       </c>
       <c r="E761">
         <v>1987</v>
@@ -20852,13 +20838,13 @@
     </row>
     <row r="762" spans="1:6">
       <c r="A762" t="s">
-        <v>2061</v>
+        <v>2053</v>
       </c>
       <c r="B762" t="s">
-        <v>2174</v>
+        <v>2166</v>
       </c>
       <c r="C762" t="s">
-        <v>2175</v>
+        <v>2167</v>
       </c>
       <c r="E762">
         <v>1952</v>
@@ -20869,13 +20855,13 @@
     </row>
     <row r="763" spans="1:6">
       <c r="A763" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B763" t="s">
-        <v>2176</v>
+        <v>2168</v>
       </c>
       <c r="C763" t="s">
-        <v>2177</v>
+        <v>2169</v>
       </c>
       <c r="E763">
         <v>2000</v>
@@ -20886,13 +20872,13 @@
     </row>
     <row r="764" spans="1:6">
       <c r="A764" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="B764" t="s">
-        <v>2178</v>
+        <v>2170</v>
       </c>
       <c r="C764" t="s">
-        <v>2179</v>
+        <v>2171</v>
       </c>
       <c r="E764">
         <v>2018</v>
@@ -20903,13 +20889,13 @@
     </row>
     <row r="765" spans="1:6">
       <c r="A765" t="s">
-        <v>2051</v>
+        <v>2044</v>
       </c>
       <c r="B765" t="s">
-        <v>2180</v>
+        <v>2172</v>
       </c>
       <c r="C765" t="s">
-        <v>2180</v>
+        <v>2172</v>
       </c>
       <c r="E765">
         <v>1977</v>
@@ -20920,13 +20906,13 @@
     </row>
     <row r="766" spans="1:6">
       <c r="A766" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B766" t="s">
-        <v>2181</v>
+        <v>2173</v>
       </c>
       <c r="C766" t="s">
-        <v>2182</v>
+        <v>2174</v>
       </c>
       <c r="E766">
         <v>1994</v>
@@ -20937,13 +20923,13 @@
     </row>
     <row r="767" spans="1:6">
       <c r="A767" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B767" t="s">
-        <v>2183</v>
+        <v>2175</v>
       </c>
       <c r="C767" t="s">
-        <v>2183</v>
+        <v>2175</v>
       </c>
       <c r="E767">
         <v>1972</v>
@@ -20954,13 +20940,13 @@
     </row>
     <row r="768" spans="1:6">
       <c r="A768" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B768" t="s">
         <v>1212</v>
       </c>
       <c r="C768" t="s">
-        <v>2184</v>
+        <v>2176</v>
       </c>
       <c r="E768">
         <v>2002</v>
@@ -20971,13 +20957,13 @@
     </row>
     <row r="769" spans="1:6">
       <c r="A769" t="s">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="B769" t="s">
-        <v>2185</v>
+        <v>2177</v>
       </c>
       <c r="C769" t="s">
-        <v>2186</v>
+        <v>2178</v>
       </c>
       <c r="E769">
         <v>1974</v>
@@ -20988,13 +20974,13 @@
     </row>
     <row r="770" spans="1:6">
       <c r="A770" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B770" t="s">
-        <v>2188</v>
+        <v>2180</v>
       </c>
       <c r="C770" t="s">
-        <v>2187</v>
+        <v>2179</v>
       </c>
       <c r="E770">
         <v>1978</v>
@@ -21005,13 +20991,13 @@
     </row>
     <row r="771" spans="1:6">
       <c r="A771" t="s">
-        <v>2087</v>
+        <v>2079</v>
       </c>
       <c r="B771" t="s">
-        <v>2189</v>
+        <v>2181</v>
       </c>
       <c r="C771" t="s">
-        <v>2190</v>
+        <v>2182</v>
       </c>
       <c r="E771">
         <v>2004</v>
@@ -21022,13 +21008,13 @@
     </row>
     <row r="772" spans="1:6">
       <c r="A772" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="B772" t="s">
-        <v>2191</v>
+        <v>2183</v>
       </c>
       <c r="C772" t="s">
-        <v>2192</v>
+        <v>2184</v>
       </c>
       <c r="E772">
         <v>1979</v>
@@ -21039,13 +21025,13 @@
     </row>
     <row r="773" spans="1:6">
       <c r="A773" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B773" t="s">
-        <v>2193</v>
+        <v>2185</v>
       </c>
       <c r="C773" t="s">
-        <v>2194</v>
+        <v>2186</v>
       </c>
       <c r="E773">
         <v>1984</v>
@@ -21056,13 +21042,13 @@
     </row>
     <row r="774" spans="1:6">
       <c r="A774" t="s">
-        <v>2076</v>
+        <v>2068</v>
       </c>
       <c r="B774" t="s">
-        <v>2195</v>
+        <v>2187</v>
       </c>
       <c r="C774" t="s">
-        <v>2196</v>
+        <v>2188</v>
       </c>
       <c r="E774">
         <v>1974</v>
@@ -21073,13 +21059,13 @@
     </row>
     <row r="775" spans="1:6">
       <c r="A775" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="B775" t="s">
-        <v>2197</v>
+        <v>2189</v>
       </c>
       <c r="C775" t="s">
-        <v>2198</v>
+        <v>2190</v>
       </c>
       <c r="E775">
         <v>2011</v>
@@ -21090,13 +21076,13 @@
     </row>
     <row r="776" spans="1:6">
       <c r="A776" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B776" t="s">
-        <v>2199</v>
+        <v>2191</v>
       </c>
       <c r="C776" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="E776">
         <v>1995</v>
@@ -21107,13 +21093,13 @@
     </row>
     <row r="777" spans="1:6">
       <c r="A777" t="s">
-        <v>2201</v>
+        <v>2193</v>
       </c>
       <c r="B777" t="s">
-        <v>2200</v>
+        <v>2192</v>
       </c>
       <c r="C777" t="s">
-        <v>2202</v>
+        <v>2194</v>
       </c>
       <c r="E777">
         <v>2006</v>
@@ -21124,13 +21110,13 @@
     </row>
     <row r="778" spans="1:6">
       <c r="A778" t="s">
-        <v>2203</v>
+        <v>2195</v>
       </c>
       <c r="B778" s="8" t="s">
-        <v>2204</v>
+        <v>2196</v>
       </c>
       <c r="C778" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
       <c r="E778">
         <v>1958</v>
@@ -21141,13 +21127,13 @@
     </row>
     <row r="779" spans="1:6">
       <c r="A779" t="s">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="B779" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
       <c r="C779" t="s">
-        <v>2206</v>
+        <v>2198</v>
       </c>
       <c r="E779">
         <v>1993</v>
@@ -21158,13 +21144,13 @@
     </row>
     <row r="780" spans="1:6">
       <c r="A780" s="1" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B780" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
       <c r="C780" t="s">
-        <v>2209</v>
+        <v>2201</v>
       </c>
       <c r="E780">
         <v>2008</v>
@@ -21175,13 +21161,13 @@
     </row>
     <row r="781" spans="1:6">
       <c r="A781" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B781" t="s">
-        <v>2210</v>
+        <v>2202</v>
       </c>
       <c r="C781" t="s">
-        <v>2211</v>
+        <v>2203</v>
       </c>
       <c r="E781">
         <v>2005</v>
@@ -21192,13 +21178,13 @@
     </row>
     <row r="782" spans="1:6">
       <c r="A782" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B782" t="s">
-        <v>2213</v>
+        <v>2205</v>
       </c>
       <c r="C782" t="s">
-        <v>2212</v>
+        <v>2204</v>
       </c>
       <c r="E782">
         <v>1995</v>
@@ -21209,13 +21195,13 @@
     </row>
     <row r="783" spans="1:6">
       <c r="A783" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="B783" t="s">
-        <v>2214</v>
+        <v>2206</v>
       </c>
       <c r="C783" t="s">
-        <v>2215</v>
+        <v>2207</v>
       </c>
       <c r="E783">
         <v>1978</v>
@@ -21226,13 +21212,13 @@
     </row>
     <row r="784" spans="1:6">
       <c r="A784" t="s">
-        <v>2066</v>
+        <v>2058</v>
       </c>
       <c r="B784" t="s">
-        <v>2217</v>
+        <v>2209</v>
       </c>
       <c r="C784" t="s">
-        <v>2216</v>
+        <v>2208</v>
       </c>
       <c r="E784">
         <v>1974</v>
@@ -21243,13 +21229,13 @@
     </row>
     <row r="785" spans="1:6">
       <c r="A785" t="s">
-        <v>2065</v>
+        <v>2057</v>
       </c>
       <c r="B785" t="s">
-        <v>2218</v>
+        <v>2210</v>
       </c>
       <c r="C785" t="s">
-        <v>2218</v>
+        <v>2210</v>
       </c>
       <c r="E785">
         <v>1963</v>
@@ -21260,13 +21246,13 @@
     </row>
     <row r="786" spans="1:6">
       <c r="A786" t="s">
-        <v>2088</v>
+        <v>2080</v>
       </c>
       <c r="B786" t="s">
-        <v>2219</v>
+        <v>2211</v>
       </c>
       <c r="C786" t="s">
-        <v>2220</v>
+        <v>2212</v>
       </c>
       <c r="E786">
         <v>2005</v>
@@ -21277,13 +21263,13 @@
     </row>
     <row r="787" spans="1:6">
       <c r="A787" t="s">
-        <v>2221</v>
+        <v>2213</v>
       </c>
       <c r="B787" t="s">
-        <v>2222</v>
+        <v>2214</v>
       </c>
       <c r="C787" t="s">
-        <v>2223</v>
+        <v>2215</v>
       </c>
       <c r="E787">
         <v>1978</v>
@@ -21294,13 +21280,13 @@
     </row>
     <row r="788" spans="1:6">
       <c r="A788" t="s">
-        <v>2224</v>
+        <v>2216</v>
       </c>
       <c r="B788" t="s">
-        <v>2225</v>
+        <v>2217</v>
       </c>
       <c r="C788" t="s">
-        <v>2225</v>
+        <v>2217</v>
       </c>
       <c r="E788">
         <v>1977</v>
@@ -21311,13 +21297,13 @@
     </row>
     <row r="789" spans="1:6">
       <c r="A789" t="s">
-        <v>2226</v>
+        <v>2218</v>
       </c>
       <c r="B789" t="s">
-        <v>2227</v>
+        <v>2219</v>
       </c>
       <c r="C789" t="s">
-        <v>2228</v>
+        <v>2220</v>
       </c>
       <c r="E789">
         <v>1986</v>
@@ -21328,13 +21314,13 @@
     </row>
     <row r="790" spans="1:6">
       <c r="A790" t="s">
-        <v>2229</v>
+        <v>2221</v>
       </c>
       <c r="B790" t="s">
-        <v>2230</v>
+        <v>2222</v>
       </c>
       <c r="C790" t="s">
-        <v>2231</v>
+        <v>2223</v>
       </c>
       <c r="E790">
         <v>1965</v>
@@ -21345,13 +21331,13 @@
     </row>
     <row r="791" spans="1:6">
       <c r="A791" t="s">
-        <v>2232</v>
+        <v>2224</v>
       </c>
       <c r="B791" t="s">
-        <v>2233</v>
+        <v>2225</v>
       </c>
       <c r="C791" t="s">
-        <v>2234</v>
+        <v>2226</v>
       </c>
       <c r="E791">
         <v>2003</v>
@@ -21365,10 +21351,10 @@
         <v>1991</v>
       </c>
       <c r="B792" t="s">
-        <v>2235</v>
+        <v>2227</v>
       </c>
       <c r="C792" t="s">
-        <v>2236</v>
+        <v>2228</v>
       </c>
       <c r="E792">
         <v>1997</v>
@@ -21379,13 +21365,13 @@
     </row>
     <row r="793" spans="1:6">
       <c r="A793" t="s">
-        <v>2062</v>
+        <v>2054</v>
       </c>
       <c r="B793" t="s">
-        <v>2237</v>
+        <v>2229</v>
       </c>
       <c r="C793" t="s">
-        <v>2238</v>
+        <v>2230</v>
       </c>
       <c r="E793">
         <v>1959</v>
@@ -21396,13 +21382,13 @@
     </row>
     <row r="794" spans="1:6">
       <c r="A794" t="s">
-        <v>2239</v>
+        <v>2231</v>
       </c>
       <c r="B794" t="s">
-        <v>2240</v>
+        <v>2232</v>
       </c>
       <c r="C794" t="s">
-        <v>2241</v>
+        <v>2233</v>
       </c>
       <c r="E794">
         <v>1992</v>
@@ -21413,13 +21399,13 @@
     </row>
     <row r="795" spans="1:6">
       <c r="A795" t="s">
-        <v>2073</v>
+        <v>2065</v>
       </c>
       <c r="B795" t="s">
-        <v>2242</v>
+        <v>2234</v>
       </c>
       <c r="C795" t="s">
-        <v>2243</v>
+        <v>2235</v>
       </c>
       <c r="E795">
         <v>1989</v>
@@ -21430,13 +21416,13 @@
     </row>
     <row r="796" spans="1:6">
       <c r="A796" t="s">
-        <v>2067</v>
+        <v>2059</v>
       </c>
       <c r="B796" t="s">
-        <v>2244</v>
+        <v>2236</v>
       </c>
       <c r="C796" t="s">
-        <v>2067</v>
+        <v>2059</v>
       </c>
       <c r="E796">
         <v>1959</v>
@@ -21447,13 +21433,13 @@
     </row>
     <row r="797" spans="1:6">
       <c r="A797" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="B797" t="s">
-        <v>2245</v>
+        <v>2237</v>
       </c>
       <c r="C797" t="s">
-        <v>2246</v>
+        <v>2238</v>
       </c>
       <c r="E797">
         <v>1991</v>
@@ -21464,13 +21450,13 @@
     </row>
     <row r="798" spans="1:6">
       <c r="A798" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B798" t="s">
-        <v>2247</v>
+        <v>2239</v>
       </c>
       <c r="C798" t="s">
-        <v>2248</v>
+        <v>2240</v>
       </c>
       <c r="E798">
         <v>1991</v>
@@ -21481,13 +21467,13 @@
     </row>
     <row r="799" spans="1:6">
       <c r="A799" t="s">
-        <v>2085</v>
+        <v>2077</v>
       </c>
       <c r="B799" t="s">
-        <v>2249</v>
+        <v>2241</v>
       </c>
       <c r="C799" t="s">
-        <v>2250</v>
+        <v>2242</v>
       </c>
       <c r="E799">
         <v>1999</v>
@@ -21498,13 +21484,13 @@
     </row>
     <row r="800" spans="1:6">
       <c r="A800" t="s">
-        <v>2074</v>
+        <v>2066</v>
       </c>
       <c r="B800" t="s">
-        <v>2251</v>
+        <v>2243</v>
       </c>
       <c r="C800" t="s">
-        <v>2252</v>
+        <v>2244</v>
       </c>
       <c r="E800">
         <v>1968</v>
@@ -21515,13 +21501,13 @@
     </row>
     <row r="801" spans="1:6">
       <c r="A801" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
       <c r="B801" t="s">
-        <v>2253</v>
+        <v>2245</v>
       </c>
       <c r="C801" t="s">
-        <v>2254</v>
+        <v>2246</v>
       </c>
       <c r="E801">
         <v>1994</v>
@@ -21532,13 +21518,13 @@
     </row>
     <row r="802" spans="1:6">
       <c r="A802" t="s">
-        <v>2255</v>
+        <v>2247</v>
       </c>
       <c r="B802" t="s">
-        <v>2256</v>
+        <v>2248</v>
       </c>
       <c r="C802" t="s">
-        <v>2257</v>
+        <v>2249</v>
       </c>
       <c r="E802">
         <v>1996</v>
@@ -21555,7 +21541,7 @@
         <v>1000</v>
       </c>
       <c r="C803" t="s">
-        <v>2258</v>
+        <v>2250</v>
       </c>
       <c r="E803">
         <v>1993</v>
@@ -21566,13 +21552,13 @@
     </row>
     <row r="804" spans="1:6">
       <c r="A804" t="s">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="B804" t="s">
-        <v>2259</v>
+        <v>2251</v>
       </c>
       <c r="C804" t="s">
-        <v>2260</v>
+        <v>2252</v>
       </c>
       <c r="E804">
         <v>1998</v>
@@ -21583,13 +21569,13 @@
     </row>
     <row r="805" spans="1:6">
       <c r="A805" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B805" t="s">
-        <v>2261</v>
+        <v>2253</v>
       </c>
       <c r="C805" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
       <c r="E805">
         <v>1981</v>
@@ -21617,13 +21603,13 @@
     </row>
     <row r="807" spans="1:6">
       <c r="A807" t="s">
-        <v>2263</v>
+        <v>2255</v>
       </c>
       <c r="B807" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
       <c r="C807" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
       <c r="E807">
         <v>1992</v>
@@ -21634,13 +21620,13 @@
     </row>
     <row r="808" spans="1:6">
       <c r="A808" t="s">
-        <v>2068</v>
+        <v>2060</v>
       </c>
       <c r="B808" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="C808" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="E808">
         <v>1959</v>
@@ -21651,13 +21637,13 @@
     </row>
     <row r="809" spans="1:6">
       <c r="A809" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="B809" t="s">
-        <v>2267</v>
+        <v>2259</v>
       </c>
       <c r="C809" t="s">
-        <v>2268</v>
+        <v>2260</v>
       </c>
       <c r="E809">
         <v>2010</v>
@@ -21668,13 +21654,13 @@
     </row>
     <row r="810" spans="1:6">
       <c r="A810" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
       <c r="B810" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
       <c r="C810" t="s">
-        <v>2270</v>
+        <v>2262</v>
       </c>
       <c r="E810">
         <v>1964</v>
@@ -21685,13 +21671,13 @@
     </row>
     <row r="811" spans="1:6">
       <c r="A811" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="B811" t="s">
-        <v>2271</v>
+        <v>2263</v>
       </c>
       <c r="C811" t="s">
-        <v>2272</v>
+        <v>2264</v>
       </c>
       <c r="E811">
         <v>1980</v>
@@ -21702,13 +21688,13 @@
     </row>
     <row r="812" spans="1:6">
       <c r="A812" t="s">
-        <v>2273</v>
+        <v>2265</v>
       </c>
       <c r="B812" t="s">
-        <v>2274</v>
+        <v>2266</v>
       </c>
       <c r="C812" t="s">
-        <v>2275</v>
+        <v>2267</v>
       </c>
       <c r="E812">
         <v>1990</v>
@@ -21719,13 +21705,13 @@
     </row>
     <row r="813" spans="1:6">
       <c r="A813" t="s">
-        <v>2058</v>
+        <v>2050</v>
       </c>
       <c r="B813" t="s">
-        <v>2276</v>
+        <v>2268</v>
       </c>
       <c r="C813" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
       <c r="E813">
         <v>1997</v>
@@ -21736,13 +21722,13 @@
     </row>
     <row r="814" spans="1:6">
       <c r="A814" t="s">
-        <v>2278</v>
+        <v>2270</v>
       </c>
       <c r="B814" t="s">
-        <v>2280</v>
+        <v>2272</v>
       </c>
       <c r="C814" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
       <c r="E814">
         <v>2007</v>
@@ -21753,13 +21739,13 @@
     </row>
     <row r="815" spans="1:6">
       <c r="A815" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="B815" t="s">
-        <v>2281</v>
+        <v>2273</v>
       </c>
       <c r="C815" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
       <c r="E815">
         <v>2014</v>
@@ -21770,13 +21756,13 @@
     </row>
     <row r="816" spans="1:6">
       <c r="A816" t="s">
-        <v>2054</v>
+        <v>2047</v>
       </c>
       <c r="B816" t="s">
-        <v>2283</v>
+        <v>2275</v>
       </c>
       <c r="C816" t="s">
-        <v>2283</v>
+        <v>2275</v>
       </c>
       <c r="E816">
         <v>1988</v>
@@ -21787,13 +21773,13 @@
     </row>
     <row r="817" spans="1:6">
       <c r="A817" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
       <c r="B817" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="C817" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="E817">
         <v>1962</v>
@@ -21804,13 +21790,13 @@
     </row>
     <row r="818" spans="1:6">
       <c r="A818" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="B818" t="s">
-        <v>2287</v>
+        <v>2279</v>
       </c>
       <c r="C818" t="s">
-        <v>2288</v>
+        <v>2280</v>
       </c>
       <c r="E818">
         <v>1972</v>
@@ -21821,13 +21807,13 @@
     </row>
     <row r="819" spans="1:6">
       <c r="A819" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B819" t="s">
-        <v>2289</v>
+        <v>2281</v>
       </c>
       <c r="C819" t="s">
-        <v>2290</v>
+        <v>2282</v>
       </c>
       <c r="E819">
         <v>1988</v>
@@ -21838,19 +21824,195 @@
     </row>
     <row r="820" spans="1:6">
       <c r="A820" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B820" t="s">
-        <v>2291</v>
+        <v>2283</v>
       </c>
       <c r="C820" t="s">
-        <v>2292</v>
+        <v>2284</v>
       </c>
       <c r="E820">
         <v>1988</v>
       </c>
       <c r="F820" t="s">
         <v>969</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6">
+      <c r="A821" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B821" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C821" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E821">
+        <v>1983</v>
+      </c>
+      <c r="F821" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6">
+      <c r="A822" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C822" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E822">
+        <v>1986</v>
+      </c>
+      <c r="F822" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6">
+      <c r="A823" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B823" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C823" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E823">
+        <v>1973</v>
+      </c>
+      <c r="F823" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6">
+      <c r="A824" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B824" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C824" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E824">
+        <v>1968</v>
+      </c>
+      <c r="F824" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6">
+      <c r="A825" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B825" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C825" s="10" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E825">
+        <v>2013</v>
+      </c>
+      <c r="F825" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6">
+      <c r="A826" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B826" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C826" t="s">
+        <v>622</v>
+      </c>
+      <c r="E826">
+        <v>1966</v>
+      </c>
+      <c r="F826" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6">
+      <c r="A827" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B827" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C827" s="10" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E827">
+        <v>1967</v>
+      </c>
+      <c r="F827" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6">
+      <c r="A828" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B828" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C828" s="10"/>
+      <c r="E828">
+        <v>1982</v>
+      </c>
+      <c r="F828" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6">
+      <c r="A829" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B829" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E829">
+        <v>1995</v>
+      </c>
+      <c r="F829" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6">
+      <c r="A830" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B830" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E830">
+        <v>1975</v>
+      </c>
+      <c r="F830" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6">
+      <c r="A831" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B831" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E831">
+        <v>1969</v>
+      </c>
+      <c r="F831" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -21866,6 +22028,8 @@
     <hyperlink ref="C348" r:id="rId6" display="https://music.youtube.com/browse/MPREb_6jEL3ZwgoLw" xr:uid="{4D6F0B90-DD9A-BC46-923C-0953DC55F9CA}"/>
     <hyperlink ref="C506" r:id="rId7" display="https://music.youtube.com/browse/MPREb_K8qWMWVqXGi" xr:uid="{53EB5BB4-301A-3F4F-8AAE-35CC2433F3E1}"/>
     <hyperlink ref="A322" r:id="rId8" display="https://radioparadise.com/music/song/37357/Kasabian-Ovary_Stripe" xr:uid="{E1777167-732C-E544-B0F8-E3373805EB0F}"/>
+    <hyperlink ref="A827" r:id="rId9" display="https://music.youtube.com/channel/UCJ5KnH3ypqm67hiPLOcGvRQ" xr:uid="{102824E8-28C1-C94C-9B86-FD22370D68A1}"/>
+    <hyperlink ref="C827" r:id="rId10" display="https://music.youtube.com/browse/MPREb_jyNU2UBdySi" xr:uid="{57A8CDE5-8C72-8A42-B618-1E4459F8109C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EBEEB7-525D-3F4F-A121-E93CED856546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17C0BF4-E0DC-464A-9F30-C488C8A4C12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Id Media Type" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!$C$2:$C$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!$C$1:$C$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$801</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4074" uniqueCount="2959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4083" uniqueCount="2940">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -7212,9 +7212,6 @@
     <t>Shawn Colvin</t>
   </si>
   <si>
-    <t>Alison Krauss and Union Station</t>
-  </si>
-  <si>
     <t>John Hammond</t>
   </si>
   <si>
@@ -7239,9 +7236,6 @@
     <t>Cousteau</t>
   </si>
   <si>
-    <t>Ani DiFranco</t>
-  </si>
-  <si>
     <t>Nanci Griffith</t>
   </si>
   <si>
@@ -7260,9 +7254,6 @@
     <t>Nick Lowe</t>
   </si>
   <si>
-    <t>Amy Correia</t>
-  </si>
-  <si>
     <t>Paul McCartney</t>
   </si>
   <si>
@@ -7302,9 +7293,6 @@
     <t>Luka Bloom</t>
   </si>
   <si>
-    <t>Action Figure Party</t>
-  </si>
-  <si>
     <t>Old 97's</t>
   </si>
   <si>
@@ -7341,18 +7329,6 @@
     <t>Continental Drifters</t>
   </si>
   <si>
-    <t>Bjork</t>
-  </si>
-  <si>
-    <t>Alana Davis</t>
-  </si>
-  <si>
-    <t>Afro Celt Sound System</t>
-  </si>
-  <si>
-    <t>Blind Boys of Alabama</t>
-  </si>
-  <si>
     <t>Cesaria Evora</t>
   </si>
   <si>
@@ -7362,9 +7338,6 @@
     <t>Joe Henry</t>
   </si>
   <si>
-    <t>Anders Osborne</t>
-  </si>
-  <si>
     <t>The Actual Tigers</t>
   </si>
   <si>
@@ -7392,9 +7365,6 @@
     <t>Patty Griffin</t>
   </si>
   <si>
-    <t>Beth Orton</t>
-  </si>
-  <si>
     <t>Neil Finn</t>
   </si>
   <si>
@@ -7422,9 +7392,6 @@
     <t>Peter Wolf</t>
   </si>
   <si>
-    <t>Angelique Kidjo</t>
-  </si>
-  <si>
     <t>Gomez</t>
   </si>
   <si>
@@ -7554,9 +7521,6 @@
     <t>Josh Ritter</t>
   </si>
   <si>
-    <t>Annie Lennox</t>
-  </si>
-  <si>
     <t>Ben Harper</t>
   </si>
   <si>
@@ -7575,15 +7539,9 @@
     <t>Chris Smither</t>
   </si>
   <si>
-    <t>Alexi Murdoch</t>
-  </si>
-  <si>
     <t>Daniel Lanois</t>
   </si>
   <si>
-    <t>Allman Brothers Band</t>
-  </si>
-  <si>
     <t>Stephen Clair</t>
   </si>
   <si>
@@ -7638,9 +7596,6 @@
     <t>The Kennedys</t>
   </si>
   <si>
-    <t>Amos Lee</t>
-  </si>
-  <si>
     <t>Mary Gauthier</t>
   </si>
   <si>
@@ -7695,9 +7650,6 @@
     <t>The New Pornographers</t>
   </si>
   <si>
-    <t>Bettye LaVette</t>
-  </si>
-  <si>
     <t>Mark Knopfler &amp; Emmylou Harris</t>
   </si>
   <si>
@@ -7872,9 +7824,6 @@
     <t>M. Ward</t>
   </si>
   <si>
-    <t>Brendan Benson</t>
-  </si>
-  <si>
     <t>Grizzly Bear</t>
   </si>
   <si>
@@ -7899,24 +7848,15 @@
     <t>Dan Auerbach</t>
   </si>
   <si>
-    <t>Ben Gibbard &amp; Jay Farrar</t>
-  </si>
-  <si>
     <t>Camera Obscura</t>
   </si>
   <si>
-    <t>Black Crowes</t>
-  </si>
-  <si>
     <t>Justin Townes Earle</t>
   </si>
   <si>
     <t>Bell X1</t>
   </si>
   <si>
-    <t>Animal Collective</t>
-  </si>
-  <si>
     <t>Deer Tick</t>
   </si>
   <si>
@@ -7944,9 +7884,6 @@
     <t>Jakob Dylan</t>
   </si>
   <si>
-    <t>Black Dub</t>
-  </si>
-  <si>
     <t>The Secret Sisters</t>
   </si>
   <si>
@@ -7968,9 +7905,6 @@
     <t>The Head &amp; The Heart</t>
   </si>
   <si>
-    <t>Blitzen Trapper</t>
-  </si>
-  <si>
     <t>David Wax Museum</t>
   </si>
   <si>
@@ -8034,9 +7968,6 @@
     <t>Drive‑By Truckers</t>
   </si>
   <si>
-    <t>Alabama Shakes</t>
-  </si>
-  <si>
     <t>Jack White</t>
   </si>
   <si>
@@ -8046,18 +7977,12 @@
     <t>Father John Misty</t>
   </si>
   <si>
-    <t>Beach House</t>
-  </si>
-  <si>
     <t>Donald Fagen</t>
   </si>
   <si>
     <t>Sharon Van Etten</t>
   </si>
   <si>
-    <t>Ben Howard</t>
-  </si>
-  <si>
     <t>Michael Kiwanuka</t>
   </si>
   <si>
@@ -8094,9 +8019,6 @@
     <t>The Walkmen</t>
   </si>
   <si>
-    <t>Allen Stone</t>
-  </si>
-  <si>
     <t>Frank Ocean</t>
   </si>
   <si>
@@ -8112,9 +8034,6 @@
     <t>Glen Hansard</t>
   </si>
   <si>
-    <t>Ben Sollee</t>
-  </si>
-  <si>
     <t>Gotye</t>
   </si>
   <si>
@@ -8124,9 +8043,6 @@
     <t>Of Monsters and Men</t>
   </si>
   <si>
-    <t>Benjamin Gibbard</t>
-  </si>
-  <si>
     <t>The Tallest Man on Earth</t>
   </si>
   <si>
@@ -8154,9 +8070,6 @@
     <t>Dr. Dog</t>
   </si>
   <si>
-    <t>Amy Cook</t>
-  </si>
-  <si>
     <t>Phosphorescent</t>
   </si>
   <si>
@@ -8175,12 +8088,6 @@
     <t>John Grant</t>
   </si>
   <si>
-    <t>Arctic Monkeys</t>
-  </si>
-  <si>
-    <t>Aloe Blacc</t>
-  </si>
-  <si>
     <t>Chvrches</t>
   </si>
   <si>
@@ -8214,9 +8121,6 @@
     <t>Yeah Yeah Yeahs</t>
   </si>
   <si>
-    <t>Billie Joe &amp; Norah</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -8277,9 +8181,6 @@
     <t>Sylvan Esso</t>
   </si>
   <si>
-    <t>Benjamin Booker</t>
-  </si>
-  <si>
     <t>Sam Smith</t>
   </si>
   <si>
@@ -8298,9 +8199,6 @@
     <t>The New Basement Tapes</t>
   </si>
   <si>
-    <t>Ásgeir</t>
-  </si>
-  <si>
     <t>Temples</t>
   </si>
   <si>
@@ -8322,9 +8220,6 @@
     <t>Parquet Courts</t>
   </si>
   <si>
-    <t>Ages &amp; Ages</t>
-  </si>
-  <si>
     <t>Mac DeMarco</t>
   </si>
   <si>
@@ -8415,15 +8310,9 @@
     <t>Tuxedo</t>
   </si>
   <si>
-    <t>BØRNS</t>
-  </si>
-  <si>
     <t>The Arcs</t>
   </si>
   <si>
-    <t>Alessia Cara</t>
-  </si>
-  <si>
     <t>Sam Outlaw</t>
   </si>
   <si>
@@ -8481,18 +8370,12 @@
     <t>Warpaint</t>
   </si>
   <si>
-    <t>Angel Olsen</t>
-  </si>
-  <si>
     <t>Margaret Glaspy</t>
   </si>
   <si>
     <t>Seratones</t>
   </si>
   <si>
-    <t>Bob Weir</t>
-  </si>
-  <si>
     <t>Brian Fallon</t>
   </si>
   <si>
@@ -8517,9 +8400,6 @@
     <t>Dinosaur Jr.</t>
   </si>
   <si>
-    <t>A Tribe Called Quest</t>
-  </si>
-  <si>
     <t>Pixies</t>
   </si>
   <si>
@@ -8544,9 +8424,6 @@
     <t>Maggie Rogers</t>
   </si>
   <si>
-    <t>Blood Orange</t>
-  </si>
-  <si>
     <t>Hiss Golden Messenger</t>
   </si>
   <si>
@@ -8559,9 +8436,6 @@
     <t>Declan McKenna</t>
   </si>
   <si>
-    <t>Andrew Bird</t>
-  </si>
-  <si>
     <t>Solange</t>
   </si>
   <si>
@@ -8571,9 +8445,6 @@
     <t>Gregg Allman</t>
   </si>
   <si>
-    <t>Alice Merton</t>
-  </si>
-  <si>
     <t>Lukas Nelson &amp; Promise of the Real</t>
   </si>
   <si>
@@ -8658,9 +8529,6 @@
     <t>Snail Mail</t>
   </si>
   <si>
-    <t>boygenius</t>
-  </si>
-  <si>
     <t>Jealous of the Birds</t>
   </si>
   <si>
@@ -8685,18 +8553,12 @@
     <t>Amanda Shires</t>
   </si>
   <si>
-    <t>Amy Helm</t>
-  </si>
-  <si>
     <t>Erika Wennerstrom</t>
   </si>
   <si>
     <t>Emily King</t>
   </si>
   <si>
-    <t>Big Red Machine</t>
-  </si>
-  <si>
     <t>Hippo Campus</t>
   </si>
   <si>
@@ -8715,15 +8577,9 @@
     <t>The Highwomen</t>
   </si>
   <si>
-    <t>Better Oblivion Community Center</t>
-  </si>
-  <si>
     <t>Orville Peck</t>
   </si>
   <si>
-    <t>Billie Eilish</t>
-  </si>
-  <si>
     <t>Yola</t>
   </si>
   <si>
@@ -8736,9 +8592,6 @@
     <t>Weyes Blood</t>
   </si>
   <si>
-    <t>Adia Victoria</t>
-  </si>
-  <si>
     <t>Jesse Malin</t>
   </si>
   <si>
@@ -8754,9 +8607,6 @@
     <t>Mattiel</t>
   </si>
   <si>
-    <t>Angie McMahon</t>
-  </si>
-  <si>
     <t>Rodrigo y Gabriela</t>
   </si>
   <si>
@@ -8784,9 +8634,6 @@
     <t>Crosby, Stills &amp; Nash</t>
   </si>
   <si>
-    <t>Beyoncé</t>
-  </si>
-  <si>
     <t>Television</t>
   </si>
   <si>
@@ -8799,15 +8646,9 @@
     <t>Deep Sea Diver</t>
   </si>
   <si>
-    <t>Blu DeTiger</t>
-  </si>
-  <si>
     <t>The War and Treaty</t>
   </si>
   <si>
-    <t>Adrianne Lenker</t>
-  </si>
-  <si>
     <t>Car Seat Headrest</t>
   </si>
   <si>
@@ -8847,9 +8688,6 @@
     <t>Wet Leg</t>
   </si>
   <si>
-    <t>Allison Russell</t>
-  </si>
-  <si>
     <t>Stephen Sanchez</t>
   </si>
   <si>
@@ -8874,9 +8712,6 @@
     <t>Alvvays</t>
   </si>
   <si>
-    <t>Bomba Estéreo &amp; Manu Chao</t>
-  </si>
-  <si>
     <t>Plains</t>
   </si>
   <si>
@@ -8886,15 +8721,9 @@
     <t>Nikki Lane</t>
   </si>
   <si>
-    <t>Allison Ponthier</t>
-  </si>
-  <si>
     <t>Cuco</t>
   </si>
   <si>
-    <t>Arlo Parks</t>
-  </si>
-  <si>
     <t>Dehd</t>
   </si>
   <si>
@@ -8913,15 +8742,9 @@
     <t>The Smile</t>
   </si>
   <si>
-    <t>Bartees Strange</t>
-  </si>
-  <si>
     <t>Marcus King</t>
   </si>
   <si>
-    <t>Alex G</t>
-  </si>
-  <si>
     <t>Momma</t>
   </si>
   <si>
@@ -8937,9 +8760,6 @@
     <t>Thee Sacred Souls</t>
   </si>
   <si>
-    <t>Beck &amp; Phoenix</t>
-  </si>
-  <si>
     <t>Caroline Polachek</t>
   </si>
   <si>
@@ -8961,9 +8781,6 @@
     <t>Daisy Jones &amp; The Six</t>
   </si>
   <si>
-    <t>Abraham Alexander</t>
-  </si>
-  <si>
     <t>Bully</t>
   </si>
   <si>
@@ -8979,9 +8796,6 @@
     <t>MJ Lenderman</t>
   </si>
   <si>
-    <t>Billy Strings</t>
-  </si>
-  <si>
     <t>Suki Waterhouse</t>
   </si>
   <si>
@@ -9009,9 +8823,6 @@
     <t>Sierra Ferrell</t>
   </si>
   <si>
-    <t>Arooj Aftab</t>
-  </si>
-  <si>
     <t>Joe P</t>
   </si>
   <si>
@@ -9024,7 +8835,139 @@
     <t>Sammy Rae &amp; The Friends</t>
   </si>
   <si>
-    <t>Billy Allen + The Pollies</t>
+    <t>Castanets</t>
+  </si>
+  <si>
+    <t>A Man Under the Influence</t>
+  </si>
+  <si>
+    <t>The Lucky One</t>
+  </si>
+  <si>
+    <t>Alison Krauss &amp; Union Station</t>
+  </si>
+  <si>
+    <t>New Favorite</t>
+  </si>
+  <si>
+    <t>Something Good</t>
+  </si>
+  <si>
+    <t>An Awesome Good</t>
+  </si>
+  <si>
+    <t>Archie, Marry Me</t>
+  </si>
+  <si>
+    <t>Leave it Alone</t>
+  </si>
+  <si>
+    <t>To the Sunset</t>
+  </si>
+  <si>
+    <t>The Magician</t>
+  </si>
+  <si>
+    <t>The Party</t>
+  </si>
+  <si>
+    <t>Shine</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Brighter Than Sunshine</t>
+  </si>
+  <si>
+    <t>Strange &amp; Beautiful</t>
+  </si>
+  <si>
+    <t>One Crowded Hour</t>
+  </si>
+  <si>
+    <t>Moo, You Bloody Choir</t>
+  </si>
+  <si>
+    <t>Something to Talk About</t>
+  </si>
+  <si>
+    <t>About a Boy (Soundtrack)</t>
+  </si>
+  <si>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t>Beatopia</t>
+  </si>
+  <si>
+    <t>Hiding Bottles</t>
+  </si>
+  <si>
+    <t>So That You Might Hear Me</t>
+  </si>
+  <si>
+    <t>So Nice (Summer Samba)</t>
+  </si>
+  <si>
+    <t>Tanto Tempo</t>
+  </si>
+  <si>
+    <t>East Harlem</t>
+  </si>
+  <si>
+    <t>The Rip Tide</t>
+  </si>
+  <si>
+    <t>Rocky Took a Lover</t>
+  </si>
+  <si>
+    <t>Flock</t>
+  </si>
+  <si>
+    <t>The Boy with the Arab Strap</t>
+  </si>
+  <si>
+    <t>Diamonds on the Inside</t>
+  </si>
+  <si>
+    <t>How it Should Be (Sha Sha)</t>
+  </si>
+  <si>
+    <t>Sha Sha</t>
+  </si>
+  <si>
+    <t>Catch My Disease</t>
+  </si>
+  <si>
+    <t>Awake is the New Sleep</t>
+  </si>
+  <si>
+    <t>Crazy for You</t>
+  </si>
+  <si>
+    <t>Billie Joe &amp; Norah Jones</t>
+  </si>
+  <si>
+    <t>Long Time Gone</t>
+  </si>
+  <si>
+    <t>Foreverly</t>
+  </si>
+  <si>
+    <t>I Wanna Get Better</t>
+  </si>
+  <si>
+    <t>Have a Heart</t>
+  </si>
+  <si>
+    <t>Nick of Time</t>
+  </si>
+  <si>
+    <t>Comback Kid (That's my Dog)</t>
+  </si>
+  <si>
+    <t>Loverboy</t>
   </si>
 </sst>
 </file>
@@ -9457,7 +9400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="A1:A651"/>
+  <dimension ref="A1:A564"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -9466,67 +9409,67 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2789</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>2937</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>2384</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>2862</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>2885</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>2399</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>2724</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>2628</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>2398</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>2366</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>2757</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>2923</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>2475</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -9536,3187 +9479,2752 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>2354</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>2648</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>2912</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>2899</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>2477</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>2676</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2661</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2907</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>2844</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>2496</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>2668</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>2370</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>2845</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>2404</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>2803</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>2888</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>2422</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>2777</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>2424</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>2868</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>2363</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>2588</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>2468</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>2498</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>2675</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>2914</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>2953</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>2716</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>2555</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>2388</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>2921</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>2896</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>2632</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>2726</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>2333</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>2929</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>2611</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>2587</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>2535</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>2583</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>2469</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>2635</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>2529</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>2494</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>2654</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>2709</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>2658</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>2702</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>2414</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>2855</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>2515</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>2878</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>2848</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>2857</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>2688</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>2958</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>2943</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>2397</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>2585</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>2598</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>2925</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>2400</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>2606</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>2798</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>2883</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>111</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>2780</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>2908</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>2435</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>2755</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>2836</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>2574</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>2781</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>2480</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>2549</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>2851</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>547</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>2824</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>2472</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>2442</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>2581</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>2378</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>2432</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>2530</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>2938</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>2853</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>2622</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>2536</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>2584</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>2886</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>2930</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>2828</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>2542</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>2522</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>2377</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>2401</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>2801</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>2701</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>2903</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>2825</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>2474</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>2714</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>2420</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>2677</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>2809</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>2431</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>2860</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>2650</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>2729</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>2565</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>2396</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>2700</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>2362</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>2390</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>2821</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>2877</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>2875</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>2913</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>2936</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>2459</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>2718</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>2582</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>2348</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>2554</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>2476</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>2315</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>2652</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>2341</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>2331</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>2373</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>2579</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>2359</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>2537</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>192</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>2386</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>2607</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>2600</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>2440</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>2802</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>2882</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>2589</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>2915</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>2409</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>2663</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>2939</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>2379</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>2577</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>2752</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>2620</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>2788</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>2639</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>2525</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>2393</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>2633</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>2667</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>2329</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>2627</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>2561</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>2739</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>2792</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>2814</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>2473</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>2686</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>2746</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>2507</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>2721</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>2847</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>2314</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>2380</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>2846</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>2466</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>2651</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>2948</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>2950</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>2576</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>2772</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>2706</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>2951</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>2592</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>2737</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>2813</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>2613</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>2910</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>2897</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>2458</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>2692</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>2812</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>2505</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>2649</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>2679</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>2372</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>2774</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>2336</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>2608</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>2630</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>2947</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>2347</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>2736</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>2653</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>2027</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>2534</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>2425</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>2655</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>2452</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>2543</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>2640</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>2387</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>2326</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>2770</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>2806</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>2575</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>2874</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>2671</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>2786</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>2578</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>2849</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>2799</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>2656</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>2741</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>2704</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>2817</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>2601</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>2940</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>2416</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>2949</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>2580</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>2642</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>2548</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>2731</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>2412</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>2703</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>2852</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>2389</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>2629</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" t="s">
-        <v>2504</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>2829</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>2532</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>2697</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>2597</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>2621</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>2517</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>2602</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>2567</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>2483</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>2745</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>2826</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>2339</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>2773</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>2743</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>2368</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>2637</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>2837</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>2351</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>2617</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>2747</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>2816</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>2493</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>2562</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>2662</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>2734</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>2863</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>2485</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>2795</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>2337</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>2408</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>2403</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>2954</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>2365</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>2541</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>2540</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>2666</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>2360</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>2674</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>2355</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>2319</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>2501</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>2395</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" t="s">
-        <v>2955</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" t="s">
-        <v>2941</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" t="s">
-        <v>2394</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" t="s">
-        <v>2417</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" t="s">
-        <v>2556</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" t="s">
-        <v>2785</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" t="s">
-        <v>2488</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" t="s">
-        <v>2467</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>2506</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>2445</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>2462</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" t="s">
-        <v>2727</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" t="s">
-        <v>2586</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" t="s">
-        <v>2323</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>2832</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" t="s">
-        <v>2419</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" t="s">
-        <v>2470</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" t="s">
-        <v>2891</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" t="s">
-        <v>2749</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" t="s">
-        <v>2446</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>2768</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>2450</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" t="s">
-        <v>2819</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" t="s">
-        <v>2890</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" t="s">
-        <v>2426</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>2451</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>2349</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>2518</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>2682</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" t="s">
-        <v>2705</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" t="s">
-        <v>2733</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" t="s">
-        <v>2765</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" t="s">
-        <v>2926</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" t="s">
-        <v>2623</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" t="s">
-        <v>2683</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" t="s">
-        <v>2872</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" t="s">
-        <v>2594</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>2453</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>2742</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>2374</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>2570</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" t="s">
-        <v>2763</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" t="s">
-        <v>2546</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340" t="s">
-        <v>2427</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>2596</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>2673</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" t="s">
-        <v>2876</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" t="s">
-        <v>2850</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345" t="s">
-        <v>2810</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>2794</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>2762</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" t="s">
-        <v>2482</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" t="s">
-        <v>2418</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" t="s">
-        <v>2376</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="351" spans="1:1">
       <c r="A351" t="s">
-        <v>2356</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" t="s">
-        <v>2689</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" t="s">
-        <v>2833</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="354" spans="1:1">
       <c r="A354" t="s">
-        <v>2344</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" t="s">
-        <v>2787</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" t="s">
-        <v>2839</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>2350</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" t="s">
-        <v>2383</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="359" spans="1:1">
       <c r="A359" t="s">
-        <v>2808</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" t="s">
-        <v>2454</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="361" spans="1:1">
       <c r="A361" t="s">
-        <v>2471</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" t="s">
-        <v>2573</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" t="s">
-        <v>2725</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" t="s">
-        <v>2484</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="365" spans="1:1">
       <c r="A365" t="s">
-        <v>2761</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" t="s">
-        <v>2864</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" t="s">
-        <v>2797</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>2511</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>2672</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" t="s">
-        <v>2822</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" t="s">
-        <v>2330</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" t="s">
-        <v>2922</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>2778</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" t="s">
-        <v>2805</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>2328</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" t="s">
-        <v>2516</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" t="s">
-        <v>2744</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" t="s">
-        <v>2753</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" t="s">
-        <v>2321</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" t="s">
-        <v>2332</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" t="s">
-        <v>2497</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>2449</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>2510</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384" t="s">
-        <v>2894</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" t="s">
-        <v>2751</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" t="s">
-        <v>2867</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>2595</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>2463</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>2557</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>2956</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" t="s">
-        <v>2609</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" t="s">
-        <v>2643</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" t="s">
-        <v>2406</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" t="s">
-        <v>2636</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="395" spans="1:1">
       <c r="A395" t="s">
-        <v>2626</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" t="s">
-        <v>2503</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" t="s">
-        <v>2492</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" t="s">
-        <v>2678</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>2827</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>2942</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>2430</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>2411</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>2924</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>2823</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="406" spans="1:1">
       <c r="A406" t="s">
-        <v>2572</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" t="s">
-        <v>2625</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" t="s">
-        <v>2695</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" t="s">
-        <v>2887</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" t="s">
-        <v>2590</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" t="s">
-        <v>2918</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" t="s">
-        <v>2364</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" t="s">
-        <v>2357</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" t="s">
-        <v>2841</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>2880</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>2415</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>2447</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>2481</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>2428</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>2691</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>2369</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>2513</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>2614</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>2911</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>2865</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>1034</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>2325</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>2657</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>2680</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>2385</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>2644</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>2489</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>2381</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>2547</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>2856</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>2904</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>2946</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>2723</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" t="s">
-        <v>2342</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="441" spans="1:1">
       <c r="A441" t="s">
-        <v>2371</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="442" spans="1:1">
       <c r="A442" t="s">
-        <v>2500</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="443" spans="1:1">
       <c r="A443" t="s">
-        <v>2437</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="444" spans="1:1">
       <c r="A444" t="s">
-        <v>2738</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445" t="s">
-        <v>2423</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="446" spans="1:1">
       <c r="A446" t="s">
-        <v>2539</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="447" spans="1:1">
       <c r="A447" t="s">
-        <v>2713</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" t="s">
-        <v>2438</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="449" spans="1:1">
       <c r="A449" t="s">
-        <v>2322</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" t="s">
-        <v>2815</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="451" spans="1:1">
       <c r="A451" t="s">
-        <v>2669</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="452" spans="1:1">
       <c r="A452" t="s">
-        <v>2735</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="453" spans="1:1">
       <c r="A453" t="s">
-        <v>2790</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" t="s">
-        <v>2909</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="455" spans="1:1">
       <c r="A455" t="s">
-        <v>2645</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" t="s">
-        <v>2870</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="457" spans="1:1">
       <c r="A457" t="s">
-        <v>2338</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" t="s">
-        <v>2796</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="459" spans="1:1">
       <c r="A459" t="s">
-        <v>2487</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="460" spans="1:1">
       <c r="A460" t="s">
-        <v>2563</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="461" spans="1:1">
       <c r="A461" t="s">
-        <v>2568</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" t="s">
-        <v>2760</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="463" spans="1:1">
       <c r="A463" t="s">
-        <v>2352</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="464" spans="1:1">
       <c r="A464" t="s">
-        <v>2499</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="465" spans="1:1">
       <c r="A465" t="s">
-        <v>2479</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="466" spans="1:1">
       <c r="A466" t="s">
-        <v>2932</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="467" spans="1:1">
       <c r="A467" t="s">
-        <v>2830</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="468" spans="1:1">
       <c r="A468" t="s">
-        <v>2711</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="469" spans="1:1">
       <c r="A469" t="s">
-        <v>2523</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="470" spans="1:1">
       <c r="A470" t="s">
-        <v>2838</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="471" spans="1:1">
       <c r="A471" t="s">
-        <v>2933</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472" t="s">
-        <v>2681</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="473" spans="1:1">
       <c r="A473" t="s">
-        <v>2318</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="474" spans="1:1">
       <c r="A474" t="s">
-        <v>2361</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475" t="s">
-        <v>2443</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476" t="s">
-        <v>2491</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477" t="s">
-        <v>2545</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478" t="s">
-        <v>2616</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="479" spans="1:1">
       <c r="A479" t="s">
-        <v>2375</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="480" spans="1:1">
       <c r="A480" t="s">
-        <v>2591</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="481" spans="1:1">
       <c r="A481" t="s">
-        <v>2448</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="482" spans="1:1">
       <c r="A482" t="s">
-        <v>2382</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="483" spans="1:1">
       <c r="A483" t="s">
-        <v>2869</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="484" spans="1:1">
       <c r="A484" t="s">
-        <v>2638</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="485" spans="1:1">
       <c r="A485" t="s">
-        <v>2892</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="486" spans="1:1">
       <c r="A486" t="s">
-        <v>2392</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="487" spans="1:1">
       <c r="A487" t="s">
-        <v>2465</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="488" spans="1:1">
       <c r="A488" t="s">
-        <v>2945</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="489" spans="1:1">
       <c r="A489" t="s">
-        <v>2346</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="490" spans="1:1">
       <c r="A490" t="s">
-        <v>2343</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="491" spans="1:1">
       <c r="A491" t="s">
-        <v>2553</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="492" spans="1:1">
       <c r="A492" t="s">
-        <v>2610</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="493" spans="1:1">
       <c r="A493" t="s">
-        <v>2783</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="494" spans="1:1">
       <c r="A494" t="s">
-        <v>2758</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="495" spans="1:1">
       <c r="A495" t="s">
-        <v>2367</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="496" spans="1:1">
       <c r="A496" t="s">
-        <v>2710</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="497" spans="1:1">
       <c r="A497" t="s">
-        <v>2934</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="498" spans="1:1">
       <c r="A498" t="s">
-        <v>2957</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="499" spans="1:1">
       <c r="A499" t="s">
-        <v>2693</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="500" spans="1:1">
       <c r="A500" t="s">
-        <v>2455</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="501" spans="1:1">
       <c r="A501" t="s">
-        <v>2791</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="502" spans="1:1">
       <c r="A502" t="s">
-        <v>2919</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="503" spans="1:1">
       <c r="A503" t="s">
-        <v>2916</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="504" spans="1:1">
       <c r="A504" t="s">
-        <v>2558</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="505" spans="1:1">
       <c r="A505" t="s">
-        <v>2750</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="506" spans="1:1">
       <c r="A506" t="s">
-        <v>2779</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="507" spans="1:1">
       <c r="A507" t="s">
-        <v>2935</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="508" spans="1:1">
       <c r="A508" t="s">
-        <v>2410</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="509" spans="1:1">
       <c r="A509" t="s">
-        <v>2552</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511" t="s">
-        <v>2457</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="512" spans="1:1">
       <c r="A512" t="s">
-        <v>2353</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="513" spans="1:1">
       <c r="A513" t="s">
-        <v>2531</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="514" spans="1:1">
       <c r="A514" t="s">
-        <v>2569</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="515" spans="1:1">
       <c r="A515" t="s">
-        <v>2313</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="516" spans="1:1">
       <c r="A516" t="s">
-        <v>2641</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="517" spans="1:1">
       <c r="A517" t="s">
-        <v>2512</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="518" spans="1:1">
       <c r="A518" t="s">
-        <v>2952</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="519" spans="1:1">
       <c r="A519" t="s">
-        <v>2316</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="520" spans="1:1">
       <c r="A520" t="s">
-        <v>2764</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="521" spans="1:1">
       <c r="A521" t="s">
-        <v>2820</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="522" spans="1:1">
       <c r="A522" t="s">
-        <v>2835</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="523" spans="1:1">
       <c r="A523" t="s">
-        <v>2866</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="524" spans="1:1">
       <c r="A524" t="s">
-        <v>2842</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="525" spans="1:1">
       <c r="A525" t="s">
-        <v>2804</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="526" spans="1:1">
       <c r="A526" t="s">
-        <v>2421</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="527" spans="1:1">
       <c r="A527" t="s">
-        <v>2728</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="528" spans="1:1">
       <c r="A528" t="s">
-        <v>2889</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="529" spans="1:1">
       <c r="A529" t="s">
-        <v>2434</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="530" spans="1:1">
       <c r="A530" t="s">
-        <v>2719</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="531" spans="1:1">
       <c r="A531" t="s">
-        <v>2624</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="532" spans="1:1">
       <c r="A532" t="s">
-        <v>1915</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="533" spans="1:1">
       <c r="A533" t="s">
-        <v>2478</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="534" spans="1:1">
       <c r="A534" t="s">
-        <v>2740</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="535" spans="1:1">
       <c r="A535" t="s">
-        <v>2900</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="536" spans="1:1">
       <c r="A536" t="s">
-        <v>2317</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="537" spans="1:1">
       <c r="A537" t="s">
-        <v>2340</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="538" spans="1:1">
       <c r="A538" t="s">
-        <v>2901</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="539" spans="1:1">
       <c r="A539" t="s">
-        <v>2461</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="540" spans="1:1">
       <c r="A540" t="s">
-        <v>2720</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="541" spans="1:1">
       <c r="A541" t="s">
-        <v>2800</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="542" spans="1:1">
       <c r="A542" t="s">
-        <v>2944</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="543" spans="1:1">
       <c r="A543" t="s">
-        <v>2782</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="544" spans="1:1">
       <c r="A544" t="s">
-        <v>2831</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="545" spans="1:1">
       <c r="A545" t="s">
-        <v>2439</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="546" spans="1:1">
       <c r="A546" t="s">
-        <v>2444</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="547" spans="1:1">
       <c r="A547" t="s">
-        <v>2708</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="548" spans="1:1">
       <c r="A548" t="s">
-        <v>2615</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="549" spans="1:1">
       <c r="A549" t="s">
-        <v>2784</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="550" spans="1:1">
       <c r="A550" t="s">
-        <v>2879</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="551" spans="1:1">
       <c r="A551" t="s">
-        <v>2717</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="552" spans="1:1">
       <c r="A552" t="s">
-        <v>2694</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="553" spans="1:1">
       <c r="A553" t="s">
-        <v>2906</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="554" spans="1:1">
       <c r="A554" t="s">
-        <v>2405</v>
+        <v>349</v>
       </c>
     </row>
     <row r="555" spans="1:1">
       <c r="A555" t="s">
-        <v>2730</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="556" spans="1:1">
       <c r="A556" t="s">
-        <v>2756</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="557" spans="1:1">
       <c r="A557" t="s">
-        <v>2895</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="558" spans="1:1">
       <c r="A558" t="s">
-        <v>2551</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="559" spans="1:1">
       <c r="A559" t="s">
-        <v>2544</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="560" spans="1:1">
       <c r="A560" t="s">
-        <v>2456</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="561" spans="1:1">
       <c r="A561" t="s">
-        <v>2722</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="562" spans="1:1">
       <c r="A562" t="s">
-        <v>2769</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="563" spans="1:1">
       <c r="A563" t="s">
-        <v>2893</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="564" spans="1:1">
       <c r="A564" t="s">
-        <v>2604</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1">
-      <c r="A565" t="s">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1">
-      <c r="A566" t="s">
-        <v>2665</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1">
-      <c r="A567" t="s">
-        <v>2559</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1">
-      <c r="A568" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1">
-      <c r="A569" t="s">
-        <v>2526</v>
-      </c>
-    </row>
-    <row r="570" spans="1:1">
-      <c r="A570" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1">
-      <c r="A571" t="s">
-        <v>2593</v>
-      </c>
-    </row>
-    <row r="572" spans="1:1">
-      <c r="A572" t="s">
-        <v>2605</v>
-      </c>
-    </row>
-    <row r="573" spans="1:1">
-      <c r="A573" t="s">
-        <v>2917</v>
-      </c>
-    </row>
-    <row r="574" spans="1:1">
-      <c r="A574" t="s">
-        <v>2854</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1">
-      <c r="A575" t="s">
-        <v>2527</v>
-      </c>
-    </row>
-    <row r="576" spans="1:1">
-      <c r="A576" t="s">
-        <v>2698</v>
-      </c>
-    </row>
-    <row r="577" spans="1:1">
-      <c r="A577" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="578" spans="1:1">
-      <c r="A578" t="s">
-        <v>2927</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1">
-      <c r="A579" t="s">
-        <v>2834</v>
-      </c>
-    </row>
-    <row r="580" spans="1:1">
-      <c r="A580" t="s">
-        <v>2902</v>
-      </c>
-    </row>
-    <row r="581" spans="1:1">
-      <c r="A581" t="s">
-        <v>2670</v>
-      </c>
-    </row>
-    <row r="582" spans="1:1">
-      <c r="A582" t="s">
-        <v>2571</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1">
-      <c r="A583" t="s">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="584" spans="1:1">
-      <c r="A584" t="s">
-        <v>2646</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1">
-      <c r="A585" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1">
-      <c r="A586" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1">
-      <c r="A587" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="588" spans="1:1">
-      <c r="A588" t="s">
-        <v>2564</v>
-      </c>
-    </row>
-    <row r="589" spans="1:1">
-      <c r="A589" t="s">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1">
-      <c r="A590" t="s">
-        <v>2775</v>
-      </c>
-    </row>
-    <row r="591" spans="1:1">
-      <c r="A591" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="592" spans="1:1">
-      <c r="A592" t="s">
-        <v>2599</v>
-      </c>
-    </row>
-    <row r="593" spans="1:1">
-      <c r="A593" t="s">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="594" spans="1:1">
-      <c r="A594" t="s">
-        <v>2618</v>
-      </c>
-    </row>
-    <row r="595" spans="1:1">
-      <c r="A595" t="s">
-        <v>2748</v>
-      </c>
-    </row>
-    <row r="596" spans="1:1">
-      <c r="A596" t="s">
-        <v>2521</v>
-      </c>
-    </row>
-    <row r="597" spans="1:1">
-      <c r="A597" t="s">
-        <v>2659</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1">
-      <c r="A598" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="599" spans="1:1">
-      <c r="A599" t="s">
-        <v>2871</v>
-      </c>
-    </row>
-    <row r="600" spans="1:1">
-      <c r="A600" t="s">
-        <v>2647</v>
-      </c>
-    </row>
-    <row r="601" spans="1:1">
-      <c r="A601" t="s">
-        <v>2884</v>
-      </c>
-    </row>
-    <row r="602" spans="1:1">
-      <c r="A602" t="s">
-        <v>2690</v>
-      </c>
-    </row>
-    <row r="603" spans="1:1">
-      <c r="A603" t="s">
-        <v>2402</v>
-      </c>
-    </row>
-    <row r="604" spans="1:1">
-      <c r="A604" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="605" spans="1:1">
-      <c r="A605" t="s">
-        <v>2928</v>
-      </c>
-    </row>
-    <row r="606" spans="1:1">
-      <c r="A606" t="s">
-        <v>2811</v>
-      </c>
-    </row>
-    <row r="607" spans="1:1">
-      <c r="A607" t="s">
-        <v>2528</v>
-      </c>
-    </row>
-    <row r="608" spans="1:1">
-      <c r="A608" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="609" spans="1:1">
-      <c r="A609" t="s">
-        <v>2767</v>
-      </c>
-    </row>
-    <row r="610" spans="1:1">
-      <c r="A610" t="s">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="611" spans="1:1">
-      <c r="A611" t="s">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="612" spans="1:1">
-      <c r="A612" t="s">
-        <v>2840</v>
-      </c>
-    </row>
-    <row r="613" spans="1:1">
-      <c r="A613" t="s">
-        <v>2279</v>
-      </c>
-    </row>
-    <row r="614" spans="1:1">
-      <c r="A614" t="s">
-        <v>2320</v>
-      </c>
-    </row>
-    <row r="615" spans="1:1">
-      <c r="A615" t="s">
-        <v>2685</v>
-      </c>
-    </row>
-    <row r="616" spans="1:1">
-      <c r="A616" t="s">
-        <v>2433</v>
-      </c>
-    </row>
-    <row r="617" spans="1:1">
-      <c r="A617" t="s">
-        <v>2707</v>
-      </c>
-    </row>
-    <row r="618" spans="1:1">
-      <c r="A618" t="s">
-        <v>2619</v>
-      </c>
-    </row>
-    <row r="619" spans="1:1">
-      <c r="A619" t="s">
-        <v>2612</v>
-      </c>
-    </row>
-    <row r="620" spans="1:1">
-      <c r="A620" t="s">
-        <v>2754</v>
-      </c>
-    </row>
-    <row r="621" spans="1:1">
-      <c r="A621" t="s">
-        <v>2566</v>
-      </c>
-    </row>
-    <row r="622" spans="1:1">
-      <c r="A622" t="s">
-        <v>2712</v>
-      </c>
-    </row>
-    <row r="623" spans="1:1">
-      <c r="A623" t="s">
-        <v>2931</v>
-      </c>
-    </row>
-    <row r="624" spans="1:1">
-      <c r="A624" t="s">
-        <v>2771</v>
-      </c>
-    </row>
-    <row r="625" spans="1:1">
-      <c r="A625" t="s">
-        <v>2696</v>
-      </c>
-    </row>
-    <row r="626" spans="1:1">
-      <c r="A626" t="s">
-        <v>2560</v>
-      </c>
-    </row>
-    <row r="627" spans="1:1">
-      <c r="A627" t="s">
-        <v>2345</v>
-      </c>
-    </row>
-    <row r="628" spans="1:1">
-      <c r="A628" t="s">
-        <v>2905</v>
-      </c>
-    </row>
-    <row r="629" spans="1:1">
-      <c r="A629" t="s">
-        <v>2391</v>
-      </c>
-    </row>
-    <row r="630" spans="1:1">
-      <c r="A630" t="s">
-        <v>2684</v>
-      </c>
-    </row>
-    <row r="631" spans="1:1">
-      <c r="A631" t="s">
-        <v>2664</v>
-      </c>
-    </row>
-    <row r="632" spans="1:1">
-      <c r="A632" t="s">
-        <v>2776</v>
-      </c>
-    </row>
-    <row r="633" spans="1:1">
-      <c r="A633" t="s">
-        <v>2881</v>
-      </c>
-    </row>
-    <row r="634" spans="1:1">
-      <c r="A634" t="s">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="635" spans="1:1">
-      <c r="A635" t="s">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="636" spans="1:1">
-      <c r="A636" t="s">
-        <v>2861</v>
-      </c>
-    </row>
-    <row r="637" spans="1:1">
-      <c r="A637" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="638" spans="1:1">
-      <c r="A638" t="s">
-        <v>2859</v>
-      </c>
-    </row>
-    <row r="639" spans="1:1">
-      <c r="A639" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="640" spans="1:1">
-      <c r="A640" t="s">
-        <v>2407</v>
-      </c>
-    </row>
-    <row r="641" spans="1:1">
-      <c r="A641" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="642" spans="1:1">
-      <c r="A642" t="s">
-        <v>2699</v>
-      </c>
-    </row>
-    <row r="643" spans="1:1">
-      <c r="A643" t="s">
-        <v>2334</v>
-      </c>
-    </row>
-    <row r="644" spans="1:1">
-      <c r="A644" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="645" spans="1:1">
-      <c r="A645" t="s">
-        <v>2759</v>
-      </c>
-    </row>
-    <row r="646" spans="1:1">
-      <c r="A646" t="s">
-        <v>2687</v>
-      </c>
-    </row>
-    <row r="647" spans="1:1">
-      <c r="A647" t="s">
-        <v>2793</v>
-      </c>
-    </row>
-    <row r="648" spans="1:1">
-      <c r="A648" t="s">
-        <v>2858</v>
-      </c>
-    </row>
-    <row r="649" spans="1:1">
-      <c r="A649" t="s">
-        <v>2732</v>
-      </c>
-    </row>
-    <row r="650" spans="1:1">
-      <c r="A650" t="s">
-        <v>2843</v>
-      </c>
-    </row>
-    <row r="651" spans="1:1">
-      <c r="A651" t="s">
-        <v>2524</v>
+        <v>2508</v>
       </c>
     </row>
   </sheetData>
@@ -12727,7 +12235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F843"/>
+  <dimension ref="A1:F867"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -13480,7 +12988,7 @@
     </row>
     <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
-        <v>2508</v>
+        <v>2493</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>568</v>
@@ -17327,7 +16835,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>2873</v>
+        <v>2823</v>
       </c>
       <c r="B260" t="s">
         <v>1024</v>
@@ -27197,7 +26705,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="833" spans="2:4">
+    <row r="833" spans="1:6">
       <c r="B833" t="s">
         <v>2301</v>
       </c>
@@ -27205,7 +26713,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="834" spans="2:4">
+    <row r="834" spans="1:6">
       <c r="B834" t="s">
         <v>2302</v>
       </c>
@@ -27213,7 +26721,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="835" spans="2:4">
+    <row r="835" spans="1:6">
       <c r="B835" t="s">
         <v>2303</v>
       </c>
@@ -27221,7 +26729,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="836" spans="2:4">
+    <row r="836" spans="1:6">
       <c r="B836" t="s">
         <v>2304</v>
       </c>
@@ -27229,7 +26737,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="837" spans="2:4">
+    <row r="837" spans="1:6">
       <c r="B837" t="s">
         <v>2305</v>
       </c>
@@ -27237,7 +26745,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="838" spans="2:4">
+    <row r="838" spans="1:6">
       <c r="B838" t="s">
         <v>2306</v>
       </c>
@@ -27245,7 +26753,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="839" spans="2:4">
+    <row r="839" spans="1:6">
       <c r="B839" t="s">
         <v>2307</v>
       </c>
@@ -27253,7 +26761,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="840" spans="2:4">
+    <row r="840" spans="1:6">
       <c r="B840" t="s">
         <v>2308</v>
       </c>
@@ -27261,7 +26769,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="841" spans="2:4">
+    <row r="841" spans="1:6">
       <c r="B841" t="s">
         <v>2309</v>
       </c>
@@ -27269,7 +26777,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="842" spans="2:4">
+    <row r="842" spans="1:6">
       <c r="B842" t="s">
         <v>2310</v>
       </c>
@@ -27277,12 +26785,420 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="843" spans="2:4">
+    <row r="843" spans="1:6">
       <c r="B843" t="s">
         <v>2311</v>
       </c>
       <c r="D843" t="s">
         <v>2312</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6">
+      <c r="A844" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B844" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C844" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E844">
+        <v>2001</v>
+      </c>
+      <c r="F844" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6">
+      <c r="A845" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B845" t="s">
+        <v>2897</v>
+      </c>
+      <c r="C845" t="s">
+        <v>2899</v>
+      </c>
+      <c r="E845">
+        <v>2001</v>
+      </c>
+      <c r="F845" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6">
+      <c r="A846" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B846" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C846" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E846">
+        <v>2012</v>
+      </c>
+      <c r="F846" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6">
+      <c r="A847" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B847" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C847" t="s">
+        <v>2853</v>
+      </c>
+      <c r="E847">
+        <v>2014</v>
+      </c>
+      <c r="F847" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6">
+      <c r="A848" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B848" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C848" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E848">
+        <v>2018</v>
+      </c>
+      <c r="F848" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6">
+      <c r="A849" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B849" t="s">
+        <v>2905</v>
+      </c>
+      <c r="C849" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E849">
+        <v>2016</v>
+      </c>
+      <c r="F849" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6">
+      <c r="A850" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B850" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C850" s="10" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E850">
+        <v>2005</v>
+      </c>
+      <c r="F850" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6">
+      <c r="A851" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B851" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C851" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E851">
+        <v>2005</v>
+      </c>
+      <c r="F851" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6">
+      <c r="A852" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B852" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C852" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E852">
+        <v>2006</v>
+      </c>
+      <c r="F852" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6">
+      <c r="A853" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B853" t="s">
+        <v>2913</v>
+      </c>
+      <c r="C853" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E853">
+        <v>2002</v>
+      </c>
+      <c r="F853" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6">
+      <c r="A854" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B854" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C854" t="s">
+        <v>2916</v>
+      </c>
+      <c r="E854">
+        <v>2022</v>
+      </c>
+      <c r="F854" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6">
+      <c r="A855" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B855" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C855" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E855">
+        <v>2019</v>
+      </c>
+      <c r="F855" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6">
+      <c r="A856" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B856" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C856" t="s">
+        <v>2920</v>
+      </c>
+      <c r="E856">
+        <v>2000</v>
+      </c>
+      <c r="F856" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6">
+      <c r="A857" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B857" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C857" t="s">
+        <v>2922</v>
+      </c>
+      <c r="E857">
+        <v>2011</v>
+      </c>
+      <c r="F857" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6">
+      <c r="A858" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B858" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C858" t="s">
+        <v>2924</v>
+      </c>
+      <c r="E858">
+        <v>2005</v>
+      </c>
+      <c r="F858" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6">
+      <c r="A859" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B859" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C859" t="s">
+        <v>2925</v>
+      </c>
+      <c r="E859">
+        <v>1998</v>
+      </c>
+      <c r="F859" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6">
+      <c r="A860" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B860" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C860" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E860">
+        <v>2003</v>
+      </c>
+      <c r="F860" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6">
+      <c r="A861" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B861" t="s">
+        <v>2927</v>
+      </c>
+      <c r="C861" t="s">
+        <v>2928</v>
+      </c>
+      <c r="E861">
+        <v>2002</v>
+      </c>
+      <c r="F861" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6">
+      <c r="A862" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B862" t="s">
+        <v>2929</v>
+      </c>
+      <c r="C862" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E862">
+        <v>2001</v>
+      </c>
+      <c r="F862" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6">
+      <c r="A863" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B863" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C863" t="s">
+        <v>2931</v>
+      </c>
+      <c r="E863">
+        <v>2010</v>
+      </c>
+      <c r="F863" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6">
+      <c r="A864" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B864" t="s">
+        <v>2933</v>
+      </c>
+      <c r="C864" t="s">
+        <v>2934</v>
+      </c>
+      <c r="E864">
+        <v>2013</v>
+      </c>
+      <c r="F864" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6">
+      <c r="A865" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C865" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E865">
+        <v>2014</v>
+      </c>
+      <c r="F865" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6">
+      <c r="A866" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B866" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C866" t="s">
+        <v>2937</v>
+      </c>
+      <c r="E866">
+        <v>1989</v>
+      </c>
+      <c r="F866" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6">
+      <c r="A867" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C867" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E867">
+        <v>2011</v>
+      </c>
+      <c r="F867" t="s">
+        <v>967</v>
       </c>
     </row>
   </sheetData>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A79DDD2-52CA-EB4F-AE32-599D883EFFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0074F04A-DECB-7E45-954F-D0EBB2AF8B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$801</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$889</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="2909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4069" uniqueCount="2897">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -7122,9 +7122,6 @@
     <t>Mark Knopfler</t>
   </si>
   <si>
-    <t>Dr. John</t>
-  </si>
-  <si>
     <t>Marah</t>
   </si>
   <si>
@@ -7245,9 +7242,6 @@
     <t>Los Super Seven</t>
   </si>
   <si>
-    <t>Diana Krall</t>
-  </si>
-  <si>
     <t>Eric Clapton</t>
   </si>
   <si>
@@ -7263,9 +7257,6 @@
     <t>Old 97's</t>
   </si>
   <si>
-    <t>David Mead</t>
-  </si>
-  <si>
     <t>Grant‑Lee Phillips</t>
   </si>
   <si>
@@ -7281,9 +7272,6 @@
     <t>Ron Sexsmith</t>
   </si>
   <si>
-    <t>Don Conoscenti</t>
-  </si>
-  <si>
     <t>Jonatha Brooke</t>
   </si>
   <si>
@@ -7308,9 +7296,6 @@
     <t>Jimmy Smith</t>
   </si>
   <si>
-    <t>Del McCoury Band</t>
-  </si>
-  <si>
     <t>Shannon McNally</t>
   </si>
   <si>
@@ -7389,9 +7374,6 @@
     <t>Susan Tedeschi</t>
   </si>
   <si>
-    <t>Dayna Kurtz</t>
-  </si>
-  <si>
     <t>Tom Waits</t>
   </si>
   <si>
@@ -7461,9 +7443,6 @@
     <t>Rosanne Cash</t>
   </si>
   <si>
-    <t>Erin McKeown</t>
-  </si>
-  <si>
     <t>Josh Ritter</t>
   </si>
   <si>
@@ -7563,9 +7542,6 @@
     <t>Josh Rose</t>
   </si>
   <si>
-    <t>Eliza Gilkyson</t>
-  </si>
-  <si>
     <t>The Rolling Stones</t>
   </si>
   <si>
@@ -7608,9 +7584,6 @@
     <t>Yusuf</t>
   </si>
   <si>
-    <t>Dixie Chicks</t>
-  </si>
-  <si>
     <t>The Flaming Lips</t>
   </si>
   <si>
@@ -7638,9 +7611,6 @@
     <t>Belle &amp; Sebastian</t>
   </si>
   <si>
-    <t>David Ford</t>
-  </si>
-  <si>
     <t>Gecko Turner</t>
   </si>
   <si>
@@ -7749,9 +7719,6 @@
     <t>Felice Brothers</t>
   </si>
   <si>
-    <t>Diane Birch</t>
-  </si>
-  <si>
     <t>Heartless Bastards</t>
   </si>
   <si>
@@ -7770,9 +7737,6 @@
     <t>Bell X1</t>
   </si>
   <si>
-    <t>Deer Tick</t>
-  </si>
-  <si>
     <t>Mumford &amp; Sons</t>
   </si>
   <si>
@@ -7800,9 +7764,6 @@
     <t>The Secret Sisters</t>
   </si>
   <si>
-    <t>Dawes</t>
-  </si>
-  <si>
     <t>Imelda May</t>
   </si>
   <si>
@@ -7818,9 +7779,6 @@
     <t>The Head &amp; The Heart</t>
   </si>
   <si>
-    <t>David Wax Museum</t>
-  </si>
-  <si>
     <t>Garland Jeffreys</t>
   </si>
   <si>
@@ -7857,9 +7815,6 @@
     <t>Trombone Shorty</t>
   </si>
   <si>
-    <t>Diego Garcia</t>
-  </si>
-  <si>
     <t>James Blake</t>
   </si>
   <si>
@@ -7875,9 +7830,6 @@
     <t>Middle Brother</t>
   </si>
   <si>
-    <t>Drive‑By Truckers</t>
-  </si>
-  <si>
     <t>Jack White</t>
   </si>
   <si>
@@ -7887,9 +7839,6 @@
     <t>Father John Misty</t>
   </si>
   <si>
-    <t>Donald Fagen</t>
-  </si>
-  <si>
     <t>Sharon Van Etten</t>
   </si>
   <si>
@@ -7902,9 +7851,6 @@
     <t>Rodriguez</t>
   </si>
   <si>
-    <t>Dirty Projectors</t>
-  </si>
-  <si>
     <t>Graham Parker &amp; The Rumour</t>
   </si>
   <si>
@@ -7932,9 +7878,6 @@
     <t>Frank Ocean</t>
   </si>
   <si>
-    <t>Everest</t>
-  </si>
-  <si>
     <t>Glen Hansard</t>
   </si>
   <si>
@@ -7959,9 +7902,6 @@
     <t>Jens Lekman</t>
   </si>
   <si>
-    <t>Delta Spirit</t>
-  </si>
-  <si>
     <t>Wanda Jackson</t>
   </si>
   <si>
@@ -8151,9 +8091,6 @@
     <t>Perfume Genius</t>
   </si>
   <si>
-    <t>Dum Dum Girls</t>
-  </si>
-  <si>
     <t>Stephen Malkmus &amp; The Jicks</t>
   </si>
   <si>
@@ -8172,9 +8109,6 @@
     <t>Jamie xx</t>
   </si>
   <si>
-    <t>EL VY</t>
-  </si>
-  <si>
     <t>Jeff Lynne’s ELO</t>
   </si>
   <si>
@@ -8283,18 +8217,12 @@
     <t>Lucius</t>
   </si>
   <si>
-    <t>Dinosaur Jr.</t>
-  </si>
-  <si>
     <t>Pixies</t>
   </si>
   <si>
     <t>Santigold</t>
   </si>
   <si>
-    <t>Dylan LeBlanc</t>
-  </si>
-  <si>
     <t>Yeasayer</t>
   </si>
   <si>
@@ -8316,9 +8244,6 @@
     <t>Sturgill Simpson</t>
   </si>
   <si>
-    <t>Declan McKenna</t>
-  </si>
-  <si>
     <t>Solange</t>
   </si>
   <si>
@@ -8343,9 +8268,6 @@
     <t>Flo Morrissey &amp; Matthew E. White</t>
   </si>
   <si>
-    <t>Earl St. Clair</t>
-  </si>
-  <si>
     <t>Phoebe Bridgers</t>
   </si>
   <si>
@@ -8421,12 +8343,6 @@
     <t>Amanda Shires</t>
   </si>
   <si>
-    <t>Erika Wennerstrom</t>
-  </si>
-  <si>
-    <t>Emily King</t>
-  </si>
-  <si>
     <t>Hippo Campus</t>
   </si>
   <si>
@@ -8502,9 +8418,6 @@
     <t>Waxahatchee</t>
   </si>
   <si>
-    <t>Deep Sea Diver</t>
-  </si>
-  <si>
     <t>The War and Treaty</t>
   </si>
   <si>
@@ -8574,9 +8487,6 @@
     <t>Nikki Lane</t>
   </si>
   <si>
-    <t>Dehd</t>
-  </si>
-  <si>
     <t>Say She She</t>
   </si>
   <si>
@@ -8625,9 +8535,6 @@
     <t>Shakey Graves</t>
   </si>
   <si>
-    <t>Devon Gilfillian</t>
-  </si>
-  <si>
     <t>Indigo De Souza</t>
   </si>
   <si>
@@ -8871,10 +8778,67 @@
     <t>Dave Matthews Band</t>
   </si>
   <si>
-    <t>Ants Marching</t>
-  </si>
-  <si>
-    <t>Under the Table and Dreaming</t>
+    <t>Grace is Gone</t>
+  </si>
+  <si>
+    <t>Busted Stuff</t>
+  </si>
+  <si>
+    <t>Strange Overtones</t>
+  </si>
+  <si>
+    <t>Everything that Happens will Happen Today</t>
+  </si>
+  <si>
+    <t>Everyday</t>
+  </si>
+  <si>
+    <t>Cowboy Take Me Away</t>
+  </si>
+  <si>
+    <t>Shame (2010 Deluxe Edition)</t>
+  </si>
+  <si>
+    <t>Where'd All the Time Go？</t>
+  </si>
+  <si>
+    <t>Mercy</t>
+  </si>
+  <si>
+    <t>Rockferry</t>
+  </si>
+  <si>
+    <t>You Dance</t>
+  </si>
+  <si>
+    <t>Up From Below</t>
+  </si>
+  <si>
+    <t>World Party</t>
+  </si>
+  <si>
+    <t>Is it Like Today</t>
+  </si>
+  <si>
+    <t>Bang!</t>
+  </si>
+  <si>
+    <t>Ex’s &amp; Oh’s</t>
+  </si>
+  <si>
+    <t>Love Stuff</t>
+  </si>
+  <si>
+    <t>Two More Bottles of Wine</t>
+  </si>
+  <si>
+    <t>Promises</t>
+  </si>
+  <si>
+    <t>The Cream of Clapton</t>
+  </si>
+  <si>
+    <t>Quarter Moon in a Ten Cent Town</t>
   </si>
 </sst>
 </file>
@@ -9307,7 +9271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="A1:A503"/>
+  <dimension ref="A1:A462"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -9316,1267 +9280,1267 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2350</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>2496</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>2371</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>2556</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>2550</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>2413</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>2722</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>2784</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>2540</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>2808</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>2386</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>2603</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>2825</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>2365</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>2533</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>2680</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>2711</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>2584</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2486</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2377</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>2579</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>2607</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>2324</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>2575</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>2519</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>2667</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>2714</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>2731</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>2443</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>2623</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>2674</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>2471</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>2651</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>2758</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>2311</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>2366</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>2757</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>2437</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>2594</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>2833</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>2578</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>2835</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>2532</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>2698</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>2640</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>2836</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>2543</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>2665</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>2730</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>2562</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>2806</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>2796</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>2430</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>2628</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>2729</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>2469</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>2593</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>2616</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>2361</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>2700</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>2330</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>2577</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>2497</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>2832</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>2340</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>2664</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>2595</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>2024</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>2494</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>2400</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>2596</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>2424</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>2502</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>2585</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>2372</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>2321</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>2696</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>2725</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>2531</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>2778</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>2610</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>2709</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>2534</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>2759</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>2720</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>2597</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>2669</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>2638</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>2734</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>2551</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>2826</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>2392</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>2834</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>2535</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>2587</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>2507</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>2659</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>2389</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>2637</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>2761</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>2374</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>2576</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>2468</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>2742</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>2492</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>2633</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>2548</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>2570</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>2480</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>2552</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>2524</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>2448</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>2673</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>2740</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>2333</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>2699</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>2671</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>2358</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>2582</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>2749</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>2343</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>2566</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>2675</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>2733</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>2458</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>2520</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>2602</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>2662</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>2768</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>2450</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>2717</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>2331</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>2385</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>2381</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>2838</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>2355</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>2500</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>2499</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>2606</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>2351</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>2613</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>2346</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>2315</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>2465</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>2379</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>2839</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>2827</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>2378</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>2393</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>2514</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>2708</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>2453</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>2438</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>2470</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>2417</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>2433</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>2656</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>2538</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>2319</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>2745</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>2395</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>2440</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>2790</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>2677</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>2418</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>2694</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>2422</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>2736</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>2789</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>2401</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>2423</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>2341</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>2481</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>2619</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>2639</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>2661</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>2691</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>2817</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>2571</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>2620</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>2776</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>2545</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>2425</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>2670</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>2362</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>2527</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>2689</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>2505</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>2402</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>2547</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>2612</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>2780</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>2760</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>2727</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>2716</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>2688</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>2447</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>2394</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>2364</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>2347</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>2625</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>2746</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>2337</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>2751</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>2342</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>2369</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>2726</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>2426</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>2441</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>2530</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>2654</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>2449</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>2687</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>2769</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>2719</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>2475</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>2611</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>2738</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>2325</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>2814</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>2703</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>2724</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>2323</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>2479</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>2672</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>2681</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>2317</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>2326</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>2461</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>2421</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>2474</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>2793</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>2679</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>2772</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>2546</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>2434</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>2515</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>2840</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>2558</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>2588</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>2383</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>2581</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>2574</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>2735</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>2467</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>2457</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>2615</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>2741</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>2828</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -10586,1247 +10550,1042 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>2388</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>2815</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>2739</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>2529</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>2573</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>2631</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>2786</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>2541</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>2811</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>2354</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>2348</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>2753</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>2782</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>2391</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>2419</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>2403</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>2627</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>2359</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>2477</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>2563</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>2807</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>2770</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>1031</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>2320</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>2598</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>2617</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>2370</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>2589</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>2454</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>2367</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>2506</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>2764</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>2801</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>2831</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>2653</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>2390</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>2335</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>2360</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>2464</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>2410</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>2666</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" t="s">
-        <v>2399</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" t="s">
-        <v>2498</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" t="s">
-        <v>2646</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" t="s">
-        <v>2411</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" t="s">
-        <v>2318</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" t="s">
-        <v>2732</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" t="s">
-        <v>2608</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" t="s">
-        <v>2663</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>2712</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>2805</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>2590</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" t="s">
-        <v>2774</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" t="s">
-        <v>2332</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" t="s">
-        <v>2718</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>2452</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" t="s">
-        <v>2521</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" t="s">
-        <v>2525</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" t="s">
-        <v>2686</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" t="s">
-        <v>2344</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" t="s">
-        <v>2463</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>2445</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>2821</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" t="s">
-        <v>2743</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" t="s">
-        <v>2644</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" t="s">
-        <v>2484</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>2750</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>2822</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>2618</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>2314</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" t="s">
-        <v>2352</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" t="s">
-        <v>2415</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" t="s">
-        <v>2456</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" t="s">
-        <v>2504</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" t="s">
-        <v>2565</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" t="s">
-        <v>2363</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" t="s">
-        <v>2542</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" t="s">
-        <v>2420</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>2368</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>2773</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>2583</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>2791</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" t="s">
-        <v>2376</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" t="s">
-        <v>2436</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340" t="s">
-        <v>2830</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>2339</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>2336</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" t="s">
-        <v>2511</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" t="s">
-        <v>2559</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345" t="s">
-        <v>2706</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>2684</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>2357</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" t="s">
-        <v>2643</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" t="s">
-        <v>2823</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" t="s">
-        <v>2841</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="351" spans="1:1">
       <c r="A351" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" t="s">
-        <v>2427</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" t="s">
-        <v>2713</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="354" spans="1:1">
       <c r="A354" t="s">
-        <v>2812</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" t="s">
-        <v>2809</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" t="s">
-        <v>2516</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>2678</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" t="s">
-        <v>2704</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="359" spans="1:1">
       <c r="A359" t="s">
-        <v>2824</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" t="s">
-        <v>2387</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="361" spans="1:1">
       <c r="A361" t="s">
-        <v>2510</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" t="s">
-        <v>2580</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" t="s">
-        <v>2429</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" t="s">
-        <v>2345</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="365" spans="1:1">
       <c r="A365" t="s">
-        <v>2491</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" t="s">
-        <v>2526</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" t="s">
-        <v>2310</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>2586</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>2476</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" t="s">
-        <v>2837</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" t="s">
-        <v>2312</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" t="s">
-        <v>2690</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>2737</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" t="s">
-        <v>2748</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>2771</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" t="s">
-        <v>2754</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" t="s">
-        <v>2723</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" t="s">
-        <v>2397</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" t="s">
-        <v>2657</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" t="s">
-        <v>2788</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" t="s">
-        <v>2407</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>2649</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>2572</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384" t="s">
-        <v>1912</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" t="s">
-        <v>2444</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" t="s">
-        <v>2668</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>2798</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>2313</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>2334</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>2799</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" t="s">
-        <v>2432</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" t="s">
-        <v>2650</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" t="s">
-        <v>2721</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" t="s">
-        <v>2829</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="395" spans="1:1">
       <c r="A395" t="s">
-        <v>2705</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>2744</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" t="s">
-        <v>2412</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" t="s">
-        <v>2416</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" t="s">
-        <v>2642</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>2564</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>2707</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>2781</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>2648</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>2630</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>2803</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="406" spans="1:1">
       <c r="A406" t="s">
-        <v>2382</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" t="s">
-        <v>2658</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" t="s">
-        <v>2683</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" t="s">
-        <v>2794</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" t="s">
-        <v>2509</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" t="s">
-        <v>2503</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" t="s">
-        <v>2428</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" t="s">
-        <v>2652</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" t="s">
-        <v>2695</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>2792</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>2554</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>2455</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>2605</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>2517</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>2451</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>2487</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>2404</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>2544</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>2555</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>2810</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>2763</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>2488</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>2634</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>2460</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>2818</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>2747</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>2800</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>2609</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>2528</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>2466</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>2591</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>2647</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>2478</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439" t="s">
-        <v>2322</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" t="s">
-        <v>2522</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="441" spans="1:1">
       <c r="A441" t="s">
-        <v>2482</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="442" spans="1:1">
       <c r="A442" t="s">
-        <v>2701</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="443" spans="1:1">
       <c r="A443" t="s">
-        <v>2473</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="444" spans="1:1">
       <c r="A444" t="s">
-        <v>2549</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445" t="s">
-        <v>2813</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="446" spans="1:1">
       <c r="A446" t="s">
-        <v>2567</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="447" spans="1:1">
       <c r="A447" t="s">
-        <v>2676</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" t="s">
-        <v>2483</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="449" spans="1:1">
       <c r="A449" t="s">
-        <v>2599</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="451" spans="1:1">
       <c r="A451" t="s">
-        <v>2775</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="452" spans="1:1">
       <c r="A452" t="s">
-        <v>2592</v>
+        <v>349</v>
       </c>
     </row>
     <row r="453" spans="1:1">
       <c r="A453" t="s">
-        <v>2785</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" t="s">
-        <v>2626</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="455" spans="1:1">
       <c r="A455" t="s">
-        <v>2380</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" t="s">
-        <v>2600</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="457" spans="1:1">
       <c r="A457" t="s">
-        <v>2819</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" t="s">
-        <v>2728</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="459" spans="1:1">
       <c r="A459" t="s">
-        <v>2489</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="460" spans="1:1">
       <c r="A460" t="s">
-        <v>2409</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="461" spans="1:1">
       <c r="A461" t="s">
-        <v>2693</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" t="s">
-        <v>2414</v>
-      </c>
-    </row>
-    <row r="463" spans="1:1">
-      <c r="A463" t="s">
-        <v>2692</v>
-      </c>
-    </row>
-    <row r="464" spans="1:1">
-      <c r="A464" t="s">
-        <v>2752</v>
-      </c>
-    </row>
-    <row r="465" spans="1:1">
-      <c r="A465" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="466" spans="1:1">
-      <c r="A466" t="s">
-        <v>2316</v>
-      </c>
-    </row>
-    <row r="467" spans="1:1">
-      <c r="A467" t="s">
-        <v>2622</v>
-      </c>
-    </row>
-    <row r="468" spans="1:1">
-      <c r="A468" t="s">
-        <v>2406</v>
-      </c>
-    </row>
-    <row r="469" spans="1:1">
-      <c r="A469" t="s">
-        <v>2641</v>
-      </c>
-    </row>
-    <row r="470" spans="1:1">
-      <c r="A470" t="s">
-        <v>2568</v>
-      </c>
-    </row>
-    <row r="471" spans="1:1">
-      <c r="A471" t="s">
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="472" spans="1:1">
-      <c r="A472" t="s">
-        <v>2682</v>
-      </c>
-    </row>
-    <row r="473" spans="1:1">
-      <c r="A473" t="s">
-        <v>2523</v>
-      </c>
-    </row>
-    <row r="474" spans="1:1">
-      <c r="A474" t="s">
-        <v>2645</v>
-      </c>
-    </row>
-    <row r="475" spans="1:1">
-      <c r="A475" t="s">
-        <v>2820</v>
-      </c>
-    </row>
-    <row r="476" spans="1:1">
-      <c r="A476" t="s">
-        <v>2697</v>
-      </c>
-    </row>
-    <row r="477" spans="1:1">
-      <c r="A477" t="s">
-        <v>2632</v>
-      </c>
-    </row>
-    <row r="478" spans="1:1">
-      <c r="A478" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="479" spans="1:1">
-      <c r="A479" t="s">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="480" spans="1:1">
-      <c r="A480" t="s">
-        <v>2802</v>
-      </c>
-    </row>
-    <row r="481" spans="1:1">
-      <c r="A481" t="s">
-        <v>2375</v>
-      </c>
-    </row>
-    <row r="482" spans="1:1">
-      <c r="A482" t="s">
-        <v>2621</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1">
-      <c r="A483" t="s">
-        <v>2604</v>
-      </c>
-    </row>
-    <row r="484" spans="1:1">
-      <c r="A484" t="s">
-        <v>2702</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1">
-      <c r="A485" t="s">
-        <v>2783</v>
-      </c>
-    </row>
-    <row r="486" spans="1:1">
-      <c r="A486" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="487" spans="1:1">
-      <c r="A487" t="s">
-        <v>2797</v>
-      </c>
-    </row>
-    <row r="488" spans="1:1">
-      <c r="A488" t="s">
-        <v>2767</v>
-      </c>
-    </row>
-    <row r="489" spans="1:1">
-      <c r="A489" t="s">
-        <v>2349</v>
-      </c>
-    </row>
-    <row r="490" spans="1:1">
-      <c r="A490" t="s">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="491" spans="1:1">
-      <c r="A491" t="s">
-        <v>2435</v>
-      </c>
-    </row>
-    <row r="492" spans="1:1">
-      <c r="A492" t="s">
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="493" spans="1:1">
-      <c r="A493" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="494" spans="1:1">
-      <c r="A494" t="s">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="495" spans="1:1">
-      <c r="A495" t="s">
-        <v>2328</v>
-      </c>
-    </row>
-    <row r="496" spans="1:1">
-      <c r="A496" t="s">
-        <v>2493</v>
-      </c>
-    </row>
-    <row r="497" spans="1:1">
-      <c r="A497" t="s">
-        <v>2685</v>
-      </c>
-    </row>
-    <row r="498" spans="1:1">
-      <c r="A498" t="s">
-        <v>2624</v>
-      </c>
-    </row>
-    <row r="499" spans="1:1">
-      <c r="A499" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="500" spans="1:1">
-      <c r="A500" t="s">
-        <v>2765</v>
-      </c>
-    </row>
-    <row r="501" spans="1:1">
-      <c r="A501" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="502" spans="1:1">
-      <c r="A502" t="s">
-        <v>2755</v>
-      </c>
-    </row>
-    <row r="503" spans="1:1">
-      <c r="A503" t="s">
-        <v>2485</v>
+        <v>2477</v>
       </c>
     </row>
   </sheetData>
@@ -11837,7 +11596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F878"/>
+  <dimension ref="A1:F889"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -12244,20 +12003,20 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>2906</v>
+        <v>2875</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2907</v>
+        <v>2876</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2908</v>
+        <v>2877</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="F25" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="1" customFormat="1">
@@ -12573,7 +12332,7 @@
     </row>
     <row r="44" spans="1:6" s="1" customFormat="1">
       <c r="A44" s="1" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>527</v>
@@ -12590,7 +12349,7 @@
     </row>
     <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
-        <v>2472</v>
+        <v>2464</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>565</v>
@@ -16437,7 +16196,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>2777</v>
+        <v>2749</v>
       </c>
       <c r="B260" t="s">
         <v>1021</v>
@@ -26397,13 +26156,13 @@
     </row>
     <row r="844" spans="1:6">
       <c r="A844" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="B844" t="s">
-        <v>2842</v>
+        <v>2811</v>
       </c>
       <c r="C844" t="s">
-        <v>2843</v>
+        <v>2812</v>
       </c>
       <c r="E844">
         <v>2001</v>
@@ -26414,13 +26173,13 @@
     </row>
     <row r="845" spans="1:6">
       <c r="A845" t="s">
-        <v>2845</v>
+        <v>2814</v>
       </c>
       <c r="B845" t="s">
-        <v>2844</v>
+        <v>2813</v>
       </c>
       <c r="C845" t="s">
-        <v>2846</v>
+        <v>2815</v>
       </c>
       <c r="E845">
         <v>2001</v>
@@ -26431,13 +26190,13 @@
     </row>
     <row r="846" spans="1:6">
       <c r="A846" t="s">
-        <v>2601</v>
+        <v>2582</v>
       </c>
       <c r="B846" t="s">
-        <v>2847</v>
+        <v>2816</v>
       </c>
       <c r="C846" t="s">
-        <v>2848</v>
+        <v>2817</v>
       </c>
       <c r="E846">
         <v>2012</v>
@@ -26448,13 +26207,13 @@
     </row>
     <row r="847" spans="1:6">
       <c r="A847" t="s">
-        <v>2804</v>
+        <v>2775</v>
       </c>
       <c r="B847" t="s">
-        <v>2849</v>
+        <v>2818</v>
       </c>
       <c r="C847" t="s">
-        <v>2804</v>
+        <v>2775</v>
       </c>
       <c r="E847">
         <v>2014</v>
@@ -26465,13 +26224,13 @@
     </row>
     <row r="848" spans="1:6">
       <c r="A848" t="s">
-        <v>2756</v>
+        <v>2730</v>
       </c>
       <c r="B848" t="s">
-        <v>2850</v>
+        <v>2819</v>
       </c>
       <c r="C848" t="s">
-        <v>2851</v>
+        <v>2820</v>
       </c>
       <c r="E848">
         <v>2018</v>
@@ -26482,13 +26241,13 @@
     </row>
     <row r="849" spans="1:6">
       <c r="A849" t="s">
-        <v>2787</v>
+        <v>2758</v>
       </c>
       <c r="B849" t="s">
-        <v>2852</v>
+        <v>2821</v>
       </c>
       <c r="C849" t="s">
-        <v>2853</v>
+        <v>2822</v>
       </c>
       <c r="E849">
         <v>2016</v>
@@ -26499,13 +26258,13 @@
     </row>
     <row r="850" spans="1:6">
       <c r="A850" t="s">
-        <v>2398</v>
+        <v>2393</v>
       </c>
       <c r="B850" t="s">
-        <v>2854</v>
+        <v>2823</v>
       </c>
       <c r="C850" s="10" t="s">
-        <v>2855</v>
+        <v>2824</v>
       </c>
       <c r="E850">
         <v>2005</v>
@@ -26516,13 +26275,13 @@
     </row>
     <row r="851" spans="1:6">
       <c r="A851" t="s">
-        <v>2462</v>
+        <v>2455</v>
       </c>
       <c r="B851" t="s">
-        <v>2856</v>
+        <v>2825</v>
       </c>
       <c r="C851" t="s">
-        <v>2857</v>
+        <v>2826</v>
       </c>
       <c r="E851">
         <v>2005</v>
@@ -26533,13 +26292,13 @@
     </row>
     <row r="852" spans="1:6">
       <c r="A852" t="s">
-        <v>2513</v>
+        <v>2503</v>
       </c>
       <c r="B852" t="s">
-        <v>2858</v>
+        <v>2827</v>
       </c>
       <c r="C852" t="s">
-        <v>2859</v>
+        <v>2828</v>
       </c>
       <c r="E852">
         <v>2006</v>
@@ -26550,13 +26309,13 @@
     </row>
     <row r="853" spans="1:6">
       <c r="A853" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="B853" t="s">
-        <v>2860</v>
+        <v>2829</v>
       </c>
       <c r="C853" t="s">
-        <v>2861</v>
+        <v>2830</v>
       </c>
       <c r="E853">
         <v>2002</v>
@@ -26567,13 +26326,13 @@
     </row>
     <row r="854" spans="1:6">
       <c r="A854" t="s">
-        <v>2795</v>
+        <v>2766</v>
       </c>
       <c r="B854" t="s">
-        <v>2862</v>
+        <v>2831</v>
       </c>
       <c r="C854" t="s">
-        <v>2863</v>
+        <v>2832</v>
       </c>
       <c r="E854">
         <v>2022</v>
@@ -26584,13 +26343,13 @@
     </row>
     <row r="855" spans="1:6">
       <c r="A855" t="s">
-        <v>2655</v>
+        <v>2635</v>
       </c>
       <c r="B855" t="s">
-        <v>2864</v>
+        <v>2833</v>
       </c>
       <c r="C855" t="s">
-        <v>2865</v>
+        <v>2834</v>
       </c>
       <c r="E855">
         <v>2019</v>
@@ -26601,13 +26360,13 @@
     </row>
     <row r="856" spans="1:6">
       <c r="A856" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="B856" t="s">
-        <v>2866</v>
+        <v>2835</v>
       </c>
       <c r="C856" t="s">
-        <v>2867</v>
+        <v>2836</v>
       </c>
       <c r="E856">
         <v>2000</v>
@@ -26618,13 +26377,13 @@
     </row>
     <row r="857" spans="1:6">
       <c r="A857" t="s">
-        <v>2560</v>
+        <v>2546</v>
       </c>
       <c r="B857" t="s">
-        <v>2868</v>
+        <v>2837</v>
       </c>
       <c r="C857" t="s">
-        <v>2869</v>
+        <v>2838</v>
       </c>
       <c r="E857">
         <v>2011</v>
@@ -26635,13 +26394,13 @@
     </row>
     <row r="858" spans="1:6">
       <c r="A858" t="s">
-        <v>2539</v>
+        <v>2528</v>
       </c>
       <c r="B858" t="s">
-        <v>2870</v>
+        <v>2839</v>
       </c>
       <c r="C858" t="s">
-        <v>2871</v>
+        <v>2840</v>
       </c>
       <c r="E858">
         <v>2005</v>
@@ -26652,13 +26411,13 @@
     </row>
     <row r="859" spans="1:6">
       <c r="A859" t="s">
-        <v>2495</v>
+        <v>2486</v>
       </c>
       <c r="B859" t="s">
-        <v>2872</v>
+        <v>2841</v>
       </c>
       <c r="C859" t="s">
-        <v>2872</v>
+        <v>2841</v>
       </c>
       <c r="E859">
         <v>1998</v>
@@ -26669,13 +26428,13 @@
     </row>
     <row r="860" spans="1:6">
       <c r="A860" t="s">
-        <v>2439</v>
+        <v>2432</v>
       </c>
       <c r="B860" t="s">
-        <v>2873</v>
+        <v>2842</v>
       </c>
       <c r="C860" t="s">
-        <v>2873</v>
+        <v>2842</v>
       </c>
       <c r="E860">
         <v>2003</v>
@@ -26686,13 +26445,13 @@
     </row>
     <row r="861" spans="1:6">
       <c r="A861" t="s">
-        <v>2490</v>
+        <v>2481</v>
       </c>
       <c r="B861" t="s">
-        <v>2874</v>
+        <v>2843</v>
       </c>
       <c r="C861" t="s">
-        <v>2875</v>
+        <v>2844</v>
       </c>
       <c r="E861">
         <v>2002</v>
@@ -26703,13 +26462,13 @@
     </row>
     <row r="862" spans="1:6">
       <c r="A862" t="s">
-        <v>2459</v>
+        <v>2452</v>
       </c>
       <c r="B862" t="s">
-        <v>2876</v>
+        <v>2845</v>
       </c>
       <c r="C862" t="s">
-        <v>2877</v>
+        <v>2846</v>
       </c>
       <c r="E862">
         <v>2001</v>
@@ -26720,13 +26479,13 @@
     </row>
     <row r="863" spans="1:6">
       <c r="A863" t="s">
-        <v>2636</v>
+        <v>2616</v>
       </c>
       <c r="B863" t="s">
-        <v>2878</v>
+        <v>2847</v>
       </c>
       <c r="C863" t="s">
-        <v>2878</v>
+        <v>2847</v>
       </c>
       <c r="E863">
         <v>2010</v>
@@ -26737,13 +26496,13 @@
     </row>
     <row r="864" spans="1:6">
       <c r="A864" t="s">
-        <v>2879</v>
+        <v>2848</v>
       </c>
       <c r="B864" t="s">
-        <v>2880</v>
+        <v>2849</v>
       </c>
       <c r="C864" t="s">
-        <v>2881</v>
+        <v>2850</v>
       </c>
       <c r="E864">
         <v>2013</v>
@@ -26754,13 +26513,13 @@
     </row>
     <row r="865" spans="1:6">
       <c r="A865" t="s">
-        <v>2816</v>
+        <v>2786</v>
       </c>
       <c r="B865" t="s">
-        <v>2882</v>
+        <v>2851</v>
       </c>
       <c r="C865" t="s">
-        <v>2882</v>
+        <v>2851</v>
       </c>
       <c r="E865">
         <v>2014</v>
@@ -26771,13 +26530,13 @@
     </row>
     <row r="866" spans="1:6">
       <c r="A866" t="s">
-        <v>2408</v>
+        <v>2403</v>
       </c>
       <c r="B866" t="s">
-        <v>2883</v>
+        <v>2852</v>
       </c>
       <c r="C866" t="s">
-        <v>2884</v>
+        <v>2853</v>
       </c>
       <c r="E866">
         <v>1989</v>
@@ -26788,13 +26547,13 @@
     </row>
     <row r="867" spans="1:6">
       <c r="A867" t="s">
-        <v>2553</v>
+        <v>2540</v>
       </c>
       <c r="B867" t="s">
-        <v>2885</v>
+        <v>2854</v>
       </c>
       <c r="C867" t="s">
-        <v>2886</v>
+        <v>2855</v>
       </c>
       <c r="E867">
         <v>2011</v>
@@ -26805,13 +26564,13 @@
     </row>
     <row r="868" spans="1:6">
       <c r="A868" t="s">
-        <v>2442</v>
+        <v>2435</v>
       </c>
       <c r="B868" t="s">
-        <v>2887</v>
+        <v>2856</v>
       </c>
       <c r="C868" t="s">
-        <v>2888</v>
+        <v>2857</v>
       </c>
       <c r="E868">
         <v>1995</v>
@@ -26822,13 +26581,13 @@
     </row>
     <row r="869" spans="1:6">
       <c r="A869" t="s">
-        <v>2762</v>
+        <v>2734</v>
       </c>
       <c r="B869" t="s">
-        <v>2889</v>
+        <v>2858</v>
       </c>
       <c r="C869" t="s">
-        <v>2890</v>
+        <v>2859</v>
       </c>
       <c r="E869">
         <v>2022</v>
@@ -26839,13 +26598,13 @@
     </row>
     <row r="870" spans="1:6">
       <c r="A870" t="s">
-        <v>2537</v>
+        <v>2526</v>
       </c>
       <c r="B870" t="s">
-        <v>2891</v>
+        <v>2860</v>
       </c>
       <c r="C870" t="s">
-        <v>2892</v>
+        <v>2861</v>
       </c>
       <c r="E870">
         <v>2009</v>
@@ -26856,13 +26615,13 @@
     </row>
     <row r="871" spans="1:6">
       <c r="A871" t="s">
-        <v>2501</v>
+        <v>2491</v>
       </c>
       <c r="B871" t="s">
-        <v>2893</v>
+        <v>2862</v>
       </c>
       <c r="C871" t="s">
-        <v>2893</v>
+        <v>2862</v>
       </c>
       <c r="E871">
         <v>2013</v>
@@ -26873,13 +26632,13 @@
     </row>
     <row r="872" spans="1:6">
       <c r="A872" t="s">
-        <v>2522</v>
+        <v>2512</v>
       </c>
       <c r="B872" t="s">
-        <v>2894</v>
+        <v>2863</v>
       </c>
       <c r="C872" t="s">
-        <v>2895</v>
+        <v>2864</v>
       </c>
       <c r="E872">
         <v>1987</v>
@@ -26890,13 +26649,13 @@
     </row>
     <row r="873" spans="1:6">
       <c r="A873" t="s">
-        <v>2396</v>
+        <v>2391</v>
       </c>
       <c r="B873" t="s">
-        <v>2896</v>
+        <v>2865</v>
       </c>
       <c r="C873" t="s">
-        <v>2897</v>
+        <v>2866</v>
       </c>
       <c r="E873">
         <v>2012</v>
@@ -26907,13 +26666,13 @@
     </row>
     <row r="874" spans="1:6">
       <c r="A874" t="s">
-        <v>2614</v>
+        <v>2594</v>
       </c>
       <c r="B874" t="s">
-        <v>2898</v>
+        <v>2867</v>
       </c>
       <c r="C874" t="s">
-        <v>2899</v>
+        <v>2868</v>
       </c>
       <c r="E874">
         <v>2013</v>
@@ -26924,13 +26683,13 @@
     </row>
     <row r="875" spans="1:6">
       <c r="A875" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="B875" t="s">
-        <v>2900</v>
+        <v>2869</v>
       </c>
       <c r="C875" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="E875">
         <v>2000</v>
@@ -26941,13 +26700,13 @@
     </row>
     <row r="876" spans="1:6">
       <c r="A876" t="s">
-        <v>2779</v>
+        <v>2751</v>
       </c>
       <c r="B876" t="s">
-        <v>2901</v>
+        <v>2870</v>
       </c>
       <c r="C876" t="s">
-        <v>2902</v>
+        <v>2871</v>
       </c>
       <c r="E876">
         <v>1970</v>
@@ -26958,13 +26717,13 @@
     </row>
     <row r="877" spans="1:6">
       <c r="A877" t="s">
-        <v>2536</v>
+        <v>2525</v>
       </c>
       <c r="B877" t="s">
-        <v>2903</v>
+        <v>2872</v>
       </c>
       <c r="C877" t="s">
-        <v>2903</v>
+        <v>2872</v>
       </c>
       <c r="E877">
         <v>2017</v>
@@ -26975,18 +26734,205 @@
     </row>
     <row r="878" spans="1:6">
       <c r="A878" t="s">
-        <v>2512</v>
+        <v>2502</v>
       </c>
       <c r="B878" t="s">
-        <v>2904</v>
+        <v>2873</v>
       </c>
       <c r="C878" t="s">
-        <v>2905</v>
+        <v>2874</v>
       </c>
       <c r="E878">
         <v>2017</v>
       </c>
       <c r="F878" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6">
+      <c r="A879" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C879" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E879">
+        <v>2004</v>
+      </c>
+      <c r="F879" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6">
+      <c r="A880" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B880" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C880" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E880">
+        <v>2015</v>
+      </c>
+      <c r="F880" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6">
+      <c r="A881" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C881" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E881">
+        <v>1999</v>
+      </c>
+      <c r="F881" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6">
+      <c r="A882" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B882" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C882" t="s">
+        <v>2882</v>
+      </c>
+      <c r="E882">
+        <v>2010</v>
+      </c>
+      <c r="F882" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6">
+      <c r="A883" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C883" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E883">
+        <v>2007</v>
+      </c>
+      <c r="F883" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6">
+      <c r="A884" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B884" t="s">
+        <v>2886</v>
+      </c>
+      <c r="C884" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E884">
+        <v>2003</v>
+      </c>
+      <c r="F884" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6">
+      <c r="A885" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B885" t="s">
+        <v>741</v>
+      </c>
+      <c r="C885" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E885">
+        <v>2009</v>
+      </c>
+      <c r="F885" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6">
+      <c r="A886" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B886" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C886" t="s">
+        <v>2890</v>
+      </c>
+      <c r="E886">
+        <v>1993</v>
+      </c>
+      <c r="F886" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6">
+      <c r="A887" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2891</v>
+      </c>
+      <c r="C887" t="s">
+        <v>2892</v>
+      </c>
+      <c r="E887">
+        <v>2015</v>
+      </c>
+      <c r="F887" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6">
+      <c r="A888" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B888" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C888" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E888">
+        <v>1978</v>
+      </c>
+      <c r="F888" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6">
+      <c r="A889" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C889" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E889">
+        <v>2010</v>
+      </c>
+      <c r="F889" t="s">
         <v>964</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0074F04A-DECB-7E45-954F-D0EBB2AF8B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CC48F0-308B-FB47-A9A2-A460E3D6DBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4069" uniqueCount="2897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="2882">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -7137,9 +7137,6 @@
     <t>Sinéad O’Connor</t>
   </si>
   <si>
-    <t>Garcia, Grisman &amp; Rice</t>
-  </si>
-  <si>
     <t>Jimmie Dale Gilmore</t>
   </si>
   <si>
@@ -7536,9 +7533,6 @@
     <t>Jackie Greene</t>
   </si>
   <si>
-    <t>Frank Black</t>
-  </si>
-  <si>
     <t>Josh Rose</t>
   </si>
   <si>
@@ -7716,9 +7710,6 @@
     <t>Grizzly Bear</t>
   </si>
   <si>
-    <t>Felice Brothers</t>
-  </si>
-  <si>
     <t>Heartless Bastards</t>
   </si>
   <si>
@@ -7743,9 +7734,6 @@
     <t>Robert Plant</t>
   </si>
   <si>
-    <t>Fistful of Mercy</t>
-  </si>
-  <si>
     <t>The Gaslight Anthem</t>
   </si>
   <si>
@@ -7779,9 +7767,6 @@
     <t>The Head &amp; The Heart</t>
   </si>
   <si>
-    <t>Garland Jeffreys</t>
-  </si>
-  <si>
     <t>Mayer Hawthorne</t>
   </si>
   <si>
@@ -7794,9 +7779,6 @@
     <t>tUnE‑yArDs</t>
   </si>
   <si>
-    <t>Florence and the Machine</t>
-  </si>
-  <si>
     <t>Nicole Atkins</t>
   </si>
   <si>
@@ -7833,12 +7815,6 @@
     <t>Jack White</t>
   </si>
   <si>
-    <t>Gary Clark Jr.</t>
-  </si>
-  <si>
-    <t>Father John Misty</t>
-  </si>
-  <si>
     <t>Sharon Van Etten</t>
   </si>
   <si>
@@ -7875,9 +7851,6 @@
     <t>The Walkmen</t>
   </si>
   <si>
-    <t>Frank Ocean</t>
-  </si>
-  <si>
     <t>Glen Hansard</t>
   </si>
   <si>
@@ -7938,9 +7911,6 @@
     <t>Minor Alps</t>
   </si>
   <si>
-    <t>Franz Ferdinand</t>
-  </si>
-  <si>
     <t>Okkervil River</t>
   </si>
   <si>
@@ -8010,9 +7980,6 @@
     <t>Lake Street Dive</t>
   </si>
   <si>
-    <t>Field Report</t>
-  </si>
-  <si>
     <t>Trigger Hippy</t>
   </si>
   <si>
@@ -8085,9 +8052,6 @@
     <t>Glass Animals</t>
   </si>
   <si>
-    <t>FKA Twigs</t>
-  </si>
-  <si>
     <t>Perfume Genius</t>
   </si>
   <si>
@@ -8178,15 +8142,9 @@
     <t>Unknown Mortal Orchestra</t>
   </si>
   <si>
-    <t>FFS</t>
-  </si>
-  <si>
     <t>Jarryd James</t>
   </si>
   <si>
-    <t>G. Love &amp; Special Sauce</t>
-  </si>
-  <si>
     <t>The Record Company</t>
   </si>
   <si>
@@ -8262,12 +8220,6 @@
     <t>This Is The Kit</t>
   </si>
   <si>
-    <t>Francis &amp; The Lights (feat. Chance the Rapper)</t>
-  </si>
-  <si>
-    <t>Flo Morrissey &amp; Matthew E. White</t>
-  </si>
-  <si>
     <t>Phoebe Bridgers</t>
   </si>
   <si>
@@ -8451,9 +8403,6 @@
     <t>beabadoobee</t>
   </si>
   <si>
-    <t>Fontaines D.C.</t>
-  </si>
-  <si>
     <t>Wet Leg</t>
   </si>
   <si>
@@ -8481,9 +8430,6 @@
     <t>Plains</t>
   </si>
   <si>
-    <t>Foals</t>
-  </si>
-  <si>
     <t>Nikki Lane</t>
   </si>
   <si>
@@ -8556,18 +8502,9 @@
     <t>Gigi Perez</t>
   </si>
   <si>
-    <t>Fantastic Cat</t>
-  </si>
-  <si>
     <t>Infinity Song</t>
   </si>
   <si>
-    <t>Faye Webster</t>
-  </si>
-  <si>
-    <t>Finneas</t>
-  </si>
-  <si>
     <t>Sierra Ferrell</t>
   </si>
   <si>
@@ -8839,6 +8776,24 @@
   </si>
   <si>
     <t>Quarter Moon in a Ten Cent Town</t>
+  </si>
+  <si>
+    <t>Stacy's Mom</t>
+  </si>
+  <si>
+    <t>Welcome Interstate Managers</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>We Are the 21st Century Ambassadors of Peace &amp; Magic</t>
+  </si>
+  <si>
+    <t>Bad Reputation</t>
+  </si>
+  <si>
+    <t>The Perfect World</t>
   </si>
 </sst>
 </file>
@@ -9271,7 +9226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="A1:A462"/>
+  <dimension ref="A1:A438"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -9280,2312 +9235,2192 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2802</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>2562</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>2804</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>2522</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>2676</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>2620</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>2805</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>2531</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>2645</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>2705</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>2548</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>2777</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>2767</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>2424</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>2608</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>2704</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>2462</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>2575</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>2596</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>2360</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2678</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2329</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>2543</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>2561</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>2487</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>2801</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>2339</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>2644</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>2576</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>2024</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>2485</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>2395</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>2577</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>2418</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>2492</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>2567</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>2369</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>2321</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>2674</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>2700</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>2521</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>2750</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>2590</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>2687</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>2523</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>2731</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>2696</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>2578</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>2648</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>2618</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>2708</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>2538</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>2795</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>2387</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>2803</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>2524</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>2569</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>2497</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>2639</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>2384</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>2617</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>2733</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>2371</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>2560</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>2461</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>2716</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>2483</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>2613</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>2536</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>2555</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>2472</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>2539</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>2514</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>2441</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>2652</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>2714</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>2332</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>2677</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>2650</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>2357</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>2565</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>2723</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>2342</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>2552</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>2653</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>2707</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>2451</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>2510</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>2583</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>2642</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>2740</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>2443</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>2693</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>2330</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>2381</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>2377</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>2807</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>2354</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>2490</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>2489</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>2586</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>2350</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>2593</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>2345</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>2315</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>2458</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>2375</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>2808</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>2796</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>2374</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>2388</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>2504</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>2686</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>2446</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>2431</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>2463</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>2411</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>2427</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>2636</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>2319</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>2719</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>2390</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>2433</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>2761</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>2655</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>2412</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>2672</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>2416</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>2710</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>2760</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>2396</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>2417</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>2340</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>2473</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>2599</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>2619</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>2641</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>2669</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>2787</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>2556</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>2600</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>2748</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>2533</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>2419</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>2649</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>2361</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>2517</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>2667</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>2495</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>2397</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>2535</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>2592</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>2752</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>2732</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>2702</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>2692</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>2666</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>2440</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>2389</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>2363</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>2346</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>2605</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>2720</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>2336</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>2688</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>2725</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>2341</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>2367</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>2701</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>2420</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>2434</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>2520</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>2634</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>2442</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>2665</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>2741</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>2695</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>2467</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>2591</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>2712</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>2324</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>2784</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>2681</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>2699</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>2323</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>2471</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>2651</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>2659</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>2317</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>2325</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>2454</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>2415</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>2466</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>2764</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>2657</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>2744</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>2534</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>2428</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>2505</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>2809</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>2544</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>2570</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>2379</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>2564</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>2559</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>2709</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>2460</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>2450</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>2595</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>2715</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>2797</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>2400</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>2383</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>2785</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>2713</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>2519</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>2558</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>2611</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>2757</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>2529</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>2781</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>2353</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>2347</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>2727</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>2754</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>2386</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>2413</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>2439</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>2398</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>2607</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>2358</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>2469</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>2549</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>2778</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>2742</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>1031</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>2320</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>2579</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>2597</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>2368</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>2571</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>2447</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>2365</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>2496</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>2736</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>2772</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>2800</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>2633</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>2385</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>2334</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>2359</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" t="s">
-        <v>2405</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>2646</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>2394</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>2488</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>2626</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>2406</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>2706</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>2588</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>2643</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>2689</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>2776</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>2572</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>2746</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>2331</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>2694</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>2445</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>2511</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>2515</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>2664</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>2343</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>2456</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>2438</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>2791</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>2717</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>2624</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>2476</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>2724</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>2792</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>2598</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>2314</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>2351</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>2409</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>2449</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>2494</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>2551</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>2362</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>2530</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>2414</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>2366</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>2745</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>2566</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>2762</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" t="s">
-        <v>2373</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" t="s">
-        <v>2430</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" t="s">
-        <v>2799</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" t="s">
-        <v>2338</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" t="s">
-        <v>2335</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" t="s">
-        <v>2501</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" t="s">
-        <v>2545</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" t="s">
-        <v>2684</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>2662</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>2356</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>2623</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" t="s">
-        <v>2793</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" t="s">
-        <v>2810</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" t="s">
-        <v>2609</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>2421</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" t="s">
-        <v>2690</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" t="s">
-        <v>2782</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" t="s">
-        <v>2779</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" t="s">
-        <v>2506</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" t="s">
-        <v>2656</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>2682</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>2794</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" t="s">
-        <v>2382</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" t="s">
-        <v>2500</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" t="s">
-        <v>2563</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>2423</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>2344</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>2482</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>2516</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" t="s">
-        <v>2310</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" t="s">
-        <v>2568</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" t="s">
-        <v>2468</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" t="s">
-        <v>2806</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" t="s">
-        <v>2312</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" t="s">
-        <v>2668</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" t="s">
-        <v>2711</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" t="s">
-        <v>2722</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>2743</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>2728</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>2698</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>2392</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" t="s">
-        <v>2637</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" t="s">
-        <v>2759</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340" t="s">
-        <v>2402</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>2629</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>2557</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" t="s">
-        <v>1912</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" t="s">
-        <v>2437</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345" t="s">
-        <v>2647</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>2769</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>2313</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" t="s">
-        <v>2333</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" t="s">
-        <v>2770</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" t="s">
-        <v>2426</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="351" spans="1:1">
       <c r="A351" t="s">
-        <v>2630</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" t="s">
-        <v>2697</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" t="s">
-        <v>2798</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="354" spans="1:1">
       <c r="A354" t="s">
-        <v>2683</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" t="s">
-        <v>2718</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" t="s">
-        <v>2407</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>2410</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" t="s">
-        <v>2622</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="359" spans="1:1">
       <c r="A359" t="s">
-        <v>2550</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" t="s">
-        <v>2685</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="361" spans="1:1">
       <c r="A361" t="s">
-        <v>2753</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" t="s">
-        <v>2628</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" t="s">
-        <v>2610</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" t="s">
-        <v>2774</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="365" spans="1:1">
       <c r="A365" t="s">
-        <v>2378</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" t="s">
-        <v>2638</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" t="s">
-        <v>2661</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>2765</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>2499</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" t="s">
-        <v>2493</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" t="s">
-        <v>2422</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" t="s">
-        <v>2632</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>2673</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" t="s">
-        <v>2763</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>2541</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" t="s">
-        <v>2448</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" t="s">
-        <v>2585</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" t="s">
-        <v>2507</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" t="s">
-        <v>2444</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" t="s">
-        <v>2478</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" t="s">
-        <v>2399</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>2532</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>2542</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384" t="s">
-        <v>2780</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" t="s">
-        <v>2735</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" t="s">
-        <v>2479</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>2614</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>2453</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>2788</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>2721</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" t="s">
-        <v>2771</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" t="s">
-        <v>2589</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" t="s">
-        <v>2518</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" t="s">
-        <v>2459</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="395" spans="1:1">
       <c r="A395" t="s">
-        <v>2573</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>2627</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" t="s">
-        <v>2470</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" t="s">
-        <v>2322</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" t="s">
-        <v>2512</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>2474</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>2679</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>2465</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>2537</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>2783</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="406" spans="1:1">
       <c r="A406" t="s">
-        <v>2654</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" t="s">
-        <v>2475</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" t="s">
-        <v>2580</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" t="s">
-        <v>2425</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" t="s">
-        <v>2747</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" t="s">
-        <v>2574</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" t="s">
-        <v>2756</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" t="s">
-        <v>2606</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" t="s">
-        <v>2376</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>2581</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>2789</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>2703</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>2480</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>2404</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>2671</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>2408</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>2670</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>2726</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>2276</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>2316</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>2602</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>2401</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>2621</v>
+        <v>349</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>2554</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>2547</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>2660</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>2513</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>2625</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>2790</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>2675</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>2612</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>2508</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>2337</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" t="s">
-        <v>2773</v>
-      </c>
-    </row>
-    <row r="440" spans="1:1">
-      <c r="A440" t="s">
-        <v>2372</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1">
-      <c r="A441" t="s">
-        <v>2601</v>
-      </c>
-    </row>
-    <row r="442" spans="1:1">
-      <c r="A442" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="443" spans="1:1">
-      <c r="A443" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="444" spans="1:1">
-      <c r="A444" t="s">
-        <v>2755</v>
-      </c>
-    </row>
-    <row r="445" spans="1:1">
-      <c r="A445" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="446" spans="1:1">
-      <c r="A446" t="s">
-        <v>2768</v>
-      </c>
-    </row>
-    <row r="447" spans="1:1">
-      <c r="A447" t="s">
-        <v>2739</v>
-      </c>
-    </row>
-    <row r="448" spans="1:1">
-      <c r="A448" t="s">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="449" spans="1:1">
-      <c r="A449" t="s">
-        <v>2738</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1">
-      <c r="A450" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1">
-      <c r="A451" t="s">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1">
-      <c r="A452" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="453" spans="1:1">
-      <c r="A453" t="s">
-        <v>2615</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1">
-      <c r="A454" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="455" spans="1:1">
-      <c r="A455" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="456" spans="1:1">
-      <c r="A456" t="s">
-        <v>2663</v>
-      </c>
-    </row>
-    <row r="457" spans="1:1">
-      <c r="A457" t="s">
-        <v>2604</v>
-      </c>
-    </row>
-    <row r="458" spans="1:1">
-      <c r="A458" t="s">
-        <v>2691</v>
-      </c>
-    </row>
-    <row r="459" spans="1:1">
-      <c r="A459" t="s">
-        <v>2737</v>
-      </c>
-    </row>
-    <row r="460" spans="1:1">
-      <c r="A460" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="461" spans="1:1">
-      <c r="A461" t="s">
-        <v>2729</v>
-      </c>
-    </row>
-    <row r="462" spans="1:1">
-      <c r="A462" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
     </row>
   </sheetData>
@@ -11596,7 +11431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F889"/>
+  <dimension ref="A1:F892"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -12003,13 +11838,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>2875</v>
+        <v>2854</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2876</v>
+        <v>2855</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2877</v>
+        <v>2856</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1">
@@ -12349,7 +12184,7 @@
     </row>
     <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>565</v>
@@ -16196,7 +16031,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>2749</v>
+        <v>2733</v>
       </c>
       <c r="B260" t="s">
         <v>1021</v>
@@ -26156,13 +25991,13 @@
     </row>
     <row r="844" spans="1:6">
       <c r="A844" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="B844" t="s">
-        <v>2811</v>
+        <v>2790</v>
       </c>
       <c r="C844" t="s">
-        <v>2812</v>
+        <v>2791</v>
       </c>
       <c r="E844">
         <v>2001</v>
@@ -26173,13 +26008,13 @@
     </row>
     <row r="845" spans="1:6">
       <c r="A845" t="s">
-        <v>2814</v>
+        <v>2793</v>
       </c>
       <c r="B845" t="s">
-        <v>2813</v>
+        <v>2792</v>
       </c>
       <c r="C845" t="s">
-        <v>2815</v>
+        <v>2794</v>
       </c>
       <c r="E845">
         <v>2001</v>
@@ -26190,13 +26025,13 @@
     </row>
     <row r="846" spans="1:6">
       <c r="A846" t="s">
-        <v>2582</v>
+        <v>2573</v>
       </c>
       <c r="B846" t="s">
-        <v>2816</v>
+        <v>2795</v>
       </c>
       <c r="C846" t="s">
-        <v>2817</v>
+        <v>2796</v>
       </c>
       <c r="E846">
         <v>2012</v>
@@ -26207,13 +26042,13 @@
     </row>
     <row r="847" spans="1:6">
       <c r="A847" t="s">
-        <v>2775</v>
+        <v>2758</v>
       </c>
       <c r="B847" t="s">
-        <v>2818</v>
+        <v>2797</v>
       </c>
       <c r="C847" t="s">
-        <v>2775</v>
+        <v>2758</v>
       </c>
       <c r="E847">
         <v>2014</v>
@@ -26224,13 +26059,13 @@
     </row>
     <row r="848" spans="1:6">
       <c r="A848" t="s">
-        <v>2730</v>
+        <v>2714</v>
       </c>
       <c r="B848" t="s">
-        <v>2819</v>
+        <v>2798</v>
       </c>
       <c r="C848" t="s">
-        <v>2820</v>
+        <v>2799</v>
       </c>
       <c r="E848">
         <v>2018</v>
@@ -26241,13 +26076,13 @@
     </row>
     <row r="849" spans="1:6">
       <c r="A849" t="s">
-        <v>2758</v>
+        <v>2742</v>
       </c>
       <c r="B849" t="s">
-        <v>2821</v>
+        <v>2800</v>
       </c>
       <c r="C849" t="s">
-        <v>2822</v>
+        <v>2801</v>
       </c>
       <c r="E849">
         <v>2016</v>
@@ -26258,13 +26093,13 @@
     </row>
     <row r="850" spans="1:6">
       <c r="A850" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="B850" t="s">
-        <v>2823</v>
+        <v>2802</v>
       </c>
       <c r="C850" s="10" t="s">
-        <v>2824</v>
+        <v>2803</v>
       </c>
       <c r="E850">
         <v>2005</v>
@@ -26275,13 +26110,13 @@
     </row>
     <row r="851" spans="1:6">
       <c r="A851" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B851" t="s">
-        <v>2825</v>
+        <v>2804</v>
       </c>
       <c r="C851" t="s">
-        <v>2826</v>
+        <v>2805</v>
       </c>
       <c r="E851">
         <v>2005</v>
@@ -26292,13 +26127,13 @@
     </row>
     <row r="852" spans="1:6">
       <c r="A852" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B852" t="s">
-        <v>2827</v>
+        <v>2806</v>
       </c>
       <c r="C852" t="s">
-        <v>2828</v>
+        <v>2807</v>
       </c>
       <c r="E852">
         <v>2006</v>
@@ -26309,13 +26144,13 @@
     </row>
     <row r="853" spans="1:6">
       <c r="A853" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="B853" t="s">
-        <v>2829</v>
+        <v>2808</v>
       </c>
       <c r="C853" t="s">
-        <v>2830</v>
+        <v>2809</v>
       </c>
       <c r="E853">
         <v>2002</v>
@@ -26326,13 +26161,13 @@
     </row>
     <row r="854" spans="1:6">
       <c r="A854" t="s">
-        <v>2766</v>
+        <v>2750</v>
       </c>
       <c r="B854" t="s">
-        <v>2831</v>
+        <v>2810</v>
       </c>
       <c r="C854" t="s">
-        <v>2832</v>
+        <v>2811</v>
       </c>
       <c r="E854">
         <v>2022</v>
@@ -26343,13 +26178,13 @@
     </row>
     <row r="855" spans="1:6">
       <c r="A855" t="s">
-        <v>2635</v>
+        <v>2624</v>
       </c>
       <c r="B855" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C855" t="s">
-        <v>2834</v>
+        <v>2813</v>
       </c>
       <c r="E855">
         <v>2019</v>
@@ -26363,10 +26198,10 @@
         <v>2326</v>
       </c>
       <c r="B856" t="s">
-        <v>2835</v>
+        <v>2814</v>
       </c>
       <c r="C856" t="s">
-        <v>2836</v>
+        <v>2815</v>
       </c>
       <c r="E856">
         <v>2000</v>
@@ -26377,13 +26212,13 @@
     </row>
     <row r="857" spans="1:6">
       <c r="A857" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="B857" t="s">
-        <v>2837</v>
+        <v>2816</v>
       </c>
       <c r="C857" t="s">
-        <v>2838</v>
+        <v>2817</v>
       </c>
       <c r="E857">
         <v>2011</v>
@@ -26394,13 +26229,13 @@
     </row>
     <row r="858" spans="1:6">
       <c r="A858" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="B858" t="s">
-        <v>2839</v>
+        <v>2818</v>
       </c>
       <c r="C858" t="s">
-        <v>2840</v>
+        <v>2819</v>
       </c>
       <c r="E858">
         <v>2005</v>
@@ -26411,13 +26246,13 @@
     </row>
     <row r="859" spans="1:6">
       <c r="A859" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="B859" t="s">
-        <v>2841</v>
+        <v>2820</v>
       </c>
       <c r="C859" t="s">
-        <v>2841</v>
+        <v>2820</v>
       </c>
       <c r="E859">
         <v>1998</v>
@@ -26428,13 +26263,13 @@
     </row>
     <row r="860" spans="1:6">
       <c r="A860" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B860" t="s">
-        <v>2842</v>
+        <v>2821</v>
       </c>
       <c r="C860" t="s">
-        <v>2842</v>
+        <v>2821</v>
       </c>
       <c r="E860">
         <v>2003</v>
@@ -26445,13 +26280,13 @@
     </row>
     <row r="861" spans="1:6">
       <c r="A861" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="B861" t="s">
-        <v>2843</v>
+        <v>2822</v>
       </c>
       <c r="C861" t="s">
-        <v>2844</v>
+        <v>2823</v>
       </c>
       <c r="E861">
         <v>2002</v>
@@ -26462,13 +26297,13 @@
     </row>
     <row r="862" spans="1:6">
       <c r="A862" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="B862" t="s">
-        <v>2845</v>
+        <v>2824</v>
       </c>
       <c r="C862" t="s">
-        <v>2846</v>
+        <v>2825</v>
       </c>
       <c r="E862">
         <v>2001</v>
@@ -26479,13 +26314,13 @@
     </row>
     <row r="863" spans="1:6">
       <c r="A863" t="s">
-        <v>2616</v>
+        <v>2606</v>
       </c>
       <c r="B863" t="s">
-        <v>2847</v>
+        <v>2826</v>
       </c>
       <c r="C863" t="s">
-        <v>2847</v>
+        <v>2826</v>
       </c>
       <c r="E863">
         <v>2010</v>
@@ -26496,13 +26331,13 @@
     </row>
     <row r="864" spans="1:6">
       <c r="A864" t="s">
-        <v>2848</v>
+        <v>2827</v>
       </c>
       <c r="B864" t="s">
-        <v>2849</v>
+        <v>2828</v>
       </c>
       <c r="C864" t="s">
-        <v>2850</v>
+        <v>2829</v>
       </c>
       <c r="E864">
         <v>2013</v>
@@ -26513,13 +26348,13 @@
     </row>
     <row r="865" spans="1:6">
       <c r="A865" t="s">
-        <v>2786</v>
+        <v>2768</v>
       </c>
       <c r="B865" t="s">
-        <v>2851</v>
+        <v>2830</v>
       </c>
       <c r="C865" t="s">
-        <v>2851</v>
+        <v>2830</v>
       </c>
       <c r="E865">
         <v>2014</v>
@@ -26530,13 +26365,13 @@
     </row>
     <row r="866" spans="1:6">
       <c r="A866" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="B866" t="s">
-        <v>2852</v>
+        <v>2831</v>
       </c>
       <c r="C866" t="s">
-        <v>2853</v>
+        <v>2832</v>
       </c>
       <c r="E866">
         <v>1989</v>
@@ -26547,13 +26382,13 @@
     </row>
     <row r="867" spans="1:6">
       <c r="A867" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B867" t="s">
-        <v>2854</v>
+        <v>2833</v>
       </c>
       <c r="C867" t="s">
-        <v>2855</v>
+        <v>2834</v>
       </c>
       <c r="E867">
         <v>2011</v>
@@ -26564,13 +26399,13 @@
     </row>
     <row r="868" spans="1:6">
       <c r="A868" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="B868" t="s">
-        <v>2856</v>
+        <v>2835</v>
       </c>
       <c r="C868" t="s">
-        <v>2857</v>
+        <v>2836</v>
       </c>
       <c r="E868">
         <v>1995</v>
@@ -26581,13 +26416,13 @@
     </row>
     <row r="869" spans="1:6">
       <c r="A869" t="s">
-        <v>2734</v>
+        <v>2718</v>
       </c>
       <c r="B869" t="s">
-        <v>2858</v>
+        <v>2837</v>
       </c>
       <c r="C869" t="s">
-        <v>2859</v>
+        <v>2838</v>
       </c>
       <c r="E869">
         <v>2022</v>
@@ -26598,13 +26433,13 @@
     </row>
     <row r="870" spans="1:6">
       <c r="A870" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="B870" t="s">
-        <v>2860</v>
+        <v>2839</v>
       </c>
       <c r="C870" t="s">
-        <v>2861</v>
+        <v>2840</v>
       </c>
       <c r="E870">
         <v>2009</v>
@@ -26615,13 +26450,13 @@
     </row>
     <row r="871" spans="1:6">
       <c r="A871" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="B871" t="s">
-        <v>2862</v>
+        <v>2841</v>
       </c>
       <c r="C871" t="s">
-        <v>2862</v>
+        <v>2841</v>
       </c>
       <c r="E871">
         <v>2013</v>
@@ -26632,13 +26467,13 @@
     </row>
     <row r="872" spans="1:6">
       <c r="A872" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="B872" t="s">
-        <v>2863</v>
+        <v>2842</v>
       </c>
       <c r="C872" t="s">
-        <v>2864</v>
+        <v>2843</v>
       </c>
       <c r="E872">
         <v>1987</v>
@@ -26649,13 +26484,13 @@
     </row>
     <row r="873" spans="1:6">
       <c r="A873" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="B873" t="s">
-        <v>2865</v>
+        <v>2844</v>
       </c>
       <c r="C873" t="s">
-        <v>2866</v>
+        <v>2845</v>
       </c>
       <c r="E873">
         <v>2012</v>
@@ -26666,13 +26501,13 @@
     </row>
     <row r="874" spans="1:6">
       <c r="A874" t="s">
-        <v>2594</v>
+        <v>2585</v>
       </c>
       <c r="B874" t="s">
-        <v>2867</v>
+        <v>2846</v>
       </c>
       <c r="C874" t="s">
-        <v>2868</v>
+        <v>2847</v>
       </c>
       <c r="E874">
         <v>2013</v>
@@ -26683,13 +26518,13 @@
     </row>
     <row r="875" spans="1:6">
       <c r="A875" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B875" t="s">
-        <v>2869</v>
+        <v>2848</v>
       </c>
       <c r="C875" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="E875">
         <v>2000</v>
@@ -26700,13 +26535,13 @@
     </row>
     <row r="876" spans="1:6">
       <c r="A876" t="s">
-        <v>2751</v>
+        <v>2735</v>
       </c>
       <c r="B876" t="s">
-        <v>2870</v>
+        <v>2849</v>
       </c>
       <c r="C876" t="s">
-        <v>2871</v>
+        <v>2850</v>
       </c>
       <c r="E876">
         <v>1970</v>
@@ -26717,13 +26552,13 @@
     </row>
     <row r="877" spans="1:6">
       <c r="A877" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="B877" t="s">
-        <v>2872</v>
+        <v>2851</v>
       </c>
       <c r="C877" t="s">
-        <v>2872</v>
+        <v>2851</v>
       </c>
       <c r="E877">
         <v>2017</v>
@@ -26734,13 +26569,13 @@
     </row>
     <row r="878" spans="1:6">
       <c r="A878" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="B878" t="s">
-        <v>2873</v>
+        <v>2852</v>
       </c>
       <c r="C878" t="s">
-        <v>2874</v>
+        <v>2853</v>
       </c>
       <c r="E878">
         <v>2017</v>
@@ -26751,13 +26586,13 @@
     </row>
     <row r="879" spans="1:6">
       <c r="A879" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B879" t="s">
-        <v>2878</v>
+        <v>2857</v>
       </c>
       <c r="C879" t="s">
-        <v>2879</v>
+        <v>2858</v>
       </c>
       <c r="E879">
         <v>2004</v>
@@ -26768,13 +26603,13 @@
     </row>
     <row r="880" spans="1:6">
       <c r="A880" t="s">
-        <v>2658</v>
+        <v>2646</v>
       </c>
       <c r="B880" t="s">
-        <v>2880</v>
+        <v>2859</v>
       </c>
       <c r="C880" t="s">
-        <v>2880</v>
+        <v>2859</v>
       </c>
       <c r="E880">
         <v>2015</v>
@@ -26785,10 +26620,10 @@
     </row>
     <row r="881" spans="1:6">
       <c r="A881" t="s">
-        <v>2763</v>
+        <v>2747</v>
       </c>
       <c r="B881" t="s">
-        <v>2881</v>
+        <v>2860</v>
       </c>
       <c r="C881" t="s">
         <v>1331</v>
@@ -26802,13 +26637,13 @@
     </row>
     <row r="882" spans="1:6">
       <c r="A882" t="s">
-        <v>2587</v>
+        <v>2578</v>
       </c>
       <c r="B882" t="s">
-        <v>2883</v>
+        <v>2862</v>
       </c>
       <c r="C882" t="s">
-        <v>2882</v>
+        <v>2861</v>
       </c>
       <c r="E882">
         <v>2010</v>
@@ -26819,13 +26654,13 @@
     </row>
     <row r="883" spans="1:6">
       <c r="A883" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B883" t="s">
-        <v>2884</v>
+        <v>2863</v>
       </c>
       <c r="C883" t="s">
-        <v>2885</v>
+        <v>2864</v>
       </c>
       <c r="E883">
         <v>2007</v>
@@ -26836,13 +26671,13 @@
     </row>
     <row r="884" spans="1:6">
       <c r="A884" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B884" t="s">
-        <v>2886</v>
+        <v>2865</v>
       </c>
       <c r="C884" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="E884">
         <v>2003</v>
@@ -26853,13 +26688,13 @@
     </row>
     <row r="885" spans="1:6">
       <c r="A885" t="s">
-        <v>2603</v>
+        <v>2593</v>
       </c>
       <c r="B885" t="s">
         <v>741</v>
       </c>
       <c r="C885" t="s">
-        <v>2887</v>
+        <v>2866</v>
       </c>
       <c r="E885">
         <v>2009</v>
@@ -26870,13 +26705,13 @@
     </row>
     <row r="886" spans="1:6">
       <c r="A886" t="s">
-        <v>2888</v>
+        <v>2867</v>
       </c>
       <c r="B886" t="s">
-        <v>2889</v>
+        <v>2868</v>
       </c>
       <c r="C886" t="s">
-        <v>2890</v>
+        <v>2869</v>
       </c>
       <c r="E886">
         <v>1993</v>
@@ -26887,13 +26722,13 @@
     </row>
     <row r="887" spans="1:6">
       <c r="A887" t="s">
-        <v>2631</v>
+        <v>2620</v>
       </c>
       <c r="B887" t="s">
-        <v>2891</v>
+        <v>2870</v>
       </c>
       <c r="C887" t="s">
-        <v>2892</v>
+        <v>2871</v>
       </c>
       <c r="E887">
         <v>2015</v>
@@ -26907,10 +26742,10 @@
         <v>2311</v>
       </c>
       <c r="B888" t="s">
-        <v>2893</v>
+        <v>2872</v>
       </c>
       <c r="C888" t="s">
-        <v>2896</v>
+        <v>2875</v>
       </c>
       <c r="E888">
         <v>1978</v>
@@ -26921,18 +26756,69 @@
     </row>
     <row r="889" spans="1:6">
       <c r="A889" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="B889" t="s">
-        <v>2894</v>
+        <v>2873</v>
       </c>
       <c r="C889" t="s">
-        <v>2895</v>
+        <v>2874</v>
       </c>
       <c r="E889">
         <v>2010</v>
       </c>
       <c r="F889" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6">
+      <c r="A890" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B890" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C890" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E890">
+        <v>2003</v>
+      </c>
+      <c r="F890" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6">
+      <c r="A891" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B891" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C891" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E891">
+        <v>2013</v>
+      </c>
+      <c r="F891" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6">
+      <c r="A892" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B892" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C892" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E892">
+        <v>1994</v>
+      </c>
+      <c r="F892" t="s">
         <v>964</v>
       </c>
     </row>

--- a/PlayLists.xlsx
+++ b/PlayLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian.mcgrath/onlineradio_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A69C42-50EB-164D-84BA-D3EBAE893E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ACC126-6467-C647-825C-0B3126D9A8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="34380" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="26" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$877</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Music Media Type'!$A$1:$F$859</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="2829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="2778">
   <si>
     <t>Elvis Presley</t>
   </si>
@@ -6771,9 +6771,6 @@
     <t>Marvin Pontiac</t>
   </si>
   <si>
-    <t>Bebel Gilberto</t>
-  </si>
-  <si>
     <t>Willie Nelson</t>
   </si>
   <si>
@@ -6843,9 +6840,6 @@
     <t>Richard Thompson</t>
   </si>
   <si>
-    <t>Cousteau</t>
-  </si>
-  <si>
     <t>Nanci Griffith</t>
   </si>
   <si>
@@ -6957,9 +6951,6 @@
     <t>Kasey Chambers</t>
   </si>
   <si>
-    <t>Chuck Prophet</t>
-  </si>
-  <si>
     <t>Solomon Burke</t>
   </si>
   <si>
@@ -6990,9 +6981,6 @@
     <t>Spoon</t>
   </si>
   <si>
-    <t>Bonnie Raitt</t>
-  </si>
-  <si>
     <t>Tift Merritt</t>
   </si>
   <si>
@@ -7086,12 +7074,6 @@
     <t>Lyle Lovett</t>
   </si>
   <si>
-    <t>Bruce Cockburn</t>
-  </si>
-  <si>
-    <t>Eastmountainsouth</t>
-  </si>
-  <si>
     <t>Stephen Clair</t>
   </si>
   <si>
@@ -7221,9 +7203,6 @@
     <t>Thom Yorke</t>
   </si>
   <si>
-    <t>Ben Kweller</t>
-  </si>
-  <si>
     <t>Shawn Mullins</t>
   </si>
   <si>
@@ -7233,9 +7212,6 @@
     <t>Willie Nile</t>
   </si>
   <si>
-    <t>Golden Smog</t>
-  </si>
-  <si>
     <t>Belle &amp; Sebastian</t>
   </si>
   <si>
@@ -7248,9 +7224,6 @@
     <t>John Doe</t>
   </si>
   <si>
-    <t>Cat Empire</t>
-  </si>
-  <si>
     <t>Grace Potter</t>
   </si>
   <si>
@@ -7281,9 +7254,6 @@
     <t>Ryan Shaw</t>
   </si>
   <si>
-    <t>Dan Wilson</t>
-  </si>
-  <si>
     <t>José González</t>
   </si>
   <si>
@@ -7353,9 +7323,6 @@
     <t>Justin Townes Earle</t>
   </si>
   <si>
-    <t>Bell X1</t>
-  </si>
-  <si>
     <t>Mumford &amp; Sons</t>
   </si>
   <si>
@@ -7401,9 +7368,6 @@
     <t>Sallie Ford &amp; The Sound Outside</t>
   </si>
   <si>
-    <t>Beirut</t>
-  </si>
-  <si>
     <t>tUnE‑yArDs</t>
   </si>
   <si>
@@ -7479,9 +7443,6 @@
     <t>The Walkmen</t>
   </si>
   <si>
-    <t>Glen Hansard</t>
-  </si>
-  <si>
     <t>Gotye</t>
   </si>
   <si>
@@ -7512,9 +7473,6 @@
     <t>John Fullbright</t>
   </si>
   <si>
-    <t>Dr. Dog</t>
-  </si>
-  <si>
     <t>Phosphorescent</t>
   </si>
   <si>
@@ -7533,9 +7491,6 @@
     <t>John Grant</t>
   </si>
   <si>
-    <t>Chvrches</t>
-  </si>
-  <si>
     <t>Minor Alps</t>
   </si>
   <si>
@@ -7572,9 +7527,6 @@
     <t>Nick Cave &amp; The Bad Seeds</t>
   </si>
   <si>
-    <t>Foxygen</t>
-  </si>
-  <si>
     <t>San Fermin</t>
   </si>
   <si>
@@ -7650,9 +7602,6 @@
     <t>Mac DeMarco</t>
   </si>
   <si>
-    <t>Bear’s Den</t>
-  </si>
-  <si>
     <t>Jungle</t>
   </si>
   <si>
@@ -7929,9 +7878,6 @@
     <t>J.S. Ondara</t>
   </si>
   <si>
-    <t>CAAMP</t>
-  </si>
-  <si>
     <t>The Highwomen</t>
   </si>
   <si>
@@ -8001,9 +7947,6 @@
     <t>Mt. Joy</t>
   </si>
   <si>
-    <t>Andy Shauf</t>
-  </si>
-  <si>
     <t>Sparks</t>
   </si>
   <si>
@@ -8172,12 +8115,6 @@
     <t>To the Sunset</t>
   </si>
   <si>
-    <t>The Magician</t>
-  </si>
-  <si>
-    <t>The Party</t>
-  </si>
-  <si>
     <t>Brighter Than Sunshine</t>
   </si>
   <si>
@@ -8196,42 +8133,12 @@
     <t>Beatopia</t>
   </si>
   <si>
-    <t>Hiding Bottles</t>
-  </si>
-  <si>
-    <t>So That You Might Hear Me</t>
-  </si>
-  <si>
-    <t>So Nice (Summer Samba)</t>
-  </si>
-  <si>
-    <t>Tanto Tempo</t>
-  </si>
-  <si>
-    <t>East Harlem</t>
-  </si>
-  <si>
-    <t>The Rip Tide</t>
-  </si>
-  <si>
-    <t>Rocky Took a Lover</t>
-  </si>
-  <si>
-    <t>Flock</t>
-  </si>
-  <si>
     <t>The Boy with the Arab Strap</t>
   </si>
   <si>
     <t>Diamonds on the Inside</t>
   </si>
   <si>
-    <t>How it Should Be (Sha Sha)</t>
-  </si>
-  <si>
-    <t>Sha Sha</t>
-  </si>
-  <si>
     <t>Catch My Disease</t>
   </si>
   <si>
@@ -8241,72 +8148,27 @@
     <t>Crazy for You</t>
   </si>
   <si>
-    <t>Billie Joe &amp; Norah Jones</t>
-  </si>
-  <si>
-    <t>Long Time Gone</t>
-  </si>
-  <si>
-    <t>Foreverly</t>
-  </si>
-  <si>
     <t>I Wanna Get Better</t>
   </si>
   <si>
-    <t>Have a Heart</t>
-  </si>
-  <si>
-    <t>Nick of Time</t>
-  </si>
-  <si>
     <t>Comback Kid (That's my Dog)</t>
   </si>
   <si>
     <t>Loverboy</t>
   </si>
   <si>
-    <t>Wondering Where the Lions Are</t>
-  </si>
-  <si>
-    <t>Waiting for a Miracle</t>
-  </si>
-  <si>
-    <t>Lavender Girl</t>
-  </si>
-  <si>
-    <t>Lavender Days</t>
-  </si>
-  <si>
     <t>French Navy</t>
   </si>
   <si>
     <t>My Maudlin Career</t>
   </si>
   <si>
-    <t>Brighter Than Gold</t>
-  </si>
-  <si>
     <t>Talk of the Town</t>
   </si>
   <si>
     <t>The Singles</t>
   </si>
   <si>
-    <t>Summertime Thing</t>
-  </si>
-  <si>
-    <t>No Other Love</t>
-  </si>
-  <si>
-    <t>The Mother We Share</t>
-  </si>
-  <si>
-    <t>The Bones of What You Believe</t>
-  </si>
-  <si>
-    <t>The Last Good Day of the Year</t>
-  </si>
-  <si>
     <t>Teach Your Children</t>
   </si>
   <si>
@@ -8316,12 +8178,6 @@
     <t>Waiting on a Song</t>
   </si>
   <si>
-    <t>Closing Time</t>
-  </si>
-  <si>
-    <t>Re-Covered</t>
-  </si>
-  <si>
     <t>Dave Matthews Band</t>
   </si>
   <si>
@@ -8343,21 +8199,12 @@
     <t>Cowboy Take Me Away</t>
   </si>
   <si>
-    <t>Shame (2010 Deluxe Edition)</t>
-  </si>
-  <si>
-    <t>Where'd All the Time Go？</t>
-  </si>
-  <si>
     <t>Mercy</t>
   </si>
   <si>
     <t>Rockferry</t>
   </si>
   <si>
-    <t>You Dance</t>
-  </si>
-  <si>
     <t>Up From Below</t>
   </si>
   <si>
@@ -8394,12 +8241,6 @@
     <t>Welcome Interstate Managers</t>
   </si>
   <si>
-    <t>San Francisco</t>
-  </si>
-  <si>
-    <t>We Are the 21st Century Ambassadors of Peace &amp; Magic</t>
-  </si>
-  <si>
     <t>Between the Buttons</t>
   </si>
   <si>
@@ -8623,6 +8464,12 @@
   </si>
   <si>
     <t>Day &amp; Age</t>
+  </si>
+  <si>
+    <t>How We Operate</t>
+  </si>
+  <si>
+    <t>See the World</t>
   </si>
 </sst>
 </file>
@@ -9070,7 +8917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217A8E0-1CCB-644D-B989-DEFE8896B575}">
-  <dimension ref="A1:A434"/>
+  <dimension ref="A1:A430"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -9079,2172 +8926,2152 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2447</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1910</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2276</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2448</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2299</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2371</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>2439</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>2251</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>2206</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>2541</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>2565</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>2399</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>2613</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>2461</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>2552</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>2400</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>2594</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>2561</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>2449</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>2515</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>2488</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>2571</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>2414</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>2656</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>2269</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>2662</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>2401</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>2441</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>2376</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>2508</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>2266</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>2487</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>2596</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>2253</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>2434</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>2342</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>2579</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>2363</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>2483</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>2412</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>2429</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>2352</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>2415</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>2392</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>2322</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>2519</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>2577</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>2216</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>2543</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>2517</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>2240</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>2437</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>2586</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>2225</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>2426</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>2520</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>2570</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>2332</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>2388</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>2454</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>2511</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>2603</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>2324</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>2558</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>2214</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>2263</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>2259</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>2664</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>2237</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>2369</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>2368</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>2457</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>2233</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>2464</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>2228</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>2200</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>2339</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>2257</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>2665</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>2657</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>2256</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>2270</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>2382</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>2551</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>2327</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>2312</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>2343</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>2292</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>2308</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>2505</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>2404</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>2204</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>2582</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>2272</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>2314</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>2624</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>2522</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>2293</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>2539</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>2573</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>2623</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>2277</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>2298</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>2223</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>2353</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>2469</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>2489</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>2510</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>2536</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>2648</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>2430</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>2470</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>2611</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>2409</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>2300</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>2516</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>2243</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>2395</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>2534</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>2374</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>2278</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>2411</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>2463</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>2615</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>2595</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>2567</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>2557</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>2533</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>2321</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>2271</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>2245</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>2229</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>2475</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>2583</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>2220</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>2553</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>2588</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>2224</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>2249</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>2566</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>2301</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>2315</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>2398</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>2503</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>2323</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>2532</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>2604</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>2560</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>2347</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>2462</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>2575</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>2645</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>2546</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>2564</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>2208</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>2351</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>2518</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>2526</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>2202</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>2210</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>2335</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>2296</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>2346</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>2627</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>2524</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>2607</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>2309</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>2383</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>2666</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>2442</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>2261</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>2436</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>2433</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>2572</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>2341</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>2331</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>2466</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>2578</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>2658</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>2281</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>2265</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>2646</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>2576</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>2432</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>2481</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>2620</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>2406</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>2642</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>2236</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>2230</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>2590</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>2617</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>2268</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>2294</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>2320</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>2279</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>2477</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>2241</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>2349</v>
+        <v>924</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>2423</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>2639</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>2605</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>924</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>2205</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>2450</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>2467</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>2250</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>2443</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>2328</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>2247</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>2375</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>2599</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>2634</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>2661</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>2502</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>2267</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>2218</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>2242</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>2338</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>2286</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>2513</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>2275</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>2367</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>2495</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>2287</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>2203</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>2569</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>2459</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>2512</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>2554</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>2638</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>2444</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>2609</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>2215</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>2559</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>2326</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>2389</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>2393</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>2531</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>2226</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>2337</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>2319</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>2652</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>2580</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>2493</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>2356</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>2587</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>2653</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>2468</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>2199</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>2234</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>2290</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>2330</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>2373</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>2425</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>2244</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>2407</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>2295</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>2248</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>2608</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>2438</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>2625</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>2255</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>2311</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>2660</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>2222</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>2219</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>2380</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>2420</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>2549</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>2529</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>2239</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>2492</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>2654</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>2667</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>2479</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>2302</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>2555</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>2643</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>2640</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>2384</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>2523</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>2547</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>2655</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>2264</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>2379</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>2435</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>2304</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>2227</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>2362</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>2394</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>2440</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>2348</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>2663</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>2197</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>2535</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>2574</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>2585</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>2606</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>2591</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>2563</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>2274</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>2506</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>2622</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>2283</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>2431</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>1798</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>2318</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>2514</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>2631</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>2198</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>2217</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>2632</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>2307</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>2499</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>2562</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>2659</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>2548</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>2581</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>2288</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>2291</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>2491</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>2424</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>2550</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>2616</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>2497</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>2480</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>2636</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>2260</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>2507</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>2528</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>2628</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>2378</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>2372</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>2303</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>2501</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>2540</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>2626</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>2417</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>2329</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>2456</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>2385</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>2325</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>2358</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>2280</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>2408</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>2418</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>2641</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>2598</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>2359</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>2484</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>2334</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>2649</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>2584</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>2633</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>2460</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>2396</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>2340</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>2445</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>2496</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>2350</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>2207</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>2390</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>2354</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>2544</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>2345</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>2413</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>2644</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>2427</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>2521</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>2355</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>2451</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>2306</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>2610</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>2446</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>2619</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>2476</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>2258</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>2452</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>2650</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>2568</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>2360</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>2285</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>2538</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>2289</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>2537</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>2589</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>2162</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>2201</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>2472</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>2282</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>2490</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>2428</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>2422</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>2391</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>2494</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>2651</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>2542</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>2482</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>2386</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>2221</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>2635</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>2254</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>2471</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>2455</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>2545</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>2618</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>2377</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>2630</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>2602</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>2231</v>
+        <v>343</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>2601</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>2310</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>2262</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>343</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>2485</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>2212</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>2364</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>2530</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>2474</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>2556</v>
-      </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>2592</v>
-      </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>2357</v>
+        <v>2351</v>
       </c>
     </row>
   </sheetData>
@@ -11255,7 +11082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}">
-  <dimension ref="A1:F877"/>
+  <dimension ref="A1:F861"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -11290,10 +11117,10 @@
         <v>337</v>
       </c>
       <c r="B2" t="s">
-        <v>2758</v>
+        <v>2705</v>
       </c>
       <c r="C2" t="s">
-        <v>2759</v>
+        <v>2706</v>
       </c>
       <c r="F2" t="s">
         <v>857</v>
@@ -11335,13 +11162,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>2761</v>
+        <v>2708</v>
       </c>
       <c r="B5" t="s">
-        <v>2760</v>
+        <v>2707</v>
       </c>
       <c r="C5" t="s">
-        <v>2762</v>
+        <v>2709</v>
       </c>
       <c r="F5" t="s">
         <v>856</v>
@@ -11352,7 +11179,7 @@
         <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>2763</v>
+        <v>2710</v>
       </c>
       <c r="C6" t="s">
         <v>401</v>
@@ -11392,7 +11219,7 @@
         <v>406</v>
       </c>
       <c r="C8" t="s">
-        <v>2799</v>
+        <v>2746</v>
       </c>
       <c r="E8">
         <v>1980</v>
@@ -11423,10 +11250,10 @@
         <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2801</v>
+        <v>2748</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2800</v>
+        <v>2747</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1">
@@ -11441,10 +11268,10 @@
         <v>429</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2802</v>
+        <v>2749</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2802</v>
+        <v>2749</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1">
@@ -11459,10 +11286,10 @@
         <v>438</v>
       </c>
       <c r="B12" t="s">
-        <v>2803</v>
+        <v>2750</v>
       </c>
       <c r="C12" t="s">
-        <v>2804</v>
+        <v>2751</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1">
@@ -11495,7 +11322,7 @@
         <v>432</v>
       </c>
       <c r="B14" t="s">
-        <v>2805</v>
+        <v>2752</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>433</v>
@@ -11515,10 +11342,10 @@
         <v>434</v>
       </c>
       <c r="B15" t="s">
-        <v>2806</v>
+        <v>2753</v>
       </c>
       <c r="C15" t="s">
-        <v>2807</v>
+        <v>2754</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1">
@@ -11553,10 +11380,10 @@
         <v>439</v>
       </c>
       <c r="B17" t="s">
-        <v>2808</v>
+        <v>2755</v>
       </c>
       <c r="C17" t="s">
-        <v>2809</v>
+        <v>2756</v>
       </c>
       <c r="E17" s="1">
         <v>1977</v>
@@ -11570,10 +11397,10 @@
         <v>195</v>
       </c>
       <c r="B18" t="s">
-        <v>2810</v>
+        <v>2757</v>
       </c>
       <c r="C18" t="s">
-        <v>2811</v>
+        <v>2758</v>
       </c>
       <c r="E18" s="1">
         <v>1985</v>
@@ -11587,7 +11414,7 @@
         <v>313</v>
       </c>
       <c r="B19" t="s">
-        <v>2812</v>
+        <v>2759</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>313</v>
@@ -11644,7 +11471,7 @@
         <v>446</v>
       </c>
       <c r="B22" t="s">
-        <v>2764</v>
+        <v>2711</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>447</v>
@@ -11696,13 +11523,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>2728</v>
+        <v>2680</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2729</v>
+        <v>2681</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2730</v>
+        <v>2682</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1">
@@ -11717,7 +11544,7 @@
         <v>164</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2765</v>
+        <v>2712</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>453</v>
@@ -11734,10 +11561,10 @@
         <v>454</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2766</v>
+        <v>2713</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2767</v>
+        <v>2714</v>
       </c>
       <c r="E27" s="1">
         <v>1982</v>
@@ -11865,7 +11692,7 @@
         <v>472</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2813</v>
+        <v>2760</v>
       </c>
       <c r="E34" s="1">
         <v>1966</v>
@@ -11919,7 +11746,7 @@
         <v>480</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2768</v>
+        <v>2715</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>481</v>
@@ -11994,7 +11821,7 @@
         <v>488</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2769</v>
+        <v>2716</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>431</v>
@@ -12011,13 +11838,13 @@
     </row>
     <row r="42" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2770</v>
+        <v>2717</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2771</v>
+        <v>2718</v>
       </c>
       <c r="E42" s="1">
         <v>1987</v>
@@ -12028,13 +11855,13 @@
     </row>
     <row r="43" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>2344</v>
+        <v>2338</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2755</v>
+        <v>2702</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2754</v>
+        <v>2701</v>
       </c>
       <c r="E43" s="1">
         <v>1967</v>
@@ -12079,13 +11906,13 @@
     </row>
     <row r="46" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>2772</v>
+        <v>2719</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2773</v>
+        <v>2720</v>
       </c>
       <c r="E46" s="1">
         <v>1982</v>
@@ -12168,10 +11995,10 @@
         <v>504</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2774</v>
+        <v>2721</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2775</v>
+        <v>2722</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1">
@@ -12490,7 +12317,7 @@
         <v>545</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>2777</v>
+        <v>2724</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>582</v>
@@ -12580,10 +12407,10 @@
         <v>1942</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2778</v>
+        <v>2725</v>
       </c>
       <c r="C74" t="s">
-        <v>2779</v>
+        <v>2726</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1">
@@ -12616,7 +12443,7 @@
         <v>142</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2780</v>
+        <v>2727</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>142</v>
@@ -12634,10 +12461,10 @@
         <v>560</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2781</v>
+        <v>2728</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>2782</v>
+        <v>2729</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1">
@@ -12652,7 +12479,7 @@
         <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>2783</v>
+        <v>2730</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>284</v>
@@ -12688,7 +12515,7 @@
         <v>564</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2784</v>
+        <v>2731</v>
       </c>
       <c r="C80" t="s">
         <v>1158</v>
@@ -12904,7 +12731,7 @@
         <v>594</v>
       </c>
       <c r="B92" t="s">
-        <v>2785</v>
+        <v>2732</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>595</v>
@@ -13192,10 +13019,10 @@
         <v>634</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>2786</v>
+        <v>2733</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>2787</v>
+        <v>2734</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1">
@@ -13246,10 +13073,10 @@
         <v>12</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>2788</v>
+        <v>2735</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>2788</v>
+        <v>2735</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1">
@@ -13318,7 +13145,7 @@
         <v>66</v>
       </c>
       <c r="B115" t="s">
-        <v>2789</v>
+        <v>2736</v>
       </c>
       <c r="C115" t="s">
         <v>646</v>
@@ -13354,10 +13181,10 @@
         <v>48</v>
       </c>
       <c r="B117" t="s">
-        <v>2790</v>
+        <v>2737</v>
       </c>
       <c r="C117" t="s">
-        <v>2791</v>
+        <v>2738</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1">
@@ -13534,10 +13361,10 @@
         <v>110</v>
       </c>
       <c r="B127" t="s">
-        <v>2794</v>
+        <v>2741</v>
       </c>
       <c r="C127" t="s">
-        <v>2795</v>
+        <v>2742</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1">
@@ -13570,10 +13397,10 @@
         <v>113</v>
       </c>
       <c r="B129" t="s">
-        <v>2792</v>
+        <v>2739</v>
       </c>
       <c r="C129" t="s">
-        <v>2793</v>
+        <v>2740</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1">
@@ -13585,13 +13412,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>2814</v>
+        <v>2761</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>2815</v>
+        <v>2762</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>2815</v>
+        <v>2762</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1">
@@ -13606,10 +13433,10 @@
         <v>124</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>2816</v>
+        <v>2763</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>2796</v>
+        <v>2743</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1">
@@ -13621,13 +13448,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>2817</v>
+        <v>2764</v>
       </c>
       <c r="B132" t="s">
-        <v>2818</v>
+        <v>2765</v>
       </c>
       <c r="C132" t="s">
-        <v>2819</v>
+        <v>2766</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1">
@@ -13660,10 +13487,10 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>2797</v>
+        <v>2744</v>
       </c>
       <c r="C134" t="s">
-        <v>2798</v>
+        <v>2745</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1">
@@ -13678,10 +13505,10 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>2820</v>
+        <v>2767</v>
       </c>
       <c r="C135" t="s">
-        <v>2821</v>
+        <v>2768</v>
       </c>
       <c r="D135" s="13"/>
       <c r="E135" s="13">
@@ -13804,10 +13631,10 @@
         <v>684</v>
       </c>
       <c r="B142" t="s">
-        <v>2822</v>
+        <v>2769</v>
       </c>
       <c r="C142" t="s">
-        <v>2823</v>
+        <v>2770</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1">
@@ -13894,7 +13721,7 @@
         <v>67</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>2824</v>
+        <v>2771</v>
       </c>
       <c r="C147" t="s">
         <v>1395</v>
@@ -13930,7 +13757,7 @@
         <v>80</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>2825</v>
+        <v>2772</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>80</v>
@@ -13948,10 +13775,10 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>2757</v>
+        <v>2704</v>
       </c>
       <c r="C150" t="s">
-        <v>2756</v>
+        <v>2703</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1">
@@ -14092,10 +13919,10 @@
         <v>131</v>
       </c>
       <c r="B158" t="s">
-        <v>2826</v>
+        <v>2773</v>
       </c>
       <c r="C158" t="s">
-        <v>2827</v>
+        <v>2774</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1">
@@ -14113,7 +13940,7 @@
         <v>2099</v>
       </c>
       <c r="C159" t="s">
-        <v>2828</v>
+        <v>2775</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1">
@@ -15706,7 +15533,7 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>2612</v>
+        <v>2594</v>
       </c>
       <c r="B248" t="s">
         <v>914</v>
@@ -16731,7 +16558,7 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>2776</v>
+        <v>2723</v>
       </c>
       <c r="B305" t="s">
         <v>1060</v>
@@ -25666,13 +25493,13 @@
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="B832" t="s">
-        <v>2668</v>
+        <v>2649</v>
       </c>
       <c r="C832" t="s">
-        <v>2669</v>
+        <v>2650</v>
       </c>
       <c r="E832">
         <v>2001</v>
@@ -25683,13 +25510,13 @@
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
-        <v>2671</v>
+        <v>2652</v>
       </c>
       <c r="B833" t="s">
-        <v>2670</v>
+        <v>2651</v>
       </c>
       <c r="C833" t="s">
-        <v>2672</v>
+        <v>2653</v>
       </c>
       <c r="E833">
         <v>2001</v>
@@ -25700,13 +25527,13 @@
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
-        <v>2453</v>
+        <v>2440</v>
       </c>
       <c r="B834" t="s">
-        <v>2673</v>
+        <v>2654</v>
       </c>
       <c r="C834" t="s">
-        <v>2674</v>
+        <v>2655</v>
       </c>
       <c r="E834">
         <v>2012</v>
@@ -25717,13 +25544,13 @@
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
-        <v>2637</v>
+        <v>2618</v>
       </c>
       <c r="B835" t="s">
-        <v>2675</v>
+        <v>2656</v>
       </c>
       <c r="C835" t="s">
-        <v>2637</v>
+        <v>2618</v>
       </c>
       <c r="E835">
         <v>2014</v>
@@ -25734,13 +25561,13 @@
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
-        <v>2593</v>
+        <v>2576</v>
       </c>
       <c r="B836" t="s">
-        <v>2676</v>
+        <v>2657</v>
       </c>
       <c r="C836" t="s">
-        <v>2677</v>
+        <v>2658</v>
       </c>
       <c r="E836">
         <v>2018</v>
@@ -25751,33 +25578,33 @@
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
-        <v>2621</v>
+        <v>2330</v>
       </c>
       <c r="B837" t="s">
-        <v>2678</v>
+        <v>2659</v>
       </c>
       <c r="C837" t="s">
-        <v>2679</v>
+        <v>2660</v>
       </c>
       <c r="E837">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="F837" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
-        <v>2336</v>
+        <v>2250</v>
       </c>
       <c r="B838" t="s">
-        <v>2680</v>
+        <v>2661</v>
       </c>
       <c r="C838" t="s">
-        <v>2681</v>
+        <v>2662</v>
       </c>
       <c r="E838">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="F838" t="s">
         <v>857</v>
@@ -25785,16 +25612,16 @@
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
-        <v>2252</v>
+        <v>2610</v>
       </c>
       <c r="B839" t="s">
-        <v>2682</v>
+        <v>2663</v>
       </c>
       <c r="C839" t="s">
-        <v>2683</v>
+        <v>2664</v>
       </c>
       <c r="E839">
-        <v>2002</v>
+        <v>2022</v>
       </c>
       <c r="F839" t="s">
         <v>857</v>
@@ -25802,67 +25629,67 @@
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
-        <v>2629</v>
+        <v>2358</v>
       </c>
       <c r="B840" t="s">
-        <v>2684</v>
+        <v>2665</v>
       </c>
       <c r="C840" t="s">
-        <v>2685</v>
+        <v>2665</v>
       </c>
       <c r="E840">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="F840" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="841" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A841" s="2" t="s">
-        <v>2504</v>
-      </c>
-      <c r="B841" s="2" t="s">
-        <v>2686</v>
-      </c>
-      <c r="C841" s="2" t="s">
-        <v>2687</v>
-      </c>
-      <c r="E841" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F841" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A841" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B841" t="s">
+        <v>2666</v>
+      </c>
+      <c r="C841" t="s">
+        <v>2666</v>
+      </c>
+      <c r="E841">
+        <v>2003</v>
+      </c>
+      <c r="F841" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>2211</v>
+        <v>2327</v>
       </c>
       <c r="B842" t="s">
-        <v>2688</v>
+        <v>2667</v>
       </c>
       <c r="C842" t="s">
-        <v>2689</v>
+        <v>2668</v>
       </c>
       <c r="E842">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="F842" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
-        <v>2421</v>
+        <v>2470</v>
       </c>
       <c r="B843" t="s">
-        <v>2690</v>
+        <v>2669</v>
       </c>
       <c r="C843" t="s">
-        <v>2691</v>
+        <v>2669</v>
       </c>
       <c r="E843">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F843" t="s">
         <v>856</v>
@@ -25870,16 +25697,16 @@
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
-        <v>2405</v>
+        <v>2628</v>
       </c>
       <c r="B844" t="s">
-        <v>2692</v>
+        <v>2670</v>
       </c>
       <c r="C844" t="s">
-        <v>2693</v>
+        <v>2670</v>
       </c>
       <c r="E844">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="F844" t="s">
         <v>857</v>
@@ -25887,101 +25714,101 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
-        <v>2366</v>
+        <v>2405</v>
       </c>
       <c r="B845" t="s">
-        <v>2694</v>
+        <v>2671</v>
       </c>
       <c r="C845" t="s">
-        <v>2694</v>
+        <v>2672</v>
       </c>
       <c r="E845">
-        <v>1998</v>
+        <v>2011</v>
       </c>
       <c r="F845" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
-        <v>2313</v>
+        <v>2393</v>
       </c>
       <c r="B846" t="s">
-        <v>2695</v>
+        <v>2673</v>
       </c>
       <c r="C846" t="s">
-        <v>2695</v>
+        <v>2674</v>
       </c>
       <c r="E846">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="F846" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
-        <v>2361</v>
+        <v>2380</v>
       </c>
       <c r="B847" t="s">
-        <v>2696</v>
+        <v>2675</v>
       </c>
       <c r="C847" t="s">
-        <v>2697</v>
+        <v>2676</v>
       </c>
       <c r="E847">
-        <v>2002</v>
+        <v>1987</v>
       </c>
       <c r="F847" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
-        <v>2333</v>
+        <v>2596</v>
       </c>
       <c r="B848" t="s">
-        <v>2698</v>
+        <v>2677</v>
       </c>
       <c r="C848" t="s">
-        <v>2699</v>
+        <v>2678</v>
       </c>
       <c r="E848">
-        <v>2001</v>
+        <v>1970</v>
       </c>
       <c r="F848" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
-        <v>2486</v>
+        <v>2392</v>
       </c>
       <c r="B849" t="s">
-        <v>2700</v>
+        <v>2679</v>
       </c>
       <c r="C849" t="s">
-        <v>2700</v>
+        <v>2679</v>
       </c>
       <c r="E849">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="F849" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
-        <v>2701</v>
+        <v>2231</v>
       </c>
       <c r="B850" t="s">
-        <v>2702</v>
+        <v>2683</v>
       </c>
       <c r="C850" t="s">
-        <v>2703</v>
+        <v>2684</v>
       </c>
       <c r="E850">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="F850" t="s">
         <v>857</v>
@@ -25989,16 +25816,16 @@
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
-        <v>2647</v>
+        <v>2508</v>
       </c>
       <c r="B851" t="s">
-        <v>2704</v>
+        <v>2685</v>
       </c>
       <c r="C851" t="s">
-        <v>2704</v>
+        <v>2685</v>
       </c>
       <c r="E851">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F851" t="s">
         <v>857</v>
@@ -26006,16 +25833,16 @@
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
-        <v>2284</v>
+        <v>2607</v>
       </c>
       <c r="B852" t="s">
-        <v>2705</v>
+        <v>2686</v>
       </c>
       <c r="C852" t="s">
-        <v>2706</v>
+        <v>1224</v>
       </c>
       <c r="E852">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="F852" t="s">
         <v>856</v>
@@ -26023,16 +25850,16 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
-        <v>2416</v>
+        <v>2377</v>
       </c>
       <c r="B853" t="s">
-        <v>2707</v>
+        <v>2687</v>
       </c>
       <c r="C853" t="s">
-        <v>2708</v>
+        <v>2688</v>
       </c>
       <c r="E853">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="F853" t="s">
         <v>857</v>
@@ -26040,33 +25867,33 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
-        <v>2316</v>
+        <v>2458</v>
       </c>
       <c r="B854" t="s">
-        <v>2709</v>
+        <v>657</v>
       </c>
       <c r="C854" t="s">
-        <v>2710</v>
+        <v>2689</v>
       </c>
       <c r="E854">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="F854" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
-        <v>2597</v>
+        <v>2690</v>
       </c>
       <c r="B855" t="s">
-        <v>2711</v>
+        <v>2691</v>
       </c>
       <c r="C855" t="s">
-        <v>2712</v>
+        <v>2692</v>
       </c>
       <c r="E855">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="F855" t="s">
         <v>857</v>
@@ -26074,33 +25901,33 @@
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
-        <v>2403</v>
+        <v>2484</v>
       </c>
       <c r="B856" t="s">
-        <v>2713</v>
+        <v>2693</v>
       </c>
       <c r="C856" t="s">
-        <v>2714</v>
+        <v>2694</v>
       </c>
       <c r="E856">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F856" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
-        <v>2370</v>
+        <v>2196</v>
       </c>
       <c r="B857" t="s">
-        <v>2715</v>
+        <v>2695</v>
       </c>
       <c r="C857" t="s">
-        <v>2715</v>
+        <v>2698</v>
       </c>
       <c r="E857">
-        <v>2013</v>
+        <v>1978</v>
       </c>
       <c r="F857" t="s">
         <v>857</v>
@@ -26108,16 +25935,16 @@
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
-        <v>2390</v>
+        <v>2244</v>
       </c>
       <c r="B858" t="s">
-        <v>2716</v>
+        <v>2696</v>
       </c>
       <c r="C858" t="s">
-        <v>2717</v>
+        <v>2697</v>
       </c>
       <c r="E858">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="F858" t="s">
         <v>857</v>
@@ -26125,33 +25952,33 @@
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
-        <v>2273</v>
+        <v>2301</v>
       </c>
       <c r="B859" t="s">
-        <v>2718</v>
+        <v>2699</v>
       </c>
       <c r="C859" t="s">
-        <v>2719</v>
+        <v>2700</v>
       </c>
       <c r="E859">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="F859" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
-        <v>2465</v>
+        <v>1910</v>
       </c>
       <c r="B860" t="s">
-        <v>2720</v>
+        <v>1213</v>
       </c>
       <c r="C860" t="s">
-        <v>2721</v>
+        <v>2043</v>
       </c>
       <c r="E860">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="F860" t="s">
         <v>856</v>
@@ -26159,295 +25986,23 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
-        <v>2235</v>
+        <v>2273</v>
       </c>
       <c r="B861" t="s">
-        <v>2722</v>
+        <v>2777</v>
       </c>
       <c r="C861" t="s">
-        <v>2235</v>
+        <v>2776</v>
       </c>
       <c r="E861">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="F861" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A862" t="s">
-        <v>2614</v>
-      </c>
-      <c r="B862" t="s">
-        <v>2723</v>
-      </c>
-      <c r="C862" t="s">
-        <v>2724</v>
-      </c>
-      <c r="E862">
-        <v>1970</v>
-      </c>
-      <c r="F862" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A863" t="s">
-        <v>2402</v>
-      </c>
-      <c r="B863" t="s">
-        <v>2725</v>
-      </c>
-      <c r="C863" t="s">
-        <v>2725</v>
-      </c>
-      <c r="E863">
-        <v>2017</v>
-      </c>
-      <c r="F863" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A864" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B864" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C864" t="s">
-        <v>2727</v>
-      </c>
-      <c r="E864">
-        <v>2017</v>
-      </c>
-      <c r="F864" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A865" t="s">
-        <v>2232</v>
-      </c>
-      <c r="B865" t="s">
-        <v>2731</v>
-      </c>
-      <c r="C865" t="s">
-        <v>2732</v>
-      </c>
-      <c r="E865">
-        <v>2004</v>
-      </c>
-      <c r="F865" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A866" t="s">
-        <v>2525</v>
-      </c>
-      <c r="B866" t="s">
-        <v>2733</v>
-      </c>
-      <c r="C866" t="s">
-        <v>2733</v>
-      </c>
-      <c r="E866">
-        <v>2015</v>
-      </c>
-      <c r="F866" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A867" t="s">
-        <v>2626</v>
-      </c>
-      <c r="B867" t="s">
-        <v>2734</v>
-      </c>
-      <c r="C867" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E867">
-        <v>1999</v>
-      </c>
-      <c r="F867" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A868" t="s">
-        <v>2458</v>
-      </c>
-      <c r="B868" t="s">
-        <v>2736</v>
-      </c>
-      <c r="C868" t="s">
-        <v>2735</v>
-      </c>
-      <c r="E868">
-        <v>2010</v>
-      </c>
-      <c r="F868" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A869" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B869" t="s">
-        <v>2737</v>
-      </c>
-      <c r="C869" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E869">
-        <v>2007</v>
-      </c>
-      <c r="F869" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A870" t="s">
-        <v>2317</v>
-      </c>
-      <c r="B870" t="s">
-        <v>2739</v>
-      </c>
-      <c r="C870" t="s">
-        <v>2317</v>
-      </c>
-      <c r="E870">
-        <v>2003</v>
-      </c>
-      <c r="F870" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A871" t="s">
-        <v>2473</v>
-      </c>
-      <c r="B871" t="s">
-        <v>657</v>
-      </c>
-      <c r="C871" t="s">
-        <v>2740</v>
-      </c>
-      <c r="E871">
-        <v>2009</v>
-      </c>
-      <c r="F871" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A872" t="s">
-        <v>2741</v>
-      </c>
-      <c r="B872" t="s">
-        <v>2742</v>
-      </c>
-      <c r="C872" t="s">
-        <v>2743</v>
-      </c>
-      <c r="E872">
-        <v>1993</v>
-      </c>
-      <c r="F872" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A873" t="s">
-        <v>2500</v>
-      </c>
-      <c r="B873" t="s">
-        <v>2744</v>
-      </c>
-      <c r="C873" t="s">
-        <v>2745</v>
-      </c>
-      <c r="E873">
-        <v>2015</v>
-      </c>
-      <c r="F873" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A874" t="s">
-        <v>2196</v>
-      </c>
-      <c r="B874" t="s">
-        <v>2746</v>
-      </c>
-      <c r="C874" t="s">
-        <v>2749</v>
-      </c>
-      <c r="E874">
-        <v>1978</v>
-      </c>
-      <c r="F874" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A875" t="s">
-        <v>2246</v>
-      </c>
-      <c r="B875" t="s">
-        <v>2747</v>
-      </c>
-      <c r="C875" t="s">
-        <v>2748</v>
-      </c>
-      <c r="E875">
-        <v>2010</v>
-      </c>
-      <c r="F875" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A876" t="s">
-        <v>2305</v>
-      </c>
-      <c r="B876" t="s">
-        <v>2750</v>
-      </c>
-      <c r="C876" t="s">
-        <v>2751</v>
-      </c>
-      <c r="E876">
-        <v>2003</v>
-      </c>
-      <c r="F876" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A877" t="s">
-        <v>2478</v>
-      </c>
-      <c r="B877" t="s">
-        <v>2752</v>
-      </c>
-      <c r="C877" t="s">
-        <v>2753</v>
-      </c>
-      <c r="E877">
-        <v>2013</v>
-      </c>
-      <c r="F877" t="s">
-        <v>856</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F877" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}"/>
+  <autoFilter ref="A1:F859" xr:uid="{C27CC9A7-A557-E74E-AC1D-5C0872EF2F23}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A50:E424">
     <sortCondition ref="E50:E424"/>
   </sortState>
